--- a/data/DGT.MI.xlsx
+++ b/data/DGT.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">DGT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05767059326172</t>
+    <t xml:space="preserve">2.0576708316803</t>
   </si>
   <si>
     <t xml:space="preserve">2.03047680854797</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">2.00509595870972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04860591888428</t>
+    <t xml:space="preserve">2.04860615730286</t>
   </si>
   <si>
     <t xml:space="preserve">1.99421834945679</t>
@@ -80,58 +80,58 @@
     <t xml:space="preserve">1.8763781785965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97065019607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92714035511017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93076598644257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85824906826019</t>
+    <t xml:space="preserve">1.97065043449402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92714011669159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93076622486115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8582489490509</t>
   </si>
   <si>
     <t xml:space="preserve">1.80839347839355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8256162405014</t>
+    <t xml:space="preserve">1.82561612129211</t>
   </si>
   <si>
     <t xml:space="preserve">1.75128638744354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64704310894012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75581872463226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71321487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68964695930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73134410381317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76760280132294</t>
+    <t xml:space="preserve">1.64704298973083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75581884384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71321475505829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68964684009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73134434223175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76760268211365</t>
   </si>
   <si>
     <t xml:space="preserve">1.72862493991852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7585381269455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81292581558228</t>
+    <t xml:space="preserve">1.75853824615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81292569637299</t>
   </si>
   <si>
     <t xml:space="preserve">1.83105516433716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7685090303421</t>
+    <t xml:space="preserve">1.76850891113281</t>
   </si>
   <si>
     <t xml:space="preserve">1.6751434803009</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">1.74947333335876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69871139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74766039848328</t>
+    <t xml:space="preserve">1.69871151447296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74766051769257</t>
   </si>
   <si>
     <t xml:space="preserve">1.70777606964111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70868277549744</t>
+    <t xml:space="preserve">1.70868253707886</t>
   </si>
   <si>
     <t xml:space="preserve">1.69508576393127</t>
@@ -158,37 +158,37 @@
     <t xml:space="preserve">1.77666735649109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70143091678619</t>
+    <t xml:space="preserve">1.7014307975769</t>
   </si>
   <si>
     <t xml:space="preserve">1.69055342674255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73497009277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64069771766663</t>
+    <t xml:space="preserve">1.73496997356415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64069783687592</t>
   </si>
   <si>
     <t xml:space="preserve">1.62982034683228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63163316249847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68692755699158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68602097034454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6733306646347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7404088973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70415019989014</t>
+    <t xml:space="preserve">1.63163328170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68692743778229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68602108955383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67333054542542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74040877819061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70415031909943</t>
   </si>
   <si>
     <t xml:space="preserve">1.75672519207001</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">1.64885604381561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64794957637787</t>
+    <t xml:space="preserve">1.64794969558716</t>
   </si>
   <si>
     <t xml:space="preserve">1.68420827388763</t>
@@ -209,16 +209,16 @@
     <t xml:space="preserve">1.72137320041656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72227954864502</t>
+    <t xml:space="preserve">1.72227942943573</t>
   </si>
   <si>
     <t xml:space="preserve">1.67786276340485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63253962993622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66335964202881</t>
+    <t xml:space="preserve">1.63253974914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66335940361023</t>
   </si>
   <si>
     <t xml:space="preserve">1.66517233848572</t>
@@ -227,16 +227,16 @@
     <t xml:space="preserve">1.65429484844208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81111288070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79026424884796</t>
+    <t xml:space="preserve">1.81111311912537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79026436805725</t>
   </si>
   <si>
     <t xml:space="preserve">1.78754484653473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78935790061951</t>
+    <t xml:space="preserve">1.78935778141022</t>
   </si>
   <si>
     <t xml:space="preserve">1.66154646873474</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">1.69961786270142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66245305538177</t>
+    <t xml:space="preserve">1.66245293617249</t>
   </si>
   <si>
     <t xml:space="preserve">1.68330156803131</t>
@@ -260,37 +260,37 @@
     <t xml:space="preserve">1.569087266922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58902931213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48297345638275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49566388130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49203813076019</t>
+    <t xml:space="preserve">1.58902943134308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48297333717346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49566376209259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4920380115509</t>
   </si>
   <si>
     <t xml:space="preserve">1.53192234039307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48387980461121</t>
+    <t xml:space="preserve">1.48387956619263</t>
   </si>
   <si>
     <t xml:space="preserve">1.45215368270874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4856926202774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42858564853668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4594053030014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49294424057007</t>
+    <t xml:space="preserve">1.48569285869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42858552932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45940542221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49294435977936</t>
   </si>
   <si>
     <t xml:space="preserve">1.46031165122986</t>
@@ -299,19 +299,19 @@
     <t xml:space="preserve">1.4412761926651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45034062862396</t>
+    <t xml:space="preserve">1.45034074783325</t>
   </si>
   <si>
     <t xml:space="preserve">1.46846997737885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42586600780487</t>
+    <t xml:space="preserve">1.42586612701416</t>
   </si>
   <si>
     <t xml:space="preserve">1.31255829334259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36422669887543</t>
+    <t xml:space="preserve">1.36422657966614</t>
   </si>
   <si>
     <t xml:space="preserve">1.34156513214111</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">1.33250045776367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2781126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19653105735779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17296314239502</t>
+    <t xml:space="preserve">1.27811253070831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19653117656708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17296302318573</t>
   </si>
   <si>
     <t xml:space="preserve">1.18746650218964</t>
@@ -362,43 +362,43 @@
     <t xml:space="preserve">1.08684897422791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09500730037689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09410071372986</t>
+    <t xml:space="preserve">1.0950071811676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09410059452057</t>
   </si>
   <si>
     <t xml:space="preserve">1.12038803100586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09228789806366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10769760608673</t>
+    <t xml:space="preserve">1.09228777885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10769772529602</t>
   </si>
   <si>
     <t xml:space="preserve">1.10951066017151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12129473686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09682011604309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08956849575043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08866190910339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07234561443329</t>
+    <t xml:space="preserve">1.1212944984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09682023525238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08956837654114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08866202831268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07234573364258</t>
   </si>
   <si>
     <t xml:space="preserve">1.05149686336517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12310755252838</t>
+    <t xml:space="preserve">1.12310743331909</t>
   </si>
   <si>
     <t xml:space="preserve">1.10135245323181</t>
@@ -407,19 +407,19 @@
     <t xml:space="preserve">1.08322322368622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08775544166565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11404287815094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15120780467987</t>
+    <t xml:space="preserve">1.08775556087494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11404275894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15120792388916</t>
   </si>
   <si>
     <t xml:space="preserve">1.21466040611267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18474721908569</t>
+    <t xml:space="preserve">1.1847470998764</t>
   </si>
   <si>
     <t xml:space="preserve">1.14576923847198</t>
@@ -428,37 +428,37 @@
     <t xml:space="preserve">1.12220120429993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0623744726181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03336787223816</t>
+    <t xml:space="preserve">1.06237459182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03336775302887</t>
   </si>
   <si>
     <t xml:space="preserve">0.934563279151917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.945440769195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977167069911957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956318438053131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933656692504883</t>
+    <t xml:space="preserve">0.945440888404846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977166950702667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956318318843842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933656752109528</t>
   </si>
   <si>
     <t xml:space="preserve">1.01523840427399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04877734184265</t>
+    <t xml:space="preserve">1.04877746105194</t>
   </si>
   <si>
     <t xml:space="preserve">1.0360871553421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02430295944214</t>
+    <t xml:space="preserve">1.02430307865143</t>
   </si>
   <si>
     <t xml:space="preserve">0.990764081478119</t>
@@ -467,16 +467,16 @@
     <t xml:space="preserve">1.05059063434601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11494934558868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12854623794556</t>
+    <t xml:space="preserve">1.11494946479797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12854635715485</t>
   </si>
   <si>
     <t xml:space="preserve">1.07506501674652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06418752670288</t>
+    <t xml:space="preserve">1.06418764591217</t>
   </si>
   <si>
     <t xml:space="preserve">1.02067720890045</t>
@@ -485,46 +485,46 @@
     <t xml:space="preserve">0.997109174728394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00617396831512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988044679164886</t>
+    <t xml:space="preserve">1.00617384910583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988044619560242</t>
   </si>
   <si>
     <t xml:space="preserve">1.03880655765533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05965518951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04243230819702</t>
+    <t xml:space="preserve">1.05965507030487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04243218898773</t>
   </si>
   <si>
     <t xml:space="preserve">1.06328105926514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05693578720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10407173633575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10497832298279</t>
+    <t xml:space="preserve">1.05693566799164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10407185554504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10497844219208</t>
   </si>
   <si>
     <t xml:space="preserve">1.07597136497498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12492036819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1031653881073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2110344171524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19562458992004</t>
+    <t xml:space="preserve">1.12492060661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10316526889801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21103429794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19562470912933</t>
   </si>
   <si>
     <t xml:space="preserve">1.21284747123718</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">1.15392732620239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20559561252594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20196986198425</t>
+    <t xml:space="preserve">1.20559573173523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20196974277496</t>
   </si>
   <si>
     <t xml:space="preserve">1.23188304901123</t>
@@ -548,31 +548,31 @@
     <t xml:space="preserve">1.25363826751709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25817036628723</t>
+    <t xml:space="preserve">1.25817048549652</t>
   </si>
   <si>
     <t xml:space="preserve">1.26088988780975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.255450963974</t>
+    <t xml:space="preserve">1.25545120239258</t>
   </si>
   <si>
     <t xml:space="preserve">1.28717732429504</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30893242359161</t>
+    <t xml:space="preserve">1.3089325428009</t>
   </si>
   <si>
     <t xml:space="preserve">1.30530655384064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.412269115448</t>
+    <t xml:space="preserve">1.41226899623871</t>
   </si>
   <si>
     <t xml:space="preserve">1.37963664531708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40320467948914</t>
+    <t xml:space="preserve">1.40320444107056</t>
   </si>
   <si>
     <t xml:space="preserve">1.35244262218475</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">1.35697484016418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35969424247742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34065866470337</t>
+    <t xml:space="preserve">1.35969436168671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34065854549408</t>
   </si>
   <si>
     <t xml:space="preserve">1.32343578338623</t>
@@ -593,64 +593,64 @@
     <t xml:space="preserve">1.35062968730927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32887470722198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26995444297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1947181224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14395606517792</t>
+    <t xml:space="preserve">1.3288745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26995456218719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19471800327301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14395618438721</t>
   </si>
   <si>
     <t xml:space="preserve">1.24548006057739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25001239776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.268141746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23278963565826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24185419082642</t>
+    <t xml:space="preserve">1.25001227855682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26814162731171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23278951644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24185431003571</t>
   </si>
   <si>
     <t xml:space="preserve">1.28173863887787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26451575756073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28264486789703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25091874599457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26904797554016</t>
+    <t xml:space="preserve">1.26451563835144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28264498710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25091886520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26904809474945</t>
   </si>
   <si>
     <t xml:space="preserve">1.33159399032593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29624199867249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28536438941956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31437122821808</t>
+    <t xml:space="preserve">1.29624211788177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28536427021027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31437134742737</t>
   </si>
   <si>
     <t xml:space="preserve">1.30983889102936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31799697875977</t>
+    <t xml:space="preserve">1.31799709796906</t>
   </si>
   <si>
     <t xml:space="preserve">1.29896128177643</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">1.3778235912323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3352198600769</t>
+    <t xml:space="preserve">1.33521997928619</t>
   </si>
   <si>
     <t xml:space="preserve">1.2617963552475</t>
@@ -668,31 +668,31 @@
     <t xml:space="preserve">1.3107453584671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30711948871613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34247159957886</t>
+    <t xml:space="preserve">1.30711960792542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34247171878815</t>
   </si>
   <si>
     <t xml:space="preserve">1.29442894458771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32434237003326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33884561061859</t>
+    <t xml:space="preserve">1.32434225082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33884572982788</t>
   </si>
   <si>
     <t xml:space="preserve">1.31165182590485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27992558479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30621302127838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31618428230286</t>
+    <t xml:space="preserve">1.27992570400238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30621314048767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31618416309357</t>
   </si>
   <si>
     <t xml:space="preserve">1.30349361896515</t>
@@ -701,52 +701,52 @@
     <t xml:space="preserve">1.27720630168915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26632869243622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28355145454407</t>
+    <t xml:space="preserve">1.26632857322693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28355157375336</t>
   </si>
   <si>
     <t xml:space="preserve">1.25907707214355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24910604953766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27539312839508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25273180007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.347003698349</t>
+    <t xml:space="preserve">1.24910593032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27539324760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25273168087006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34700381755829</t>
   </si>
   <si>
     <t xml:space="preserve">1.34972310066223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2926162481308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32978117465973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23369586467743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22372484207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.229163646698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20468926429749</t>
+    <t xml:space="preserve">1.29261612892151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32978105545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23369598388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22372496128082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22916376590729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2046891450882</t>
   </si>
   <si>
     <t xml:space="preserve">1.22191214561462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2191926240921</t>
+    <t xml:space="preserve">1.21919250488281</t>
   </si>
   <si>
     <t xml:space="preserve">1.22100567817688</t>
@@ -758,37 +758,37 @@
     <t xml:space="preserve">1.22463142871857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21012794971466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1865599155426</t>
+    <t xml:space="preserve">1.21012806892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18655979633331</t>
   </si>
   <si>
     <t xml:space="preserve">1.17477595806122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17840158939362</t>
+    <t xml:space="preserve">1.17840170860291</t>
   </si>
   <si>
     <t xml:space="preserve">1.15211427211761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15845966339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08594274520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10588490962982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07959711551666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10679113864899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13217222690582</t>
+    <t xml:space="preserve">1.15845954418182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08594250679016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10588479042053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07959723472595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1067910194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13217210769653</t>
   </si>
   <si>
     <t xml:space="preserve">1.16933715343475</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">1.22644436359406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23822844028473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24457359313965</t>
+    <t xml:space="preserve">1.23822832107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24457347393036</t>
   </si>
   <si>
     <t xml:space="preserve">1.2518253326416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24004137516022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20378267765045</t>
+    <t xml:space="preserve">1.24004125595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20378279685974</t>
   </si>
   <si>
     <t xml:space="preserve">1.20650196075439</t>
@@ -818,28 +818,28 @@
     <t xml:space="preserve">1.24094760417938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23097658157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21194100379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23460257053375</t>
+    <t xml:space="preserve">1.2309764623642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21194088459015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23460268974304</t>
   </si>
   <si>
     <t xml:space="preserve">1.24638652801514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27629995346069</t>
+    <t xml:space="preserve">1.2762998342514</t>
   </si>
   <si>
     <t xml:space="preserve">1.27086102962494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29805505275726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2255380153656</t>
+    <t xml:space="preserve">1.29805493354797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22553789615631</t>
   </si>
   <si>
     <t xml:space="preserve">1.15574014186859</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">1.11857533454895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16027247905731</t>
+    <t xml:space="preserve">1.1602725982666</t>
   </si>
   <si>
     <t xml:space="preserve">1.16661775112152</t>
@@ -860,10 +860,10 @@
     <t xml:space="preserve">1.18112111091614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19925045967102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11676216125488</t>
+    <t xml:space="preserve">1.19925034046173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11676239967346</t>
   </si>
   <si>
     <t xml:space="preserve">1.09319412708282</t>
@@ -872,25 +872,25 @@
     <t xml:space="preserve">1.09772670269012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17658889293671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17930817604065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21375381946564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21556663513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2862708568573</t>
+    <t xml:space="preserve">1.176589012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17930829524994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21375370025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21556675434113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28627097606659</t>
   </si>
   <si>
     <t xml:space="preserve">1.28989684581757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28445816040039</t>
+    <t xml:space="preserve">1.2844580411911</t>
   </si>
   <si>
     <t xml:space="preserve">1.38960766792297</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">1.4004852771759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41408216953278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38235580921173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37057173252106</t>
+    <t xml:space="preserve">1.41408228874207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38235592842102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37057185173035</t>
   </si>
   <si>
     <t xml:space="preserve">1.32796823978424</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">1.35516202449799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38416874408722</t>
+    <t xml:space="preserve">1.38416886329651</t>
   </si>
   <si>
     <t xml:space="preserve">1.42224025726318</t>
@@ -932,16 +932,16 @@
     <t xml:space="preserve">1.36694610118866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40773689746857</t>
+    <t xml:space="preserve">1.40773677825928</t>
   </si>
   <si>
     <t xml:space="preserve">1.39957869052887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39685928821564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38326263427734</t>
+    <t xml:space="preserve">1.39685940742493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38326239585876</t>
   </si>
   <si>
     <t xml:space="preserve">1.38688826560974</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">1.50926077365875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57724547386169</t>
+    <t xml:space="preserve">1.57724559307098</t>
   </si>
   <si>
     <t xml:space="preserve">1.57271313667297</t>
@@ -962,16 +962,16 @@
     <t xml:space="preserve">1.55005168914795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51379299163818</t>
+    <t xml:space="preserve">1.51379323005676</t>
   </si>
   <si>
     <t xml:space="preserve">1.48659920692444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44580841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48206686973572</t>
+    <t xml:space="preserve">1.44580829143524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48206675052643</t>
   </si>
   <si>
     <t xml:space="preserve">1.43221151828766</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">1.52739000320435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37329113483429</t>
+    <t xml:space="preserve">1.37329125404358</t>
   </si>
   <si>
     <t xml:space="preserve">1.39142060279846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34609735012054</t>
+    <t xml:space="preserve">1.34609746932983</t>
   </si>
   <si>
     <t xml:space="preserve">1.29170954227448</t>
@@ -1001,91 +1001,91 @@
     <t xml:space="preserve">1.31890344619751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33703279495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27358043193817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39595293998718</t>
+    <t xml:space="preserve">1.3370326757431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27358031272888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39595282077789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30077433586121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33341026306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31476104259491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30543649196625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31942343711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24482715129852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24948930740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23084032535553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21219110488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2541515827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23550248146057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22617793083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19354200363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19820427894592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2401647567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27280080318451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29611217975616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31009876728058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3287478685379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28212535381317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26813840866089</t>
   </si>
   <si>
     <t xml:space="preserve">1.30077421665192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33341014385223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3147611618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30543661117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31942343711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24482703208923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24948930740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23084032535553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21219110488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2541515827179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23550260066986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22617793083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19354200363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19820415973663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2401647567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27280080318451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29611206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31009876728058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32874798774719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28212523460388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26813840866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30077433586121</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.21685338020325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18887972831726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1655684709549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20286643505096</t>
+    <t xml:space="preserve">1.18887984752655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16556835174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20286655426025</t>
   </si>
   <si>
     <t xml:space="preserve">1.17489290237427</t>
@@ -1094,19 +1094,19 @@
     <t xml:space="preserve">1.1795551776886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20752894878387</t>
+    <t xml:space="preserve">1.2075287103653</t>
   </si>
   <si>
     <t xml:space="preserve">1.32408571243286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34739696979523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17023074626923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14691936969757</t>
+    <t xml:space="preserve">1.34739708900452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17023062705994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14691948890686</t>
   </si>
   <si>
     <t xml:space="preserve">1.13293242454529</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">1.27746295928955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22151565551758</t>
+    <t xml:space="preserve">1.22151553630829</t>
   </si>
   <si>
     <t xml:space="preserve">1.15624392032623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18421733379364</t>
+    <t xml:space="preserve">1.18421745300293</t>
   </si>
   <si>
     <t xml:space="preserve">1.28678750991821</t>
@@ -1136,13 +1136,13 @@
     <t xml:space="preserve">1.1515816450119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13759469985962</t>
+    <t xml:space="preserve">1.13759458065033</t>
   </si>
   <si>
     <t xml:space="preserve">1.36138391494751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29144966602325</t>
+    <t xml:space="preserve">1.29144978523254</t>
   </si>
   <si>
     <t xml:space="preserve">1.3427346944809</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">1.33807253837585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11428344249725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1049587726593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14225721359253</t>
+    <t xml:space="preserve">1.11428332328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10495889186859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14225709438324</t>
   </si>
   <si>
     <t xml:space="preserve">1.27810609340668</t>
@@ -67877,7 +67877,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6911111111</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>42500</v>
@@ -67898,6 +67898,32 @@
         <v>824</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6912962963</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>39500</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>1.9650000333786</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>819</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DGT.MI.xlsx
+++ b/data/DGT.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">DGT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05767059326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03047680854797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96702444553375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00509595870972</t>
+    <t xml:space="preserve">2.0576708316803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03047704696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96702456474304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00509524345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.04860615730286</t>
@@ -62,55 +62,55 @@
     <t xml:space="preserve">1.99421858787537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97971498966217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94889521598816</t>
+    <t xml:space="preserve">1.97971487045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94889533519745</t>
   </si>
   <si>
     <t xml:space="preserve">1.88544285297394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91444969177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89632022380829</t>
+    <t xml:space="preserve">1.91444981098175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89632058143616</t>
   </si>
   <si>
     <t xml:space="preserve">1.87637805938721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97065019607544</t>
+    <t xml:space="preserve">1.97065031528473</t>
   </si>
   <si>
     <t xml:space="preserve">1.9271399974823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93076622486115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8582489490509</t>
+    <t xml:space="preserve">1.93076610565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85824906826019</t>
   </si>
   <si>
     <t xml:space="preserve">1.80839359760284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82561612129211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75128626823425</t>
+    <t xml:space="preserve">1.8256162405014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75128638744354</t>
   </si>
   <si>
     <t xml:space="preserve">1.64704310894012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75581872463226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71321487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68964684009552</t>
+    <t xml:space="preserve">1.75581860542297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71321499347687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68964695930481</t>
   </si>
   <si>
     <t xml:space="preserve">1.73134422302246</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">1.81292581558228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83105516433716</t>
+    <t xml:space="preserve">1.83105504512787</t>
   </si>
   <si>
     <t xml:space="preserve">1.76850914955139</t>
@@ -140,25 +140,25 @@
     <t xml:space="preserve">1.74947333335876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69871139526367</t>
+    <t xml:space="preserve">1.69871127605438</t>
   </si>
   <si>
     <t xml:space="preserve">1.74766039848328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7077761888504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70868253707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69508576393127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77666735649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7014307975769</t>
+    <t xml:space="preserve">1.70777606964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70868265628815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69508564472198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7766672372818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70143067836761</t>
   </si>
   <si>
     <t xml:space="preserve">1.69055342674255</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">1.73497009277344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64069771766663</t>
+    <t xml:space="preserve">1.64069795608521</t>
   </si>
   <si>
     <t xml:space="preserve">1.62982034683228</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">1.63163316249847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68692755699158</t>
+    <t xml:space="preserve">1.68692743778229</t>
   </si>
   <si>
     <t xml:space="preserve">1.68602108955383</t>
@@ -188,25 +188,25 @@
     <t xml:space="preserve">1.74040877819061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70415031909943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75672519207001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68783390522003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64885592460632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64794945716858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68420815467834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72137308120728</t>
+    <t xml:space="preserve">1.70415019989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75672507286072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68783402442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64885604381561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64794957637787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68420803546906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72137320041656</t>
   </si>
   <si>
     <t xml:space="preserve">1.72227954864502</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">1.67786276340485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6325398683548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66335964202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66517245769501</t>
+    <t xml:space="preserve">1.63253962993622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66335940361023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66517233848572</t>
   </si>
   <si>
     <t xml:space="preserve">1.65429484844208</t>
@@ -230,16 +230,16 @@
     <t xml:space="preserve">1.81111299991608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79026436805725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78754508495331</t>
+    <t xml:space="preserve">1.79026424884796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78754484653473</t>
   </si>
   <si>
     <t xml:space="preserve">1.78935778141022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66154634952545</t>
+    <t xml:space="preserve">1.66154646873474</t>
   </si>
   <si>
     <t xml:space="preserve">1.69961798191071</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">1.66245293617249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68330156803131</t>
+    <t xml:space="preserve">1.6833016872406</t>
   </si>
   <si>
     <t xml:space="preserve">1.65882706642151</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">1.60353291034698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56908714771271</t>
+    <t xml:space="preserve">1.569087266922</t>
   </si>
   <si>
     <t xml:space="preserve">1.58902955055237</t>
@@ -272,34 +272,34 @@
     <t xml:space="preserve">1.4920380115509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53192245960236</t>
+    <t xml:space="preserve">1.53192222118378</t>
   </si>
   <si>
     <t xml:space="preserve">1.4838799238205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45215356349945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48569273948669</t>
+    <t xml:space="preserve">1.45215368270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48569285869598</t>
   </si>
   <si>
     <t xml:space="preserve">1.42858552932739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4594053030014</t>
+    <t xml:space="preserve">1.45940518379211</t>
   </si>
   <si>
     <t xml:space="preserve">1.49294435977936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46031177043915</t>
+    <t xml:space="preserve">1.46031165122986</t>
   </si>
   <si>
     <t xml:space="preserve">1.44127607345581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45034074783325</t>
+    <t xml:space="preserve">1.45034050941467</t>
   </si>
   <si>
     <t xml:space="preserve">1.46846985816956</t>
@@ -311,43 +311,43 @@
     <t xml:space="preserve">1.31255829334259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36422657966614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34156513214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36875891685486</t>
+    <t xml:space="preserve">1.36422681808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3415652513504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36875903606415</t>
   </si>
   <si>
     <t xml:space="preserve">1.33250045776367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27811253070831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19653105735779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17296314239502</t>
+    <t xml:space="preserve">1.27811276912689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19653117656708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17296302318573</t>
   </si>
   <si>
     <t xml:space="preserve">1.18746638298035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17568242549896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15483379364014</t>
+    <t xml:space="preserve">1.17568230628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15483391284943</t>
   </si>
   <si>
     <t xml:space="preserve">1.09863305091858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12401401996613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13307869434357</t>
+    <t xml:space="preserve">1.12401390075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13307857513428</t>
   </si>
   <si>
     <t xml:space="preserve">1.1258270740509</t>
@@ -356,13 +356,13 @@
     <t xml:space="preserve">1.11313652992249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06962621212006</t>
+    <t xml:space="preserve">1.06962633132935</t>
   </si>
   <si>
     <t xml:space="preserve">1.08684897422791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09500730037689</t>
+    <t xml:space="preserve">1.09500706195831</t>
   </si>
   <si>
     <t xml:space="preserve">1.09410071372986</t>
@@ -377,28 +377,28 @@
     <t xml:space="preserve">1.10769772529602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10951054096222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12129461765289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0968199968338</t>
+    <t xml:space="preserve">1.10951066017151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12129473686218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09682011604309</t>
   </si>
   <si>
     <t xml:space="preserve">1.08956849575043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08866190910339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07234561443329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05149710178375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12310743331909</t>
+    <t xml:space="preserve">1.0886617898941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07234573364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05149686336517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12310755252838</t>
   </si>
   <si>
     <t xml:space="preserve">1.10135245323181</t>
@@ -407,79 +407,79 @@
     <t xml:space="preserve">1.08322322368622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08775556087494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11404275894165</t>
+    <t xml:space="preserve">1.08775568008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11404299736023</t>
   </si>
   <si>
     <t xml:space="preserve">1.15120792388916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21466040611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1847470998764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1457691192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12220108509064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0623744726181</t>
+    <t xml:space="preserve">1.21466028690338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18474698066711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14576900005341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12220096588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06237459182739</t>
   </si>
   <si>
     <t xml:space="preserve">1.03336775302887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.934563279151917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945440709590912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977167129516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956318259239197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933656811714172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01523840427399</t>
+    <t xml:space="preserve">0.934563338756561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945440888404846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977167010307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956318497657776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933656752109528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01523852348328</t>
   </si>
   <si>
     <t xml:space="preserve">1.04877746105194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0360871553421</t>
+    <t xml:space="preserve">1.03608727455139</t>
   </si>
   <si>
     <t xml:space="preserve">1.02430307865143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990763962268829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05059063434601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11494934558868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12854635715485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07506489753723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06418752670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02067720890045</t>
+    <t xml:space="preserve">0.990764141082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05059051513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11494946479797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12854623794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07506501674652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06418764591217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02067732810974</t>
   </si>
   <si>
     <t xml:space="preserve">0.997109293937683</t>
@@ -488,31 +488,31 @@
     <t xml:space="preserve">1.00617384910583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988044619560242</t>
+    <t xml:space="preserve">0.988044679164886</t>
   </si>
   <si>
     <t xml:space="preserve">1.03880643844604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05965495109558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04243218898773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06328094005585</t>
+    <t xml:space="preserve">1.05965518951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04243242740631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06328105926514</t>
   </si>
   <si>
     <t xml:space="preserve">1.05693578720093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10407185554504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10497844219208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07597148418427</t>
+    <t xml:space="preserve">1.10407197475433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1049782037735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07597160339355</t>
   </si>
   <si>
     <t xml:space="preserve">1.12492048740387</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">1.1031653881073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21103453636169</t>
+    <t xml:space="preserve">1.2110344171524</t>
   </si>
   <si>
     <t xml:space="preserve">1.19562458992004</t>
@@ -530,73 +530,73 @@
     <t xml:space="preserve">1.21284735202789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14667558670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1539272069931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20559585094452</t>
+    <t xml:space="preserve">1.14667546749115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15392732620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20559573173523</t>
   </si>
   <si>
     <t xml:space="preserve">1.20196986198425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23188328742981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25363838672638</t>
+    <t xml:space="preserve">1.23188304901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2536381483078</t>
   </si>
   <si>
     <t xml:space="preserve">1.25817060470581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26089000701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25545120239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28717732429504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30893230438232</t>
+    <t xml:space="preserve">1.26089012622833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25545108318329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28717720508575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30893242359161</t>
   </si>
   <si>
     <t xml:space="preserve">1.30530667304993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.412269115448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37963652610779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40320467948914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35244262218475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35697484016418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.359694480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34065854549408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32343590259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35062968730927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32887470722198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26995456218719</t>
+    <t xml:space="preserve">1.41226923465729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3796364068985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40320456027985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35244274139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35697507858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35969460010529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34065878391266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32343602180481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35062980651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32887446880341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26995468139648</t>
   </si>
   <si>
     <t xml:space="preserve">1.1947181224823</t>
@@ -605,28 +605,28 @@
     <t xml:space="preserve">1.14395618438721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24548006057739</t>
+    <t xml:space="preserve">1.2454799413681</t>
   </si>
   <si>
     <t xml:space="preserve">1.25001239776611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.268141746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23278975486755</t>
+    <t xml:space="preserve">1.26814162731171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23278963565826</t>
   </si>
   <si>
     <t xml:space="preserve">1.24185431003571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28173840045929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26451563835144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28264486789703</t>
+    <t xml:space="preserve">1.28173851966858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26451575756073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28264510631561</t>
   </si>
   <si>
     <t xml:space="preserve">1.25091874599457</t>
@@ -635,49 +635,49 @@
     <t xml:space="preserve">1.26904821395874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33159399032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2962418794632</t>
+    <t xml:space="preserve">1.33159387111664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29624199867249</t>
   </si>
   <si>
     <t xml:space="preserve">1.28536438941956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31437110900879</t>
+    <t xml:space="preserve">1.31437146663666</t>
   </si>
   <si>
     <t xml:space="preserve">1.30983889102936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31799709796906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29896128177643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3778235912323</t>
+    <t xml:space="preserve">1.31799697875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29896140098572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37782347202301</t>
   </si>
   <si>
     <t xml:space="preserve">1.3352198600769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2617963552475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31074547767639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30711960792542</t>
+    <t xml:space="preserve">1.26179623603821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31074523925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30711948871613</t>
   </si>
   <si>
     <t xml:space="preserve">1.34247148036957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29442894458771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32434225082397</t>
+    <t xml:space="preserve">1.294429063797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32434213161469</t>
   </si>
   <si>
     <t xml:space="preserve">1.33884572982788</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">1.31165194511414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27992570400238</t>
+    <t xml:space="preserve">1.27992558479309</t>
   </si>
   <si>
     <t xml:space="preserve">1.30621302127838</t>
@@ -695,43 +695,43 @@
     <t xml:space="preserve">1.31618416309357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30349361896515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27720618247986</t>
+    <t xml:space="preserve">1.30349373817444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27720630168915</t>
   </si>
   <si>
     <t xml:space="preserve">1.26632869243622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28355145454407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25907731056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24910604953766</t>
+    <t xml:space="preserve">1.28355157375336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25907707214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24910593032837</t>
   </si>
   <si>
     <t xml:space="preserve">1.27539324760437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25273180007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34700381755829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34972321987152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29261600971222</t>
+    <t xml:space="preserve">1.25273168087006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34700393676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34972333908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2926162481308</t>
   </si>
   <si>
     <t xml:space="preserve">1.32978105545044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23369586467743</t>
+    <t xml:space="preserve">1.23369598388672</t>
   </si>
   <si>
     <t xml:space="preserve">1.22372496128082</t>
@@ -740,16 +740,16 @@
     <t xml:space="preserve">1.229163646698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20468938350677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22191214561462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21919274330139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22100555896759</t>
+    <t xml:space="preserve">1.20468926429749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22191202640533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2191926240921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2210054397583</t>
   </si>
   <si>
     <t xml:space="preserve">1.21828615665436</t>
@@ -758,118 +758,118 @@
     <t xml:space="preserve">1.22463142871857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21012806892395</t>
+    <t xml:space="preserve">1.21012783050537</t>
   </si>
   <si>
     <t xml:space="preserve">1.1865599155426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17477607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17840182781219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1521143913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15845954418182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08594238758087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10588479042053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07959723472595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10679113864899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13217222690582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16933715343475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22644436359406</t>
+    <t xml:space="preserve">1.17477595806122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17840170860291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15211451053619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1584597826004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08594226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10588490962982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07959735393524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10679137706757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13217210769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16933703422546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22644424438477</t>
   </si>
   <si>
     <t xml:space="preserve">1.23822844028473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24457347393036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2518253326416</t>
+    <t xml:space="preserve">1.24457359313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25182545185089</t>
   </si>
   <si>
     <t xml:space="preserve">1.24004125595093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20378279685974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20650231838226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24094772338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23097670078278</t>
+    <t xml:space="preserve">1.20378267765045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20650219917297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24094760417938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23097681999207</t>
   </si>
   <si>
     <t xml:space="preserve">1.21194100379944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23460257053375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24638640880585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27629971504211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27086102962494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29805493354797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22553789615631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15574014186859</t>
+    <t xml:space="preserve">1.23460233211517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24638652801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27629995346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27086091041565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29805481433868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22553777694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15574026107788</t>
   </si>
   <si>
     <t xml:space="preserve">1.11857521533966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16027247905731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16661775112152</t>
+    <t xml:space="preserve">1.1602725982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16661787033081</t>
   </si>
   <si>
     <t xml:space="preserve">1.16480469703674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18112123012543</t>
+    <t xml:space="preserve">1.18112111091614</t>
   </si>
   <si>
     <t xml:space="preserve">1.19925045967102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11676216125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09319424629211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09772658348083</t>
+    <t xml:space="preserve">1.11676239967346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09319412708282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09772646427155</t>
   </si>
   <si>
     <t xml:space="preserve">1.17658877372742</t>
@@ -878,79 +878,79 @@
     <t xml:space="preserve">1.17930829524994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21375370025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21556663513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28627097606659</t>
+    <t xml:space="preserve">1.21375393867493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21556675434113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28627073764801</t>
   </si>
   <si>
     <t xml:space="preserve">1.28989672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2844580411911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38960754871368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40048515796661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41408216953278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38235604763031</t>
+    <t xml:space="preserve">1.28445792198181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38960766792297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4004852771759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41408205032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38235592842102</t>
   </si>
   <si>
     <t xml:space="preserve">1.37057185173035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32796823978424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36513328552246</t>
+    <t xml:space="preserve">1.32796812057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36513316631317</t>
   </si>
   <si>
     <t xml:space="preserve">1.35516214370728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38416874408722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42224037647247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38054299354553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38870120048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36694598197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40773689746857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39957869052887</t>
+    <t xml:space="preserve">1.38416886329651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42224025726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38054287433624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38870108127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36694610118866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40773677825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39957880973816</t>
   </si>
   <si>
     <t xml:space="preserve">1.39685928821564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38326239585876</t>
+    <t xml:space="preserve">1.38326251506805</t>
   </si>
   <si>
     <t xml:space="preserve">1.38688826560974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50926089286804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57724547386169</t>
+    <t xml:space="preserve">1.50926077365875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5772453546524</t>
   </si>
   <si>
     <t xml:space="preserve">1.57271313667297</t>
@@ -959,16 +959,16 @@
     <t xml:space="preserve">1.54551935195923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55005168914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51379311084747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48659920692444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44580841064453</t>
+    <t xml:space="preserve">1.55005156993866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51379299163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48659908771515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44580829143524</t>
   </si>
   <si>
     <t xml:space="preserve">1.48206698894501</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">1.43221139907837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5409871339798</t>
+    <t xml:space="preserve">1.54098701477051</t>
   </si>
   <si>
     <t xml:space="preserve">1.52285766601562</t>
@@ -986,19 +986,19 @@
     <t xml:space="preserve">1.52739000320435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37329137325287</t>
+    <t xml:space="preserve">1.37329125404358</t>
   </si>
   <si>
     <t xml:space="preserve">1.39142060279846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34609735012054</t>
+    <t xml:space="preserve">1.34609746932983</t>
   </si>
   <si>
     <t xml:space="preserve">1.29170954227448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31890344619751</t>
+    <t xml:space="preserve">1.31890368461609</t>
   </si>
   <si>
     <t xml:space="preserve">1.33703279495239</t>
@@ -1010,325 +1010,322 @@
     <t xml:space="preserve">1.39595293998718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30077409744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33341002464294</t>
+    <t xml:space="preserve">1.30077421665192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33341014385223</t>
   </si>
   <si>
     <t xml:space="preserve">1.3147611618042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30543661117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31942331790924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24482703208923</t>
+    <t xml:space="preserve">1.30543673038483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31942343711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24482691287994</t>
   </si>
   <si>
     <t xml:space="preserve">1.24948930740356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23084032535553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21219110488892</t>
+    <t xml:space="preserve">1.23084020614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21219098567963</t>
   </si>
   <si>
     <t xml:space="preserve">1.2541515827179</t>
   </si>
   <si>
+    <t xml:space="preserve">1.23550260066986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2261780500412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19354200363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19820415973663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2401647567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27280068397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29611194133759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31009888648987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3287478685379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28212523460388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26813840866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21685326099396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18887984752655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16556823253632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20286655426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17489290237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1795551776886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2075287103653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32408559322357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34739708900452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17023050785065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14691925048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13293266296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25881385803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746307849884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22151565551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15624380111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18421745300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28678739070892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16090595722198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1515816450119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13759481906891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3613840341568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29144978523254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34273481369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33807241916656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11428332328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10495889186859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14225697517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27810597419739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29230725765228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37278068065643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34437811374664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32544338703156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30177462100983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55266213417053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41065037250519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31124210357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31597578525543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28757357597351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3065083026886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33964455127716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42011797428131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40591669082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35384559631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39644908905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3207094669342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3349107503891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28283977508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27337229251862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26390469074249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25917112827301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29704105854034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2449699640274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23076856136322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22130119800568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2165675163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22603487968445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24023616313934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21183383464813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26863861083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20710015296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24970364570618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25443756580353</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.23550248146057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2261780500412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19354200363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19820415973663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24016463756561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27280068397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29611206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31009876728058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3287478685379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28212523460388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26813852787018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30077421665192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21685338020325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18887960910797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1655684709549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20286655426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17489290237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1795551776886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2075287103653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32408559322357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34739720821381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17023074626923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14691925048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13293242454529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25881373882294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746307849884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22151565551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15624403953552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18421745300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2867876291275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16090631484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15158152580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13759469985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36138391494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29144990444183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34273493289948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33807241916656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11428332328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1049587726593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14225709438324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27810597419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29230725765228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37278056144714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34437823295593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32544338703156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30177474021912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55266213417053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41065037250519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31124198436737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31597590446472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28757357597351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30650842189789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33964431285858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42011785507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40591669082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35384559631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39644908905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3207094669342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33491063117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28283965587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27337241172791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26390492916107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25917112827301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29704093933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24497008323669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2307687997818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22130131721497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2165675163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22603487968445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24023616313934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21183383464813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26863861083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20710003376007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24970376491547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25443744659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23550236225128</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.16923034191132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18343150615692</t>
+    <t xml:space="preserve">1.18343138694763</t>
   </si>
   <si>
     <t xml:space="preserve">1.2023663520813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14082813262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12189304828644</t>
+    <t xml:space="preserve">1.1408280134201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12189316749573</t>
   </si>
   <si>
     <t xml:space="preserve">1.11715936660767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10295808315277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06982219219208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01775121688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989348769187927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979881227016449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965680181980133</t>
+    <t xml:space="preserve">1.10295820236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06982207298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01775109767914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989348709583282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979881167411804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965680062770844</t>
   </si>
   <si>
     <t xml:space="preserve">0.914555907249451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937277734279633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92023628950119</t>
+    <t xml:space="preserve">0.937277793884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92023640871048</t>
   </si>
   <si>
     <t xml:space="preserve">0.880473077297211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927810311317444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946745276451111</t>
+    <t xml:space="preserve">0.927810251712799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946745216846466</t>
   </si>
   <si>
     <t xml:space="preserve">0.956212639808655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0224848985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07928967475891</t>
+    <t xml:space="preserve">1.02248477935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07928955554962</t>
   </si>
   <si>
     <t xml:space="preserve">1.10769188404083</t>
@@ -1337,7 +1334,7 @@
     <t xml:space="preserve">1.13609433174133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05562090873718</t>
+    <t xml:space="preserve">1.05562078952789</t>
   </si>
   <si>
     <t xml:space="preserve">1.09349071979523</t>
@@ -1349,46 +1346,46 @@
     <t xml:space="preserve">1.06508839130402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07455563545227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04615342617035</t>
+    <t xml:space="preserve">1.07455587387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04615354537964</t>
   </si>
   <si>
     <t xml:space="preserve">1.03668606281281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04141986370087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11242544651031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12662672996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08875691890717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.098224401474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05088710784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03195226192474</t>
+    <t xml:space="preserve">1.04141974449158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1124255657196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12662696838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08875703811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09822428226471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05088722705841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03195238113403</t>
   </si>
   <si>
     <t xml:space="preserve">1.02721858024597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17869782447815</t>
+    <t xml:space="preserve">1.17869770526886</t>
   </si>
   <si>
     <t xml:space="preserve">1.15976285934448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15029537677765</t>
+    <t xml:space="preserve">1.15029549598694</t>
   </si>
   <si>
     <t xml:space="preserve">1.16449666023254</t>
@@ -1406,25 +1403,25 @@
     <t xml:space="preserve">1.13136053085327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08402323722839</t>
+    <t xml:space="preserve">1.08402335643768</t>
   </si>
   <si>
     <t xml:space="preserve">1.00828373432159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984615087509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994082391262054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01301741600037</t>
+    <t xml:space="preserve">0.98461502790451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994082450866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01301729679108</t>
   </si>
   <si>
     <t xml:space="preserve">1.1881650686264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33017694950104</t>
+    <t xml:space="preserve">1.33017706871033</t>
   </si>
   <si>
     <t xml:space="preserve">1.40118300914764</t>
@@ -1436,7 +1433,10 @@
     <t xml:space="preserve">1.33027982711792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32551193237305</t>
+    <t xml:space="preserve">1.31597566604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32551181316376</t>
   </si>
   <si>
     <t xml:space="preserve">1.33981597423553</t>
@@ -1445,13 +1445,13 @@
     <t xml:space="preserve">1.33504796028137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36365616321564</t>
+    <t xml:space="preserve">1.36365604400635</t>
   </si>
   <si>
     <t xml:space="preserve">1.32074379920959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35412001609802</t>
+    <t xml:space="preserve">1.35411989688873</t>
   </si>
   <si>
     <t xml:space="preserve">1.3445839881897</t>
@@ -1460,34 +1460,34 @@
     <t xml:space="preserve">1.40180027484894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36842393875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34935200214386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35888803005219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30167186260223</t>
+    <t xml:space="preserve">1.36842405796051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34935212135315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3588879108429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30167174339294</t>
   </si>
   <si>
     <t xml:space="preserve">1.3922643661499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.382728099823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41133630275726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38749623298645</t>
+    <t xml:space="preserve">1.38272833824158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41133642196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38749635219574</t>
   </si>
   <si>
     <t xml:space="preserve">1.37319219112396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4304084777832</t>
+    <t xml:space="preserve">1.43040859699249</t>
   </si>
   <si>
     <t xml:space="preserve">1.47808885574341</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">1.45901668071747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43994462490082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41610455513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51623296737671</t>
+    <t xml:space="preserve">1.43994450569153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41610443592072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.516233086586</t>
   </si>
   <si>
     <t xml:space="preserve">1.50669693946838</t>
@@ -1526,31 +1526,31 @@
     <t xml:space="preserve">1.54484117031097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54007315635681</t>
+    <t xml:space="preserve">1.54007303714752</t>
   </si>
   <si>
     <t xml:space="preserve">1.58298528194427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57344937324524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68788206577301</t>
+    <t xml:space="preserve">1.57344925403595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68788194656372</t>
   </si>
   <si>
     <t xml:space="preserve">1.65450572967529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70695424079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7641704082489</t>
+    <t xml:space="preserve">1.70695412158966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76417052745819</t>
   </si>
   <si>
     <t xml:space="preserve">1.74509835243225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72602617740631</t>
+    <t xml:space="preserve">1.7260262966156</t>
   </si>
   <si>
     <t xml:space="preserve">1.69741797447205</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">1.67357790470123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64020168781281</t>
+    <t xml:space="preserve">1.64020180702209</t>
   </si>
   <si>
     <t xml:space="preserve">1.61159348487854</t>
@@ -1571,16 +1571,16 @@
     <t xml:space="preserve">1.60682547092438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64973771572113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71172201633453</t>
+    <t xml:space="preserve">1.64973783493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71172213554382</t>
   </si>
   <si>
     <t xml:space="preserve">1.64496970176697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61636161804199</t>
+    <t xml:space="preserve">1.6163614988327</t>
   </si>
   <si>
     <t xml:space="preserve">1.62112963199615</t>
@@ -1589,31 +1589,31 @@
     <t xml:space="preserve">1.63066565990448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63543367385864</t>
+    <t xml:space="preserve">1.63543379306793</t>
   </si>
   <si>
     <t xml:space="preserve">1.77847456932068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75940239429474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68311393260956</t>
+    <t xml:space="preserve">1.75940251350403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68311405181885</t>
   </si>
   <si>
     <t xml:space="preserve">1.71649014949799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77370643615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81185066699982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8261547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79754662513733</t>
+    <t xml:space="preserve">1.77370655536652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81185078620911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82615482807159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79754674434662</t>
   </si>
   <si>
     <t xml:space="preserve">1.788010597229</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">1.80708277225494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76893842220306</t>
+    <t xml:space="preserve">1.76893866062164</t>
   </si>
   <si>
     <t xml:space="preserve">1.73556232452393</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">1.74033033847809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72125816345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78324246406555</t>
+    <t xml:space="preserve">1.72125828266144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78324258327484</t>
   </si>
   <si>
     <t xml:space="preserve">1.74986636638641</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">1.67834603786469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6640419960022</t>
+    <t xml:space="preserve">1.66404187679291</t>
   </si>
   <si>
     <t xml:space="preserve">1.69265007972717</t>
@@ -1661,37 +1661,37 @@
     <t xml:space="preserve">1.80231475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75463438034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79277873039246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56868135929108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65927386283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59252154827118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52576899528503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59728932380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7021861076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85953092575073</t>
+    <t xml:space="preserve">1.75463449954987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79277861118317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5686811208725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65927374362946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59252142906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52576887607574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59728944301605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70218598842621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85953104496002</t>
   </si>
   <si>
     <t xml:space="preserve">1.89767515659332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92628347873688</t>
+    <t xml:space="preserve">1.92628335952759</t>
   </si>
   <si>
     <t xml:space="preserve">1.82138681411743</t>
@@ -1703,10 +1703,10 @@
     <t xml:space="preserve">1.86429905891418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90721142292023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94535553455353</t>
+    <t xml:space="preserve">1.90721130371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94535541534424</t>
   </si>
   <si>
     <t xml:space="preserve">1.99303579330444</t>
@@ -1715,25 +1715,25 @@
     <t xml:space="preserve">2.0597882270813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00257205963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07886028289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12654066085815</t>
+    <t xml:space="preserve">2.00257182121277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07886052131653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12654042243958</t>
   </si>
   <si>
     <t xml:space="preserve">2.1074686050415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08839631080627</t>
+    <t xml:space="preserve">2.08839654922485</t>
   </si>
   <si>
     <t xml:space="preserve">2.09793257713318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14561295509338</t>
+    <t xml:space="preserve">2.1456127166748</t>
   </si>
   <si>
     <t xml:space="preserve">2.27911758422852</t>
@@ -1745,19 +1745,19 @@
     <t xml:space="preserve">2.22190117835999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25050926208496</t>
+    <t xml:space="preserve">2.25050950050354</t>
   </si>
   <si>
     <t xml:space="preserve">2.02164387702942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01210761070251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9739636182785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98349964618683</t>
+    <t xml:space="preserve">2.01210808753967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97396349906921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98349976539612</t>
   </si>
   <si>
     <t xml:space="preserve">2.03118014335632</t>
@@ -1769,22 +1769,22 @@
     <t xml:space="preserve">2.09847211837769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08884620666504</t>
+    <t xml:space="preserve">2.08884596824646</t>
   </si>
   <si>
     <t xml:space="preserve">2.10809803009033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00221180915833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95408177375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03108978271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02146410942078</t>
+    <t xml:space="preserve">2.0022120475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95408189296722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03109002113342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0214638710022</t>
   </si>
   <si>
     <t xml:space="preserve">2.05996799468994</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">1.94445586204529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97333383560181</t>
+    <t xml:space="preserve">1.97333407402039</t>
   </si>
   <si>
     <t xml:space="preserve">1.93482995033264</t>
@@ -1805,16 +1805,16 @@
     <t xml:space="preserve">1.83856964111328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82894361019135</t>
+    <t xml:space="preserve">1.82894372940063</t>
   </si>
   <si>
     <t xml:space="preserve">1.86744773387909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88669979572296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707364559174</t>
+    <t xml:space="preserve">1.88669967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707376480103</t>
   </si>
   <si>
     <t xml:space="preserve">1.89632570743561</t>
@@ -1829,10 +1829,10 @@
     <t xml:space="preserve">2.05034208297729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11772441864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1562283039093</t>
+    <t xml:space="preserve">2.11772418022156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15622854232788</t>
   </si>
   <si>
     <t xml:space="preserve">2.20435833930969</t>
@@ -1856,13 +1856,13 @@
     <t xml:space="preserve">2.27174043655396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30061864852905</t>
+    <t xml:space="preserve">2.30061841011047</t>
   </si>
   <si>
     <t xml:space="preserve">2.2813663482666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18510627746582</t>
+    <t xml:space="preserve">2.1851065158844</t>
   </si>
   <si>
     <t xml:space="preserve">2.19473242759705</t>
@@ -1877,10 +1877,10 @@
     <t xml:space="preserve">2.01183795928955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8722608089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96370792388916</t>
+    <t xml:space="preserve">1.87226068973541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96370780467987</t>
   </si>
   <si>
     <t xml:space="preserve">2.06959414482117</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">2.29099249839783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36800074577332</t>
+    <t xml:space="preserve">2.36800098419189</t>
   </si>
   <si>
     <t xml:space="preserve">2.38725280761719</t>
@@ -1931,10 +1931,10 @@
     <t xml:space="preserve">2.21398448944092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31987071037292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4450089931488</t>
+    <t xml:space="preserve">2.31987047195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44500875473022</t>
   </si>
   <si>
     <t xml:space="preserve">2.45463490486145</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">2.52201700210571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50276494026184</t>
+    <t xml:space="preserve">2.50276470184326</t>
   </si>
   <si>
     <t xml:space="preserve">2.59902501106262</t>
@@ -1964,16 +1964,16 @@
     <t xml:space="preserve">2.51239085197449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47388696670532</t>
+    <t xml:space="preserve">2.47388672828674</t>
   </si>
   <si>
     <t xml:space="preserve">2.48351287841797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53164291381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63752913475037</t>
+    <t xml:space="preserve">2.53164315223694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63752937316895</t>
   </si>
   <si>
     <t xml:space="preserve">2.69528532028198</t>
@@ -1985,10 +1985,10 @@
     <t xml:space="preserve">2.71453738212585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67603349685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60865116119385</t>
+    <t xml:space="preserve">2.67603325843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60865139961243</t>
   </si>
   <si>
     <t xml:space="preserve">2.66640734672546</t>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">2.58939909934998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56052088737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6279034614563</t>
+    <t xml:space="preserve">2.56052112579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62790322303772</t>
   </si>
   <si>
     <t xml:space="preserve">2.55089521408081</t>
@@ -20153,7 +20153,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G667" t="s">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20439,7 +20439,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G678" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20465,7 +20465,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G679" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20491,7 +20491,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G680" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20517,7 +20517,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G681" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20543,7 +20543,7 @@
         <v>1.25</v>
       </c>
       <c r="G682" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -20569,7 +20569,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G683" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20595,7 +20595,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G684" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20621,7 +20621,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G685" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20647,7 +20647,7 @@
         <v>1.25</v>
       </c>
       <c r="G686" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20777,7 +20777,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G691" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -20829,7 +20829,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G693" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20855,7 +20855,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G694" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -20985,7 +20985,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G699" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21011,7 +21011,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G700" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21037,7 +21037,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G701" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21115,7 +21115,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G704" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21193,7 +21193,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G707" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21219,7 +21219,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G708" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21245,7 +21245,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G709" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21271,7 +21271,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G710" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21297,7 +21297,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G711" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21323,7 +21323,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G712" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21375,7 +21375,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G714" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21401,7 +21401,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G715" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21427,7 +21427,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G716" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21453,7 +21453,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G717" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21557,7 +21557,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G721" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21635,7 +21635,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G724" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21687,7 +21687,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G726" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21713,7 +21713,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G727" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21817,7 +21817,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G731" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21843,7 +21843,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G732" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21895,7 +21895,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G734" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -21921,7 +21921,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G735" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -21947,7 +21947,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G736" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -21973,7 +21973,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G737" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22181,7 +22181,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G745" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22207,7 +22207,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G746" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22285,7 +22285,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G749" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22311,7 +22311,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G750" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22363,7 +22363,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G752" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22389,7 +22389,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G753" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22415,7 +22415,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G754" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22441,7 +22441,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G755" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22467,7 +22467,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G756" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22493,7 +22493,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G757" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22519,7 +22519,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G758" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22545,7 +22545,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G759" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22571,7 +22571,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G760" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22597,7 +22597,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G761" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22623,7 +22623,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G762" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22649,7 +22649,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G763" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22675,7 +22675,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G764" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22701,7 +22701,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G765" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22727,7 +22727,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G766" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -22831,7 +22831,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G770" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22857,7 +22857,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G771" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22883,7 +22883,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G772" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22909,7 +22909,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G773" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22935,7 +22935,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G774" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23117,7 +23117,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G781" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23143,7 +23143,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G782" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23221,7 +23221,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G785" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23247,7 +23247,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G786" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23273,7 +23273,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G787" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23299,7 +23299,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G788" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23325,7 +23325,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G789" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23351,7 +23351,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G790" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23377,7 +23377,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G791" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23403,7 +23403,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G792" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23429,7 +23429,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G793" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23455,7 +23455,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G794" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23481,7 +23481,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G795" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23507,7 +23507,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G796" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23533,7 +23533,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G797" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23559,7 +23559,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G798" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23585,7 +23585,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G799" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23611,7 +23611,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G800" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23663,7 +23663,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G802" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23689,7 +23689,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G803" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23715,7 +23715,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G804" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23793,7 +23793,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G807" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23871,7 +23871,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G810" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23923,7 +23923,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G812" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24001,7 +24001,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G815" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24079,7 +24079,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G818" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24105,7 +24105,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G819" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24157,7 +24157,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G821" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24183,7 +24183,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G822" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24209,7 +24209,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G823" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24235,7 +24235,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G824" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24261,7 +24261,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G825" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24287,7 +24287,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G826" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24313,7 +24313,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G827" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24339,7 +24339,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G828" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24365,7 +24365,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G829" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24391,7 +24391,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G830" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24417,7 +24417,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G831" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24469,7 +24469,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G833" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24495,7 +24495,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G834" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24521,7 +24521,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G835" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24573,7 +24573,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G837" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24599,7 +24599,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G838" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24781,7 +24781,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G845" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24833,7 +24833,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G847" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24859,7 +24859,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G848" t="s">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24911,7 +24911,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G850" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24937,7 +24937,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G851" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25041,7 +25041,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G855" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25067,7 +25067,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G856" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25093,7 +25093,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G857" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25119,7 +25119,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G858" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25145,7 +25145,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G859" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25171,7 +25171,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G860" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25223,7 +25223,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G862" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25249,7 +25249,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G863" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25275,7 +25275,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G864" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25301,7 +25301,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G865" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25327,7 +25327,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G866" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25353,7 +25353,7 @@
         <v>1.25</v>
       </c>
       <c r="G867" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25379,7 +25379,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G868" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25405,7 +25405,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G869" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25431,7 +25431,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G870" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25457,7 +25457,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G871" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25483,7 +25483,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G872" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25509,7 +25509,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G873" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25535,7 +25535,7 @@
         <v>1.25</v>
       </c>
       <c r="G874" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25561,7 +25561,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G875" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25587,7 +25587,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G876" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -25613,7 +25613,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G877" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -25639,7 +25639,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G878" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25665,7 +25665,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G879" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -25795,7 +25795,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G884" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25821,7 +25821,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G885" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25847,7 +25847,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G886" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -25873,7 +25873,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G887" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -25899,7 +25899,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G888" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -25925,7 +25925,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G889" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -25951,7 +25951,7 @@
         <v>1.375</v>
       </c>
       <c r="G890" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -25977,7 +25977,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G891" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26003,7 +26003,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G892" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26029,7 +26029,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G893" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26055,7 +26055,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G894" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26081,7 +26081,7 @@
         <v>1.375</v>
       </c>
       <c r="G895" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26107,7 +26107,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G896" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26133,7 +26133,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G897" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26159,7 +26159,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G898" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26185,7 +26185,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G899" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26211,7 +26211,7 @@
         <v>1.5</v>
       </c>
       <c r="G900" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26237,7 +26237,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G901" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26263,7 +26263,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G902" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26289,7 +26289,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G903" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26315,7 +26315,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G904" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26341,7 +26341,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G905" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26367,7 +26367,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G906" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26393,7 +26393,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G907" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26419,7 +26419,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G908" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26445,7 +26445,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G909" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26471,7 +26471,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G910" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26497,7 +26497,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G911" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26523,7 +26523,7 @@
         <v>1.375</v>
       </c>
       <c r="G912" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26549,7 +26549,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G913" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -26575,7 +26575,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G914" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -26601,7 +26601,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G915" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -26627,7 +26627,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G916" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -26653,7 +26653,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G917" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -26679,7 +26679,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G918" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26705,7 +26705,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G919" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -26731,7 +26731,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G920" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -26757,7 +26757,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G921" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26783,7 +26783,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G922" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26809,7 +26809,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G923" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26835,7 +26835,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G924" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26861,7 +26861,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G925" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -26887,7 +26887,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G926" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26913,7 +26913,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G927" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26939,7 +26939,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G928" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26965,7 +26965,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G929" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26991,7 +26991,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G930" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27017,7 +27017,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G931" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27043,7 +27043,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G932" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27069,7 +27069,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G933" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -27095,7 +27095,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G934" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -27121,7 +27121,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G935" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -27147,7 +27147,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G936" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27173,7 +27173,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G937" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27199,7 +27199,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G938" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -27225,7 +27225,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G939" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27251,7 +27251,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G940" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27277,7 +27277,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G941" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27303,7 +27303,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G942" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27329,7 +27329,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G943" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27355,7 +27355,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G944" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27381,7 +27381,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G945" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27407,7 +27407,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G946" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27433,7 +27433,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G947" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27459,7 +27459,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G948" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27485,7 +27485,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G949" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27511,7 +27511,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G950" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27537,7 +27537,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G951" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -27563,7 +27563,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G952" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -27589,7 +27589,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G953" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27615,7 +27615,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G954" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -27641,7 +27641,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G955" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -27667,7 +27667,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G956" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27693,7 +27693,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G957" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27719,7 +27719,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G958" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27745,7 +27745,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G959" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27771,7 +27771,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G960" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27797,7 +27797,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G961" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27823,7 +27823,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G962" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27849,7 +27849,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G963" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27875,7 +27875,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G964" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27901,7 +27901,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G965" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27927,7 +27927,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G966" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27953,7 +27953,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G967" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27979,7 +27979,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G968" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28005,7 +28005,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G969" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -28031,7 +28031,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G970" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -28057,7 +28057,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G971" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -28083,7 +28083,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G972" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28109,7 +28109,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G973" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28135,7 +28135,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G974" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28161,7 +28161,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G975" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28187,7 +28187,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G976" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -28213,7 +28213,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G977" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28239,7 +28239,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G978" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28265,7 +28265,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G979" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28291,7 +28291,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G980" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28317,7 +28317,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G981" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28343,7 +28343,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G982" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28369,7 +28369,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G983" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28395,7 +28395,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G984" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28421,7 +28421,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G985" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28447,7 +28447,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G986" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28473,7 +28473,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G987" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28499,7 +28499,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G988" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28525,7 +28525,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G989" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28551,7 +28551,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G990" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -28577,7 +28577,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G991" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -28603,7 +28603,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G992" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28629,7 +28629,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G993" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28655,7 +28655,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G994" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -28681,7 +28681,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G995" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -28707,7 +28707,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G996" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -28733,7 +28733,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G997" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -28759,7 +28759,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G998" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28785,7 +28785,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G999" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28811,7 +28811,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1000" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28837,7 +28837,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1001" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28863,7 +28863,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1002" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28889,7 +28889,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1003" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28915,7 +28915,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1004" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28941,7 +28941,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1005" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28967,7 +28967,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1006" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28993,7 +28993,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1007" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29019,7 +29019,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1008" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29045,7 +29045,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1009" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29071,7 +29071,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1010" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29097,7 +29097,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1011" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29123,7 +29123,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1012" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29149,7 +29149,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1013" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29175,7 +29175,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1014" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29201,7 +29201,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1015" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -29227,7 +29227,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1016" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29253,7 +29253,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1017" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29279,7 +29279,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1018" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29305,7 +29305,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1019" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29331,7 +29331,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1020" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29357,7 +29357,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1021" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29383,7 +29383,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1022" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29409,7 +29409,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1023" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29435,7 +29435,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1024" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29461,7 +29461,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1025" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29487,7 +29487,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1026" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29513,7 +29513,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1027" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29539,7 +29539,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1028" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29565,7 +29565,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1029" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29591,7 +29591,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1030" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -29617,7 +29617,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1031" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -29643,7 +29643,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1032" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29669,7 +29669,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1033" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29695,7 +29695,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1034" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29721,7 +29721,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1035" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29747,7 +29747,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1036" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29773,7 +29773,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1037" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29799,7 +29799,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1038" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29825,7 +29825,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1039" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29851,7 +29851,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1040" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29877,7 +29877,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1041" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29903,7 +29903,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1042" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29929,7 +29929,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1043" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29955,7 +29955,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1044" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29981,7 +29981,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1045" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -30007,7 +30007,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1046" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30033,7 +30033,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1047" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -30059,7 +30059,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1048" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30085,7 +30085,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1049" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30111,7 +30111,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1050" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -30137,7 +30137,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1051" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30163,7 +30163,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1052" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30189,7 +30189,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1053" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -30215,7 +30215,7 @@
         <v>1.25</v>
       </c>
       <c r="G1054" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -30241,7 +30241,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1055" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -30267,7 +30267,7 @@
         <v>1.25</v>
       </c>
       <c r="G1056" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30293,7 +30293,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1057" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30319,7 +30319,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G1058" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30345,7 +30345,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1059" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30371,7 +30371,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1060" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30397,7 +30397,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1061" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30423,7 +30423,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1062" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30449,7 +30449,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1063" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30475,7 +30475,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1064" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -30501,7 +30501,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1065" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30527,7 +30527,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G1066" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30553,7 +30553,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1067" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -30579,7 +30579,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1068" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -30605,7 +30605,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G1069" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -30631,7 +30631,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1070" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -30657,7 +30657,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1071" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30683,7 +30683,7 @@
         <v>1</v>
       </c>
       <c r="G1072" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30709,7 +30709,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1073" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30735,7 +30735,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1074" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -30761,7 +30761,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1075" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30787,7 +30787,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G1076" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30813,7 +30813,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1077" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30839,7 +30839,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1078" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30865,7 +30865,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1079" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -30891,7 +30891,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1080" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30917,7 +30917,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1081" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30943,7 +30943,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1082" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30969,7 +30969,7 @@
         <v>1.125</v>
       </c>
       <c r="G1083" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30995,7 +30995,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1084" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -31021,7 +31021,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1085" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -31047,7 +31047,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1086" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31073,7 +31073,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1087" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -31099,7 +31099,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1088" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31125,7 +31125,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1089" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31151,7 +31151,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1090" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31177,7 +31177,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1091" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31203,7 +31203,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1092" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31229,7 +31229,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1093" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -31255,7 +31255,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1094" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31281,7 +31281,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1095" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31307,7 +31307,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1096" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31333,7 +31333,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1097" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31359,7 +31359,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G1098" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31385,7 +31385,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1099" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31411,7 +31411,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1100" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31437,7 +31437,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1101" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31463,7 +31463,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1102" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31489,7 +31489,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1103" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31515,7 +31515,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1104" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31541,7 +31541,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1105" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -31567,7 +31567,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1106" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -31593,7 +31593,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1107" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31619,7 +31619,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1108" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -31645,7 +31645,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1109" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -31671,7 +31671,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1110" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -31697,7 +31697,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1111" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31723,7 +31723,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1112" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31749,7 +31749,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1113" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31775,7 +31775,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1114" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31801,7 +31801,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1115" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31827,7 +31827,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1116" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31853,7 +31853,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1117" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31879,7 +31879,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1118" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31905,7 +31905,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1119" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31931,7 +31931,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1120" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31957,7 +31957,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1121" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31983,7 +31983,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1122" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -32009,7 +32009,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G1123" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -32035,7 +32035,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G1124" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -32061,7 +32061,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1125" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -32087,7 +32087,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1126" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -32113,7 +32113,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1127" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32139,7 +32139,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1128" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -32165,7 +32165,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1129" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -32191,7 +32191,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1130" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -32217,7 +32217,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1131" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32243,7 +32243,7 @@
         <v>1.25</v>
       </c>
       <c r="G1132" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -32269,7 +32269,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1133" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32295,7 +32295,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1134" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32321,7 +32321,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1135" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32347,7 +32347,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1136" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32373,7 +32373,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1137" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32399,7 +32399,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1138" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32425,7 +32425,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1139" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32451,7 +32451,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1140" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32477,7 +32477,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1141" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -32503,7 +32503,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1142" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32529,7 +32529,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1143" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32555,7 +32555,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1144" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -32581,7 +32581,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1145" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -32607,7 +32607,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1146" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -32633,7 +32633,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1147" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -32659,7 +32659,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1148" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -32685,7 +32685,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1149" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32711,7 +32711,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1150" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32737,7 +32737,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1151" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32763,7 +32763,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1152" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32789,7 +32789,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G1153" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32815,7 +32815,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1154" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32841,7 +32841,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1155" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32867,7 +32867,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1156" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32893,7 +32893,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1157" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32919,7 +32919,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1158" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32945,7 +32945,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1159" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32971,7 +32971,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1160" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32997,7 +32997,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1161" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -33023,7 +33023,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1162" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -33049,7 +33049,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1163" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33075,7 +33075,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1164" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -33101,7 +33101,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1165" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33127,7 +33127,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1166" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33153,7 +33153,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1167" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33179,7 +33179,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1168" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33205,7 +33205,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1169" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -33231,7 +33231,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1170" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33257,7 +33257,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1171" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33283,7 +33283,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1172" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33309,7 +33309,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1173" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33335,7 +33335,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1174" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33361,7 +33361,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1175" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33387,7 +33387,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1176" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33413,7 +33413,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1177" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33439,7 +33439,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1178" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33465,7 +33465,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1179" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33491,7 +33491,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1180" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33517,7 +33517,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1181" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33543,7 +33543,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1182" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -33569,7 +33569,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1183" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -33595,7 +33595,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1184" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -33621,7 +33621,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1185" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33647,7 +33647,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1186" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -33673,7 +33673,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1187" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33699,7 +33699,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1188" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33725,7 +33725,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1189" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33751,7 +33751,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1190" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33777,7 +33777,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1191" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33803,7 +33803,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1192" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33829,7 +33829,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1193" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33855,7 +33855,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1194" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33881,7 +33881,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1195" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33907,7 +33907,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1196" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33933,7 +33933,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33959,7 +33959,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1198" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33985,7 +33985,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1199" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -34011,7 +34011,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1200" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -34037,7 +34037,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1201" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -34063,7 +34063,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1202" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -34089,7 +34089,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1203" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -34115,7 +34115,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1204" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34141,7 +34141,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1205" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34167,7 +34167,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1206" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34193,7 +34193,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1207" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34219,7 +34219,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1208" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34245,7 +34245,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1209" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34271,7 +34271,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1210" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34297,7 +34297,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1211" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34323,7 +34323,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1212" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34349,7 +34349,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1213" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34375,7 +34375,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1214" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34401,7 +34401,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1215" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34427,7 +34427,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1216" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34453,7 +34453,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1217" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34479,7 +34479,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1218" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -34505,7 +34505,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1219" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34531,7 +34531,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1220" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34557,7 +34557,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1221" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -34583,7 +34583,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1222" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -34609,7 +34609,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1223" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -34635,7 +34635,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1224" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -34661,7 +34661,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1225" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -34687,7 +34687,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1226" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34713,7 +34713,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1227" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34739,7 +34739,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1228" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34765,7 +34765,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1229" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34791,7 +34791,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1230" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34817,7 +34817,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1231" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34843,7 +34843,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1232" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34869,7 +34869,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1233" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34895,7 +34895,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1234" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34921,7 +34921,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1235" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34947,7 +34947,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1236" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34973,7 +34973,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1237" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34999,7 +34999,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1238" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -35025,7 +35025,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1239" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -35051,7 +35051,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1240" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -35077,7 +35077,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1241" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -35103,7 +35103,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1242" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35129,7 +35129,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1243" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35155,7 +35155,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1244" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35181,7 +35181,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1245" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35207,7 +35207,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1246" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35233,7 +35233,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1247" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35259,7 +35259,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1248" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35285,7 +35285,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1249" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35311,7 +35311,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1250" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35337,7 +35337,7 @@
         <v>1.125</v>
       </c>
       <c r="G1251" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35363,7 +35363,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1252" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35389,7 +35389,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1253" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35415,7 +35415,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1254" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35441,7 +35441,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1255" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35467,7 +35467,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1256" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35493,7 +35493,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1257" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35519,7 +35519,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1258" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35545,7 +35545,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1259" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35571,7 +35571,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1260" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -35597,7 +35597,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1261" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -35623,7 +35623,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1262" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -35649,7 +35649,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1263" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -35675,7 +35675,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1264" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35701,7 +35701,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1265" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35727,7 +35727,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1266" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35753,7 +35753,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1267" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35779,7 +35779,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1268" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35805,7 +35805,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1269" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35831,7 +35831,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1270" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35857,7 +35857,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1271" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35883,7 +35883,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G1272" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35909,7 +35909,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1273" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35935,7 +35935,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1274" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35961,7 +35961,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1275" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35987,7 +35987,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1276" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -36013,7 +36013,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1277" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -36039,7 +36039,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1278" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -36065,7 +36065,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1279" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -36091,7 +36091,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1280" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -36117,7 +36117,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1281" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36143,7 +36143,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1282" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36169,7 +36169,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1283" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36195,7 +36195,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1284" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36221,7 +36221,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1285" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36247,7 +36247,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1286" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36273,7 +36273,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1287" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36299,7 +36299,7 @@
         <v>1.375</v>
       </c>
       <c r="G1288" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36325,7 +36325,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1289" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36351,7 +36351,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1290" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36377,7 +36377,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1291" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36403,7 +36403,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1292" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36429,7 +36429,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1293" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36455,7 +36455,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1294" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36481,7 +36481,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1295" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36507,7 +36507,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1296" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36533,7 +36533,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1297" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36559,7 +36559,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1298" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -36585,7 +36585,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1299" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -36611,7 +36611,7 @@
         <v>1.375</v>
       </c>
       <c r="G1300" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36637,7 +36637,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1301" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36663,7 +36663,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1302" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36689,7 +36689,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1303" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36715,7 +36715,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1304" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36741,7 +36741,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1305" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36767,7 +36767,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1306" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36793,7 +36793,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1307" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36819,7 +36819,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1308" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36845,7 +36845,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1309" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36871,7 +36871,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1310" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36897,7 +36897,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1311" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36923,7 +36923,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1312" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36949,7 +36949,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1313" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36975,7 +36975,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1314" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -37001,7 +37001,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1315" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -37027,7 +37027,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1316" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -37053,7 +37053,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1317" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -37079,7 +37079,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1318" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -37105,7 +37105,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1319" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -37131,7 +37131,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1320" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -37157,7 +37157,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1321" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -37183,7 +37183,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1322" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37209,7 +37209,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1323" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -37235,7 +37235,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1324" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -37261,7 +37261,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1325" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37287,7 +37287,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1326" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37313,7 +37313,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1327" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37339,7 +37339,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1328" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37365,7 +37365,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1329" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37391,7 +37391,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1330" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37417,7 +37417,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1331" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37443,7 +37443,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1332" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37469,7 +37469,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1333" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37495,7 +37495,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1334" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37521,7 +37521,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1335" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37547,7 +37547,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1336" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37573,7 +37573,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1337" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37599,7 +37599,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1338" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37625,7 +37625,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1339" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37651,7 +37651,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1340" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37677,7 +37677,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1341" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37703,7 +37703,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1342" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37729,7 +37729,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1343" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37755,7 +37755,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1344" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37781,7 +37781,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1345" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37807,7 +37807,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1346" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37833,7 +37833,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1347" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37859,7 +37859,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -37885,7 +37885,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1349" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -37911,7 +37911,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1350" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37937,7 +37937,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1351" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37963,7 +37963,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1352" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37989,7 +37989,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1353" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -38015,7 +38015,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1354" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -38041,7 +38041,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1355" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -38067,7 +38067,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1356" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -38093,7 +38093,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1357" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -38119,7 +38119,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1358" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -38145,7 +38145,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1359" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -38171,7 +38171,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1360" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -38197,7 +38197,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1361" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -38223,7 +38223,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1362" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -38249,7 +38249,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1363" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38275,7 +38275,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38301,7 +38301,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1365" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38327,7 +38327,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1366" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38353,7 +38353,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1367" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38379,7 +38379,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1368" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38405,7 +38405,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1369" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38431,7 +38431,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1370" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38457,7 +38457,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1371" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38483,7 +38483,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1372" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38509,7 +38509,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1373" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38535,7 +38535,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1374" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38561,7 +38561,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1375" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38587,7 +38587,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1376" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38613,7 +38613,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1377" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38639,7 +38639,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1378" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38665,7 +38665,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1379" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38691,7 +38691,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1380" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38717,7 +38717,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1381" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38743,7 +38743,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1382" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38769,7 +38769,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1383" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38795,7 +38795,7 @@
         <v>1.5</v>
       </c>
       <c r="G1384" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38821,7 +38821,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1385" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38847,7 +38847,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1386" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38873,7 +38873,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1387" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38899,7 +38899,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1388" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38925,7 +38925,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1389" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38951,7 +38951,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1390" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38977,7 +38977,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1391" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -39003,7 +39003,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1392" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -39029,7 +39029,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1393" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -39055,7 +39055,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1394" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -39081,7 +39081,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1395" t="s">
-        <v>391</v>
+        <v>473</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -39107,7 +39107,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1396" t="s">
-        <v>391</v>
+        <v>473</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -39835,7 +39835,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1424" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39913,7 +39913,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1427" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39965,7 +39965,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1429" t="s">
-        <v>391</v>
+        <v>473</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -40069,7 +40069,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1433" t="s">
-        <v>391</v>
+        <v>473</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -67923,25 +67923,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.6577546296</v>
+        <v>45968.6790509259</v>
       </c>
       <c r="B2505" t="n">
-        <v>5000</v>
+        <v>9500</v>
       </c>
       <c r="C2505" t="n">
-        <v>2.02999997138977</v>
+        <v>2.01999998092651</v>
       </c>
       <c r="D2505" t="n">
-        <v>2.00999999046326</v>
+        <v>1.96000003814697</v>
       </c>
       <c r="E2505" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="F2505" t="n">
         <v>2.01999998092651</v>
       </c>
-      <c r="F2505" t="n">
-        <v>2.00999999046326</v>
-      </c>
       <c r="G2505" t="s">
-        <v>799</v>
+        <v>818</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/DGT.MI.xlsx
+++ b/data/DGT.MI.xlsx
@@ -44,67 +44,67 @@
     <t xml:space="preserve">DGT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0576708316803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03047704696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96702456474304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00509548187256</t>
+    <t xml:space="preserve">2.05767059326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03047680854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96702444553375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00509595870972</t>
   </si>
   <si>
     <t xml:space="preserve">2.04860615730286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9942182302475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971487045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94889533519745</t>
+    <t xml:space="preserve">1.99421834945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971510887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94889509677887</t>
   </si>
   <si>
     <t xml:space="preserve">1.88544285297394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91444957256317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89632058143616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87637805938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97065043449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92714011669159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93076622486115</t>
+    <t xml:space="preserve">1.91444945335388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89632046222687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8763781785965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97065031528473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92714023590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93076586723328</t>
   </si>
   <si>
     <t xml:space="preserve">1.85824906826019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80839347839355</t>
+    <t xml:space="preserve">1.80839359760284</t>
   </si>
   <si>
     <t xml:space="preserve">1.8256162405014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75128650665283</t>
+    <t xml:space="preserve">1.75128638744354</t>
   </si>
   <si>
     <t xml:space="preserve">1.64704310894012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75581860542297</t>
+    <t xml:space="preserve">1.75581872463226</t>
   </si>
   <si>
     <t xml:space="preserve">1.71321499347687</t>
@@ -119,25 +119,25 @@
     <t xml:space="preserve">1.76760280132294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72862470149994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7585381269455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81292581558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83105516433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7685090303421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67514336109161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74947345256805</t>
+    <t xml:space="preserve">1.72862482070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75853800773621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81292593479156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83105504512787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76850914955139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67514359951019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74947333335876</t>
   </si>
   <si>
     <t xml:space="preserve">1.69871151447296</t>
@@ -149,19 +149,19 @@
     <t xml:space="preserve">1.70777606964111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70868265628815</t>
+    <t xml:space="preserve">1.70868253707886</t>
   </si>
   <si>
     <t xml:space="preserve">1.69508564472198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7766672372818</t>
+    <t xml:space="preserve">1.77666735649109</t>
   </si>
   <si>
     <t xml:space="preserve">1.7014307975769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69055330753326</t>
+    <t xml:space="preserve">1.69055318832397</t>
   </si>
   <si>
     <t xml:space="preserve">1.73497009277344</t>
@@ -173,46 +173,46 @@
     <t xml:space="preserve">1.62982034683228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63163316249847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68692755699158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68602097034454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67333042621613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74040877819061</t>
+    <t xml:space="preserve">1.63163304328918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68692743778229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68602120876312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67333054542542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74040865898132</t>
   </si>
   <si>
     <t xml:space="preserve">1.70415019989014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75672495365143</t>
+    <t xml:space="preserve">1.75672507286072</t>
   </si>
   <si>
     <t xml:space="preserve">1.68783390522003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64885604381561</t>
+    <t xml:space="preserve">1.64885592460632</t>
   </si>
   <si>
     <t xml:space="preserve">1.64794957637787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68420827388763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72137331962585</t>
+    <t xml:space="preserve">1.68420803546906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72137308120728</t>
   </si>
   <si>
     <t xml:space="preserve">1.72227954864502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67786276340485</t>
+    <t xml:space="preserve">1.67786288261414</t>
   </si>
   <si>
     <t xml:space="preserve">1.63253974914551</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">1.66335940361023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66517233848572</t>
+    <t xml:space="preserve">1.66517245769501</t>
   </si>
   <si>
     <t xml:space="preserve">1.65429496765137</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">1.79026424884796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78754496574402</t>
+    <t xml:space="preserve">1.78754472732544</t>
   </si>
   <si>
     <t xml:space="preserve">1.78935778141022</t>
@@ -242,13 +242,13 @@
     <t xml:space="preserve">1.66154646873474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69961786270142</t>
+    <t xml:space="preserve">1.69961798191071</t>
   </si>
   <si>
     <t xml:space="preserve">1.66245305538177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68330156803131</t>
+    <t xml:space="preserve">1.68330144882202</t>
   </si>
   <si>
     <t xml:space="preserve">1.65882706642151</t>
@@ -260,25 +260,25 @@
     <t xml:space="preserve">1.569087266922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58902966976166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48297321796417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49566376209259</t>
+    <t xml:space="preserve">1.58902955055237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48297345638275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49566388130188</t>
   </si>
   <si>
     <t xml:space="preserve">1.4920380115509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53192222118378</t>
+    <t xml:space="preserve">1.53192245960236</t>
   </si>
   <si>
     <t xml:space="preserve">1.48387980461121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45215368270874</t>
+    <t xml:space="preserve">1.45215356349945</t>
   </si>
   <si>
     <t xml:space="preserve">1.48569285869598</t>
@@ -287,46 +287,46 @@
     <t xml:space="preserve">1.42858552932739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4594053030014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49294435977936</t>
+    <t xml:space="preserve">1.45940518379211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49294447898865</t>
   </si>
   <si>
     <t xml:space="preserve">1.46031177043915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44127607345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45034062862396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46846985816956</t>
+    <t xml:space="preserve">1.44127595424652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45034050941467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46846997737885</t>
   </si>
   <si>
     <t xml:space="preserve">1.42586612701416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3125581741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36422669887543</t>
+    <t xml:space="preserve">1.31255829334259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36422657966614</t>
   </si>
   <si>
     <t xml:space="preserve">1.34156513214111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36875891685486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33250045776367</t>
+    <t xml:space="preserve">1.36875915527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33250057697296</t>
   </si>
   <si>
     <t xml:space="preserve">1.2781126499176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19653105735779</t>
+    <t xml:space="preserve">1.19653117656708</t>
   </si>
   <si>
     <t xml:space="preserve">1.17296302318573</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">1.18746638298035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17568254470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15483367443085</t>
+    <t xml:space="preserve">1.17568242549896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15483391284943</t>
   </si>
   <si>
     <t xml:space="preserve">1.09863305091858</t>
@@ -353,49 +353,49 @@
     <t xml:space="preserve">1.1258270740509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11313652992249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06962621212006</t>
+    <t xml:space="preserve">1.1131364107132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06962645053864</t>
   </si>
   <si>
     <t xml:space="preserve">1.08684909343719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0950071811676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09410071372986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12038826942444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09228777885437</t>
+    <t xml:space="preserve">1.09500706195831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09410083293915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12038815021515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09228789806366</t>
   </si>
   <si>
     <t xml:space="preserve">1.10769748687744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10951066017151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12129461765289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09682023525238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08956849575043</t>
+    <t xml:space="preserve">1.10951054096222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1212944984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09682011604309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08956837654114</t>
   </si>
   <si>
     <t xml:space="preserve">1.08866190910339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07234585285187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05149686336517</t>
+    <t xml:space="preserve">1.07234573364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05149698257446</t>
   </si>
   <si>
     <t xml:space="preserve">1.12310755252838</t>
@@ -404,13 +404,13 @@
     <t xml:space="preserve">1.10135245323181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08322322368622</t>
+    <t xml:space="preserve">1.08322334289551</t>
   </si>
   <si>
     <t xml:space="preserve">1.08775556087494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11404275894165</t>
+    <t xml:space="preserve">1.11404287815094</t>
   </si>
   <si>
     <t xml:space="preserve">1.15120792388916</t>
@@ -422,55 +422,55 @@
     <t xml:space="preserve">1.18474698066711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14576923847198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12220096588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0623744726181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03336775302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934563338756561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945440828800201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977167069911957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956318378448486</t>
+    <t xml:space="preserve">1.1457691192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12220120429993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06237459182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03336751461029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934563398361206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945440888404846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977167129516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956318438053131</t>
   </si>
   <si>
     <t xml:space="preserve">0.933656752109528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01523852348328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04877758026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03608727455139</t>
+    <t xml:space="preserve">1.01523840427399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04877769947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0360871553421</t>
   </si>
   <si>
     <t xml:space="preserve">1.02430307865143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990764021873474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05059051513672</t>
+    <t xml:space="preserve">0.990764141082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05059063434601</t>
   </si>
   <si>
     <t xml:space="preserve">1.11494946479797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12854623794556</t>
+    <t xml:space="preserve">1.12854635715485</t>
   </si>
   <si>
     <t xml:space="preserve">1.07506501674652</t>
@@ -482,22 +482,22 @@
     <t xml:space="preserve">1.02067732810974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997109115123749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00617396831512</t>
+    <t xml:space="preserve">0.997109174728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00617384910583</t>
   </si>
   <si>
     <t xml:space="preserve">0.988044619560242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03880643844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05965530872345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04243242740631</t>
+    <t xml:space="preserve">1.03880655765533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05965518951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04243230819702</t>
   </si>
   <si>
     <t xml:space="preserve">1.06328094005585</t>
@@ -506,28 +506,28 @@
     <t xml:space="preserve">1.05693566799164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10407173633575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10497808456421</t>
+    <t xml:space="preserve">1.10407209396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1049782037735</t>
   </si>
   <si>
     <t xml:space="preserve">1.07597148418427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12492060661316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1031653881073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21103429794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19562458992004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21284735202789</t>
+    <t xml:space="preserve">1.12492036819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10316550731659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2110344171524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19562470912933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21284747123718</t>
   </si>
   <si>
     <t xml:space="preserve">1.14667558670044</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">1.15392732620239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20559585094452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20196974277496</t>
+    <t xml:space="preserve">1.20559561252594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20196986198425</t>
   </si>
   <si>
     <t xml:space="preserve">1.23188304901123</t>
@@ -551,28 +551,28 @@
     <t xml:space="preserve">1.25817048549652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26088988780975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25545108318329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28717732429504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30893242359161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30530667304993</t>
+    <t xml:space="preserve">1.26089000701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25545120239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28717744350433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3089325428009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30530679225922</t>
   </si>
   <si>
     <t xml:space="preserve">1.41226923465729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37963652610779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40320456027985</t>
+    <t xml:space="preserve">1.37963664531708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40320467948914</t>
   </si>
   <si>
     <t xml:space="preserve">1.35244274139404</t>
@@ -581,28 +581,28 @@
     <t xml:space="preserve">1.35697495937347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35969460010529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34065866470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32343602180481</t>
+    <t xml:space="preserve">1.35969436168671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34065842628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32343590259552</t>
   </si>
   <si>
     <t xml:space="preserve">1.35062968730927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32887446880341</t>
+    <t xml:space="preserve">1.3288745880127</t>
   </si>
   <si>
     <t xml:space="preserve">1.26995456218719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19471800327301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14395606517792</t>
+    <t xml:space="preserve">1.1947181224823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1439563035965</t>
   </si>
   <si>
     <t xml:space="preserve">1.2454799413681</t>
@@ -611,13 +611,13 @@
     <t xml:space="preserve">1.25001239776611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26814150810242</t>
+    <t xml:space="preserve">1.268141746521</t>
   </si>
   <si>
     <t xml:space="preserve">1.23278951644897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24185431003571</t>
+    <t xml:space="preserve">1.24185419082642</t>
   </si>
   <si>
     <t xml:space="preserve">1.28173863887787</t>
@@ -626,25 +626,25 @@
     <t xml:space="preserve">1.26451575756073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2826452255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25091874599457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26904809474945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33159410953522</t>
+    <t xml:space="preserve">1.28264486789703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25091862678528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26904797554016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33159399032593</t>
   </si>
   <si>
     <t xml:space="preserve">1.29624199867249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28536427021027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31437110900879</t>
+    <t xml:space="preserve">1.28536438941956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31437134742737</t>
   </si>
   <si>
     <t xml:space="preserve">1.30983889102936</t>
@@ -656,61 +656,61 @@
     <t xml:space="preserve">1.29896140098572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37782347202301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3352198600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26179611682892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31074523925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30711960792542</t>
+    <t xml:space="preserve">1.37782371044159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33521997928619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26179623603821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31074547767639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30711948871613</t>
   </si>
   <si>
     <t xml:space="preserve">1.34247148036957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29442894458771</t>
+    <t xml:space="preserve">1.294429063797</t>
   </si>
   <si>
     <t xml:space="preserve">1.32434225082397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33884561061859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31165182590485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27992570400238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30621314048767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31618416309357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30349373817444</t>
+    <t xml:space="preserve">1.33884572982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31165194511414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27992558479309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30621290206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31618428230286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30349361896515</t>
   </si>
   <si>
     <t xml:space="preserve">1.27720642089844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26632857322693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28355157375336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25907707214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24910593032837</t>
+    <t xml:space="preserve">1.26632869243622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28355133533478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25907695293427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24910581111908</t>
   </si>
   <si>
     <t xml:space="preserve">1.27539324760437</t>
@@ -722,64 +722,64 @@
     <t xml:space="preserve">1.34700393676758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34972333908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29261600971222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32978117465973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23369586467743</t>
+    <t xml:space="preserve">1.34972321987152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29261589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32978105545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23369610309601</t>
   </si>
   <si>
     <t xml:space="preserve">1.22372496128082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22916376590729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20468926429749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22191214561462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21919250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2210054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21828603744507</t>
+    <t xml:space="preserve">1.229163646698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2046891450882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22191202640533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21919274330139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22100555896759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21828615665436</t>
   </si>
   <si>
     <t xml:space="preserve">1.22463130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21012794971466</t>
+    <t xml:space="preserve">1.21012806892395</t>
   </si>
   <si>
     <t xml:space="preserve">1.1865599155426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17477595806122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17840170860291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15211427211761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15845954418182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08594238758087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10588467121124</t>
+    <t xml:space="preserve">1.17477607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17840182781219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1521143913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15845966339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08594250679016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10588479042053</t>
   </si>
   <si>
     <t xml:space="preserve">1.07959735393524</t>
@@ -788,19 +788,19 @@
     <t xml:space="preserve">1.10679125785828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13217210769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16933727264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22644436359406</t>
+    <t xml:space="preserve">1.13217198848724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16933715343475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22644424438477</t>
   </si>
   <si>
     <t xml:space="preserve">1.23822832107544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24457359313965</t>
+    <t xml:space="preserve">1.24457371234894</t>
   </si>
   <si>
     <t xml:space="preserve">1.2518253326416</t>
@@ -809,13 +809,13 @@
     <t xml:space="preserve">1.24004125595093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20378279685974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20650207996368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24094760417938</t>
+    <t xml:space="preserve">1.20378267765045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20650219917297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24094784259796</t>
   </si>
   <si>
     <t xml:space="preserve">1.23097670078278</t>
@@ -824,82 +824,82 @@
     <t xml:space="preserve">1.21194100379944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23460245132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24638664722443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2762998342514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27086091041565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29805481433868</t>
+    <t xml:space="preserve">1.23460221290588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24638652801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27629971504211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27086102962494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29805505275726</t>
   </si>
   <si>
     <t xml:space="preserve">1.22553777694702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15574026107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11857521533966</t>
+    <t xml:space="preserve">1.15574014186859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11857509613037</t>
   </si>
   <si>
     <t xml:space="preserve">1.16027247905731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16661775112152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16480469703674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18112099170685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19925045967102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11676239967346</t>
+    <t xml:space="preserve">1.16661763191223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16480481624603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18112111091614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19925034046173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11676228046417</t>
   </si>
   <si>
     <t xml:space="preserve">1.09319424629211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09772658348083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17658889293671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17930841445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21375393867493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21556663513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2862708568573</t>
+    <t xml:space="preserve">1.09772646427155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17658877372742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17930829524994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21375381946564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21556675434113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28627097606659</t>
   </si>
   <si>
     <t xml:space="preserve">1.28989672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28445780277252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38960766792297</t>
+    <t xml:space="preserve">1.2844580411911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38960778713226</t>
   </si>
   <si>
     <t xml:space="preserve">1.4004852771759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41408205032349</t>
+    <t xml:space="preserve">1.41408216953278</t>
   </si>
   <si>
     <t xml:space="preserve">1.38235604763031</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">1.37057197093964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32796812057495</t>
+    <t xml:space="preserve">1.32796823978424</t>
   </si>
   <si>
     <t xml:space="preserve">1.36513304710388</t>
@@ -917,16 +917,16 @@
     <t xml:space="preserve">1.35516214370728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3841689825058</t>
+    <t xml:space="preserve">1.38416886329651</t>
   </si>
   <si>
     <t xml:space="preserve">1.42224025726318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38054311275482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38870096206665</t>
+    <t xml:space="preserve">1.38054299354553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38870108127594</t>
   </si>
   <si>
     <t xml:space="preserve">1.36694610118866</t>
@@ -935,43 +935,43 @@
     <t xml:space="preserve">1.40773689746857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39957869052887</t>
+    <t xml:space="preserve">1.39957857131958</t>
   </si>
   <si>
     <t xml:space="preserve">1.39685940742493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38326251506805</t>
+    <t xml:space="preserve">1.38326239585876</t>
   </si>
   <si>
     <t xml:space="preserve">1.38688826560974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50926077365875</t>
+    <t xml:space="preserve">1.50926065444946</t>
   </si>
   <si>
     <t xml:space="preserve">1.57724547386169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57271313667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54551923274994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55005145072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51379311084747</t>
+    <t xml:space="preserve">1.57271337509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54551935195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55005156993866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51379299163818</t>
   </si>
   <si>
     <t xml:space="preserve">1.48659920692444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44580829143524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48206698894501</t>
+    <t xml:space="preserve">1.44580852985382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48206686973572</t>
   </si>
   <si>
     <t xml:space="preserve">1.43221139907837</t>
@@ -980,37 +980,37 @@
     <t xml:space="preserve">1.5409871339798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52285778522491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52738988399506</t>
+    <t xml:space="preserve">1.52285766601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52739012241364</t>
   </si>
   <si>
     <t xml:space="preserve">1.37329125404358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39142048358917</t>
+    <t xml:space="preserve">1.39142060279846</t>
   </si>
   <si>
     <t xml:space="preserve">1.34609746932983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29170942306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3189035654068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3370326757431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27358043193817</t>
+    <t xml:space="preserve">1.29170966148376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31890368461609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33703279495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27358031272888</t>
   </si>
   <si>
     <t xml:space="preserve">1.39595282077789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30077433586121</t>
+    <t xml:space="preserve">1.30077421665192</t>
   </si>
   <si>
     <t xml:space="preserve">1.33341026306152</t>
@@ -1031,19 +1031,19 @@
     <t xml:space="preserve">1.24948930740356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23084020614624</t>
+    <t xml:space="preserve">1.23084032535553</t>
   </si>
   <si>
     <t xml:space="preserve">1.21219098567963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25415146350861</t>
+    <t xml:space="preserve">1.2541515827179</t>
   </si>
   <si>
     <t xml:space="preserve">1.23550248146057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2261780500412</t>
+    <t xml:space="preserve">1.22617793083191</t>
   </si>
   <si>
     <t xml:space="preserve">1.19354200363159</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">1.19820415973663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24016499519348</t>
+    <t xml:space="preserve">1.2401647567749</t>
   </si>
   <si>
     <t xml:space="preserve">1.27280068397522</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">1.32874774932861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28212535381317</t>
+    <t xml:space="preserve">1.28212523460388</t>
   </si>
   <si>
     <t xml:space="preserve">1.26813840866089</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">1.18887984752655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1655684709549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20286667346954</t>
+    <t xml:space="preserve">1.16556835174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20286655426025</t>
   </si>
   <si>
     <t xml:space="preserve">1.17489290237427</t>
@@ -1100,13 +1100,13 @@
     <t xml:space="preserve">1.34739708900452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17023050785065</t>
+    <t xml:space="preserve">1.17023038864136</t>
   </si>
   <si>
     <t xml:space="preserve">1.14691936969757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13293242454529</t>
+    <t xml:space="preserve">1.13293254375458</t>
   </si>
   <si>
     <t xml:space="preserve">1.25881385803223</t>
@@ -1115,31 +1115,31 @@
     <t xml:space="preserve">1.27746307849884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22151565551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15624380111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18421745300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28678739070892</t>
+    <t xml:space="preserve">1.22151553630829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15624368190765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18421733379364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28678727149963</t>
   </si>
   <si>
     <t xml:space="preserve">1.16090607643127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1515816450119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13759469985962</t>
+    <t xml:space="preserve">1.15158152580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13759481906891</t>
   </si>
   <si>
     <t xml:space="preserve">1.3613840341568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29144966602325</t>
+    <t xml:space="preserve">1.29144978523254</t>
   </si>
   <si>
     <t xml:space="preserve">1.34273481369019</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">1.33807253837585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11428344249725</t>
+    <t xml:space="preserve">1.11428356170654</t>
   </si>
   <si>
     <t xml:space="preserve">1.1049587726593</t>
@@ -68137,7 +68137,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.5207175926</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>500</v>
@@ -68158,6 +68158,32 @@
         <v>819</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.387974537</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>1.98500001430511</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>1.98500001430511</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>1.98500001430511</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>1.98500001430511</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>821</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DGT.MI.xlsx
+++ b/data/DGT.MI.xlsx
@@ -38,79 +38,79 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08123874664307</t>
+    <t xml:space="preserve">2.08123898506165</t>
   </si>
   <si>
     <t xml:space="preserve">DGT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05767107009888</t>
+    <t xml:space="preserve">2.05767059326172</t>
   </si>
   <si>
     <t xml:space="preserve">2.03047680854797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96702468395233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0050961971283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04860615730286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99421811103821</t>
+    <t xml:space="preserve">1.96702456474304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00509572029114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04860639572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99421870708466</t>
   </si>
   <si>
     <t xml:space="preserve">1.97971487045288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94889545440674</t>
+    <t xml:space="preserve">1.94889533519745</t>
   </si>
   <si>
     <t xml:space="preserve">1.88544273376465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91444981098175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89632022380829</t>
+    <t xml:space="preserve">1.91444969177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89632034301758</t>
   </si>
   <si>
     <t xml:space="preserve">1.8763781785965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97065055370331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9271399974823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93076598644257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85824882984161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80839335918427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82561612129211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75128650665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64704322814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75581860542297</t>
+    <t xml:space="preserve">1.97065043449402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92714035511017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93076634407043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8582489490509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80839359760284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8256162405014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75128638744354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64704310894012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75581872463226</t>
   </si>
   <si>
     <t xml:space="preserve">1.71321487426758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68964672088623</t>
+    <t xml:space="preserve">1.6896470785141</t>
   </si>
   <si>
     <t xml:space="preserve">1.73134410381317</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">1.76760268211365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72862493991852</t>
+    <t xml:space="preserve">1.72862482070923</t>
   </si>
   <si>
     <t xml:space="preserve">1.75853800773621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81292593479156</t>
+    <t xml:space="preserve">1.81292569637299</t>
   </si>
   <si>
     <t xml:space="preserve">1.83105504512787</t>
@@ -137,28 +137,28 @@
     <t xml:space="preserve">1.6751434803009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74947321414948</t>
+    <t xml:space="preserve">1.74947345256805</t>
   </si>
   <si>
     <t xml:space="preserve">1.69871139526367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74766051769257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70777595043182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70868253707886</t>
+    <t xml:space="preserve">1.74766039848328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70777606964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70868265628815</t>
   </si>
   <si>
     <t xml:space="preserve">1.69508564472198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77666735649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70143091678619</t>
+    <t xml:space="preserve">1.7766672372818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7014307975769</t>
   </si>
   <si>
     <t xml:space="preserve">1.69055342674255</t>
@@ -170,88 +170,88 @@
     <t xml:space="preserve">1.64069783687592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62982034683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63163328170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68692743778229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68602108955383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67333054542542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7404088973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70415019989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75672507286072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68783402442932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64885592460632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64794945716858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68420791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72137320041656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72227942943573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67786276340485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63253962993622</t>
+    <t xml:space="preserve">1.62982022762299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63163316249847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68692755699158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68602097034454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67333042621613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74040865898132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70415031909943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75672519207001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68783390522003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64885604381561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64794957637787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68420803546906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72137308120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72227966785431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67786264419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6325398683548</t>
   </si>
   <si>
     <t xml:space="preserve">1.66335952281952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66517245769501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65429484844208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81111311912537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79026436805725</t>
+    <t xml:space="preserve">1.66517233848572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65429496765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81111288070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79026424884796</t>
   </si>
   <si>
     <t xml:space="preserve">1.78754496574402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78935790061951</t>
+    <t xml:space="preserve">1.78935766220093</t>
   </si>
   <si>
     <t xml:space="preserve">1.66154646873474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69961798191071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66245293617249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68330156803131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65882694721222</t>
+    <t xml:space="preserve">1.69961786270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66245305538177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6833016872406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65882706642151</t>
   </si>
   <si>
     <t xml:space="preserve">1.60353291034698</t>
@@ -260,13 +260,13 @@
     <t xml:space="preserve">1.569087266922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58902931213379</t>
+    <t xml:space="preserve">1.58902955055237</t>
   </si>
   <si>
     <t xml:space="preserve">1.48297333717346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49566388130188</t>
+    <t xml:space="preserve">1.4956636428833</t>
   </si>
   <si>
     <t xml:space="preserve">1.4920380115509</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">1.53192234039307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48387980461121</t>
+    <t xml:space="preserve">1.4838799238205</t>
   </si>
   <si>
     <t xml:space="preserve">1.45215356349945</t>
@@ -284,100 +284,100 @@
     <t xml:space="preserve">1.48569285869598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42858552932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45940518379211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49294447898865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46031177043915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44127607345581</t>
+    <t xml:space="preserve">1.4285854101181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4594053030014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49294435977936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46031188964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44127583503723</t>
   </si>
   <si>
     <t xml:space="preserve">1.45034062862396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46846997737885</t>
+    <t xml:space="preserve">1.46846985816956</t>
   </si>
   <si>
     <t xml:space="preserve">1.42586612701416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31255841255188</t>
+    <t xml:space="preserve">1.3125581741333</t>
   </si>
   <si>
     <t xml:space="preserve">1.36422669887543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34156513214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36875915527344</t>
+    <t xml:space="preserve">1.3415652513504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36875891685486</t>
   </si>
   <si>
     <t xml:space="preserve">1.33250045776367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2781126499176</t>
+    <t xml:space="preserve">1.27811276912689</t>
   </si>
   <si>
     <t xml:space="preserve">1.19653105735779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17296302318573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18746650218964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17568242549896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15483379364014</t>
+    <t xml:space="preserve">1.17296326160431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18746638298035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17568254470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15483367443085</t>
   </si>
   <si>
     <t xml:space="preserve">1.09863317012787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12401413917542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13307869434357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12582695484161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1131364107132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06962621212006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08684909343719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09500706195831</t>
+    <t xml:space="preserve">1.12401401996613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13307857513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1258270740509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11313652992249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06962633132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08684897422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0950071811676</t>
   </si>
   <si>
     <t xml:space="preserve">1.09410071372986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12038826942444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09228777885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10769760608673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10951066017151</t>
+    <t xml:space="preserve">1.12038815021515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09228801727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10769772529602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10951042175293</t>
   </si>
   <si>
     <t xml:space="preserve">1.12129473686218</t>
@@ -392,46 +392,46 @@
     <t xml:space="preserve">1.08866190910339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07234573364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05149686336517</t>
+    <t xml:space="preserve">1.07234561443329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05149698257446</t>
   </si>
   <si>
     <t xml:space="preserve">1.12310755252838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10135233402252</t>
+    <t xml:space="preserve">1.1013525724411</t>
   </si>
   <si>
     <t xml:space="preserve">1.08322322368622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08775556087494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11404263973236</t>
+    <t xml:space="preserve">1.08775568008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11404287815094</t>
   </si>
   <si>
     <t xml:space="preserve">1.15120792388916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21466028690338</t>
+    <t xml:space="preserve">1.21466040611267</t>
   </si>
   <si>
     <t xml:space="preserve">1.18474698066711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14576923847198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12220132350922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06237471103668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03336775302887</t>
+    <t xml:space="preserve">1.1457691192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12220108509064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06237459182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03336787223816</t>
   </si>
   <si>
     <t xml:space="preserve">0.934563279151917</t>
@@ -440,10 +440,10 @@
     <t xml:space="preserve">0.945440769195557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977167010307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956318378448486</t>
+    <t xml:space="preserve">0.977167069911957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956318199634552</t>
   </si>
   <si>
     <t xml:space="preserve">0.933656752109528</t>
@@ -452,76 +452,76 @@
     <t xml:space="preserve">1.01523840427399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04877746105194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0360871553421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02430307865143</t>
+    <t xml:space="preserve">1.04877769947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03608703613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02430319786072</t>
   </si>
   <si>
     <t xml:space="preserve">0.990764021873474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05059063434601</t>
+    <t xml:space="preserve">1.05059051513672</t>
   </si>
   <si>
     <t xml:space="preserve">1.11494946479797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12854635715485</t>
+    <t xml:space="preserve">1.12854623794556</t>
   </si>
   <si>
     <t xml:space="preserve">1.07506501674652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06418752670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02067720890045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997109055519104</t>
+    <t xml:space="preserve">1.06418740749359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02067732810974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997109353542328</t>
   </si>
   <si>
     <t xml:space="preserve">1.00617384910583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988044500350952</t>
+    <t xml:space="preserve">0.988044619560242</t>
   </si>
   <si>
     <t xml:space="preserve">1.03880655765533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05965518951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04243206977844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06328105926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05693566799164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10407197475433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10497832298279</t>
+    <t xml:space="preserve">1.05965507030487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04243242740631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06328094005585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05693554878235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10407173633575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1049782037735</t>
   </si>
   <si>
     <t xml:space="preserve">1.07597148418427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12492048740387</t>
+    <t xml:space="preserve">1.12492060661316</t>
   </si>
   <si>
     <t xml:space="preserve">1.1031653881073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2110344171524</t>
+    <t xml:space="preserve">1.21103429794312</t>
   </si>
   <si>
     <t xml:space="preserve">1.19562470912933</t>
@@ -536,19 +536,19 @@
     <t xml:space="preserve">1.15392732620239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20559573173523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20196974277496</t>
+    <t xml:space="preserve">1.20559561252594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20196998119354</t>
   </si>
   <si>
     <t xml:space="preserve">1.23188304901123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25363838672638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25817060470581</t>
+    <t xml:space="preserve">1.25363826751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25817048549652</t>
   </si>
   <si>
     <t xml:space="preserve">1.26089000701904</t>
@@ -557,46 +557,46 @@
     <t xml:space="preserve">1.25545120239258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28717732429504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30893242359161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30530667304993</t>
+    <t xml:space="preserve">1.28717720508575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3089325428009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30530679225922</t>
   </si>
   <si>
     <t xml:space="preserve">1.41226923465729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37963664531708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40320456027985</t>
+    <t xml:space="preserve">1.37963652610779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40320467948914</t>
   </si>
   <si>
     <t xml:space="preserve">1.35244274139404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35697484016418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35969424247742</t>
+    <t xml:space="preserve">1.35697507858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.359694480896</t>
   </si>
   <si>
     <t xml:space="preserve">1.34065854549408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32343602180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35062968730927</t>
+    <t xml:space="preserve">1.32343590259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35062980651855</t>
   </si>
   <si>
     <t xml:space="preserve">1.32887470722198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26995480060577</t>
+    <t xml:space="preserve">1.26995456218719</t>
   </si>
   <si>
     <t xml:space="preserve">1.1947181224823</t>
@@ -608,13 +608,13 @@
     <t xml:space="preserve">1.24548006057739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25001227855682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26814162731171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23278939723969</t>
+    <t xml:space="preserve">1.25001239776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.268141746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23278951644897</t>
   </si>
   <si>
     <t xml:space="preserve">1.24185419082642</t>
@@ -623,22 +623,22 @@
     <t xml:space="preserve">1.28173863887787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26451575756073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28264498710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25091874599457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26904821395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33159387111664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29624199867249</t>
+    <t xml:space="preserve">1.26451563835144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28264510631561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25091886520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26904809474945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33159410953522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2962418794632</t>
   </si>
   <si>
     <t xml:space="preserve">1.28536438941956</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">1.31437122821808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30983877182007</t>
+    <t xml:space="preserve">1.30983889102936</t>
   </si>
   <si>
     <t xml:space="preserve">1.31799709796906</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">1.29896140098572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37782382965088</t>
+    <t xml:space="preserve">1.3778235912323</t>
   </si>
   <si>
     <t xml:space="preserve">1.33521997928619</t>
@@ -665,16 +665,16 @@
     <t xml:space="preserve">1.26179623603821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31074547767639</t>
+    <t xml:space="preserve">1.3107453584671</t>
   </si>
   <si>
     <t xml:space="preserve">1.30711960792542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34247136116028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.294429063797</t>
+    <t xml:space="preserve">1.34247159957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29442894458771</t>
   </si>
   <si>
     <t xml:space="preserve">1.32434225082397</t>
@@ -683,58 +683,58 @@
     <t xml:space="preserve">1.33884561061859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31165182590485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27992558479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30621314048767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31618404388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30349373817444</t>
+    <t xml:space="preserve">1.31165170669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2799254655838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30621302127838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31618416309357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30349361896515</t>
   </si>
   <si>
     <t xml:space="preserve">1.27720642089844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26632857322693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28355133533478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25907707214355</t>
+    <t xml:space="preserve">1.26632845401764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28355157375336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25907695293427</t>
   </si>
   <si>
     <t xml:space="preserve">1.24910593032837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27539336681366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25273180007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34700393676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34972310066223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29261600971222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32978117465973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23369598388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22372484207153</t>
+    <t xml:space="preserve">1.27539324760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25273168087006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34700381755829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34972333908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29261612892151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32978105545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23369586467743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22372508049011</t>
   </si>
   <si>
     <t xml:space="preserve">1.229163646698</t>
@@ -752,61 +752,61 @@
     <t xml:space="preserve">1.22100555896759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21828591823578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22463142871857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21012806892395</t>
+    <t xml:space="preserve">1.21828603744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22463130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21012794971466</t>
   </si>
   <si>
     <t xml:space="preserve">1.18656015396118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17477595806122</t>
+    <t xml:space="preserve">1.17477607727051</t>
   </si>
   <si>
     <t xml:space="preserve">1.17840170860291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1521143913269</t>
+    <t xml:space="preserve">1.15211451053619</t>
   </si>
   <si>
     <t xml:space="preserve">1.15845954418182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08594262599945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10588479042053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07959747314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1067910194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13217222690582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16933715343475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22644424438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23822820186615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24457371234894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25182545185089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24004113674164</t>
+    <t xml:space="preserve">1.08594250679016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10588490962982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07959735393524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10679113864899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13217198848724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16933703422546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22644436359406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23822832107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24457359313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25182521343231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24004125595093</t>
   </si>
   <si>
     <t xml:space="preserve">1.20378279685974</t>
@@ -815,43 +815,43 @@
     <t xml:space="preserve">1.20650207996368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24094772338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23097658157349</t>
+    <t xml:space="preserve">1.24094784259796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23097670078278</t>
   </si>
   <si>
     <t xml:space="preserve">1.21194088459015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23460233211517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24638676643372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27629971504211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27086102962494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29805481433868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22553777694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15574014186859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11857509613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16027247905731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16661751270294</t>
+    <t xml:space="preserve">1.23460257053375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24638640880585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27629995346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27086091041565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29805505275726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22553789615631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1557400226593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11857521533966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1602725982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16661787033081</t>
   </si>
   <si>
     <t xml:space="preserve">1.16480481624603</t>
@@ -866,31 +866,31 @@
     <t xml:space="preserve">1.11676228046417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09319424629211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09772658348083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17658889293671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17930817604065</t>
+    <t xml:space="preserve">1.0931943655014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09772670269012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17658877372742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17930829524994</t>
   </si>
   <si>
     <t xml:space="preserve">1.21375381946564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21556675434113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28627097606659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28989660739899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28445792198181</t>
+    <t xml:space="preserve">1.21556663513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2862708568573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28989684581757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2844580411911</t>
   </si>
   <si>
     <t xml:space="preserve">1.38960766792297</t>
@@ -902,19 +902,19 @@
     <t xml:space="preserve">1.41408205032349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38235592842102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37057209014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32796812057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36513328552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3551619052887</t>
+    <t xml:space="preserve">1.38235604763031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37057185173035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32796823978424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36513316631317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35516202449799</t>
   </si>
   <si>
     <t xml:space="preserve">1.38416886329651</t>
@@ -926,58 +926,58 @@
     <t xml:space="preserve">1.38054299354553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38870120048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36694610118866</t>
+    <t xml:space="preserve">1.38870108127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36694598197937</t>
   </si>
   <si>
     <t xml:space="preserve">1.40773677825928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39957880973816</t>
+    <t xml:space="preserve">1.39957857131958</t>
   </si>
   <si>
     <t xml:space="preserve">1.39685940742493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38326251506805</t>
+    <t xml:space="preserve">1.38326263427734</t>
   </si>
   <si>
     <t xml:space="preserve">1.38688826560974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50926077365875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57724547386169</t>
+    <t xml:space="preserve">1.50926065444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5772453546524</t>
   </si>
   <si>
     <t xml:space="preserve">1.57271313667297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54551935195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55005168914795</t>
+    <t xml:space="preserve">1.54551923274994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55005156993866</t>
   </si>
   <si>
     <t xml:space="preserve">1.51379299163818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48659908771515</t>
+    <t xml:space="preserve">1.48659920692444</t>
   </si>
   <si>
     <t xml:space="preserve">1.44580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48206675052643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43221139907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54098689556122</t>
+    <t xml:space="preserve">1.48206686973572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43221163749695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54098701477051</t>
   </si>
   <si>
     <t xml:space="preserve">1.52285766601562</t>
@@ -995,91 +995,94 @@
     <t xml:space="preserve">1.34609746932983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29170954227448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31890368461609</t>
+    <t xml:space="preserve">1.29170966148376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31890344619751</t>
   </si>
   <si>
     <t xml:space="preserve">1.33703279495239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27358043193817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39595293998718</t>
+    <t xml:space="preserve">1.27358031272888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39595305919647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30077409744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33341014385223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3147611618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30543661117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31942343711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24482703208923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24948942661285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23084020614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21219098567963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2541515827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23550260066986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22617781162262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19354212284088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19820427894592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24016463756561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27280068397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29611194133759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31009876728058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32874798774719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28212511539459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26813840866089</t>
   </si>
   <si>
     <t xml:space="preserve">1.30077421665192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33341026306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31476104259491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30543661117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31942331790924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24482715129852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24948930740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23084032535553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21219098567963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2541515827179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23550248146057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2261780500412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19354212284088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19820427894592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24016487598419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27280068397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29611217975616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31009900569916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3287478685379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28212547302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26813840866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21685338020325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18887972831726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1655684709549</t>
+    <t xml:space="preserve">1.21685326099396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18887960910797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16556835174561</t>
   </si>
   <si>
     <t xml:space="preserve">1.20286643505096</t>
@@ -1088,7 +1091,7 @@
     <t xml:space="preserve">1.17489290237427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17955529689789</t>
+    <t xml:space="preserve">1.1795551776886</t>
   </si>
   <si>
     <t xml:space="preserve">1.20752882957458</t>
@@ -1100,25 +1103,25 @@
     <t xml:space="preserve">1.34739708900452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17023062705994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14691925048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13293242454529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25881385803223</t>
+    <t xml:space="preserve">1.17023050785065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14691936969757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13293254375458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25881397724152</t>
   </si>
   <si>
     <t xml:space="preserve">1.27746295928955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22151553630829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15624392032623</t>
+    <t xml:space="preserve">1.22151565551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15624380111694</t>
   </si>
   <si>
     <t xml:space="preserve">1.18421745300293</t>
@@ -1130,22 +1133,22 @@
     <t xml:space="preserve">1.16090607643127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15158152580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13759481906891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3613840341568</t>
+    <t xml:space="preserve">1.15158140659332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1375949382782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36138391494751</t>
   </si>
   <si>
     <t xml:space="preserve">1.29144978523254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34273481369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33807241916656</t>
+    <t xml:space="preserve">1.34273493289948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33807229995728</t>
   </si>
   <si>
     <t xml:space="preserve">1.11428344249725</t>
@@ -1163,37 +1166,37 @@
     <t xml:space="preserve">1.29230725765228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37278068065643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34437823295593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32544314861298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30177462100983</t>
+    <t xml:space="preserve">1.37278056144714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34437811374664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32544326782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30177450180054</t>
   </si>
   <si>
     <t xml:space="preserve">1.55266213417053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4106502532959</t>
+    <t xml:space="preserve">1.41065037250519</t>
   </si>
   <si>
     <t xml:space="preserve">1.31124210357666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31597590446472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28757357597351</t>
+    <t xml:space="preserve">1.31597566604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28757345676422</t>
   </si>
   <si>
     <t xml:space="preserve">1.30650842189789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33964431285858</t>
+    <t xml:space="preserve">1.33964443206787</t>
   </si>
   <si>
     <t xml:space="preserve">1.42011785507202</t>
@@ -1205,37 +1208,37 @@
     <t xml:space="preserve">1.35384559631348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39644908905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32070958614349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33491086959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28283965587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27337241172791</t>
+    <t xml:space="preserve">1.39644920825958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3207094669342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3349107503891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28283977508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27337229251862</t>
   </si>
   <si>
     <t xml:space="preserve">1.26390480995178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25917112827301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29704082012177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24497008323669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2307687997818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22130131721497</t>
+    <t xml:space="preserve">1.25917100906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29704093933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24496984481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23076868057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22130119800568</t>
   </si>
   <si>
     <t xml:space="preserve">1.2165675163269</t>
@@ -1244,13 +1247,13 @@
     <t xml:space="preserve">1.22603499889374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24023628234863</t>
+    <t xml:space="preserve">1.24023616313934</t>
   </si>
   <si>
     <t xml:space="preserve">1.21183395385742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26863849163055</t>
+    <t xml:space="preserve">1.26863873004913</t>
   </si>
   <si>
     <t xml:space="preserve">1.20710003376007</t>
@@ -1259,7 +1262,7 @@
     <t xml:space="preserve">1.24970364570618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25443756580353</t>
+    <t xml:space="preserve">1.25443744659424</t>
   </si>
   <si>
     <t xml:space="preserve">1.23550236225128</t>
@@ -1268,25 +1271,25 @@
     <t xml:space="preserve">1.16923022270203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18343162536621</t>
+    <t xml:space="preserve">1.18343150615692</t>
   </si>
   <si>
     <t xml:space="preserve">1.2023663520813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1408280134201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12189316749573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11715924739838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10295808315277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06982207298279</t>
+    <t xml:space="preserve">1.14082813262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12189304828644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11715936660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10295820236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06982219219208</t>
   </si>
   <si>
     <t xml:space="preserve">1.01775109767914</t>
@@ -1295,19 +1298,19 @@
     <t xml:space="preserve">0.989348649978638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979881286621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965680062770844</t>
+    <t xml:space="preserve">0.979881227016449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965680181980133</t>
   </si>
   <si>
     <t xml:space="preserve">0.914555907249451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937277734279633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92023628950119</t>
+    <t xml:space="preserve">0.937277793884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.920236349105835</t>
   </si>
   <si>
     <t xml:space="preserve">0.880473017692566</t>
@@ -1316,22 +1319,22 @@
     <t xml:space="preserve">0.927810311317444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946745276451111</t>
+    <t xml:space="preserve">0.946745157241821</t>
   </si>
   <si>
     <t xml:space="preserve">0.956212639808655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0224848985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07928955554962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10769200325012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13609433174133</t>
+    <t xml:space="preserve">1.02248501777649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07928967475891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10769188404083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13609445095062</t>
   </si>
   <si>
     <t xml:space="preserve">1.05562090873718</t>
@@ -1340,13 +1343,13 @@
     <t xml:space="preserve">1.09349071979523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06035447120667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06508851051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07455563545227</t>
+    <t xml:space="preserve">1.06035459041595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06508839130402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07455575466156</t>
   </si>
   <si>
     <t xml:space="preserve">1.04615342617035</t>
@@ -1355,19 +1358,19 @@
     <t xml:space="preserve">1.03668606281281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04141974449158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11242544651031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12662672996521</t>
+    <t xml:space="preserve">1.04141986370087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1124255657196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1266268491745</t>
   </si>
   <si>
     <t xml:space="preserve">1.08875703811646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.098224401474</t>
+    <t xml:space="preserve">1.09822452068329</t>
   </si>
   <si>
     <t xml:space="preserve">1.05088722705841</t>
@@ -1382,19 +1385,19 @@
     <t xml:space="preserve">1.17869770526886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15976285934448</t>
+    <t xml:space="preserve">1.15976297855377</t>
   </si>
   <si>
     <t xml:space="preserve">1.15029549598694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16449654102325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15502917766571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14556157588959</t>
+    <t xml:space="preserve">1.16449666023254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.155029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14556181430817</t>
   </si>
   <si>
     <t xml:space="preserve">1.17396402359009</t>
@@ -1403,7 +1406,7 @@
     <t xml:space="preserve">1.13136053085327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08402323722839</t>
+    <t xml:space="preserve">1.08402335643768</t>
   </si>
   <si>
     <t xml:space="preserve">1.00828385353088</t>
@@ -1412,16 +1415,16 @@
     <t xml:space="preserve">0.984614968299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994082510471344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01301729679108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18816518783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33017706871033</t>
+    <t xml:space="preserve">0.994082391262054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01301741600037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1881650686264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33017694950104</t>
   </si>
   <si>
     <t xml:space="preserve">1.40118300914764</t>
@@ -1433,16 +1436,13 @@
     <t xml:space="preserve">1.33027982711792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31597578525543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32551193237305</t>
+    <t xml:space="preserve">1.32551181316376</t>
   </si>
   <si>
     <t xml:space="preserve">1.33981597423553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33504784107208</t>
+    <t xml:space="preserve">1.33504796028137</t>
   </si>
   <si>
     <t xml:space="preserve">1.36365604400635</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">1.32074379920959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35412001609802</t>
+    <t xml:space="preserve">1.35411989688873</t>
   </si>
   <si>
     <t xml:space="preserve">1.3445839881897</t>
@@ -1460,46 +1460,46 @@
     <t xml:space="preserve">1.40180027484894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36842393875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34935200214386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35888803005219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30167186260223</t>
+    <t xml:space="preserve">1.36842405796051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34935212135315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3588879108429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30167174339294</t>
   </si>
   <si>
     <t xml:space="preserve">1.3922643661499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38272821903229</t>
+    <t xml:space="preserve">1.38272833824158</t>
   </si>
   <si>
     <t xml:space="preserve">1.41133642196655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38749623298645</t>
+    <t xml:space="preserve">1.38749635219574</t>
   </si>
   <si>
     <t xml:space="preserve">1.37319219112396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4304084777832</t>
+    <t xml:space="preserve">1.43040859699249</t>
   </si>
   <si>
     <t xml:space="preserve">1.47808885574341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4447124004364</t>
+    <t xml:space="preserve">1.44471251964569</t>
   </si>
   <si>
     <t xml:space="preserve">1.4065682888031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42087233066559</t>
+    <t xml:space="preserve">1.42087244987488</t>
   </si>
   <si>
     <t xml:space="preserve">1.43517661094666</t>
@@ -1508,7 +1508,7 @@
     <t xml:space="preserve">1.45901668071747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43994462490082</t>
+    <t xml:space="preserve">1.43994450569153</t>
   </si>
   <si>
     <t xml:space="preserve">1.41610443592072</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">1.54484117031097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54007315635681</t>
+    <t xml:space="preserve">1.54007303714752</t>
   </si>
   <si>
     <t xml:space="preserve">1.58298528194427</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">1.57344925403595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68788206577301</t>
+    <t xml:space="preserve">1.68788194656372</t>
   </si>
   <si>
     <t xml:space="preserve">1.65450572967529</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">1.70695412158966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7641704082489</t>
+    <t xml:space="preserve">1.76417052745819</t>
   </si>
   <si>
     <t xml:space="preserve">1.74509835243225</t>
@@ -1574,13 +1574,13 @@
     <t xml:space="preserve">1.64973783493042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71172201633453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64496982097626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61636161804199</t>
+    <t xml:space="preserve">1.71172213554382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64496970176697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6163614988327</t>
   </si>
   <si>
     <t xml:space="preserve">1.62112963199615</t>
@@ -1589,16 +1589,16 @@
     <t xml:space="preserve">1.63066565990448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63543367385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77847468852997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75940239429474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68311393260956</t>
+    <t xml:space="preserve">1.63543379306793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77847456932068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75940251350403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68311405181885</t>
   </si>
   <si>
     <t xml:space="preserve">1.71649014949799</t>
@@ -1607,16 +1607,16 @@
     <t xml:space="preserve">1.77370655536652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81185066699982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8261547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79754662513733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78801047801971</t>
+    <t xml:space="preserve">1.81185078620911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82615482807159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79754674434662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.788010597229</t>
   </si>
   <si>
     <t xml:space="preserve">1.81661880016327</t>
@@ -1628,28 +1628,28 @@
     <t xml:space="preserve">1.80708277225494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76893854141235</t>
+    <t xml:space="preserve">1.76893866062164</t>
   </si>
   <si>
     <t xml:space="preserve">1.73556232452393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73079442977905</t>
+    <t xml:space="preserve">1.73079431056976</t>
   </si>
   <si>
     <t xml:space="preserve">1.74033033847809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72125816345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78324246406555</t>
+    <t xml:space="preserve">1.72125828266144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78324258327484</t>
   </si>
   <si>
     <t xml:space="preserve">1.74986636638641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6783459186554</t>
+    <t xml:space="preserve">1.67834603786469</t>
   </si>
   <si>
     <t xml:space="preserve">1.66404187679291</t>
@@ -1667,22 +1667,22 @@
     <t xml:space="preserve">1.79277861118317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56868135929108</t>
+    <t xml:space="preserve">1.5686811208725</t>
   </si>
   <si>
     <t xml:space="preserve">1.65927374362946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59252154827118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52576899528503</t>
+    <t xml:space="preserve">1.59252142906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52576887607574</t>
   </si>
   <si>
     <t xml:space="preserve">1.59728944301605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7021861076355</t>
+    <t xml:space="preserve">1.70218598842621</t>
   </si>
   <si>
     <t xml:space="preserve">1.85953104496002</t>
@@ -1703,10 +1703,10 @@
     <t xml:space="preserve">1.86429905891418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90721142292023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94535553455353</t>
+    <t xml:space="preserve">1.90721130371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94535541534424</t>
   </si>
   <si>
     <t xml:space="preserve">1.99303579330444</t>
@@ -1715,19 +1715,19 @@
     <t xml:space="preserve">2.0597882270813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00257205963135</t>
+    <t xml:space="preserve">2.00257182121277</t>
   </si>
   <si>
     <t xml:space="preserve">2.07886052131653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12654066085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10746836662292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08839631080627</t>
+    <t xml:space="preserve">2.12654042243958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1074686050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08839654922485</t>
   </si>
   <si>
     <t xml:space="preserve">2.09793257713318</t>
@@ -1745,19 +1745,19 @@
     <t xml:space="preserve">2.22190117835999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25050926208496</t>
+    <t xml:space="preserve">2.25050950050354</t>
   </si>
   <si>
     <t xml:space="preserve">2.02164387702942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01210784912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97396373748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98349952697754</t>
+    <t xml:space="preserve">2.01210808753967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97396349906921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98349976539612</t>
   </si>
   <si>
     <t xml:space="preserve">2.03118014335632</t>
@@ -1769,22 +1769,22 @@
     <t xml:space="preserve">2.09847211837769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08884620666504</t>
+    <t xml:space="preserve">2.08884596824646</t>
   </si>
   <si>
     <t xml:space="preserve">2.10809803009033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00221180915833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95408177375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03108978271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02146410942078</t>
+    <t xml:space="preserve">2.0022120475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95408189296722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03109002113342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0214638710022</t>
   </si>
   <si>
     <t xml:space="preserve">2.05996799468994</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">1.94445586204529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97333383560181</t>
+    <t xml:space="preserve">1.97333407402039</t>
   </si>
   <si>
     <t xml:space="preserve">1.93482995033264</t>
@@ -1805,16 +1805,16 @@
     <t xml:space="preserve">1.83856964111328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82894361019135</t>
+    <t xml:space="preserve">1.82894372940063</t>
   </si>
   <si>
     <t xml:space="preserve">1.86744773387909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88669979572296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707364559174</t>
+    <t xml:space="preserve">1.88669967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707376480103</t>
   </si>
   <si>
     <t xml:space="preserve">1.89632570743561</t>
@@ -1829,10 +1829,10 @@
     <t xml:space="preserve">2.05034208297729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11772441864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1562283039093</t>
+    <t xml:space="preserve">2.11772418022156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15622854232788</t>
   </si>
   <si>
     <t xml:space="preserve">2.20435833930969</t>
@@ -1856,13 +1856,13 @@
     <t xml:space="preserve">2.27174043655396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30061864852905</t>
+    <t xml:space="preserve">2.30061841011047</t>
   </si>
   <si>
     <t xml:space="preserve">2.2813663482666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18510627746582</t>
+    <t xml:space="preserve">2.1851065158844</t>
   </si>
   <si>
     <t xml:space="preserve">2.19473242759705</t>
@@ -1877,10 +1877,10 @@
     <t xml:space="preserve">2.01183795928955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8722608089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96370792388916</t>
+    <t xml:space="preserve">1.87226068973541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96370780467987</t>
   </si>
   <si>
     <t xml:space="preserve">2.06959414482117</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">2.29099249839783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36800074577332</t>
+    <t xml:space="preserve">2.36800098419189</t>
   </si>
   <si>
     <t xml:space="preserve">2.38725280761719</t>
@@ -1931,10 +1931,10 @@
     <t xml:space="preserve">2.21398448944092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31987071037292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4450089931488</t>
+    <t xml:space="preserve">2.31987047195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44500875473022</t>
   </si>
   <si>
     <t xml:space="preserve">2.45463490486145</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">2.52201700210571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50276494026184</t>
+    <t xml:space="preserve">2.50276470184326</t>
   </si>
   <si>
     <t xml:space="preserve">2.59902501106262</t>
@@ -1964,16 +1964,16 @@
     <t xml:space="preserve">2.51239085197449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47388696670532</t>
+    <t xml:space="preserve">2.47388672828674</t>
   </si>
   <si>
     <t xml:space="preserve">2.48351287841797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53164291381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63752913475037</t>
+    <t xml:space="preserve">2.53164315223694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63752937316895</t>
   </si>
   <si>
     <t xml:space="preserve">2.69528532028198</t>
@@ -1985,10 +1985,10 @@
     <t xml:space="preserve">2.71453738212585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67603349685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60865116119385</t>
+    <t xml:space="preserve">2.67603325843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60865139961243</t>
   </si>
   <si>
     <t xml:space="preserve">2.66640734672546</t>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">2.58939909934998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56052088737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6279034614563</t>
+    <t xml:space="preserve">2.56052112579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62790322303772</t>
   </si>
   <si>
     <t xml:space="preserve">2.55089521408081</t>
@@ -20159,7 +20159,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G667" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20445,7 +20445,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G678" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20471,7 +20471,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G679" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20497,7 +20497,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G680" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20523,7 +20523,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G681" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20549,7 +20549,7 @@
         <v>1.25</v>
       </c>
       <c r="G682" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -20575,7 +20575,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G683" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20601,7 +20601,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G684" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20627,7 +20627,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G685" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20653,7 +20653,7 @@
         <v>1.25</v>
       </c>
       <c r="G686" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20783,7 +20783,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G691" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -20835,7 +20835,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G693" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20861,7 +20861,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G694" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -20991,7 +20991,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G699" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21017,7 +21017,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G700" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21043,7 +21043,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G701" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21121,7 +21121,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G704" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21199,7 +21199,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G707" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21225,7 +21225,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G708" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21251,7 +21251,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G709" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21277,7 +21277,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G710" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21303,7 +21303,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G711" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21329,7 +21329,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G712" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21381,7 +21381,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G714" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21407,7 +21407,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G715" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21433,7 +21433,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G716" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21459,7 +21459,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G717" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21563,7 +21563,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G721" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21641,7 +21641,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G724" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21693,7 +21693,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G726" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21719,7 +21719,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G727" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21823,7 +21823,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G731" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21849,7 +21849,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G732" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21901,7 +21901,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G734" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -21927,7 +21927,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G735" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -21953,7 +21953,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G736" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -21979,7 +21979,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G737" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22187,7 +22187,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G745" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22213,7 +22213,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G746" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22291,7 +22291,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G749" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22317,7 +22317,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G750" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22369,7 +22369,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G752" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22395,7 +22395,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G753" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22421,7 +22421,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G754" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22447,7 +22447,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G755" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22473,7 +22473,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G756" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22499,7 +22499,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G757" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22525,7 +22525,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G758" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22551,7 +22551,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G759" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22577,7 +22577,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G760" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22603,7 +22603,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G761" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22629,7 +22629,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G762" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22655,7 +22655,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G763" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22681,7 +22681,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G764" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22707,7 +22707,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G765" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22733,7 +22733,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G766" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -22837,7 +22837,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G770" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22863,7 +22863,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G771" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22889,7 +22889,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G772" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22915,7 +22915,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G773" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22941,7 +22941,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G774" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23123,7 +23123,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G781" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23149,7 +23149,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G782" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23227,7 +23227,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G785" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23253,7 +23253,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G786" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23279,7 +23279,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G787" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23305,7 +23305,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G788" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23331,7 +23331,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G789" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23357,7 +23357,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G790" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23383,7 +23383,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G791" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23409,7 +23409,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G792" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23435,7 +23435,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G793" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23461,7 +23461,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G794" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23487,7 +23487,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G795" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23513,7 +23513,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G796" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23539,7 +23539,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G797" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23565,7 +23565,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G798" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23591,7 +23591,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G799" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23617,7 +23617,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G800" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23669,7 +23669,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G802" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23695,7 +23695,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G803" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23721,7 +23721,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G804" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23799,7 +23799,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G807" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23877,7 +23877,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G810" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23929,7 +23929,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G812" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24007,7 +24007,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G815" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24085,7 +24085,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G818" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24111,7 +24111,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G819" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24163,7 +24163,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G821" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24189,7 +24189,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G822" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24215,7 +24215,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G823" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24241,7 +24241,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G824" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24267,7 +24267,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G825" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24293,7 +24293,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G826" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24319,7 +24319,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G827" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24345,7 +24345,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G828" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24371,7 +24371,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G829" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24397,7 +24397,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G830" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24423,7 +24423,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G831" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24475,7 +24475,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G833" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24501,7 +24501,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G834" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24527,7 +24527,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G835" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24579,7 +24579,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G837" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24605,7 +24605,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G838" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24787,7 +24787,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G845" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24839,7 +24839,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G847" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24865,7 +24865,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G848" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24917,7 +24917,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G850" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24943,7 +24943,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G851" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25047,7 +25047,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G855" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25073,7 +25073,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G856" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25099,7 +25099,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G857" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25125,7 +25125,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G858" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25151,7 +25151,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G859" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25177,7 +25177,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G860" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25229,7 +25229,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G862" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25255,7 +25255,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G863" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25281,7 +25281,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G864" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25307,7 +25307,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G865" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25333,7 +25333,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G866" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25359,7 +25359,7 @@
         <v>1.25</v>
       </c>
       <c r="G867" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25385,7 +25385,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G868" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25411,7 +25411,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G869" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25437,7 +25437,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G870" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25463,7 +25463,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G871" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25489,7 +25489,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G872" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25515,7 +25515,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G873" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25541,7 +25541,7 @@
         <v>1.25</v>
       </c>
       <c r="G874" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25567,7 +25567,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G875" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25593,7 +25593,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G876" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -25619,7 +25619,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G877" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -25645,7 +25645,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G878" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25671,7 +25671,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G879" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -25801,7 +25801,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G884" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25827,7 +25827,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G885" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25853,7 +25853,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G886" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -25879,7 +25879,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G887" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -25905,7 +25905,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G888" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -25931,7 +25931,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G889" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -25957,7 +25957,7 @@
         <v>1.375</v>
       </c>
       <c r="G890" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -25983,7 +25983,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G891" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26009,7 +26009,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G892" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26035,7 +26035,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G893" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26061,7 +26061,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G894" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26087,7 +26087,7 @@
         <v>1.375</v>
       </c>
       <c r="G895" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26113,7 +26113,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G896" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26139,7 +26139,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G897" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26165,7 +26165,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G898" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26191,7 +26191,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G899" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26217,7 +26217,7 @@
         <v>1.5</v>
       </c>
       <c r="G900" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26243,7 +26243,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G901" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26269,7 +26269,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G902" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26295,7 +26295,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G903" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26321,7 +26321,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G904" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26347,7 +26347,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G905" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26373,7 +26373,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G906" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26399,7 +26399,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G907" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26425,7 +26425,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G908" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26451,7 +26451,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G909" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26477,7 +26477,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G910" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26503,7 +26503,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G911" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26529,7 +26529,7 @@
         <v>1.375</v>
       </c>
       <c r="G912" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26555,7 +26555,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G913" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -26581,7 +26581,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G914" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -26607,7 +26607,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G915" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -26633,7 +26633,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G916" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -26659,7 +26659,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G917" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -26685,7 +26685,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G918" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26711,7 +26711,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G919" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -26737,7 +26737,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G920" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -26763,7 +26763,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G921" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26789,7 +26789,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G922" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26815,7 +26815,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G923" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26841,7 +26841,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G924" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26867,7 +26867,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G925" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -26893,7 +26893,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G926" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26919,7 +26919,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G927" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26945,7 +26945,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G928" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26971,7 +26971,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G929" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26997,7 +26997,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G930" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27023,7 +27023,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G931" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27049,7 +27049,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G932" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27075,7 +27075,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G933" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -27101,7 +27101,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G934" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -27127,7 +27127,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G935" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -27153,7 +27153,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G936" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27179,7 +27179,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G937" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27205,7 +27205,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G938" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -27231,7 +27231,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G939" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27257,7 +27257,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G940" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27283,7 +27283,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G941" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27309,7 +27309,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G942" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27335,7 +27335,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G943" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27361,7 +27361,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G944" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27387,7 +27387,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G945" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27413,7 +27413,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G946" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27439,7 +27439,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G947" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27465,7 +27465,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G948" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27491,7 +27491,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G949" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27517,7 +27517,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G950" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27543,7 +27543,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G951" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -27569,7 +27569,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G952" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -27595,7 +27595,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G953" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27621,7 +27621,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G954" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -27647,7 +27647,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G955" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -27673,7 +27673,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G956" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27699,7 +27699,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G957" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27725,7 +27725,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G958" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27751,7 +27751,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G959" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27777,7 +27777,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G960" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27803,7 +27803,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G961" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27829,7 +27829,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G962" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27855,7 +27855,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G963" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27881,7 +27881,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G964" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27907,7 +27907,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G965" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27933,7 +27933,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G966" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27959,7 +27959,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G967" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27985,7 +27985,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G968" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28011,7 +28011,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G969" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -28037,7 +28037,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G970" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -28063,7 +28063,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G971" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -28089,7 +28089,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G972" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28115,7 +28115,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G973" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28141,7 +28141,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G974" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28167,7 +28167,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G975" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28193,7 +28193,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G976" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -28219,7 +28219,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G977" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28245,7 +28245,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G978" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28271,7 +28271,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G979" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28297,7 +28297,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G980" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28323,7 +28323,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G981" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28349,7 +28349,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G982" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28375,7 +28375,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G983" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28401,7 +28401,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G984" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28427,7 +28427,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G985" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28453,7 +28453,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G986" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28479,7 +28479,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G987" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28505,7 +28505,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G988" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28531,7 +28531,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G989" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28557,7 +28557,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G990" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -28583,7 +28583,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G991" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -28609,7 +28609,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G992" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28635,7 +28635,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G993" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28661,7 +28661,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G994" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -28687,7 +28687,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G995" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -28713,7 +28713,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G996" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -28739,7 +28739,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G997" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -28765,7 +28765,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G998" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28791,7 +28791,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G999" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28817,7 +28817,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1000" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28843,7 +28843,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1001" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28869,7 +28869,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1002" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28895,7 +28895,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1003" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28921,7 +28921,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1004" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28947,7 +28947,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1005" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28973,7 +28973,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1006" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28999,7 +28999,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1007" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29025,7 +29025,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1008" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29051,7 +29051,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1009" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29077,7 +29077,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1010" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29103,7 +29103,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1011" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29129,7 +29129,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1012" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29155,7 +29155,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1013" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29181,7 +29181,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1014" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29207,7 +29207,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1015" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -29233,7 +29233,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1016" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29259,7 +29259,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1017" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29285,7 +29285,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1018" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29311,7 +29311,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1019" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29337,7 +29337,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1020" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29363,7 +29363,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1021" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29389,7 +29389,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1022" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29415,7 +29415,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1023" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29441,7 +29441,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1024" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29467,7 +29467,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1025" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29493,7 +29493,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1026" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29519,7 +29519,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1027" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29545,7 +29545,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1028" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29571,7 +29571,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1029" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29597,7 +29597,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1030" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -29623,7 +29623,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1031" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -29649,7 +29649,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1032" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29675,7 +29675,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1033" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29701,7 +29701,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1034" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29727,7 +29727,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1035" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29753,7 +29753,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1036" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29779,7 +29779,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1037" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29805,7 +29805,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1038" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29831,7 +29831,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1039" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29857,7 +29857,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1040" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29883,7 +29883,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1041" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29909,7 +29909,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1042" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29935,7 +29935,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1043" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29961,7 +29961,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1044" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29987,7 +29987,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1045" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -30013,7 +30013,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1046" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30039,7 +30039,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1047" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -30065,7 +30065,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1048" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30091,7 +30091,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1049" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30117,7 +30117,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1050" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -30143,7 +30143,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1051" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30169,7 +30169,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1052" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30195,7 +30195,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1053" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -30221,7 +30221,7 @@
         <v>1.25</v>
       </c>
       <c r="G1054" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -30247,7 +30247,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1055" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -30273,7 +30273,7 @@
         <v>1.25</v>
       </c>
       <c r="G1056" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30299,7 +30299,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1057" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30325,7 +30325,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G1058" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30351,7 +30351,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1059" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30377,7 +30377,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1060" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30403,7 +30403,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1061" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30429,7 +30429,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1062" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30455,7 +30455,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1063" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30481,7 +30481,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1064" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -30507,7 +30507,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1065" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30533,7 +30533,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G1066" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30559,7 +30559,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1067" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -30585,7 +30585,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1068" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -30611,7 +30611,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G1069" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -30637,7 +30637,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1070" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -30663,7 +30663,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1071" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30689,7 +30689,7 @@
         <v>1</v>
       </c>
       <c r="G1072" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30715,7 +30715,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1073" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30741,7 +30741,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1074" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -30767,7 +30767,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1075" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30793,7 +30793,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G1076" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30819,7 +30819,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1077" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30845,7 +30845,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1078" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30871,7 +30871,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1079" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -30897,7 +30897,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1080" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30923,7 +30923,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1081" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30949,7 +30949,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1082" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30975,7 +30975,7 @@
         <v>1.125</v>
       </c>
       <c r="G1083" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -31001,7 +31001,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1084" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -31027,7 +31027,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1085" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -31053,7 +31053,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1086" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31079,7 +31079,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1087" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -31105,7 +31105,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1088" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31131,7 +31131,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1089" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31157,7 +31157,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1090" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31183,7 +31183,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1091" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31209,7 +31209,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1092" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31235,7 +31235,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1093" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -31261,7 +31261,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1094" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31287,7 +31287,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1095" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31313,7 +31313,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1096" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31339,7 +31339,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1097" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31365,7 +31365,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G1098" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31391,7 +31391,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1099" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31417,7 +31417,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1100" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31443,7 +31443,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1101" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31469,7 +31469,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1102" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31495,7 +31495,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1103" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31521,7 +31521,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1104" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31547,7 +31547,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1105" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -31573,7 +31573,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1106" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -31599,7 +31599,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1107" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31625,7 +31625,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1108" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -31651,7 +31651,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1109" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -31677,7 +31677,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1110" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -31703,7 +31703,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1111" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31729,7 +31729,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1112" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31755,7 +31755,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1113" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31781,7 +31781,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1114" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31807,7 +31807,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1115" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31833,7 +31833,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1116" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31859,7 +31859,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1117" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31885,7 +31885,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1118" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31911,7 +31911,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1119" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31937,7 +31937,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1120" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31963,7 +31963,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1121" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31989,7 +31989,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1122" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -32015,7 +32015,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G1123" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -32041,7 +32041,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G1124" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -32067,7 +32067,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1125" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -32093,7 +32093,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1126" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -32119,7 +32119,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1127" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32145,7 +32145,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1128" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -32171,7 +32171,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1129" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -32197,7 +32197,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1130" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -32223,7 +32223,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1131" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32249,7 +32249,7 @@
         <v>1.25</v>
       </c>
       <c r="G1132" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -32275,7 +32275,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1133" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32301,7 +32301,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1134" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32327,7 +32327,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1135" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32353,7 +32353,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1136" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32379,7 +32379,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1137" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32405,7 +32405,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1138" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32431,7 +32431,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1139" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32457,7 +32457,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1140" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32483,7 +32483,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1141" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -32509,7 +32509,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1142" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32535,7 +32535,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1143" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32561,7 +32561,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1144" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -32587,7 +32587,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1145" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -32613,7 +32613,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1146" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -32639,7 +32639,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1147" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -32665,7 +32665,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1148" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -32691,7 +32691,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1149" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32717,7 +32717,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1150" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32743,7 +32743,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1151" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32769,7 +32769,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1152" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32795,7 +32795,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G1153" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32821,7 +32821,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1154" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32847,7 +32847,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1155" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32873,7 +32873,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1156" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32899,7 +32899,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1157" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32925,7 +32925,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1158" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32951,7 +32951,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1159" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32977,7 +32977,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1160" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -33003,7 +33003,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -33029,7 +33029,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1162" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -33055,7 +33055,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1163" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33081,7 +33081,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1164" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -33107,7 +33107,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1165" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33133,7 +33133,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1166" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33159,7 +33159,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1167" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33185,7 +33185,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1168" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33211,7 +33211,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1169" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -33237,7 +33237,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1170" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33263,7 +33263,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1171" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33289,7 +33289,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1172" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33315,7 +33315,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1173" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33341,7 +33341,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1174" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33367,7 +33367,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33393,7 +33393,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1176" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33419,7 +33419,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1177" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33445,7 +33445,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1178" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33471,7 +33471,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1179" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33497,7 +33497,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1180" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33523,7 +33523,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1181" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33549,7 +33549,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1182" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -33575,7 +33575,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1183" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -33601,7 +33601,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1184" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -33627,7 +33627,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1185" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33653,7 +33653,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1186" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -33679,7 +33679,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1187" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33705,7 +33705,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33731,7 +33731,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1189" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33757,7 +33757,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1190" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33783,7 +33783,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1191" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33809,7 +33809,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1192" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33835,7 +33835,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1193" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33861,7 +33861,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1194" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33887,7 +33887,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1195" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33913,7 +33913,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1196" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33939,7 +33939,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33965,7 +33965,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1198" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33991,7 +33991,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1199" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -34017,7 +34017,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1200" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -34043,7 +34043,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1201" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -34069,7 +34069,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1202" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -34095,7 +34095,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1203" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -34121,7 +34121,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1204" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34147,7 +34147,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1205" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34173,7 +34173,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1206" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34199,7 +34199,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1207" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34225,7 +34225,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1208" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34251,7 +34251,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1209" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34277,7 +34277,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1210" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34303,7 +34303,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1211" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34329,7 +34329,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1212" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34355,7 +34355,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1213" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34381,7 +34381,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1214" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34407,7 +34407,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1215" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34433,7 +34433,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1216" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34459,7 +34459,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1217" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34485,7 +34485,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1218" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -34511,7 +34511,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1219" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34537,7 +34537,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1220" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34563,7 +34563,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1221" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -34589,7 +34589,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1222" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -34615,7 +34615,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1223" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -34641,7 +34641,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1224" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -34667,7 +34667,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1225" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -34693,7 +34693,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1226" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34719,7 +34719,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1227" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34745,7 +34745,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1228" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34771,7 +34771,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1229" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34797,7 +34797,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1230" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34823,7 +34823,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1231" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34849,7 +34849,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1232" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34875,7 +34875,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1233" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34901,7 +34901,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1234" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34927,7 +34927,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1235" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34953,7 +34953,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1236" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34979,7 +34979,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1237" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -35005,7 +35005,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1238" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -35031,7 +35031,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1239" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -35057,7 +35057,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1240" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -35083,7 +35083,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1241" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -35109,7 +35109,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1242" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35135,7 +35135,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1243" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35161,7 +35161,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1244" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35187,7 +35187,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1245" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35213,7 +35213,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1246" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35239,7 +35239,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1247" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35265,7 +35265,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1248" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35291,7 +35291,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1249" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35317,7 +35317,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1250" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35343,7 +35343,7 @@
         <v>1.125</v>
       </c>
       <c r="G1251" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35369,7 +35369,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1252" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35395,7 +35395,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1253" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35421,7 +35421,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1254" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35447,7 +35447,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1255" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35473,7 +35473,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1256" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35499,7 +35499,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1257" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35525,7 +35525,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1258" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35551,7 +35551,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1259" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35577,7 +35577,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1260" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -35603,7 +35603,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1261" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -35629,7 +35629,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1262" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -35655,7 +35655,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1263" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -35681,7 +35681,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1264" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35707,7 +35707,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1265" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35733,7 +35733,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1266" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35759,7 +35759,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1267" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35785,7 +35785,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1268" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35811,7 +35811,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1269" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35837,7 +35837,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1270" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35863,7 +35863,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1271" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35889,7 +35889,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G1272" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35915,7 +35915,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1273" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35941,7 +35941,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1274" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35967,7 +35967,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1275" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35993,7 +35993,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1276" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -36019,7 +36019,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1277" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -36045,7 +36045,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1278" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -36071,7 +36071,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1279" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -36097,7 +36097,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1280" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -36123,7 +36123,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1281" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36149,7 +36149,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1282" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36175,7 +36175,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1283" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36201,7 +36201,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1284" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36227,7 +36227,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1285" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36253,7 +36253,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1286" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36279,7 +36279,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1287" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36305,7 +36305,7 @@
         <v>1.375</v>
       </c>
       <c r="G1288" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36331,7 +36331,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1289" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36357,7 +36357,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1290" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36383,7 +36383,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1291" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36409,7 +36409,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1292" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36435,7 +36435,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1293" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36461,7 +36461,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1294" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36487,7 +36487,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1295" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36513,7 +36513,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1296" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36539,7 +36539,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1297" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36565,7 +36565,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1298" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -36591,7 +36591,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1299" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -36617,7 +36617,7 @@
         <v>1.375</v>
       </c>
       <c r="G1300" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36643,7 +36643,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1301" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36669,7 +36669,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1302" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36695,7 +36695,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1303" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36721,7 +36721,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1304" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36747,7 +36747,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1305" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36773,7 +36773,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1306" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36799,7 +36799,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1307" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36825,7 +36825,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1308" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36851,7 +36851,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1309" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36877,7 +36877,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1310" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36903,7 +36903,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1311" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36929,7 +36929,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1312" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36955,7 +36955,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1313" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36981,7 +36981,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1314" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -37007,7 +37007,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1315" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -37033,7 +37033,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1316" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -37059,7 +37059,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1317" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -37085,7 +37085,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1318" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -37111,7 +37111,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1319" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -37137,7 +37137,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1320" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -37163,7 +37163,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1321" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -37189,7 +37189,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1322" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37215,7 +37215,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1323" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -37241,7 +37241,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1324" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -37267,7 +37267,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1325" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37293,7 +37293,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1326" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37319,7 +37319,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1327" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37345,7 +37345,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1328" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37371,7 +37371,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1329" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37397,7 +37397,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1330" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37423,7 +37423,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1331" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37449,7 +37449,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1332" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37475,7 +37475,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1333" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37501,7 +37501,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1334" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37527,7 +37527,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1335" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37553,7 +37553,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1336" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37579,7 +37579,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1337" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37605,7 +37605,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1338" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37631,7 +37631,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1339" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37657,7 +37657,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1340" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37683,7 +37683,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1341" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37709,7 +37709,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1342" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37735,7 +37735,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1343" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37761,7 +37761,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1344" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37787,7 +37787,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1345" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37813,7 +37813,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1346" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37839,7 +37839,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1347" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37865,7 +37865,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -37891,7 +37891,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1349" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -37917,7 +37917,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1350" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37943,7 +37943,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1351" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37969,7 +37969,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1352" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37995,7 +37995,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1353" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -38021,7 +38021,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1354" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -38047,7 +38047,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1355" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -38073,7 +38073,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1356" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -38099,7 +38099,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1357" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -38125,7 +38125,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1358" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -38151,7 +38151,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1359" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -38177,7 +38177,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1360" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -38203,7 +38203,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1361" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -38229,7 +38229,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1362" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -38255,7 +38255,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1363" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38281,7 +38281,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38307,7 +38307,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1365" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38333,7 +38333,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1366" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38359,7 +38359,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1367" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38385,7 +38385,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1368" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38411,7 +38411,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1369" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38437,7 +38437,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1370" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38463,7 +38463,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1371" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38489,7 +38489,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1372" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38515,7 +38515,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1373" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38541,7 +38541,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1374" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38567,7 +38567,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1375" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38593,7 +38593,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1376" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38619,7 +38619,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1377" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38645,7 +38645,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1378" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38671,7 +38671,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1379" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38697,7 +38697,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1380" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38723,7 +38723,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1381" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38749,7 +38749,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1382" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38775,7 +38775,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1383" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38801,7 +38801,7 @@
         <v>1.5</v>
       </c>
       <c r="G1384" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38827,7 +38827,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1385" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38853,7 +38853,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1386" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38879,7 +38879,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1387" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38905,7 +38905,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1388" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38931,7 +38931,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1389" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38957,7 +38957,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1390" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38983,7 +38983,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1391" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -39009,7 +39009,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1392" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -39035,7 +39035,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1393" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -39061,7 +39061,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1394" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -39087,7 +39087,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1395" t="s">
-        <v>473</v>
+        <v>391</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -39113,7 +39113,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1396" t="s">
-        <v>473</v>
+        <v>391</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -39841,7 +39841,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1424" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39919,7 +39919,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1427" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39971,7 +39971,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1429" t="s">
-        <v>473</v>
+        <v>391</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -40075,7 +40075,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1433" t="s">
-        <v>473</v>
+        <v>391</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -68215,7 +68215,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.4985763889</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>1500</v>
@@ -68236,6 +68236,32 @@
         <v>821</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6693634259</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>1.92499995231628</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>806</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DGT.MI.xlsx
+++ b/data/DGT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08123850822449</t>
+    <t xml:space="preserve">2.08123874664307</t>
   </si>
   <si>
     <t xml:space="preserve">DGT.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">2.05767059326172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03047704696655</t>
+    <t xml:space="preserve">2.03047680854797</t>
   </si>
   <si>
     <t xml:space="preserve">1.96702468395233</t>
@@ -56,22 +56,22 @@
     <t xml:space="preserve">2.00509572029114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04860663414001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9942182302475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971475124359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94889533519745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88544297218323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91444957256317</t>
+    <t xml:space="preserve">2.04860639572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99421846866608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971522808075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94889545440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88544285297394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91444981098175</t>
   </si>
   <si>
     <t xml:space="preserve">1.89632046222687</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">1.8763781785965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97065031528473</t>
+    <t xml:space="preserve">1.97065043449402</t>
   </si>
   <si>
     <t xml:space="preserve">1.92714023590088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93076598644257</t>
+    <t xml:space="preserve">1.93076622486115</t>
   </si>
   <si>
     <t xml:space="preserve">1.8582489490509</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">1.75128638744354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64704298973083</t>
+    <t xml:space="preserve">1.6470433473587</t>
   </si>
   <si>
     <t xml:space="preserve">1.75581884384155</t>
@@ -113,46 +113,46 @@
     <t xml:space="preserve">1.68964684009552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73134422302246</t>
+    <t xml:space="preserve">1.73134434223175</t>
   </si>
   <si>
     <t xml:space="preserve">1.76760268211365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72862493991852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75853800773621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81292569637299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83105516433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76850914955139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67514336109161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74947345256805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69871151447296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74766051769257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70777595043182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70868265628815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69508564472198</t>
+    <t xml:space="preserve">1.72862470149994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7585381269455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81292581558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83105504512787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7685090303421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67514359951019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74947333335876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69871139526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74766063690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7077761888504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70868253707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6950855255127</t>
   </si>
   <si>
     <t xml:space="preserve">1.77666735649109</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">1.70143091678619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69055330753326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73496997356415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64069795608521</t>
+    <t xml:space="preserve">1.69055342674255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73497009277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64069771766663</t>
   </si>
   <si>
     <t xml:space="preserve">1.6298201084137</t>
@@ -182,25 +182,25 @@
     <t xml:space="preserve">1.68602108955383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67333042621613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74040877819061</t>
+    <t xml:space="preserve">1.67333054542542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74040865898132</t>
   </si>
   <si>
     <t xml:space="preserve">1.70415031909943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7567253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68783390522003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64885592460632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64794957637787</t>
+    <t xml:space="preserve">1.75672519207001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68783402442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64885604381561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64794969558716</t>
   </si>
   <si>
     <t xml:space="preserve">1.68420815467834</t>
@@ -209,25 +209,25 @@
     <t xml:space="preserve">1.72137308120728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72227942943573</t>
+    <t xml:space="preserve">1.72227954864502</t>
   </si>
   <si>
     <t xml:space="preserve">1.67786300182343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63253974914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66335952281952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6651725769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65429484844208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81111288070679</t>
+    <t xml:space="preserve">1.63253962993622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66335964202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66517245769501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65429472923279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81111299991608</t>
   </si>
   <si>
     <t xml:space="preserve">1.79026424884796</t>
@@ -236,22 +236,22 @@
     <t xml:space="preserve">1.78754484653473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78935766220093</t>
+    <t xml:space="preserve">1.78935778141022</t>
   </si>
   <si>
     <t xml:space="preserve">1.66154646873474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69961786270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66245293617249</t>
+    <t xml:space="preserve">1.69961798191071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66245305538177</t>
   </si>
   <si>
     <t xml:space="preserve">1.6833016872406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65882730484009</t>
+    <t xml:space="preserve">1.6588271856308</t>
   </si>
   <si>
     <t xml:space="preserve">1.60353291034698</t>
@@ -263,16 +263,16 @@
     <t xml:space="preserve">1.58902943134308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48297345638275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49566376209259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49203789234161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53192222118378</t>
+    <t xml:space="preserve">1.48297333717346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49566388130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4920380115509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53192234039307</t>
   </si>
   <si>
     <t xml:space="preserve">1.48387968540192</t>
@@ -281,31 +281,31 @@
     <t xml:space="preserve">1.45215356349945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48569285869598</t>
+    <t xml:space="preserve">1.48569273948669</t>
   </si>
   <si>
     <t xml:space="preserve">1.42858564853668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4594053030014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49294435977936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46031165122986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44127607345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45034050941467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46846997737885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42586600780487</t>
+    <t xml:space="preserve">1.45940518379211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49294447898865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46031153202057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4412761926651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45034062862396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46847009658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42586612701416</t>
   </si>
   <si>
     <t xml:space="preserve">1.31255829334259</t>
@@ -317,82 +317,82 @@
     <t xml:space="preserve">1.34156513214111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36875891685486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33250069618225</t>
+    <t xml:space="preserve">1.36875903606415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33250033855438</t>
   </si>
   <si>
     <t xml:space="preserve">1.2781126499176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19653105735779</t>
+    <t xml:space="preserve">1.19653117656708</t>
   </si>
   <si>
     <t xml:space="preserve">1.17296290397644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18746650218964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17568254470825</t>
+    <t xml:space="preserve">1.18746638298035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17568242549896</t>
   </si>
   <si>
     <t xml:space="preserve">1.15483391284943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09863317012787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12401390075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13307845592499</t>
+    <t xml:space="preserve">1.09863305091858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12401401996613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13307857513428</t>
   </si>
   <si>
     <t xml:space="preserve">1.12582695484161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11313664913177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06962609291077</t>
+    <t xml:space="preserve">1.1131364107132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06962621212006</t>
   </si>
   <si>
     <t xml:space="preserve">1.08684909343719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09500694274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09410083293915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12038803100586</t>
+    <t xml:space="preserve">1.09500730037689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09410071372986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12038815021515</t>
   </si>
   <si>
     <t xml:space="preserve">1.09228777885437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10769772529602</t>
+    <t xml:space="preserve">1.10769760608673</t>
   </si>
   <si>
     <t xml:space="preserve">1.10951066017151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12129473686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0968199968338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08956849575043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08866214752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07234561443329</t>
+    <t xml:space="preserve">1.12129461765289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09682023525238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08956861495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08866190910339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.072345495224</t>
   </si>
   <si>
     <t xml:space="preserve">1.05149698257446</t>
@@ -401,55 +401,55 @@
     <t xml:space="preserve">1.12310755252838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10135233402252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08322322368622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08775544166565</t>
+    <t xml:space="preserve">1.10135245323181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08322310447693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08775556087494</t>
   </si>
   <si>
     <t xml:space="preserve">1.11404287815094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15120804309845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21466028690338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1847470998764</t>
+    <t xml:space="preserve">1.15120780467987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21466040611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18474698066711</t>
   </si>
   <si>
     <t xml:space="preserve">1.1457691192627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12220096588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06237483024597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03336763381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934563338756561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945440828800201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977166950702667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956318378448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933656752109528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01523852348328</t>
+    <t xml:space="preserve">1.12220120429993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06237459182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03336775302887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934563219547272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945440709590912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977167010307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956318259239197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933656811714172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01523840427399</t>
   </si>
   <si>
     <t xml:space="preserve">1.04877769947052</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">1.0360871553421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02430331707001</t>
+    <t xml:space="preserve">1.02430319786072</t>
   </si>
   <si>
     <t xml:space="preserve">0.990764021873474</t>
@@ -473,61 +473,61 @@
     <t xml:space="preserve">1.12854635715485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07506513595581</t>
+    <t xml:space="preserve">1.07506501674652</t>
   </si>
   <si>
     <t xml:space="preserve">1.06418752670288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02067732810974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997109115123749</t>
+    <t xml:space="preserve">1.02067744731903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997109234333038</t>
   </si>
   <si>
     <t xml:space="preserve">1.00617384910583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988044559955597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03880655765533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05965518951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04243230819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06328094005585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05693578720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10407197475433</t>
+    <t xml:space="preserve">0.988044619560242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03880667686462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05965530872345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04243218898773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06328105926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05693566799164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10407185554504</t>
   </si>
   <si>
     <t xml:space="preserve">1.10497808456421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07597172260284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12492048740387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10316550731659</t>
+    <t xml:space="preserve">1.07597160339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12492060661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1031653881073</t>
   </si>
   <si>
     <t xml:space="preserve">1.21103429794312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19562458992004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21284735202789</t>
+    <t xml:space="preserve">1.19562482833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21284747123718</t>
   </si>
   <si>
     <t xml:space="preserve">1.14667558670044</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">1.15392732620239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20559585094452</t>
+    <t xml:space="preserve">1.20559561252594</t>
   </si>
   <si>
     <t xml:space="preserve">1.20196974277496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23188316822052</t>
+    <t xml:space="preserve">1.23188292980194</t>
   </si>
   <si>
     <t xml:space="preserve">1.2536381483078</t>
@@ -551,28 +551,28 @@
     <t xml:space="preserve">1.25817060470581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26089000701904</t>
+    <t xml:space="preserve">1.26088988780975</t>
   </si>
   <si>
     <t xml:space="preserve">1.25545120239258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28717744350433</t>
+    <t xml:space="preserve">1.28717732429504</t>
   </si>
   <si>
     <t xml:space="preserve">1.30893242359161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30530667304993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41226923465729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3796364068985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40320456027985</t>
+    <t xml:space="preserve">1.30530655384064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.412269115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37963628768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40320467948914</t>
   </si>
   <si>
     <t xml:space="preserve">1.35244262218475</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">1.35697495937347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35969436168671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34065842628479</t>
+    <t xml:space="preserve">1.35969424247742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34065866470337</t>
   </si>
   <si>
     <t xml:space="preserve">1.32343602180481</t>
@@ -593,34 +593,34 @@
     <t xml:space="preserve">1.35062980651855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3288745880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26995456218719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19471824169159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1439563035965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24548017978668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25001215934753</t>
+    <t xml:space="preserve">1.32887470722198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26995468139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1947181224823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14395618438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24548006057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25001239776611</t>
   </si>
   <si>
     <t xml:space="preserve">1.268141746521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23278975486755</t>
+    <t xml:space="preserve">1.23278951644897</t>
   </si>
   <si>
     <t xml:space="preserve">1.24185431003571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28173875808716</t>
+    <t xml:space="preserve">1.28173851966858</t>
   </si>
   <si>
     <t xml:space="preserve">1.26451575756073</t>
@@ -629,28 +629,28 @@
     <t xml:space="preserve">1.28264498710632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25091886520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26904809474945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33159375190735</t>
+    <t xml:space="preserve">1.25091874599457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26904821395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33159387111664</t>
   </si>
   <si>
     <t xml:space="preserve">1.29624211788177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28536450862885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31437122821808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30983912944794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31799685955048</t>
+    <t xml:space="preserve">1.28536438941956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31437134742737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30983889102936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31799721717834</t>
   </si>
   <si>
     <t xml:space="preserve">1.29896152019501</t>
@@ -668,31 +668,31 @@
     <t xml:space="preserve">1.31074523925781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30711948871613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34247148036957</t>
+    <t xml:space="preserve">1.30711960792542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34247159957886</t>
   </si>
   <si>
     <t xml:space="preserve">1.294429063797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32434248924255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33884561061859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31165194511414</t>
+    <t xml:space="preserve">1.32434237003326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33884584903717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31165170669556</t>
   </si>
   <si>
     <t xml:space="preserve">1.27992558479309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30621302127838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31618404388428</t>
+    <t xml:space="preserve">1.30621290206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31618428230286</t>
   </si>
   <si>
     <t xml:space="preserve">1.30349349975586</t>
@@ -701,13 +701,13 @@
     <t xml:space="preserve">1.27720630168915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26632869243622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28355157375336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25907719135284</t>
+    <t xml:space="preserve">1.26632881164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28355145454407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25907707214355</t>
   </si>
   <si>
     <t xml:space="preserve">1.24910593032837</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">1.25273168087006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34700393676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34972333908081</t>
+    <t xml:space="preserve">1.34700381755829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34972321987152</t>
   </si>
   <si>
     <t xml:space="preserve">1.29261612892151</t>
@@ -734,13 +734,13 @@
     <t xml:space="preserve">1.23369598388672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22372484207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22916352748871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20468926429749</t>
+    <t xml:space="preserve">1.22372496128082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22916376590729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2046891450882</t>
   </si>
   <si>
     <t xml:space="preserve">1.22191202640533</t>
@@ -749,28 +749,28 @@
     <t xml:space="preserve">1.21919274330139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22100567817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21828615665436</t>
+    <t xml:space="preserve">1.22100555896759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21828627586365</t>
   </si>
   <si>
     <t xml:space="preserve">1.22463130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21012806892395</t>
+    <t xml:space="preserve">1.21012794971466</t>
   </si>
   <si>
     <t xml:space="preserve">1.1865599155426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17477583885193</t>
+    <t xml:space="preserve">1.17477595806122</t>
   </si>
   <si>
     <t xml:space="preserve">1.17840170860291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15211427211761</t>
+    <t xml:space="preserve">1.1521143913269</t>
   </si>
   <si>
     <t xml:space="preserve">1.15845954418182</t>
@@ -788,19 +788,19 @@
     <t xml:space="preserve">1.10679113864899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13217210769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16933715343475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22644448280334</t>
+    <t xml:space="preserve">1.13217198848724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16933739185333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22644436359406</t>
   </si>
   <si>
     <t xml:space="preserve">1.23822844028473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24457359313965</t>
+    <t xml:space="preserve">1.24457371234894</t>
   </si>
   <si>
     <t xml:space="preserve">1.25182521343231</t>
@@ -809,22 +809,22 @@
     <t xml:space="preserve">1.24004137516022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20378279685974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20650196075439</t>
+    <t xml:space="preserve">1.20378267765045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20650219917297</t>
   </si>
   <si>
     <t xml:space="preserve">1.24094772338867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23097681999207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21194088459015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23460257053375</t>
+    <t xml:space="preserve">1.23097658157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21194100379944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23460245132446</t>
   </si>
   <si>
     <t xml:space="preserve">1.24638652801514</t>
@@ -833,16 +833,16 @@
     <t xml:space="preserve">1.27629971504211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27086091041565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29805493354797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22553777694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15574014186859</t>
+    <t xml:space="preserve">1.27086102962494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29805505275726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22553789615631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15574026107788</t>
   </si>
   <si>
     <t xml:space="preserve">1.11857521533966</t>
@@ -851,28 +851,28 @@
     <t xml:space="preserve">1.1602725982666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1666179895401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16480493545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18112123012543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19925022125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11676251888275</t>
+    <t xml:space="preserve">1.16661787033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16480481624603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18112111091614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19925045967102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11676239967346</t>
   </si>
   <si>
     <t xml:space="preserve">1.09319424629211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09772658348083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17658877372742</t>
+    <t xml:space="preserve">1.09772670269012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17658889293671</t>
   </si>
   <si>
     <t xml:space="preserve">1.17930829524994</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">1.28627097606659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28989660739899</t>
+    <t xml:space="preserve">1.28989672660828</t>
   </si>
   <si>
     <t xml:space="preserve">1.28445792198181</t>
@@ -896,25 +896,25 @@
     <t xml:space="preserve">1.38960766792297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4004852771759</t>
+    <t xml:space="preserve">1.40048515796661</t>
   </si>
   <si>
     <t xml:space="preserve">1.41408216953278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38235569000244</t>
+    <t xml:space="preserve">1.38235580921173</t>
   </si>
   <si>
     <t xml:space="preserve">1.37057197093964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32796812057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36513328552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35516214370728</t>
+    <t xml:space="preserve">1.32796823978424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36513340473175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35516202449799</t>
   </si>
   <si>
     <t xml:space="preserve">1.38416874408722</t>
@@ -923,25 +923,25 @@
     <t xml:space="preserve">1.42224025726318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38054299354553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38870120048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36694610118866</t>
+    <t xml:space="preserve">1.38054287433624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38870131969452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36694622039795</t>
   </si>
   <si>
     <t xml:space="preserve">1.40773689746857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39957857131958</t>
+    <t xml:space="preserve">1.39957880973816</t>
   </si>
   <si>
     <t xml:space="preserve">1.39685952663422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38326263427734</t>
+    <t xml:space="preserve">1.38326239585876</t>
   </si>
   <si>
     <t xml:space="preserve">1.38688826560974</t>
@@ -950,133 +950,133 @@
     <t xml:space="preserve">1.50926065444946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5772453546524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57271313667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54551935195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55005156993866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51379299163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48659896850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44580829143524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48206698894501</t>
+    <t xml:space="preserve">1.57724559307098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57271325588226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54551947116852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55005145072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51379311084747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48659920692444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44580852985382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48206686973572</t>
   </si>
   <si>
     <t xml:space="preserve">1.43221139907837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54098689556122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52285766601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52738988399506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37329125404358</t>
+    <t xml:space="preserve">1.54098701477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52285754680634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52739000320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37329137325287</t>
   </si>
   <si>
     <t xml:space="preserve">1.39142060279846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34609758853912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29170954227448</t>
+    <t xml:space="preserve">1.34609746932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29170966148376</t>
   </si>
   <si>
     <t xml:space="preserve">1.31890368461609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33703291416168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27358055114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3959527015686</t>
+    <t xml:space="preserve">1.33703279495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27358031272888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39595282077789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30077409744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33341026306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31476104259491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30543661117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31942331790924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24482703208923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24948930740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23084032535553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21219098567963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25415146350861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23550260066986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22617793083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19354200363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19820415973663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2401647567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27280068397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29611217975616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31009876728058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3287478685379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28212535381317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2681382894516</t>
   </si>
   <si>
     <t xml:space="preserve">1.30077421665192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33341014385223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3147611618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30543661117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31942331790924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24482703208923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24948930740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23084044456482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21219110488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25415170192719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23550260066986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22617793083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19354212284088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19820415973663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2401647567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27280068397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29611206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31009888648987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32874798774719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28212535381317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26813840866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30077433586121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21685338020325</t>
+    <t xml:space="preserve">1.21685326099396</t>
   </si>
   <si>
     <t xml:space="preserve">1.18887972831726</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">1.16556835174561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20286667346954</t>
+    <t xml:space="preserve">1.20286655426025</t>
   </si>
   <si>
     <t xml:space="preserve">1.17489302158356</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">1.1795551776886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20752882957458</t>
+    <t xml:space="preserve">1.2075287103653</t>
   </si>
   <si>
     <t xml:space="preserve">1.32408571243286</t>
@@ -1106,49 +1106,49 @@
     <t xml:space="preserve">1.17023074626923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14691913127899</t>
+    <t xml:space="preserve">1.14691936969757</t>
   </si>
   <si>
     <t xml:space="preserve">1.13293254375458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25881385803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746307849884</t>
+    <t xml:space="preserve">1.25881373882294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746295928955</t>
   </si>
   <si>
     <t xml:space="preserve">1.22151565551758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15624380111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18421769142151</t>
+    <t xml:space="preserve">1.15624392032623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18421745300293</t>
   </si>
   <si>
     <t xml:space="preserve">1.28678750991821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16090607643127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15158152580261</t>
+    <t xml:space="preserve">1.16090619564056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1515816450119</t>
   </si>
   <si>
     <t xml:space="preserve">1.13759469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36138379573822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29144978523254</t>
+    <t xml:space="preserve">1.36138391494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29144990444183</t>
   </si>
   <si>
     <t xml:space="preserve">1.34273481369019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33807241916656</t>
+    <t xml:space="preserve">1.33807253837585</t>
   </si>
   <si>
     <t xml:space="preserve">1.11428344249725</t>
@@ -68348,7 +68348,7 @@
     </row>
     <row r="2521">
       <c r="A2521" s="1" t="n">
-        <v>45988.5132175926</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2521" t="n">
         <v>6500</v>
@@ -68369,6 +68369,32 @@
         <v>796</v>
       </c>
       <c r="H2521" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>45989.617349537</v>
+      </c>
+      <c r="B2522" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C2522" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>1.94500005245209</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>1.95500004291534</v>
+      </c>
+      <c r="F2522" t="n">
+        <v>1.94500005245209</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>809</v>
+      </c>
+      <c r="H2522" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DGT.MI.xlsx
+++ b/data/DGT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="827">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">DGT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05767059326172</t>
+    <t xml:space="preserve">2.0576708316803</t>
   </si>
   <si>
     <t xml:space="preserve">2.03047680854797</t>
@@ -53,22 +53,22 @@
     <t xml:space="preserve">1.96702468395233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00509572029114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04860639572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99421846866608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971522808075</t>
+    <t xml:space="preserve">2.00509595870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04860615730286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99421858787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971487045288</t>
   </si>
   <si>
     <t xml:space="preserve">1.94889545440674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88544285297394</t>
+    <t xml:space="preserve">1.88544309139252</t>
   </si>
   <si>
     <t xml:space="preserve">1.91444981098175</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">1.8763781785965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97065043449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92714023590088</t>
+    <t xml:space="preserve">1.97065055370331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92714011669159</t>
   </si>
   <si>
     <t xml:space="preserve">1.93076622486115</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">1.8582489490509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80839359760284</t>
+    <t xml:space="preserve">1.80839347839355</t>
   </si>
   <si>
     <t xml:space="preserve">1.8256162405014</t>
@@ -101,61 +101,61 @@
     <t xml:space="preserve">1.75128638744354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6470433473587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75581884384155</t>
+    <t xml:space="preserve">1.64704322814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75581860542297</t>
   </si>
   <si>
     <t xml:space="preserve">1.71321487426758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68964684009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73134434223175</t>
+    <t xml:space="preserve">1.68964695930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73134422302246</t>
   </si>
   <si>
     <t xml:space="preserve">1.76760268211365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72862470149994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7585381269455</t>
+    <t xml:space="preserve">1.72862493991852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75853824615479</t>
   </si>
   <si>
     <t xml:space="preserve">1.81292581558228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83105504512787</t>
+    <t xml:space="preserve">1.83105516433716</t>
   </si>
   <si>
     <t xml:space="preserve">1.7685090303421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67514359951019</t>
+    <t xml:space="preserve">1.6751434803009</t>
   </si>
   <si>
     <t xml:space="preserve">1.74947333335876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69871139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74766063690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7077761888504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70868253707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6950855255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77666735649109</t>
+    <t xml:space="preserve">1.69871151447296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74766027927399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70777630805969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70868265628815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69508564472198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77666747570038</t>
   </si>
   <si>
     <t xml:space="preserve">1.70143091678619</t>
@@ -170,13 +170,13 @@
     <t xml:space="preserve">1.64069771766663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6298201084137</t>
+    <t xml:space="preserve">1.62982034683228</t>
   </si>
   <si>
     <t xml:space="preserve">1.63163316249847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68692743778229</t>
+    <t xml:space="preserve">1.68692755699158</t>
   </si>
   <si>
     <t xml:space="preserve">1.68602108955383</t>
@@ -185,46 +185,46 @@
     <t xml:space="preserve">1.67333054542542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74040865898132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70415031909943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75672519207001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68783402442932</t>
+    <t xml:space="preserve">1.74040877819061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70415043830872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75672507286072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68783390522003</t>
   </si>
   <si>
     <t xml:space="preserve">1.64885604381561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64794969558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68420815467834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72137308120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72227954864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67786300182343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63253962993622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66335964202881</t>
+    <t xml:space="preserve">1.64794957637787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68420827388763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72137320041656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72227966785431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67786276340485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6325398683548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66335952281952</t>
   </si>
   <si>
     <t xml:space="preserve">1.66517245769501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65429472923279</t>
+    <t xml:space="preserve">1.65429484844208</t>
   </si>
   <si>
     <t xml:space="preserve">1.81111299991608</t>
@@ -233,85 +233,85 @@
     <t xml:space="preserve">1.79026424884796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78754484653473</t>
+    <t xml:space="preserve">1.78754496574402</t>
   </si>
   <si>
     <t xml:space="preserve">1.78935778141022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66154646873474</t>
+    <t xml:space="preserve">1.66154658794403</t>
   </si>
   <si>
     <t xml:space="preserve">1.69961798191071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66245305538177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6833016872406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6588271856308</t>
+    <t xml:space="preserve">1.6624528169632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68330180644989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65882706642151</t>
   </si>
   <si>
     <t xml:space="preserve">1.60353291034698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.569087266922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58902943134308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48297333717346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49566388130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4920380115509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53192234039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48387968540192</t>
+    <t xml:space="preserve">1.56908714771271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58902955055237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48297345638275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49566376209259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49203813076019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53192222118378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48387980461121</t>
   </si>
   <si>
     <t xml:space="preserve">1.45215356349945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48569273948669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42858564853668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45940518379211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49294447898865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46031153202057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4412761926651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45034062862396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46847009658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42586612701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31255829334259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36422681808472</t>
+    <t xml:space="preserve">1.48569285869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42858552932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4594053030014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49294435977936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46031177043915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44127607345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45034086704254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46846997737885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42586600780487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3125581741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36422669887543</t>
   </si>
   <si>
     <t xml:space="preserve">1.34156513214111</t>
@@ -320,34 +320,34 @@
     <t xml:space="preserve">1.36875903606415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33250033855438</t>
+    <t xml:space="preserve">1.33250045776367</t>
   </si>
   <si>
     <t xml:space="preserve">1.2781126499176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19653117656708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17296290397644</t>
+    <t xml:space="preserve">1.19653105735779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17296314239502</t>
   </si>
   <si>
     <t xml:space="preserve">1.18746638298035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17568242549896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15483391284943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09863305091858</t>
+    <t xml:space="preserve">1.17568254470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15483379364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09863293170929</t>
   </si>
   <si>
     <t xml:space="preserve">1.12401401996613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13307857513428</t>
+    <t xml:space="preserve">1.13307881355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.12582695484161</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">1.1131364107132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06962621212006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08684909343719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09500730037689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09410071372986</t>
+    <t xml:space="preserve">1.06962609291077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08684897422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0950071811676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09410059452057</t>
   </si>
   <si>
     <t xml:space="preserve">1.12038815021515</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">1.10769760608673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10951066017151</t>
+    <t xml:space="preserve">1.10951054096222</t>
   </si>
   <si>
     <t xml:space="preserve">1.12129461765289</t>
@@ -386,19 +386,19 @@
     <t xml:space="preserve">1.09682023525238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08956861495972</t>
+    <t xml:space="preserve">1.08956837654114</t>
   </si>
   <si>
     <t xml:space="preserve">1.08866190910339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.072345495224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05149698257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12310755252838</t>
+    <t xml:space="preserve">1.07234561443329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05149686336517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12310743331909</t>
   </si>
   <si>
     <t xml:space="preserve">1.10135245323181</t>
@@ -413,28 +413,28 @@
     <t xml:space="preserve">1.11404287815094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15120780467987</t>
+    <t xml:space="preserve">1.15120804309845</t>
   </si>
   <si>
     <t xml:space="preserve">1.21466040611267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18474698066711</t>
+    <t xml:space="preserve">1.1847470998764</t>
   </si>
   <si>
     <t xml:space="preserve">1.1457691192627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12220120429993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06237459182739</t>
+    <t xml:space="preserve">1.12220108509064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0623744726181</t>
   </si>
   <si>
     <t xml:space="preserve">1.03336775302887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.934563219547272</t>
+    <t xml:space="preserve">0.934563279151917</t>
   </si>
   <si>
     <t xml:space="preserve">0.945440709590912</t>
@@ -443,88 +443,88 @@
     <t xml:space="preserve">0.977167010307312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.956318259239197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933656811714172</t>
+    <t xml:space="preserve">0.956318438053131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933656752109528</t>
   </si>
   <si>
     <t xml:space="preserve">1.01523840427399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04877769947052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0360871553421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02430319786072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990764021873474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05059063434601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11494934558868</t>
+    <t xml:space="preserve">1.04877746105194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03608727455139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02430307865143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990764081478119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05059051513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11494958400726</t>
   </si>
   <si>
     <t xml:space="preserve">1.12854635715485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07506501674652</t>
+    <t xml:space="preserve">1.07506489753723</t>
   </si>
   <si>
     <t xml:space="preserve">1.06418752670288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02067744731903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997109234333038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00617384910583</t>
+    <t xml:space="preserve">1.02067732810974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997109293937683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00617396831512</t>
   </si>
   <si>
     <t xml:space="preserve">0.988044619560242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03880667686462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05965530872345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04243218898773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06328105926514</t>
+    <t xml:space="preserve">1.03880643844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05965507030487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04243230819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06328094005585</t>
   </si>
   <si>
     <t xml:space="preserve">1.05693566799164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10407185554504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10497808456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07597160339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12492060661316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1031653881073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21103429794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19562482833862</t>
+    <t xml:space="preserve">1.10407173633575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1049782037735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07597136497498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12492048740387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10316526889801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2110344171524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19562447071075</t>
   </si>
   <si>
     <t xml:space="preserve">1.21284747123718</t>
@@ -533,25 +533,25 @@
     <t xml:space="preserve">1.14667558670044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15392732620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20559561252594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20196974277496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23188292980194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2536381483078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25817060470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26088988780975</t>
+    <t xml:space="preserve">1.1539272069931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20559573173523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20196986198425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23188304901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25363826751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25817048549652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26089000701904</t>
   </si>
   <si>
     <t xml:space="preserve">1.25545120239258</t>
@@ -560,16 +560,16 @@
     <t xml:space="preserve">1.28717732429504</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30893242359161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30530655384064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.412269115448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37963628768921</t>
+    <t xml:space="preserve">1.30893230438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30530667304993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41226899623871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37963652610779</t>
   </si>
   <si>
     <t xml:space="preserve">1.40320467948914</t>
@@ -578,25 +578,25 @@
     <t xml:space="preserve">1.35244262218475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35697495937347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35969424247742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34065866470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32343602180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35062980651855</t>
+    <t xml:space="preserve">1.35697507858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35969436168671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34065854549408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32343578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35062968730927</t>
   </si>
   <si>
     <t xml:space="preserve">1.32887470722198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26995468139648</t>
+    <t xml:space="preserve">1.26995456218719</t>
   </si>
   <si>
     <t xml:space="preserve">1.1947181224823</t>
@@ -605,22 +605,22 @@
     <t xml:space="preserve">1.14395618438721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24548006057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25001239776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.268141746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23278951644897</t>
+    <t xml:space="preserve">1.24548017978668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25001227855682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26814162731171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23278963565826</t>
   </si>
   <si>
     <t xml:space="preserve">1.24185431003571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28173851966858</t>
+    <t xml:space="preserve">1.28173863887787</t>
   </si>
   <si>
     <t xml:space="preserve">1.26451575756073</t>
@@ -629,16 +629,16 @@
     <t xml:space="preserve">1.28264498710632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25091874599457</t>
+    <t xml:space="preserve">1.25091886520386</t>
   </si>
   <si>
     <t xml:space="preserve">1.26904821395874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33159387111664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29624211788177</t>
+    <t xml:space="preserve">1.33159410953522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29624199867249</t>
   </si>
   <si>
     <t xml:space="preserve">1.28536438941956</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">1.30983889102936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31799721717834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29896152019501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37782371044159</t>
+    <t xml:space="preserve">1.31799709796906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29896116256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3778235912323</t>
   </si>
   <si>
     <t xml:space="preserve">1.3352198600769</t>
@@ -665,19 +665,19 @@
     <t xml:space="preserve">1.26179623603821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31074523925781</t>
+    <t xml:space="preserve">1.31074547767639</t>
   </si>
   <si>
     <t xml:space="preserve">1.30711960792542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34247159957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.294429063797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32434237003326</t>
+    <t xml:space="preserve">1.34247148036957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29442894458771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32434225082397</t>
   </si>
   <si>
     <t xml:space="preserve">1.33884584903717</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">1.30621290206909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31618428230286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30349349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27720630168915</t>
+    <t xml:space="preserve">1.31618416309357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30349361896515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27720642089844</t>
   </si>
   <si>
     <t xml:space="preserve">1.26632881164551</t>
@@ -707,28 +707,28 @@
     <t xml:space="preserve">1.28355145454407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25907707214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24910593032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27539324760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25273168087006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34700381755829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34972321987152</t>
+    <t xml:space="preserve">1.25907731056213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24910604953766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27539300918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25273180007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34700393676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34972333908081</t>
   </si>
   <si>
     <t xml:space="preserve">1.29261612892151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32978105545044</t>
+    <t xml:space="preserve">1.32978093624115</t>
   </si>
   <si>
     <t xml:space="preserve">1.23369598388672</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">1.22372496128082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22916376590729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2046891450882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22191202640533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21919274330139</t>
+    <t xml:space="preserve">1.229163646698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20468938350677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22191214561462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2191926240921</t>
   </si>
   <si>
     <t xml:space="preserve">1.22100555896759</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">1.21828627586365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22463130950928</t>
+    <t xml:space="preserve">1.22463142871857</t>
   </si>
   <si>
     <t xml:space="preserve">1.21012794971466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1865599155426</t>
+    <t xml:space="preserve">1.18656003475189</t>
   </si>
   <si>
     <t xml:space="preserve">1.17477595806122</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">1.17840170860291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1521143913269</t>
+    <t xml:space="preserve">1.15211427211761</t>
   </si>
   <si>
     <t xml:space="preserve">1.15845954418182</t>
@@ -782,49 +782,49 @@
     <t xml:space="preserve">1.10588479042053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07959735393524</t>
+    <t xml:space="preserve">1.07959711551666</t>
   </si>
   <si>
     <t xml:space="preserve">1.10679113864899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13217198848724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16933739185333</t>
+    <t xml:space="preserve">1.13217210769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16933703422546</t>
   </si>
   <si>
     <t xml:space="preserve">1.22644436359406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23822844028473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24457371234894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25182521343231</t>
+    <t xml:space="preserve">1.23822855949402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24457359313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2518253326416</t>
   </si>
   <si>
     <t xml:space="preserve">1.24004137516022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20378267765045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20650219917297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24094772338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23097658157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21194100379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23460245132446</t>
+    <t xml:space="preserve">1.20378279685974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20650207996368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24094784259796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23097670078278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21194112300873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23460257053375</t>
   </si>
   <si>
     <t xml:space="preserve">1.24638652801514</t>
@@ -836,40 +836,40 @@
     <t xml:space="preserve">1.27086102962494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29805505275726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22553789615631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15574026107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11857521533966</t>
+    <t xml:space="preserve">1.29805493354797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22553777694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15574014186859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11857533454895</t>
   </si>
   <si>
     <t xml:space="preserve">1.1602725982666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16661787033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16480481624603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18112111091614</t>
+    <t xml:space="preserve">1.16661775112152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16480469703674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18112123012543</t>
   </si>
   <si>
     <t xml:space="preserve">1.19925045967102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11676239967346</t>
+    <t xml:space="preserve">1.11676216125488</t>
   </si>
   <si>
     <t xml:space="preserve">1.09319424629211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09772670269012</t>
+    <t xml:space="preserve">1.09772646427155</t>
   </si>
   <si>
     <t xml:space="preserve">1.17658889293671</t>
@@ -878,31 +878,31 @@
     <t xml:space="preserve">1.17930829524994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21375381946564</t>
+    <t xml:space="preserve">1.21375370025635</t>
   </si>
   <si>
     <t xml:space="preserve">1.21556675434113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28627097606659</t>
+    <t xml:space="preserve">1.2862708568573</t>
   </si>
   <si>
     <t xml:space="preserve">1.28989672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28445792198181</t>
+    <t xml:space="preserve">1.2844580411911</t>
   </si>
   <si>
     <t xml:space="preserve">1.38960766792297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40048515796661</t>
+    <t xml:space="preserve">1.4004852771759</t>
   </si>
   <si>
     <t xml:space="preserve">1.41408216953278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38235580921173</t>
+    <t xml:space="preserve">1.38235604763031</t>
   </si>
   <si>
     <t xml:space="preserve">1.37057197093964</t>
@@ -911,25 +911,25 @@
     <t xml:space="preserve">1.32796823978424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36513340473175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35516202449799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38416874408722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42224025726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38054287433624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38870131969452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36694622039795</t>
+    <t xml:space="preserve">1.36513328552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3551619052887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38416862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42224037647247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38054311275482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38870120048523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36694610118866</t>
   </si>
   <si>
     <t xml:space="preserve">1.40773689746857</t>
@@ -938,46 +938,46 @@
     <t xml:space="preserve">1.39957880973816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39685952663422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38326239585876</t>
+    <t xml:space="preserve">1.39685928821564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38326251506805</t>
   </si>
   <si>
     <t xml:space="preserve">1.38688826560974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50926065444946</t>
+    <t xml:space="preserve">1.50926077365875</t>
   </si>
   <si>
     <t xml:space="preserve">1.57724559307098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57271325588226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54551947116852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55005145072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51379311084747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48659920692444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44580852985382</t>
+    <t xml:space="preserve">1.57271313667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54551935195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55005156993866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51379287242889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48659908771515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44580841064453</t>
   </si>
   <si>
     <t xml:space="preserve">1.48206686973572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43221139907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54098701477051</t>
+    <t xml:space="preserve">1.43221151828766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54098689556122</t>
   </si>
   <si>
     <t xml:space="preserve">1.52285754680634</t>
@@ -986,43 +986,43 @@
     <t xml:space="preserve">1.52739000320435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37329137325287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39142060279846</t>
+    <t xml:space="preserve">1.37329125404358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39142048358917</t>
   </si>
   <si>
     <t xml:space="preserve">1.34609746932983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29170966148376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31890368461609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33703279495239</t>
+    <t xml:space="preserve">1.29170954227448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31890344619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33703255653381</t>
   </si>
   <si>
     <t xml:space="preserve">1.27358031272888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39595282077789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30077409744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33341026306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31476104259491</t>
+    <t xml:space="preserve">1.39595293998718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30077421665192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33341014385223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3147611618042</t>
   </si>
   <si>
     <t xml:space="preserve">1.30543661117554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31942331790924</t>
+    <t xml:space="preserve">1.31942319869995</t>
   </si>
   <si>
     <t xml:space="preserve">1.24482703208923</t>
@@ -1034,13 +1034,13 @@
     <t xml:space="preserve">1.23084032535553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21219098567963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25415146350861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23550260066986</t>
+    <t xml:space="preserve">1.21219110488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2541515827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23550248146057</t>
   </si>
   <si>
     <t xml:space="preserve">1.22617793083191</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">1.19354200363159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19820415973663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2401647567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27280068397522</t>
+    <t xml:space="preserve">1.19820427894592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24016487598419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27280080318451</t>
   </si>
   <si>
     <t xml:space="preserve">1.29611217975616</t>
@@ -1067,28 +1067,28 @@
     <t xml:space="preserve">1.3287478685379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28212535381317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2681382894516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30077421665192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21685326099396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18887972831726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16556835174561</t>
+    <t xml:space="preserve">1.28212523460388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26813852787018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30077433586121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21685338020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18887960910797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1655684709549</t>
   </si>
   <si>
     <t xml:space="preserve">1.20286655426025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17489302158356</t>
+    <t xml:space="preserve">1.17489290237427</t>
   </si>
   <si>
     <t xml:space="preserve">1.1795551776886</t>
@@ -1097,25 +1097,25 @@
     <t xml:space="preserve">1.2075287103653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32408571243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34739708900452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17023074626923</t>
+    <t xml:space="preserve">1.32408559322357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34739696979523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17023062705994</t>
   </si>
   <si>
     <t xml:space="preserve">1.14691936969757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13293254375458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25881373882294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746295928955</t>
+    <t xml:space="preserve">1.132932305336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25881397724152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746307849884</t>
   </si>
   <si>
     <t xml:space="preserve">1.22151565551758</t>
@@ -1124,37 +1124,37 @@
     <t xml:space="preserve">1.15624392032623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18421745300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28678750991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16090619564056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1515816450119</t>
+    <t xml:space="preserve">1.18421757221222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2867876291275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16090607643127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15158152580261</t>
   </si>
   <si>
     <t xml:space="preserve">1.13759469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36138391494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29144990444183</t>
+    <t xml:space="preserve">1.36138379573822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29144978523254</t>
   </si>
   <si>
     <t xml:space="preserve">1.34273481369019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33807253837585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11428344249725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1049587726593</t>
+    <t xml:space="preserve">1.33807229995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11428332328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10495865345001</t>
   </si>
   <si>
     <t xml:space="preserve">1.14225709438324</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">1.37278056144714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34437823295593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32544326782227</t>
+    <t xml:space="preserve">1.34437811374664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32544338703156</t>
   </si>
   <si>
     <t xml:space="preserve">1.30177474021912</t>
@@ -1187,49 +1187,49 @@
     <t xml:space="preserve">1.31124210357666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31597578525543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28757345676422</t>
+    <t xml:space="preserve">1.31597590446472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28757357597351</t>
   </si>
   <si>
     <t xml:space="preserve">1.30650842189789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33964443206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42011785507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40591657161713</t>
+    <t xml:space="preserve">1.33964431285858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42011773586273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40591669082642</t>
   </si>
   <si>
     <t xml:space="preserve">1.35384559631348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39644920825958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32070970535278</t>
+    <t xml:space="preserve">1.39644908905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3207094669342</t>
   </si>
   <si>
     <t xml:space="preserve">1.33491063117981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28283989429474</t>
+    <t xml:space="preserve">1.28283977508545</t>
   </si>
   <si>
     <t xml:space="preserve">1.27337229251862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26390480995178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2591712474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29704105854034</t>
+    <t xml:space="preserve">1.26390492916107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25917112827301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29704093933105</t>
   </si>
   <si>
     <t xml:space="preserve">1.2449699640274</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">1.22603499889374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24023616313934</t>
+    <t xml:space="preserve">1.24023628234863</t>
   </si>
   <si>
     <t xml:space="preserve">1.21183383464813</t>
@@ -1256,16 +1256,16 @@
     <t xml:space="preserve">1.26863861083984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20710015296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24970388412476</t>
+    <t xml:space="preserve">1.20710003376007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24970376491547</t>
   </si>
   <si>
     <t xml:space="preserve">1.25443744659424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23550248146057</t>
+    <t xml:space="preserve">1.23550236225128</t>
   </si>
   <si>
     <t xml:space="preserve">1.16923034191132</t>
@@ -1274,37 +1274,37 @@
     <t xml:space="preserve">1.18343150615692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20236659049988</t>
+    <t xml:space="preserve">1.20236647129059</t>
   </si>
   <si>
     <t xml:space="preserve">1.1408280134201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12189304828644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11715912818909</t>
+    <t xml:space="preserve">1.12189292907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11715936660767</t>
   </si>
   <si>
     <t xml:space="preserve">1.10295808315277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0698219537735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01775109767914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989348649978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979881167411804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965680062770844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914555907249451</t>
+    <t xml:space="preserve">1.06982207298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01775121688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989348709583282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979881286621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965680181980133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914555847644806</t>
   </si>
   <si>
     <t xml:space="preserve">0.937277734279633</t>
@@ -1325,22 +1325,22 @@
     <t xml:space="preserve">0.956212639808655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02248477935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07928955554962</t>
+    <t xml:space="preserve">1.0224848985672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07928967475891</t>
   </si>
   <si>
     <t xml:space="preserve">1.10769188404083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13609421253204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05562078952789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09349071979523</t>
+    <t xml:space="preserve">1.13609433174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05562102794647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09349060058594</t>
   </si>
   <si>
     <t xml:space="preserve">1.06035470962524</t>
@@ -1352,16 +1352,16 @@
     <t xml:space="preserve">1.07455587387085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04615342617035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03668594360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04141962528229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1124255657196</t>
+    <t xml:space="preserve">1.04615354537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03668606281281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04141986370087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11242544651031</t>
   </si>
   <si>
     <t xml:space="preserve">1.1266268491745</t>
@@ -1370,34 +1370,34 @@
     <t xml:space="preserve">1.08875691890717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09822428226471</t>
+    <t xml:space="preserve">1.098224401474</t>
   </si>
   <si>
     <t xml:space="preserve">1.05088710784912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03195238113403</t>
+    <t xml:space="preserve">1.03195226192474</t>
   </si>
   <si>
     <t xml:space="preserve">1.02721858024597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17869770526886</t>
+    <t xml:space="preserve">1.17869782447815</t>
   </si>
   <si>
     <t xml:space="preserve">1.15976285934448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15029549598694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16449642181396</t>
+    <t xml:space="preserve">1.15029537677765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16449666023254</t>
   </si>
   <si>
     <t xml:space="preserve">1.15502917766571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14556157588959</t>
+    <t xml:space="preserve">1.14556169509888</t>
   </si>
   <si>
     <t xml:space="preserve">1.17396402359009</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">1.08402323722839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0082836151123</t>
+    <t xml:space="preserve">1.00828373432159</t>
   </si>
   <si>
     <t xml:space="preserve">0.984615087509155</t>
@@ -1418,28 +1418,28 @@
     <t xml:space="preserve">0.994082391262054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01301753520966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18816530704498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33017706871033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40118300914764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36331307888031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33027994632721</t>
+    <t xml:space="preserve">1.01301741600037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18816518783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33017683029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40118288993835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3633131980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33027982711792</t>
   </si>
   <si>
     <t xml:space="preserve">1.32551181316376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33981597423553</t>
+    <t xml:space="preserve">1.33981585502625</t>
   </si>
   <si>
     <t xml:space="preserve">1.33504796028137</t>
@@ -1448,13 +1448,13 @@
     <t xml:space="preserve">1.36365604400635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32074391841888</t>
+    <t xml:space="preserve">1.32074379920959</t>
   </si>
   <si>
     <t xml:space="preserve">1.35412001609802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34458386898041</t>
+    <t xml:space="preserve">1.3445839881897</t>
   </si>
   <si>
     <t xml:space="preserve">1.40180039405823</t>
@@ -1469,25 +1469,25 @@
     <t xml:space="preserve">1.35888803005219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30167174339294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39226424694061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38272821903229</t>
+    <t xml:space="preserve">1.30167186260223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3922643661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38272833824158</t>
   </si>
   <si>
     <t xml:space="preserve">1.41133642196655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38749635219574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37319207191467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43040859699249</t>
+    <t xml:space="preserve">1.38749623298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37319219112396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4304084777832</t>
   </si>
   <si>
     <t xml:space="preserve">1.47808873653412</t>
@@ -1499,13 +1499,13 @@
     <t xml:space="preserve">1.40656840801239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42087244987488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43517649173737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45901668071747</t>
+    <t xml:space="preserve">1.42087256908417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43517661094666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45901656150818</t>
   </si>
   <si>
     <t xml:space="preserve">1.43994450569153</t>
@@ -1517,52 +1517,52 @@
     <t xml:space="preserve">1.51623296737671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50669693946838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53530502319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54484105110168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54007315635681</t>
+    <t xml:space="preserve">1.50669705867767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53530514240265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54484117031097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54007303714752</t>
   </si>
   <si>
     <t xml:space="preserve">1.58298528194427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57344925403595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68788206577301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65450572967529</t>
+    <t xml:space="preserve">1.57344937324524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68788194656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65450584888458</t>
   </si>
   <si>
     <t xml:space="preserve">1.70695412158966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7641704082489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74509847164154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7260262966156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69741809368134</t>
+    <t xml:space="preserve">1.76417052745819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74509835243225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72602605819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69741797447205</t>
   </si>
   <si>
     <t xml:space="preserve">1.66880989074707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67357802391052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64020168781281</t>
+    <t xml:space="preserve">1.67357790470123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64020180702209</t>
   </si>
   <si>
     <t xml:space="preserve">1.61159360408783</t>
@@ -1583,25 +1583,25 @@
     <t xml:space="preserve">1.6163614988327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62112963199615</t>
+    <t xml:space="preserve">1.62112975120544</t>
   </si>
   <si>
     <t xml:space="preserve">1.63066565990448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63543367385864</t>
+    <t xml:space="preserve">1.63543379306793</t>
   </si>
   <si>
     <t xml:space="preserve">1.77847456932068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75940251350403</t>
+    <t xml:space="preserve">1.75940239429474</t>
   </si>
   <si>
     <t xml:space="preserve">1.68311393260956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71649014949799</t>
+    <t xml:space="preserve">1.7164900302887</t>
   </si>
   <si>
     <t xml:space="preserve">1.77370655536652</t>
@@ -1610,10 +1610,10 @@
     <t xml:space="preserve">1.81185066699982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82615482807159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79754674434662</t>
+    <t xml:space="preserve">1.8261547088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79754650592804</t>
   </si>
   <si>
     <t xml:space="preserve">1.788010597229</t>
@@ -1625,43 +1625,43 @@
     <t xml:space="preserve">1.83092284202576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80708277225494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76893866062164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73556232452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73079442977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74033045768738</t>
+    <t xml:space="preserve">1.80708265304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76893842220306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73556244373322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73079431056976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74033033847809</t>
   </si>
   <si>
     <t xml:space="preserve">1.72125828266144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78324258327484</t>
+    <t xml:space="preserve">1.78324246406555</t>
   </si>
   <si>
     <t xml:space="preserve">1.7498664855957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67834603786469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66404175758362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69264996051788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80231463909149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75463449954987</t>
+    <t xml:space="preserve">1.6783459186554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66404187679291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69265007972717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80231475830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75463438034058</t>
   </si>
   <si>
     <t xml:space="preserve">1.79277861118317</t>
@@ -1670,28 +1670,28 @@
     <t xml:space="preserve">1.56868124008179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65927386283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5925213098526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52576911449432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59728944301605</t>
+    <t xml:space="preserve">1.65927374362946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59252142906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52576899528503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59728932380676</t>
   </si>
   <si>
     <t xml:space="preserve">1.7021861076355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85953104496002</t>
+    <t xml:space="preserve">1.85953116416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.89767527580261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92628335952759</t>
+    <t xml:space="preserve">1.92628347873688</t>
   </si>
   <si>
     <t xml:space="preserve">1.82138681411743</t>
@@ -1706,10 +1706,10 @@
     <t xml:space="preserve">1.90721130371094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94535553455353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99303567409515</t>
+    <t xml:space="preserve">1.94535541534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99303555488586</t>
   </si>
   <si>
     <t xml:space="preserve">2.0597882270813</t>
@@ -1718,22 +1718,22 @@
     <t xml:space="preserve">2.00257182121277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07886052131653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12654066085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10746836662292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08839631080627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09793257713318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1456127166748</t>
+    <t xml:space="preserve">2.07886028289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12654042243958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1074686050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08839654922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0979323387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14561295509338</t>
   </si>
   <si>
     <t xml:space="preserve">2.27911758422852</t>
@@ -1742,25 +1742,25 @@
     <t xml:space="preserve">2.19329285621643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22190117835999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25050902366638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02164387702942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01210761070251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97396349906921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98349988460541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03118014335632</t>
+    <t xml:space="preserve">2.22190093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25050926208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02164363861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01210784912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9739636182785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98349964618683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0311803817749</t>
   </si>
   <si>
     <t xml:space="preserve">2.04071617126465</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">2.09847211837769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08884620666504</t>
+    <t xml:space="preserve">2.08884644508362</t>
   </si>
   <si>
     <t xml:space="preserve">2.10809826850891</t>
@@ -1787,16 +1787,16 @@
     <t xml:space="preserve">2.0214638710022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05996799468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.944455742836</t>
+    <t xml:space="preserve">2.05996823310852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94445586204529</t>
   </si>
   <si>
     <t xml:space="preserve">1.9733339548111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93482983112335</t>
+    <t xml:space="preserve">1.93482971191406</t>
   </si>
   <si>
     <t xml:space="preserve">1.85782170295715</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">1.83856964111328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82894372940063</t>
+    <t xml:space="preserve">1.82894361019135</t>
   </si>
   <si>
     <t xml:space="preserve">1.86744773387909</t>
@@ -1826,10 +1826,10 @@
     <t xml:space="preserve">1.99258589744568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04071593284607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05034208297729</t>
+    <t xml:space="preserve">2.04071569442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05034232139587</t>
   </si>
   <si>
     <t xml:space="preserve">2.11772418022156</t>
@@ -1844,25 +1844,25 @@
     <t xml:space="preserve">2.16585445404053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14660239219666</t>
+    <t xml:space="preserve">2.14660215377808</t>
   </si>
   <si>
     <t xml:space="preserve">2.07922005653381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24286246299744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25248837471008</t>
+    <t xml:space="preserve">2.24286222457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25248861312866</t>
   </si>
   <si>
     <t xml:space="preserve">2.27174043655396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30061841011047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2813663482666</t>
+    <t xml:space="preserve">2.30061864852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28136610984802</t>
   </si>
   <si>
     <t xml:space="preserve">2.1851065158844</t>
@@ -1877,16 +1877,16 @@
     <t xml:space="preserve">2.13697624206543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01183795928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87226068973541</t>
+    <t xml:space="preserve">2.01183772087097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8722608089447</t>
   </si>
   <si>
     <t xml:space="preserve">1.96370780467987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06959438323975</t>
+    <t xml:space="preserve">2.06959414482117</t>
   </si>
   <si>
     <t xml:space="preserve">2.17548012733459</t>
@@ -1895,10 +1895,10 @@
     <t xml:space="preserve">2.23323631286621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31024479866028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35837459564209</t>
+    <t xml:space="preserve">2.3102445602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35837483406067</t>
   </si>
   <si>
     <t xml:space="preserve">2.42575693130493</t>
@@ -1925,13 +1925,13 @@
     <t xml:space="preserve">2.29099273681641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36800098419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38725280761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21398448944092</t>
+    <t xml:space="preserve">2.36800074577332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38725304603577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21398425102234</t>
   </si>
   <si>
     <t xml:space="preserve">2.31987071037292</t>
@@ -1949,13 +1949,13 @@
     <t xml:space="preserve">2.49313902854919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52201676368713</t>
+    <t xml:space="preserve">2.52201700210571</t>
   </si>
   <si>
     <t xml:space="preserve">2.50276470184326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59902501106262</t>
+    <t xml:space="preserve">2.5990252494812</t>
   </si>
   <si>
     <t xml:space="preserve">2.64715528488159</t>
@@ -1964,19 +1964,19 @@
     <t xml:space="preserve">2.54126906394958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51239109039307</t>
+    <t xml:space="preserve">2.51239085197449</t>
   </si>
   <si>
     <t xml:space="preserve">2.47388672828674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48351287841797</t>
+    <t xml:space="preserve">2.48351263999939</t>
   </si>
   <si>
     <t xml:space="preserve">2.53164315223694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63752937316895</t>
+    <t xml:space="preserve">2.63752913475037</t>
   </si>
   <si>
     <t xml:space="preserve">2.69528532028198</t>
@@ -1991,13 +1991,13 @@
     <t xml:space="preserve">2.67603325843811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60865139961243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66640734672546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5701470375061</t>
+    <t xml:space="preserve">2.60865116119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66640710830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57014727592468</t>
   </si>
   <si>
     <t xml:space="preserve">2.58939933776855</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">2.56052112579346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62790322303772</t>
+    <t xml:space="preserve">2.6279034614563</t>
   </si>
   <si>
     <t xml:space="preserve">2.55089521408081</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">2.57977318763733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38258790969849</t>
+    <t xml:space="preserve">2.38258814811707</t>
   </si>
   <si>
     <t xml:space="preserve">2.29506421089172</t>
@@ -2024,13 +2024,13 @@
     <t xml:space="preserve">2.28533935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32423877716064</t>
+    <t xml:space="preserve">2.32423901557922</t>
   </si>
   <si>
     <t xml:space="preserve">2.25616478919983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23671531677246</t>
+    <t xml:space="preserve">2.23671507835388</t>
   </si>
   <si>
     <t xml:space="preserve">2.21726560592651</t>
@@ -2042,16 +2042,16 @@
     <t xml:space="preserve">2.34368872642517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26588988304138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3047890663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24643993377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1102921962738</t>
+    <t xml:space="preserve">2.2658896446228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30478882789612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24644017219543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11029243469238</t>
   </si>
   <si>
     <t xml:space="preserve">2.15891647338867</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">2.19781565666199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16864132881165</t>
+    <t xml:space="preserve">2.16864109039307</t>
   </si>
   <si>
     <t xml:space="preserve">2.18809103965759</t>
@@ -2081,16 +2081,16 @@
     <t xml:space="preserve">2.13946676254272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09084272384644</t>
+    <t xml:space="preserve">2.09084248542786</t>
   </si>
   <si>
     <t xml:space="preserve">2.10056734085083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27561450004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08111763000488</t>
+    <t xml:space="preserve">2.27561473846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08111786842346</t>
   </si>
   <si>
     <t xml:space="preserve">1.97414433956146</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">1.98386907577515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9644193649292</t>
+    <t xml:space="preserve">1.96441948413849</t>
   </si>
   <si>
     <t xml:space="preserve">1.94496977329254</t>
@@ -2117,13 +2117,13 @@
     <t xml:space="preserve">2.02276849746704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03249335289001</t>
+    <t xml:space="preserve">2.03249311447144</t>
   </si>
   <si>
     <t xml:space="preserve">2.01304364204407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07139277458191</t>
+    <t xml:space="preserve">2.07139301300049</t>
   </si>
   <si>
     <t xml:space="preserve">2.04221820831299</t>
@@ -2135,76 +2135,79 @@
     <t xml:space="preserve">1.93524491786957</t>
   </si>
   <si>
+    <t xml:space="preserve">1.95469450950623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91579520702362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93038249015808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06166768074036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91093277931213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1491916179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00331878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86717092990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92552006244659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81854665279388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84772121906281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8866206407547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83313393592834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85258364677429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89634561538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92065763473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95961833000183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96946561336517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01870226860046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96454191207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98916029930115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00885486602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99900758266449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97931289672852</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.95469462871552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91579520702362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93038249015808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06166791915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91093289852142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1491916179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00331878662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86717092990875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92552006244659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81854677200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84772133827209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8866206407547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83313405513763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85258364677429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89634561538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92065763473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95961833000183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96946561336517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01870226860046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96454191207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98916029930115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00885486602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99900758266449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97931289672852</t>
   </si>
   <si>
     <t xml:space="preserve">1.9497709274292</t>
@@ -59500,7 +59503,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2180" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -59526,7 +59529,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2181" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59552,7 +59555,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2182" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59578,7 +59581,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2183" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59682,7 +59685,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2187" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59708,7 +59711,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2188" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59734,7 +59737,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2189" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59760,7 +59763,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2190" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59786,7 +59789,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2191" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59812,7 +59815,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2192" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59838,7 +59841,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2193" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60150,7 +60153,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2205" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60176,7 +60179,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2206" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60202,7 +60205,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2207" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60228,7 +60231,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2208" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60280,7 +60283,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2210" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60306,7 +60309,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2211" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60332,7 +60335,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2212" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60358,7 +60361,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2213" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60384,7 +60387,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2214" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60436,7 +60439,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2216" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60592,7 +60595,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60670,7 +60673,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2225" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60696,7 +60699,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2226" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60748,7 +60751,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2228" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60774,7 +60777,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2229" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60800,7 +60803,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2230" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60826,7 +60829,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2231" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60852,7 +60855,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2232" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60878,7 +60881,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2233" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60904,7 +60907,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2234" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60930,7 +60933,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2235" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60956,7 +60959,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2236" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60982,7 +60985,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2237" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61008,7 +61011,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2238" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61034,7 +61037,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2239" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61060,7 +61063,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2240" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61086,7 +61089,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G2241" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61112,7 +61115,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2242" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61138,7 +61141,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2243" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61164,7 +61167,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G2244" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61190,7 +61193,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2245" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61216,7 +61219,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2246" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61242,7 +61245,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2247" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61268,7 +61271,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2248" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61294,7 +61297,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2249" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61320,7 +61323,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2250" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61346,7 +61349,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2251" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61372,7 +61375,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2252" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61476,7 +61479,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2256" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -61502,7 +61505,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2257" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -61554,7 +61557,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2259" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -61580,7 +61583,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2260" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -61606,7 +61609,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2261" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -61632,7 +61635,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -61658,7 +61661,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2263" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -61710,7 +61713,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2265" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61736,7 +61739,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2266" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61866,7 +61869,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2271" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61892,7 +61895,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2272" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61918,7 +61921,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2273" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61944,7 +61947,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2274" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61970,7 +61973,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2275" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61996,7 +61999,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2276" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62022,7 +62025,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2277" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62048,7 +62051,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2278" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62074,7 +62077,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2279" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62100,7 +62103,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2280" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62126,7 +62129,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2281" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62152,7 +62155,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2282" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62178,7 +62181,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2283" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62204,7 +62207,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2284" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62230,7 +62233,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2285" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62256,7 +62259,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2286" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62282,7 +62285,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2287" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62308,7 +62311,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2288" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62334,7 +62337,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2289" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62360,7 +62363,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2290" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62386,7 +62389,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2291" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62412,7 +62415,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2292" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62438,7 +62441,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2293" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62464,7 +62467,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2294" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -62490,7 +62493,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2295" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -62516,7 +62519,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2296" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -62542,7 +62545,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2297" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -62568,7 +62571,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2298" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -62594,7 +62597,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2299" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -62620,7 +62623,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2300" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -62646,7 +62649,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2301" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -62672,7 +62675,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2302" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -62698,7 +62701,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2303" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62724,7 +62727,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2304" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62750,7 +62753,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62776,7 +62779,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2306" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62802,7 +62805,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G2307" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62828,7 +62831,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2308" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62854,7 +62857,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2309" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62880,7 +62883,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2310" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62906,7 +62909,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2311" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62932,7 +62935,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2312" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62958,7 +62961,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2313" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62984,7 +62987,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2314" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63010,7 +63013,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2315" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63036,7 +63039,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2316" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63062,7 +63065,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2317" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63088,7 +63091,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2318" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63114,7 +63117,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2319" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63140,7 +63143,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2320" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63166,7 +63169,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2321" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63192,7 +63195,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2322" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63218,7 +63221,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2323" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63244,7 +63247,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2324" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63270,7 +63273,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2325" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63296,7 +63299,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2326" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63322,7 +63325,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2327" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63348,7 +63351,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2328" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63374,7 +63377,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2329" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63400,7 +63403,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2330" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63426,7 +63429,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2331" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63452,7 +63455,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2332" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63478,7 +63481,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2333" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -63504,7 +63507,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2334" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -63530,7 +63533,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2335" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -63556,7 +63559,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2336" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -63582,7 +63585,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2337" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -63608,7 +63611,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2338" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -63634,7 +63637,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2339" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -63660,7 +63663,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G2340" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -63686,7 +63689,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2341" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63712,7 +63715,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2342" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63738,7 +63741,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63764,7 +63767,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2344" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63790,7 +63793,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2345" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63816,7 +63819,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2346" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63842,7 +63845,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2347" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63868,7 +63871,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63894,7 +63897,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63920,7 +63923,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2350" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63946,7 +63949,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2351" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63972,7 +63975,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G2352" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63998,7 +64001,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2353" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64024,7 +64027,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2354" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64050,7 +64053,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2355" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64076,7 +64079,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2356" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64102,7 +64105,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G2357" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64128,7 +64131,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2358" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64154,7 +64157,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G2359" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64180,7 +64183,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G2360" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64206,7 +64209,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2361" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64232,7 +64235,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2362" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64258,7 +64261,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2363" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64284,7 +64287,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G2364" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64310,7 +64313,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2365" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64336,7 +64339,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64362,7 +64365,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G2367" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64388,7 +64391,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2368" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64414,7 +64417,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2369" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64440,7 +64443,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2370" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64466,7 +64469,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2371" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64492,7 +64495,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2372" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -64518,7 +64521,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2373" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -64544,7 +64547,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G2374" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -64570,7 +64573,7 @@
         <v>1.625</v>
       </c>
       <c r="G2375" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -64596,7 +64599,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G2376" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -64622,7 +64625,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G2377" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -64648,7 +64651,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2378" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -64674,7 +64677,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G2379" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -64700,7 +64703,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2380" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64726,7 +64729,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2381" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64752,7 +64755,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2382" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64778,7 +64781,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G2383" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64804,7 +64807,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2384" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64830,7 +64833,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2385" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64856,7 +64859,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64882,7 +64885,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2387" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64908,7 +64911,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2388" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64934,7 +64937,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64960,7 +64963,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2390" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64986,7 +64989,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2391" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65012,7 +65015,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2392" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65038,7 +65041,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G2393" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65064,7 +65067,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G2394" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65090,7 +65093,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2395" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65116,7 +65119,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2396" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65142,7 +65145,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2397" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65168,7 +65171,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2398" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65194,7 +65197,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2399" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65220,7 +65223,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2400" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65246,7 +65249,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2401" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65272,7 +65275,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2402" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65298,7 +65301,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2403" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65324,7 +65327,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2404" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65350,7 +65353,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2405" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65376,7 +65379,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2406" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65428,7 +65431,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2408" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65454,7 +65457,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2409" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65480,7 +65483,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2410" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -65506,7 +65509,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2411" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65532,7 +65535,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2412" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65558,7 +65561,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2413" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65584,7 +65587,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2414" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65610,7 +65613,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2415" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65636,7 +65639,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2416" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65662,7 +65665,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2417" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65688,7 +65691,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2418" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65714,7 +65717,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2419" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65740,7 +65743,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2420" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65766,7 +65769,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2421" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65792,7 +65795,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65818,7 +65821,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2423" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65844,7 +65847,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2424" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65870,7 +65873,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2425" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65896,7 +65899,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2426" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65922,7 +65925,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2427" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65948,7 +65951,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2428" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65974,7 +65977,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2429" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66000,7 +66003,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2430" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66026,7 +66029,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2431" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66052,7 +66055,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2432" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66078,7 +66081,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2433" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66104,7 +66107,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2434" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66130,7 +66133,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2435" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66156,7 +66159,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2436" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66182,7 +66185,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2437" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66208,7 +66211,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2438" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66234,7 +66237,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2439" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66260,7 +66263,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2440" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66286,7 +66289,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2441" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66312,7 +66315,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2442" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66338,7 +66341,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2443" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66364,7 +66367,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2444" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66390,7 +66393,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2445" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66416,7 +66419,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2446" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66442,7 +66445,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2447" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66468,7 +66471,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2448" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -66494,7 +66497,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2449" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -66520,7 +66523,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2450" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66546,7 +66549,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2451" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66572,7 +66575,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2452" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66598,7 +66601,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2453" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66624,7 +66627,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2454" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66650,7 +66653,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2455" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66676,7 +66679,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2456" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66702,7 +66705,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2457" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66728,7 +66731,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2458" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66754,7 +66757,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2459" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66780,7 +66783,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2460" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66806,7 +66809,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2461" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66832,7 +66835,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2462" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66858,7 +66861,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2463" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66884,7 +66887,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2464" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66910,7 +66913,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2465" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66936,7 +66939,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2466" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66962,7 +66965,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2467" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66988,7 +66991,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2468" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67014,7 +67017,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2469" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67040,7 +67043,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2470" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67066,7 +67069,7 @@
         <v>2</v>
       </c>
       <c r="G2471" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67092,7 +67095,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2472" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67118,7 +67121,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2473" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67144,7 +67147,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2474" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67170,7 +67173,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2475" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67196,7 +67199,7 @@
         <v>2</v>
       </c>
       <c r="G2476" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67222,7 +67225,7 @@
         <v>2</v>
       </c>
       <c r="G2477" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67248,7 +67251,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2478" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67274,7 +67277,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2479" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67300,7 +67303,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2480" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67326,7 +67329,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2481" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67352,7 +67355,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2482" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67378,7 +67381,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2483" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67404,7 +67407,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2484" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67430,7 +67433,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2485" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67456,7 +67459,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2486" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67482,7 +67485,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2487" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -67508,7 +67511,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2488" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67534,7 +67537,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2489" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67560,7 +67563,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2490" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67586,7 +67589,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2491" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67612,7 +67615,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2492" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67638,7 +67641,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2493" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67664,7 +67667,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2494" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67690,7 +67693,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2495" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67716,7 +67719,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2496" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67742,7 +67745,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2497" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67768,7 +67771,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2498" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67794,7 +67797,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2499" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67820,7 +67823,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2500" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67846,7 +67849,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2501" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67872,7 +67875,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2502" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -67898,7 +67901,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2503" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -67924,7 +67927,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2504" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67950,7 +67953,7 @@
         <v>2</v>
       </c>
       <c r="G2505" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67976,7 +67979,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2506" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68002,7 +68005,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2507" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68028,7 +68031,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2508" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68054,7 +68057,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2509" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68080,7 +68083,7 @@
         <v>2</v>
       </c>
       <c r="G2510" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68106,7 +68109,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2511" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68132,7 +68135,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2512" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68158,7 +68161,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2513" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -68184,7 +68187,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2514" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -68210,7 +68213,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2515" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -68236,7 +68239,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2516" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -68262,7 +68265,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2517" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -68288,7 +68291,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2518" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -68314,7 +68317,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2519" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -68340,7 +68343,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2520" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -68366,7 +68369,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2521" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -68374,7 +68377,7 @@
     </row>
     <row r="2522">
       <c r="A2522" s="1" t="n">
-        <v>45989.617349537</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2522" t="n">
         <v>8000</v>
@@ -68392,9 +68395,35 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2522" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H2522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>45992.6820717593</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>61500</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>1.98500001430511</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>2.00999999046326</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>801</v>
+      </c>
+      <c r="H2523" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DGT.MI.xlsx
+++ b/data/DGT.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08123874664307</t>
+    <t xml:space="preserve">2.08123922348022</t>
   </si>
   <si>
     <t xml:space="preserve">DGT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0576708316803</t>
+    <t xml:space="preserve">2.05767059326172</t>
   </si>
   <si>
     <t xml:space="preserve">2.03047680854797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96702480316162</t>
+    <t xml:space="preserve">1.96702468395233</t>
   </si>
   <si>
     <t xml:space="preserve">2.00509595870972</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">2.04860615730286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9942182302475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971510887146</t>
+    <t xml:space="preserve">1.99421834945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971487045288</t>
   </si>
   <si>
     <t xml:space="preserve">1.94889533519745</t>
@@ -71,34 +71,34 @@
     <t xml:space="preserve">1.88544285297394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91444981098175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89632022380829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8763781785965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9706506729126</t>
+    <t xml:space="preserve">1.91444969177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89632046222687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87637805938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97065055370331</t>
   </si>
   <si>
     <t xml:space="preserve">1.92714011669159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93076622486115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8582489490509</t>
+    <t xml:space="preserve">1.93076598644257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85824882984161</t>
   </si>
   <si>
     <t xml:space="preserve">1.80839347839355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8256162405014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75128638744354</t>
+    <t xml:space="preserve">1.82561612129211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75128650665283</t>
   </si>
   <si>
     <t xml:space="preserve">1.64704322814941</t>
@@ -107,106 +107,106 @@
     <t xml:space="preserve">1.75581872463226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71321487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68964695930481</t>
+    <t xml:space="preserve">1.71321511268616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68964672088623</t>
   </si>
   <si>
     <t xml:space="preserve">1.73134422302246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76760280132294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72862470149994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75853788852692</t>
+    <t xml:space="preserve">1.76760268211365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72862482070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75853800773621</t>
   </si>
   <si>
     <t xml:space="preserve">1.81292581558228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83105504512787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76850914955139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67514336109161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74947345256805</t>
+    <t xml:space="preserve">1.83105492591858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76850926876068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6751434803009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74947321414948</t>
   </si>
   <si>
     <t xml:space="preserve">1.69871151447296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74766063690186</t>
+    <t xml:space="preserve">1.74766051769257</t>
   </si>
   <si>
     <t xml:space="preserve">1.70777606964111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70868253707886</t>
+    <t xml:space="preserve">1.70868265628815</t>
   </si>
   <si>
     <t xml:space="preserve">1.69508576393127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77666735649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7014307975769</t>
+    <t xml:space="preserve">1.77666747570038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70143103599548</t>
   </si>
   <si>
     <t xml:space="preserve">1.69055342674255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73497009277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64069795608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62982022762299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63163304328918</t>
+    <t xml:space="preserve">1.73496997356415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64069783687592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62982034683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63163316249847</t>
   </si>
   <si>
     <t xml:space="preserve">1.686927318573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68602097034454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67333054542542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7404088973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70415019989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75672495365143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68783414363861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64885592460632</t>
+    <t xml:space="preserve">1.68602120876312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67333042621613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74040877819061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70415043830872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75672519207001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68783390522003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64885604381561</t>
   </si>
   <si>
     <t xml:space="preserve">1.64794957637787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68420803546906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72137331962585</t>
+    <t xml:space="preserve">1.68420791625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72137308120728</t>
   </si>
   <si>
     <t xml:space="preserve">1.72227954864502</t>
@@ -221,22 +221,22 @@
     <t xml:space="preserve">1.66335952281952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66517245769501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65429484844208</t>
+    <t xml:space="preserve">1.66517233848572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65429496765137</t>
   </si>
   <si>
     <t xml:space="preserve">1.81111299991608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79026436805725</t>
+    <t xml:space="preserve">1.79026412963867</t>
   </si>
   <si>
     <t xml:space="preserve">1.78754484653473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78935778141022</t>
+    <t xml:space="preserve">1.78935790061951</t>
   </si>
   <si>
     <t xml:space="preserve">1.66154646873474</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">1.69961798191071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6624528169632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6833016872406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65882706642151</t>
+    <t xml:space="preserve">1.66245305538177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68330156803131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6588271856308</t>
   </si>
   <si>
     <t xml:space="preserve">1.60353291034698</t>
@@ -260,52 +260,52 @@
     <t xml:space="preserve">1.569087266922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58902943134308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48297333717346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4956636428833</t>
+    <t xml:space="preserve">1.58902931213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48297345638275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49566388130188</t>
   </si>
   <si>
     <t xml:space="preserve">1.4920380115509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53192234039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48387980461121</t>
+    <t xml:space="preserve">1.53192222118378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48387968540192</t>
   </si>
   <si>
     <t xml:space="preserve">1.45215356349945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48569273948669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42858552932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4594053030014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49294435977936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46031165122986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44127595424652</t>
+    <t xml:space="preserve">1.48569285869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42858564853668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45940518379211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49294424057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46031177043915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44127583503723</t>
   </si>
   <si>
     <t xml:space="preserve">1.45034062862396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46846997737885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42586612701416</t>
+    <t xml:space="preserve">1.46846985816956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42586600780487</t>
   </si>
   <si>
     <t xml:space="preserve">1.31255829334259</t>
@@ -317,34 +317,34 @@
     <t xml:space="preserve">1.34156513214111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36875903606415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33250045776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2781126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19653117656708</t>
+    <t xml:space="preserve">1.36875915527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33250033855438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27811276912689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19653129577637</t>
   </si>
   <si>
     <t xml:space="preserve">1.17296314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18746626377106</t>
+    <t xml:space="preserve">1.18746638298035</t>
   </si>
   <si>
     <t xml:space="preserve">1.17568242549896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15483367443085</t>
+    <t xml:space="preserve">1.15483391284943</t>
   </si>
   <si>
     <t xml:space="preserve">1.09863317012787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12401413917542</t>
+    <t xml:space="preserve">1.12401378154755</t>
   </si>
   <si>
     <t xml:space="preserve">1.13307857513428</t>
@@ -353,64 +353,64 @@
     <t xml:space="preserve">1.1258270740509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11313652992249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06962621212006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08684909343719</t>
+    <t xml:space="preserve">1.1131364107132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06962633132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08684897422791</t>
   </si>
   <si>
     <t xml:space="preserve">1.09500706195831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09410059452057</t>
+    <t xml:space="preserve">1.09410083293915</t>
   </si>
   <si>
     <t xml:space="preserve">1.12038815021515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09228777885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10769760608673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10951066017151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12129461765289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09682035446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08956837654114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08866190910339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07234573364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05149698257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12310755252838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1013525724411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08322310447693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08775544166565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11404275894165</t>
+    <t xml:space="preserve">1.09228789806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10769772529602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10951054096222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12129473686218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09682011604309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08956849575043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08866202831268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.072345495224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05149686336517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12310767173767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10135245323181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08322334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08775568008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11404287815094</t>
   </si>
   <si>
     <t xml:space="preserve">1.15120792388916</t>
@@ -419,34 +419,34 @@
     <t xml:space="preserve">1.21466028690338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18474698066711</t>
+    <t xml:space="preserve">1.18474686145782</t>
   </si>
   <si>
     <t xml:space="preserve">1.14576923847198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12220132350922</t>
+    <t xml:space="preserve">1.12220108509064</t>
   </si>
   <si>
     <t xml:space="preserve">1.06237459182739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03336787223816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934563279151917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945440709590912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977166950702667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956318259239197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933656811714172</t>
+    <t xml:space="preserve">1.03336763381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934563338756561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945440828800201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977167010307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956318318843842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933656752109528</t>
   </si>
   <si>
     <t xml:space="preserve">1.01523840427399</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">1.02430307865143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990764021873474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05059051513672</t>
+    <t xml:space="preserve">0.990764141082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05059063434601</t>
   </si>
   <si>
     <t xml:space="preserve">1.11494934558868</t>
@@ -473,16 +473,16 @@
     <t xml:space="preserve">1.12854623794556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07506513595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06418740749359</t>
+    <t xml:space="preserve">1.07506501674652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06418752670288</t>
   </si>
   <si>
     <t xml:space="preserve">1.02067720890045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997109115123749</t>
+    <t xml:space="preserve">0.997109174728394</t>
   </si>
   <si>
     <t xml:space="preserve">1.00617384910583</t>
@@ -491,10 +491,10 @@
     <t xml:space="preserve">0.988044738769531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03880667686462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05965530872345</t>
+    <t xml:space="preserve">1.03880643844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05965518951416</t>
   </si>
   <si>
     <t xml:space="preserve">1.04243230819702</t>
@@ -503,13 +503,13 @@
     <t xml:space="preserve">1.06328094005585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05693566799164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10407173633575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10497832298279</t>
+    <t xml:space="preserve">1.05693578720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10407185554504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1049782037735</t>
   </si>
   <si>
     <t xml:space="preserve">1.07597148418427</t>
@@ -521,22 +521,22 @@
     <t xml:space="preserve">1.10316550731659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21103429794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19562482833862</t>
+    <t xml:space="preserve">1.21103453636169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19562458992004</t>
   </si>
   <si>
     <t xml:space="preserve">1.21284747123718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14667570590973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15392732620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20559585094452</t>
+    <t xml:space="preserve">1.14667558670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15392744541168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20559561252594</t>
   </si>
   <si>
     <t xml:space="preserve">1.20196986198425</t>
@@ -548,25 +548,25 @@
     <t xml:space="preserve">1.25363838672638</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25817048549652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26088976860046</t>
+    <t xml:space="preserve">1.25817060470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26088988780975</t>
   </si>
   <si>
     <t xml:space="preserve">1.25545120239258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28717720508575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3089325428009</t>
+    <t xml:space="preserve">1.28717756271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30893230438232</t>
   </si>
   <si>
     <t xml:space="preserve">1.30530667304993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.412269115448</t>
+    <t xml:space="preserve">1.41226923465729</t>
   </si>
   <si>
     <t xml:space="preserve">1.37963652610779</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">1.35969436168671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34065854549408</t>
+    <t xml:space="preserve">1.34065842628479</t>
   </si>
   <si>
     <t xml:space="preserve">1.32343590259552</t>
@@ -593,61 +593,61 @@
     <t xml:space="preserve">1.35062980651855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32887446880341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26995468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19471788406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14395606517792</t>
+    <t xml:space="preserve">1.3288745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26995456218719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19471800327301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1439563035965</t>
   </si>
   <si>
     <t xml:space="preserve">1.2454799413681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25001239776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26814150810242</t>
+    <t xml:space="preserve">1.25001227855682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26814162731171</t>
   </si>
   <si>
     <t xml:space="preserve">1.23278951644897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24185407161713</t>
+    <t xml:space="preserve">1.24185431003571</t>
   </si>
   <si>
     <t xml:space="preserve">1.28173863887787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26451551914215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28264510631561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25091898441315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26904797554016</t>
+    <t xml:space="preserve">1.26451587677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28264498710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25091874599457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26904809474945</t>
   </si>
   <si>
     <t xml:space="preserve">1.33159399032593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29624211788177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28536427021027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31437110900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30983889102936</t>
+    <t xml:space="preserve">1.29624199867249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28536438941956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31437122821808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30983877182007</t>
   </si>
   <si>
     <t xml:space="preserve">1.31799697875977</t>
@@ -656,49 +656,49 @@
     <t xml:space="preserve">1.29896140098572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37782347202301</t>
+    <t xml:space="preserve">1.3778235912323</t>
   </si>
   <si>
     <t xml:space="preserve">1.33521997928619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26179623603821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31074547767639</t>
+    <t xml:space="preserve">1.2617963552475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3107453584671</t>
   </si>
   <si>
     <t xml:space="preserve">1.30711960792542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34247136116028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.294429063797</t>
+    <t xml:space="preserve">1.34247159957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29442918300629</t>
   </si>
   <si>
     <t xml:space="preserve">1.32434225082397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33884561061859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31165170669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27992570400238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30621302127838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31618404388428</t>
+    <t xml:space="preserve">1.33884572982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31165194511414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2799254655838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30621290206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31618416309357</t>
   </si>
   <si>
     <t xml:space="preserve">1.30349373817444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27720642089844</t>
+    <t xml:space="preserve">1.27720618247986</t>
   </si>
   <si>
     <t xml:space="preserve">1.26632857322693</t>
@@ -713,19 +713,19 @@
     <t xml:space="preserve">1.24910604953766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27539324760437</t>
+    <t xml:space="preserve">1.27539312839508</t>
   </si>
   <si>
     <t xml:space="preserve">1.25273168087006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34700393676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34972333908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29261612892151</t>
+    <t xml:space="preserve">1.34700381755829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34972321987152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29261600971222</t>
   </si>
   <si>
     <t xml:space="preserve">1.32978117465973</t>
@@ -737,55 +737,55 @@
     <t xml:space="preserve">1.22372496128082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22916376590729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2046891450882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22191214561462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21919250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2210054397583</t>
+    <t xml:space="preserve">1.229163646698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20468926429749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22191202640533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21919274330139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22100567817688</t>
   </si>
   <si>
     <t xml:space="preserve">1.21828615665436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22463142871857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21012806892395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18656003475189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17477607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17840170860291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15211451053619</t>
+    <t xml:space="preserve">1.22463119029999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21012794971466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18656015396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17477583885193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17840194702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1521143913269</t>
   </si>
   <si>
     <t xml:space="preserve">1.15845954418182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08594250679016</t>
+    <t xml:space="preserve">1.08594262599945</t>
   </si>
   <si>
     <t xml:space="preserve">1.10588479042053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07959723472595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10679125785828</t>
+    <t xml:space="preserve">1.07959735393524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10679113864899</t>
   </si>
   <si>
     <t xml:space="preserve">1.13217210769653</t>
@@ -797,34 +797,34 @@
     <t xml:space="preserve">1.22644436359406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23822820186615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24457359313965</t>
+    <t xml:space="preserve">1.23822832107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24457371234894</t>
   </si>
   <si>
     <t xml:space="preserve">1.2518253326416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24004113674164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20378279685974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20650207996368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24094772338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23097670078278</t>
+    <t xml:space="preserve">1.24004137516022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20378267765045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20650219917297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24094760417938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23097681999207</t>
   </si>
   <si>
     <t xml:space="preserve">1.21194088459015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23460245132446</t>
+    <t xml:space="preserve">1.23460233211517</t>
   </si>
   <si>
     <t xml:space="preserve">1.24638652801514</t>
@@ -833,97 +833,97 @@
     <t xml:space="preserve">1.2762998342514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27086091041565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29805493354797</t>
+    <t xml:space="preserve">1.27086102962494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29805481433868</t>
   </si>
   <si>
     <t xml:space="preserve">1.22553789615631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15574014186859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11857509613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1602725982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16661763191223</t>
+    <t xml:space="preserve">1.15574026107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11857521533966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16027247905731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16661775112152</t>
   </si>
   <si>
     <t xml:space="preserve">1.16480481624603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18112099170685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19925045967102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11676228046417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0931943655014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09772670269012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.176589012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17930829524994</t>
+    <t xml:space="preserve">1.18112111091614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19925034046173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11676239967346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09319424629211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09772658348083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17658865451813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17930817604065</t>
   </si>
   <si>
     <t xml:space="preserve">1.21375381946564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21556663513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28627097606659</t>
+    <t xml:space="preserve">1.21556675434113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2862708568573</t>
   </si>
   <si>
     <t xml:space="preserve">1.28989672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28445792198181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38960754871368</t>
+    <t xml:space="preserve">1.2844580411911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38960766792297</t>
   </si>
   <si>
     <t xml:space="preserve">1.40048515796661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41408205032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38235592842102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37057197093964</t>
+    <t xml:space="preserve">1.41408216953278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38235604763031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37057185173035</t>
   </si>
   <si>
     <t xml:space="preserve">1.32796823978424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36513304710388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3551619052887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38416886329651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42224025726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38054311275482</t>
+    <t xml:space="preserve">1.36513316631317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35516202449799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38416874408722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42224037647247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38054287433624</t>
   </si>
   <si>
     <t xml:space="preserve">1.38870108127594</t>
@@ -935,34 +935,34 @@
     <t xml:space="preserve">1.40773689746857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39957880973816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39685928821564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38326251506805</t>
+    <t xml:space="preserve">1.39957869052887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39685940742493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38326239585876</t>
   </si>
   <si>
     <t xml:space="preserve">1.38688838481903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50926077365875</t>
+    <t xml:space="preserve">1.50926065444946</t>
   </si>
   <si>
     <t xml:space="preserve">1.57724547386169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57271301746368</t>
+    <t xml:space="preserve">1.57271313667297</t>
   </si>
   <si>
     <t xml:space="preserve">1.54551935195923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55005156993866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51379311084747</t>
+    <t xml:space="preserve">1.55005145072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51379299163818</t>
   </si>
   <si>
     <t xml:space="preserve">1.48659908771515</t>
@@ -971,16 +971,16 @@
     <t xml:space="preserve">1.44580829143524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48206675052643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43221151828766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54098701477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52285778522491</t>
+    <t xml:space="preserve">1.48206686973572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43221139907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54098689556122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52285754680634</t>
   </si>
   <si>
     <t xml:space="preserve">1.52738988399506</t>
@@ -989,97 +989,97 @@
     <t xml:space="preserve">1.37329137325287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39142048358917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34609758853912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29170954227448</t>
+    <t xml:space="preserve">1.39142060279846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34609746932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29170966148376</t>
   </si>
   <si>
     <t xml:space="preserve">1.31890368461609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33703279495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27358055114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39595282077789</t>
+    <t xml:space="preserve">1.33703291416168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27358043193817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39595293998718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30077421665192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33341026306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31476104259491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30543661117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31942343711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24482715129852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24948930740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23084044456482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21219110488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25415170192719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23550260066986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22617793083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19354200363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19820415973663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2401647567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27280068397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29611206054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31009888648987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3287478685379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28212523460388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26813840866089</t>
   </si>
   <si>
     <t xml:space="preserve">1.30077433586121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33341038227081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31476104259491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30543649196625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31942343711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24482715129852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24948930740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23084032535553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21219098567963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25415146350861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23550248146057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22617793083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19354212284088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19820427894592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24016499519348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27280080318451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29611217975616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31009900569916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3287478685379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28212523460388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26813840866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30077409744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21685349941254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18887972831726</t>
+    <t xml:space="preserve">1.21685338020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18887984752655</t>
   </si>
   <si>
     <t xml:space="preserve">1.16556835174561</t>
@@ -1091,16 +1091,16 @@
     <t xml:space="preserve">1.17489290237427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17955529689789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20752882957458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32408559322357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34739696979523</t>
+    <t xml:space="preserve">1.1795551776886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20752894878387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32408583164215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34739708900452</t>
   </si>
   <si>
     <t xml:space="preserve">1.17023050785065</t>
@@ -1112,34 +1112,34 @@
     <t xml:space="preserve">1.13293254375458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25881385803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746284008026</t>
+    <t xml:space="preserve">1.25881397724152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746307849884</t>
   </si>
   <si>
     <t xml:space="preserve">1.22151553630829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15624392032623</t>
+    <t xml:space="preserve">1.15624356269836</t>
   </si>
   <si>
     <t xml:space="preserve">1.18421745300293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2867876291275</t>
+    <t xml:space="preserve">1.28678739070892</t>
   </si>
   <si>
     <t xml:space="preserve">1.16090607643127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1515816450119</t>
+    <t xml:space="preserve">1.15158140659332</t>
   </si>
   <si>
     <t xml:space="preserve">1.13759481906891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36138391494751</t>
+    <t xml:space="preserve">1.3613840341568</t>
   </si>
   <si>
     <t xml:space="preserve">1.29144978523254</t>
@@ -1151,43 +1151,43 @@
     <t xml:space="preserve">1.33807253837585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11428332328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10495889186859</t>
+    <t xml:space="preserve">1.11428356170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10495865345001</t>
   </si>
   <si>
     <t xml:space="preserve">1.14225709438324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27810597419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29230737686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37278056144714</t>
+    <t xml:space="preserve">1.27810609340668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29230725765228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37278068065643</t>
   </si>
   <si>
     <t xml:space="preserve">1.34437823295593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32544314861298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30177450180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55266213417053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4106502532959</t>
+    <t xml:space="preserve">1.32544326782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30177462100983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55266201496124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41065037250519</t>
   </si>
   <si>
     <t xml:space="preserve">1.31124210357666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31597590446472</t>
+    <t xml:space="preserve">1.31597578525543</t>
   </si>
   <si>
     <t xml:space="preserve">1.28757345676422</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">1.33964443206787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42011773586273</t>
+    <t xml:space="preserve">1.42011785507202</t>
   </si>
   <si>
     <t xml:space="preserve">1.40591669082642</t>
@@ -1208,28 +1208,28 @@
     <t xml:space="preserve">1.35384559631348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39644908905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32070958614349</t>
+    <t xml:space="preserve">1.39644920825958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32070970535278</t>
   </si>
   <si>
     <t xml:space="preserve">1.3349107503891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28283965587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27337229251862</t>
+    <t xml:space="preserve">1.28283977508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27337241172791</t>
   </si>
   <si>
     <t xml:space="preserve">1.26390480995178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25917100906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29704093933105</t>
+    <t xml:space="preserve">1.25917112827301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29704105854034</t>
   </si>
   <si>
     <t xml:space="preserve">1.2449699640274</t>
@@ -1241,25 +1241,25 @@
     <t xml:space="preserve">1.22130119800568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21656763553619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22603499889374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24023628234863</t>
+    <t xml:space="preserve">1.2165675163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22603511810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24023616313934</t>
   </si>
   <si>
     <t xml:space="preserve">1.21183383464813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26863873004913</t>
+    <t xml:space="preserve">1.26863861083984</t>
   </si>
   <si>
     <t xml:space="preserve">1.20710015296936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24970364570618</t>
+    <t xml:space="preserve">1.24970376491547</t>
   </si>
   <si>
     <t xml:space="preserve">1.25443756580353</t>
@@ -1268,16 +1268,16 @@
     <t xml:space="preserve">1.23550236225128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16923022270203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18343162536621</t>
+    <t xml:space="preserve">1.16923010349274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18343150615692</t>
   </si>
   <si>
     <t xml:space="preserve">1.20236647129059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14082813262939</t>
+    <t xml:space="preserve">1.1408280134201</t>
   </si>
   <si>
     <t xml:space="preserve">1.12189292907715</t>
@@ -1298,28 +1298,28 @@
     <t xml:space="preserve">0.989348649978638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979881286621094</t>
+    <t xml:space="preserve">0.979881167411804</t>
   </si>
   <si>
     <t xml:space="preserve">0.965680122375488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.914555847644806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937277793884277</t>
+    <t xml:space="preserve">0.914555907249451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937277734279633</t>
   </si>
   <si>
     <t xml:space="preserve">0.92023628950119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.880473017692566</t>
+    <t xml:space="preserve">0.880473077297211</t>
   </si>
   <si>
     <t xml:space="preserve">0.927810311317444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946745216846466</t>
+    <t xml:space="preserve">0.946745157241821</t>
   </si>
   <si>
     <t xml:space="preserve">0.95621258020401</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">1.04615342617035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03668594360352</t>
+    <t xml:space="preserve">1.03668606281281</t>
   </si>
   <si>
     <t xml:space="preserve">1.04141974449158</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">1.1124255657196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12662672996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08875715732574</t>
+    <t xml:space="preserve">1.1266268491745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08875703811646</t>
   </si>
   <si>
     <t xml:space="preserve">1.09822428226471</t>
@@ -1379,28 +1379,28 @@
     <t xml:space="preserve">1.03195226192474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02721869945526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17869782447815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15976297855377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15029537677765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16449666023254</t>
+    <t xml:space="preserve">1.02721858024597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17869770526886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15976285934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15029549598694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16449654102325</t>
   </si>
   <si>
     <t xml:space="preserve">1.15502917766571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14556157588959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17396402359009</t>
+    <t xml:space="preserve">1.14556169509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1739639043808</t>
   </si>
   <si>
     <t xml:space="preserve">1.13136065006256</t>
@@ -1412,13 +1412,13 @@
     <t xml:space="preserve">1.00828373432159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984614908695221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994082510471344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01301729679108</t>
+    <t xml:space="preserve">0.98461502790451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994082391262054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01301741600037</t>
   </si>
   <si>
     <t xml:space="preserve">1.18816518783569</t>
@@ -1433,19 +1433,16 @@
     <t xml:space="preserve">1.3633131980896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33027982711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31597578525543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32551193237305</t>
+    <t xml:space="preserve">1.33027994632721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32551181316376</t>
   </si>
   <si>
     <t xml:space="preserve">1.33981597423553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33504784107208</t>
+    <t xml:space="preserve">1.33504796028137</t>
   </si>
   <si>
     <t xml:space="preserve">1.36365604400635</t>
@@ -1463,7 +1460,7 @@
     <t xml:space="preserve">1.40180027484894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36842393875122</t>
+    <t xml:space="preserve">1.36842405796051</t>
   </si>
   <si>
     <t xml:space="preserve">1.34935200214386</t>
@@ -1472,37 +1469,37 @@
     <t xml:space="preserve">1.35888803005219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30167186260223</t>
+    <t xml:space="preserve">1.30167174339294</t>
   </si>
   <si>
     <t xml:space="preserve">1.3922643661499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38272821903229</t>
+    <t xml:space="preserve">1.38272833824158</t>
   </si>
   <si>
     <t xml:space="preserve">1.41133642196655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38749623298645</t>
+    <t xml:space="preserve">1.38749635219574</t>
   </si>
   <si>
     <t xml:space="preserve">1.37319219112396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4304084777832</t>
+    <t xml:space="preserve">1.43040859699249</t>
   </si>
   <si>
     <t xml:space="preserve">1.47808885574341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4447124004364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4065682888031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42087233066559</t>
+    <t xml:space="preserve">1.44471251964569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40656840801239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42087244987488</t>
   </si>
   <si>
     <t xml:space="preserve">1.43517661094666</t>
@@ -1511,13 +1508,13 @@
     <t xml:space="preserve">1.45901668071747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43994462490082</t>
+    <t xml:space="preserve">1.43994450569153</t>
   </si>
   <si>
     <t xml:space="preserve">1.41610443592072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.516233086586</t>
+    <t xml:space="preserve">1.51623296737671</t>
   </si>
   <si>
     <t xml:space="preserve">1.50669693946838</t>
@@ -1526,10 +1523,10 @@
     <t xml:space="preserve">1.53530502319336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54484117031097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54007315635681</t>
+    <t xml:space="preserve">1.54484105110168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54007303714752</t>
   </si>
   <si>
     <t xml:space="preserve">1.58298528194427</t>
@@ -1547,25 +1544,25 @@
     <t xml:space="preserve">1.70695412158966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7641704082489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74509835243225</t>
+    <t xml:space="preserve">1.76417052745819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74509847164154</t>
   </si>
   <si>
     <t xml:space="preserve">1.7260262966156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69741797447205</t>
+    <t xml:space="preserve">1.69741809368134</t>
   </si>
   <si>
     <t xml:space="preserve">1.66880989074707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67357790470123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64020180702209</t>
+    <t xml:space="preserve">1.67357802391052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64020168781281</t>
   </si>
   <si>
     <t xml:space="preserve">1.61159348487854</t>
@@ -1577,16 +1574,16 @@
     <t xml:space="preserve">1.64973783493042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71172201633453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64496982097626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61636161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62112963199615</t>
+    <t xml:space="preserve">1.71172213554382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64496970176697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6163614988327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62112951278687</t>
   </si>
   <si>
     <t xml:space="preserve">1.63066565990448</t>
@@ -1598,28 +1595,28 @@
     <t xml:space="preserve">1.77847468852997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75940239429474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68311393260956</t>
+    <t xml:space="preserve">1.75940251350403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68311405181885</t>
   </si>
   <si>
     <t xml:space="preserve">1.71649014949799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77370655536652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81185066699982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8261547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79754662513733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78801047801971</t>
+    <t xml:space="preserve">1.77370667457581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81185078620911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82615482807159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79754674434662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.788010597229</t>
   </si>
   <si>
     <t xml:space="preserve">1.81661880016327</t>
@@ -1631,10 +1628,10 @@
     <t xml:space="preserve">1.80708277225494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76893854141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73556232452393</t>
+    <t xml:space="preserve">1.76893866062164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73556244373322</t>
   </si>
   <si>
     <t xml:space="preserve">1.73079442977905</t>
@@ -1643,19 +1640,19 @@
     <t xml:space="preserve">1.74033033847809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72125816345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78324246406555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74986636638641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6783459186554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66404187679291</t>
+    <t xml:space="preserve">1.72125828266144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78324258327484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7498664855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67834603786469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66404175758362</t>
   </si>
   <si>
     <t xml:space="preserve">1.69265007972717</t>
@@ -1667,16 +1664,16 @@
     <t xml:space="preserve">1.75463449954987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79277861118317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56868135929108</t>
+    <t xml:space="preserve">1.79277873039246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5686811208725</t>
   </si>
   <si>
     <t xml:space="preserve">1.65927374362946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59252154827118</t>
+    <t xml:space="preserve">1.5925213098526</t>
   </si>
   <si>
     <t xml:space="preserve">1.52576899528503</t>
@@ -1691,13 +1688,13 @@
     <t xml:space="preserve">1.85953104496002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89767515659332</t>
+    <t xml:space="preserve">1.89767527580261</t>
   </si>
   <si>
     <t xml:space="preserve">1.92628335952759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82138681411743</t>
+    <t xml:space="preserve">1.82138693332672</t>
   </si>
   <si>
     <t xml:space="preserve">1.83569085597992</t>
@@ -1706,7 +1703,7 @@
     <t xml:space="preserve">1.86429905891418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90721142292023</t>
+    <t xml:space="preserve">1.90721130371094</t>
   </si>
   <si>
     <t xml:space="preserve">1.94535553455353</t>
@@ -1718,7 +1715,7 @@
     <t xml:space="preserve">2.0597882270813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00257205963135</t>
+    <t xml:space="preserve">2.00257182121277</t>
   </si>
   <si>
     <t xml:space="preserve">2.07886052131653</t>
@@ -1730,7 +1727,7 @@
     <t xml:space="preserve">2.10746836662292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08839631080627</t>
+    <t xml:space="preserve">2.08839654922485</t>
   </si>
   <si>
     <t xml:space="preserve">2.09793257713318</t>
@@ -1742,7 +1739,7 @@
     <t xml:space="preserve">2.27911758422852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19329309463501</t>
+    <t xml:space="preserve">2.19329285621643</t>
   </si>
   <si>
     <t xml:space="preserve">2.22190117835999</t>
@@ -1751,91 +1748,94 @@
     <t xml:space="preserve">2.25050926208496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02164387702942</t>
+    <t xml:space="preserve">2.02164363861084</t>
   </si>
   <si>
     <t xml:space="preserve">2.01210784912109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97396373748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98349952697754</t>
+    <t xml:space="preserve">1.97396349906921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98349976539612</t>
   </si>
   <si>
     <t xml:space="preserve">2.03118014335632</t>
   </si>
   <si>
+    <t xml:space="preserve">2.04071617126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09847211837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08884596824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10809803009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0022120475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95408189296722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03109002113342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0214638710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05996799468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94445586204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97333407402039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93482995033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85782170295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83856964111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82894372940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86744773387909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88669967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707376480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89632570743561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92520391941071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99258589744568</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.04071593284607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09847211837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08884620666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10809803009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00221180915833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95408177375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03108978271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02146410942078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05996799468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94445586204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97333383560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93482995033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85782170295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83856964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82894361019135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86744773387909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88669979572296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707364559174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89632570743561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92520391941071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99258589744568</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.05034208297729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11772441864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1562283039093</t>
+    <t xml:space="preserve">2.11772418022156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15622854232788</t>
   </si>
   <si>
     <t xml:space="preserve">2.20435833930969</t>
@@ -1859,13 +1859,13 @@
     <t xml:space="preserve">2.27174043655396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30061864852905</t>
+    <t xml:space="preserve">2.30061841011047</t>
   </si>
   <si>
     <t xml:space="preserve">2.2813663482666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18510627746582</t>
+    <t xml:space="preserve">2.1851065158844</t>
   </si>
   <si>
     <t xml:space="preserve">2.19473242759705</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">2.01183795928955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8722608089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96370792388916</t>
+    <t xml:space="preserve">1.87226068973541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96370780467987</t>
   </si>
   <si>
     <t xml:space="preserve">2.06959414482117</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">2.29099249839783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36800074577332</t>
+    <t xml:space="preserve">2.36800098419189</t>
   </si>
   <si>
     <t xml:space="preserve">2.38725280761719</t>
@@ -1934,10 +1934,10 @@
     <t xml:space="preserve">2.21398448944092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31987071037292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4450089931488</t>
+    <t xml:space="preserve">2.31987047195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44500875473022</t>
   </si>
   <si>
     <t xml:space="preserve">2.45463490486145</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">2.52201700210571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50276494026184</t>
+    <t xml:space="preserve">2.50276470184326</t>
   </si>
   <si>
     <t xml:space="preserve">2.59902501106262</t>
@@ -1967,16 +1967,16 @@
     <t xml:space="preserve">2.51239085197449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47388696670532</t>
+    <t xml:space="preserve">2.47388672828674</t>
   </si>
   <si>
     <t xml:space="preserve">2.48351287841797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53164291381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63752913475037</t>
+    <t xml:space="preserve">2.53164315223694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63752937316895</t>
   </si>
   <si>
     <t xml:space="preserve">2.69528532028198</t>
@@ -1988,10 +1988,10 @@
     <t xml:space="preserve">2.71453738212585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67603349685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60865116119385</t>
+    <t xml:space="preserve">2.67603325843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60865139961243</t>
   </si>
   <si>
     <t xml:space="preserve">2.66640734672546</t>
@@ -2003,10 +2003,10 @@
     <t xml:space="preserve">2.58939909934998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56052088737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6279034614563</t>
+    <t xml:space="preserve">2.56052112579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62790322303772</t>
   </si>
   <si>
     <t xml:space="preserve">2.55089521408081</t>
@@ -39090,7 +39090,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1395" t="s">
-        <v>474</v>
+        <v>391</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -39116,7 +39116,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1396" t="s">
-        <v>474</v>
+        <v>391</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -39142,7 +39142,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1397" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -39168,7 +39168,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1398" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -39194,7 +39194,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1399" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -39220,7 +39220,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1400" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -39246,7 +39246,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1401" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -39272,7 +39272,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1402" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39298,7 +39298,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1403" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39324,7 +39324,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1404" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39350,7 +39350,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1405" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39376,7 +39376,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1406" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39402,7 +39402,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1407" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39428,7 +39428,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1408" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39454,7 +39454,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1409" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39480,7 +39480,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1410" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39506,7 +39506,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1411" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39532,7 +39532,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1412" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39558,7 +39558,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1413" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39584,7 +39584,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1414" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39610,7 +39610,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1415" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39636,7 +39636,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1416" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39662,7 +39662,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1417" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39688,7 +39688,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1418" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39714,7 +39714,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1419" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39740,7 +39740,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1420" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39766,7 +39766,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1421" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39792,7 +39792,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1422" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39818,7 +39818,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1423" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39870,7 +39870,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1425" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39896,7 +39896,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1426" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39948,7 +39948,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1428" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39974,7 +39974,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1429" t="s">
-        <v>474</v>
+        <v>391</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -40000,7 +40000,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1430" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -40026,7 +40026,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1431" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -40052,7 +40052,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1432" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -40078,7 +40078,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1433" t="s">
-        <v>474</v>
+        <v>391</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -40104,7 +40104,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1434" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -40130,7 +40130,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1435" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -40156,7 +40156,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1436" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -40182,7 +40182,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1437" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -40208,7 +40208,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1438" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -40234,7 +40234,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1439" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -40260,7 +40260,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1440" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40286,7 +40286,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1441" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40312,7 +40312,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1442" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40338,7 +40338,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1443" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40364,7 +40364,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1444" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40390,7 +40390,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1445" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40416,7 +40416,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1446" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40442,7 +40442,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1447" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40468,7 +40468,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1448" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40494,7 +40494,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1449" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40520,7 +40520,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1450" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40546,7 +40546,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1451" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40572,7 +40572,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1452" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40598,7 +40598,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40624,7 +40624,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1454" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40650,7 +40650,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1455" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40676,7 +40676,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1456" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40702,7 +40702,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1457" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40728,7 +40728,7 @@
         <v>1.5</v>
       </c>
       <c r="G1458" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40754,7 +40754,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1459" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40780,7 +40780,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1460" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40806,7 +40806,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1461" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40832,7 +40832,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1462" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40858,7 +40858,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1463" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40884,7 +40884,7 @@
         <v>1.5</v>
       </c>
       <c r="G1464" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40910,7 +40910,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1465" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40936,7 +40936,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1466" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40962,7 +40962,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1467" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40988,7 +40988,7 @@
         <v>1.5</v>
       </c>
       <c r="G1468" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -41014,7 +41014,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1469" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -41040,7 +41040,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1470" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -41066,7 +41066,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1471" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -41092,7 +41092,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1472" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -41118,7 +41118,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1473" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -41144,7 +41144,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1474" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -41170,7 +41170,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1475" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -41196,7 +41196,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1476" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -41222,7 +41222,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1477" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -41248,7 +41248,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1478" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41274,7 +41274,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1479" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41300,7 +41300,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1480" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41326,7 +41326,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1481" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41352,7 +41352,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1482" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41378,7 +41378,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1483" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41404,7 +41404,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1484" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41430,7 +41430,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1485" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41456,7 +41456,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1486" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41482,7 +41482,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1487" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41508,7 +41508,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1488" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41534,7 +41534,7 @@
         <v>1.75</v>
       </c>
       <c r="G1489" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41560,7 +41560,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1490" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41586,7 +41586,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1491" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41612,7 +41612,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1492" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41638,7 +41638,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1493" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41664,7 +41664,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1494" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41690,7 +41690,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1495" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41716,7 +41716,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1496" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41742,7 +41742,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1497" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41768,7 +41768,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1498" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41794,7 +41794,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1499" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41820,7 +41820,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1500" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41846,7 +41846,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1501" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41872,7 +41872,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1502" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41898,7 +41898,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1503" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41924,7 +41924,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1504" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41950,7 +41950,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1505" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41976,7 +41976,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1506" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -42002,7 +42002,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1507" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -42028,7 +42028,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1508" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -42054,7 +42054,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1509" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -42080,7 +42080,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1510" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -42106,7 +42106,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1511" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -42132,7 +42132,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1512" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -42158,7 +42158,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1513" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -42184,7 +42184,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1514" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -42210,7 +42210,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1515" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -42236,7 +42236,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1516" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -42262,7 +42262,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1517" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42288,7 +42288,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1518" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42314,7 +42314,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1519" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42340,7 +42340,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1520" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42366,7 +42366,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1521" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42392,7 +42392,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1522" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42418,7 +42418,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1523" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42444,7 +42444,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1524" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42470,7 +42470,7 @@
         <v>1.875</v>
       </c>
       <c r="G1525" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42496,7 +42496,7 @@
         <v>1.875</v>
       </c>
       <c r="G1526" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42522,7 +42522,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1527" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42548,7 +42548,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1528" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42574,7 +42574,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1529" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42600,7 +42600,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1530" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42626,7 +42626,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1531" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42652,7 +42652,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1532" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42678,7 +42678,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1533" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42704,7 +42704,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1534" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42730,7 +42730,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1535" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42756,7 +42756,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1536" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42782,7 +42782,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1537" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42808,7 +42808,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1538" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42834,7 +42834,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1539" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42860,7 +42860,7 @@
         <v>1.875</v>
       </c>
       <c r="G1540" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42886,7 +42886,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1541" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42912,7 +42912,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1542" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42938,7 +42938,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1543" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42964,7 +42964,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1544" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42990,7 +42990,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1545" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -43016,7 +43016,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1546" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -43042,7 +43042,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1547" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -43068,7 +43068,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1548" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -43094,7 +43094,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1549" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -43120,7 +43120,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1550" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -43146,7 +43146,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1551" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -43172,7 +43172,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1552" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -43198,7 +43198,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1553" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -43224,7 +43224,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1554" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -43250,7 +43250,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1555" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -43276,7 +43276,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1556" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43302,7 +43302,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1557" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43328,7 +43328,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1558" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43354,7 +43354,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1559" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43380,7 +43380,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1560" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43406,7 +43406,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1561" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43432,7 +43432,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1562" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43458,7 +43458,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1563" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43484,7 +43484,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1564" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43510,7 +43510,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1565" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43536,7 +43536,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1566" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43562,7 +43562,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1567" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43588,7 +43588,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1568" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43614,7 +43614,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1569" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43640,7 +43640,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1570" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43666,7 +43666,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1571" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43692,7 +43692,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1572" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43718,7 +43718,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1573" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43744,7 +43744,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1574" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43770,7 +43770,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1575" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43796,7 +43796,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1576" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43822,7 +43822,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1577" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43848,7 +43848,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1578" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43874,7 +43874,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1579" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43900,7 +43900,7 @@
         <v>1.75</v>
       </c>
       <c r="G1580" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43926,7 +43926,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1581" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43952,7 +43952,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1582" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43978,7 +43978,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1583" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -44004,7 +44004,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1584" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -44030,7 +44030,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1585" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -44056,7 +44056,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1586" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -44082,7 +44082,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1587" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -44108,7 +44108,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1588" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -44134,7 +44134,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1589" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -44160,7 +44160,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1590" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -44186,7 +44186,7 @@
         <v>1.75</v>
       </c>
       <c r="G1591" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -44212,7 +44212,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1592" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -44238,7 +44238,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1593" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -44264,7 +44264,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1594" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44290,7 +44290,7 @@
         <v>1.75</v>
       </c>
       <c r="G1595" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44316,7 +44316,7 @@
         <v>1.75</v>
       </c>
       <c r="G1596" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44342,7 +44342,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1597" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44368,7 +44368,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1598" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44394,7 +44394,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1599" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44420,7 +44420,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1600" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44446,7 +44446,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1601" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44472,7 +44472,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1602" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44498,7 +44498,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1603" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44524,7 +44524,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1604" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44550,7 +44550,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1605" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44576,7 +44576,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1606" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44602,7 +44602,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1607" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44628,7 +44628,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1608" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44654,7 +44654,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1609" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44680,7 +44680,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1610" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44706,7 +44706,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1611" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44732,7 +44732,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1612" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44758,7 +44758,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1613" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44784,7 +44784,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1614" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44810,7 +44810,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1615" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44836,7 +44836,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1616" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44862,7 +44862,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1617" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44888,7 +44888,7 @@
         <v>2</v>
       </c>
       <c r="G1618" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44914,7 +44914,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1619" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44940,7 +44940,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1620" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44966,7 +44966,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1621" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44992,7 +44992,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1622" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -45018,7 +45018,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1623" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -45044,7 +45044,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1624" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -45070,7 +45070,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1625" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -45096,7 +45096,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -45122,7 +45122,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1627" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -45148,7 +45148,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1628" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -45174,7 +45174,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1629" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -45200,7 +45200,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1630" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -45226,7 +45226,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1631" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -45252,7 +45252,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1632" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -45278,7 +45278,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1633" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45304,7 +45304,7 @@
         <v>2.25</v>
       </c>
       <c r="G1634" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45330,7 +45330,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1635" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45356,7 +45356,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1636" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45382,7 +45382,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1637" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45408,7 +45408,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1638" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45434,7 +45434,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1639" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45460,7 +45460,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1640" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45486,7 +45486,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1641" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45512,7 +45512,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1642" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45538,7 +45538,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1643" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45564,7 +45564,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1644" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45590,7 +45590,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1645" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45616,7 +45616,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1646" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45642,7 +45642,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1647" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45668,7 +45668,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1648" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45694,7 +45694,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1649" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45720,7 +45720,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1650" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45746,7 +45746,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1651" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45772,7 +45772,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1652" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45798,7 +45798,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1653" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45824,7 +45824,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1654" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45850,7 +45850,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1655" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45876,7 +45876,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1656" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45902,7 +45902,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1657" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45928,7 +45928,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1658" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45954,7 +45954,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1659" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45980,7 +45980,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1660" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -46006,7 +46006,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1661" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -46032,7 +46032,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1662" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -46058,7 +46058,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1663" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -46084,7 +46084,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1664" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -46110,7 +46110,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1665" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -46136,7 +46136,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1666" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -46162,7 +46162,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1667" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -46188,7 +46188,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1668" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -46214,7 +46214,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1669" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -46240,7 +46240,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1670" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -46266,7 +46266,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1671" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -46292,7 +46292,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1672" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -46318,7 +46318,7 @@
         <v>2</v>
       </c>
       <c r="G1673" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -46344,7 +46344,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1674" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46370,7 +46370,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1675" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -46396,7 +46396,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1676" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -46422,7 +46422,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1677" t="s">
-        <v>584</v>
+        <v>604</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46474,7 +46474,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1679" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -46864,7 +46864,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1694" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46916,7 +46916,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1696" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -47358,7 +47358,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1713" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47436,7 +47436,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1716" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47462,7 +47462,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1717" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47488,7 +47488,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1718" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47540,7 +47540,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1720" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47566,7 +47566,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1721" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47592,7 +47592,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1722" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47644,7 +47644,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1724" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -48788,7 +48788,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1768" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48814,7 +48814,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1769" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48840,7 +48840,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1770" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48892,7 +48892,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1772" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48970,7 +48970,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1775" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48996,7 +48996,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1776" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -68556,7 +68556,7 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.6740393519</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>10000</v>

--- a/data/DGT.MI.xlsx
+++ b/data/DGT.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">DGT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05767059326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03047680854797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96702456474304</t>
+    <t xml:space="preserve">2.0576708316803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03047704696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96702444553375</t>
   </si>
   <si>
     <t xml:space="preserve">2.00509595870972</t>
@@ -59,19 +59,19 @@
     <t xml:space="preserve">2.04860615730286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99421834945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971475124359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94889545440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88544309139252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91444981098175</t>
+    <t xml:space="preserve">1.99421858787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971510887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94889533519745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88544285297394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91444969177246</t>
   </si>
   <si>
     <t xml:space="preserve">1.89632046222687</t>
@@ -80,40 +80,40 @@
     <t xml:space="preserve">1.8763781785965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97065043449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92714023590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93076598644257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8582489490509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80839359760284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82561635971069</t>
+    <t xml:space="preserve">1.97065031528473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92714011669159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93076610565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85824906826019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80839347839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82561612129211</t>
   </si>
   <si>
     <t xml:space="preserve">1.75128650665283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64704310894012</t>
+    <t xml:space="preserve">1.64704298973083</t>
   </si>
   <si>
     <t xml:space="preserve">1.75581860542297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71321487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68964695930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73134398460388</t>
+    <t xml:space="preserve">1.71321499347687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68964672088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73134410381317</t>
   </si>
   <si>
     <t xml:space="preserve">1.76760268211365</t>
@@ -125,19 +125,19 @@
     <t xml:space="preserve">1.7585381269455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81292581558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83105492591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7685090303421</t>
+    <t xml:space="preserve">1.81292593479156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83105504512787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76850914955139</t>
   </si>
   <si>
     <t xml:space="preserve">1.6751434803009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74947345256805</t>
+    <t xml:space="preserve">1.74947333335876</t>
   </si>
   <si>
     <t xml:space="preserve">1.69871151447296</t>
@@ -146,22 +146,22 @@
     <t xml:space="preserve">1.74766039848328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7077761888504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70868277549744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69508576393127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77666735649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7014307975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69055342674255</t>
+    <t xml:space="preserve">1.70777595043182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70868265628815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69508564472198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7766672372818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70143091678619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69055318832397</t>
   </si>
   <si>
     <t xml:space="preserve">1.73497009277344</t>
@@ -170,19 +170,19 @@
     <t xml:space="preserve">1.64069783687592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62982022762299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63163304328918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68692743778229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68602097034454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6733306646347</t>
+    <t xml:space="preserve">1.62982034683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63163316249847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68692767620087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68602120876312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67333054542542</t>
   </si>
   <si>
     <t xml:space="preserve">1.74040877819061</t>
@@ -194,19 +194,19 @@
     <t xml:space="preserve">1.75672519207001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68783390522003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64885604381561</t>
+    <t xml:space="preserve">1.68783402442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64885592460632</t>
   </si>
   <si>
     <t xml:space="preserve">1.64794945716858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68420815467834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72137308120728</t>
+    <t xml:space="preserve">1.68420803546906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72137320041656</t>
   </si>
   <si>
     <t xml:space="preserve">1.72227954864502</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">1.67786276340485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6325398683548</t>
+    <t xml:space="preserve">1.63253962993622</t>
   </si>
   <si>
     <t xml:space="preserve">1.66335940361023</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">1.81111299991608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79026436805725</t>
+    <t xml:space="preserve">1.79026412963867</t>
   </si>
   <si>
     <t xml:space="preserve">1.78754484653473</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">1.78935790061951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66154646873474</t>
+    <t xml:space="preserve">1.66154634952545</t>
   </si>
   <si>
     <t xml:space="preserve">1.69961798191071</t>
@@ -251,28 +251,28 @@
     <t xml:space="preserve">1.68330156803131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65882730484009</t>
+    <t xml:space="preserve">1.65882706642151</t>
   </si>
   <si>
     <t xml:space="preserve">1.60353291034698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56908714771271</t>
+    <t xml:space="preserve">1.569087266922</t>
   </si>
   <si>
     <t xml:space="preserve">1.58902943134308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48297333717346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49566376209259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4920380115509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53192222118378</t>
+    <t xml:space="preserve">1.48297345638275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49566388130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49203789234161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53192234039307</t>
   </si>
   <si>
     <t xml:space="preserve">1.48387980461121</t>
@@ -281,22 +281,22 @@
     <t xml:space="preserve">1.45215368270874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4856926202774</t>
+    <t xml:space="preserve">1.48569285869598</t>
   </si>
   <si>
     <t xml:space="preserve">1.4285854101181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45940542221069</t>
+    <t xml:space="preserve">1.45940518379211</t>
   </si>
   <si>
     <t xml:space="preserve">1.49294435977936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46031165122986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44127607345581</t>
+    <t xml:space="preserve">1.46031177043915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4412761926651</t>
   </si>
   <si>
     <t xml:space="preserve">1.45034062862396</t>
@@ -305,16 +305,16 @@
     <t xml:space="preserve">1.46846997737885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42586600780487</t>
+    <t xml:space="preserve">1.42586612701416</t>
   </si>
   <si>
     <t xml:space="preserve">1.31255829334259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36422646045685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3415652513504</t>
+    <t xml:space="preserve">1.36422657966614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34156513214111</t>
   </si>
   <si>
     <t xml:space="preserve">1.36875903606415</t>
@@ -323,25 +323,25 @@
     <t xml:space="preserve">1.33250045776367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27811288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1965309381485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17296302318573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18746650218964</t>
+    <t xml:space="preserve">1.2781126499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19653105735779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17296290397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18746638298035</t>
   </si>
   <si>
     <t xml:space="preserve">1.17568242549896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15483379364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09863328933716</t>
+    <t xml:space="preserve">1.15483391284943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09863305091858</t>
   </si>
   <si>
     <t xml:space="preserve">1.12401401996613</t>
@@ -353,22 +353,22 @@
     <t xml:space="preserve">1.12582695484161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11313652992249</t>
+    <t xml:space="preserve">1.1131364107132</t>
   </si>
   <si>
     <t xml:space="preserve">1.06962633132935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08684897422791</t>
+    <t xml:space="preserve">1.08684909343719</t>
   </si>
   <si>
     <t xml:space="preserve">1.0950071811676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09410059452057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12038815021515</t>
+    <t xml:space="preserve">1.09410083293915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12038826942444</t>
   </si>
   <si>
     <t xml:space="preserve">1.09228789806366</t>
@@ -377,43 +377,43 @@
     <t xml:space="preserve">1.10769760608673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10951054096222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1212944984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0968199968338</t>
+    <t xml:space="preserve">1.10951066017151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12129461765289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09682023525238</t>
   </si>
   <si>
     <t xml:space="preserve">1.08956837654114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08866190910339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07234561443329</t>
+    <t xml:space="preserve">1.0886617898941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.072345495224</t>
   </si>
   <si>
     <t xml:space="preserve">1.05149686336517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12310767173767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10135245323181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08322298526764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08775568008423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11404299736023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15120780467987</t>
+    <t xml:space="preserve">1.12310755252838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10135233402252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08322322368622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08775556087494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11404287815094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15120792388916</t>
   </si>
   <si>
     <t xml:space="preserve">1.21466028690338</t>
@@ -425,22 +425,22 @@
     <t xml:space="preserve">1.1457691192627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12220108509064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06237459182739</t>
+    <t xml:space="preserve">1.12220120429993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06237471103668</t>
   </si>
   <si>
     <t xml:space="preserve">1.03336763381958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.934563398361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945440769195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977166950702667</t>
+    <t xml:space="preserve">0.934563338756561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945440828800201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977167010307312</t>
   </si>
   <si>
     <t xml:space="preserve">0.956318438053131</t>
@@ -449,10 +449,10 @@
     <t xml:space="preserve">0.933656752109528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01523840427399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04877758026123</t>
+    <t xml:space="preserve">1.01523852348328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04877746105194</t>
   </si>
   <si>
     <t xml:space="preserve">1.0360871553421</t>
@@ -461,67 +461,67 @@
     <t xml:space="preserve">1.02430307865143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990764021873474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05059051513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11494934558868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12854623794556</t>
+    <t xml:space="preserve">0.990764141082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05059063434601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11494946479797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12854647636414</t>
   </si>
   <si>
     <t xml:space="preserve">1.07506501674652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06418752670288</t>
+    <t xml:space="preserve">1.06418764591217</t>
   </si>
   <si>
     <t xml:space="preserve">1.02067732810974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997109174728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00617384910583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988044679164886</t>
+    <t xml:space="preserve">0.997109293937683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00617372989655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988044619560242</t>
   </si>
   <si>
     <t xml:space="preserve">1.03880655765533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05965518951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0424325466156</t>
+    <t xml:space="preserve">1.05965507030487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04243218898773</t>
   </si>
   <si>
     <t xml:space="preserve">1.06328105926514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05693578720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10407185554504</t>
+    <t xml:space="preserve">1.05693566799164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10407197475433</t>
   </si>
   <si>
     <t xml:space="preserve">1.1049782037735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07597148418427</t>
+    <t xml:space="preserve">1.07597136497498</t>
   </si>
   <si>
     <t xml:space="preserve">1.12492048740387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10316526889801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21103429794312</t>
+    <t xml:space="preserve">1.1031653881073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21103453636169</t>
   </si>
   <si>
     <t xml:space="preserve">1.19562470912933</t>
@@ -530,22 +530,22 @@
     <t xml:space="preserve">1.21284747123718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14667534828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1539272069931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20559573173523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20196986198425</t>
+    <t xml:space="preserve">1.14667558670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15392732620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20559561252594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20196962356567</t>
   </si>
   <si>
     <t xml:space="preserve">1.23188292980194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2536381483078</t>
+    <t xml:space="preserve">1.25363826751709</t>
   </si>
   <si>
     <t xml:space="preserve">1.25817060470581</t>
@@ -557,10 +557,10 @@
     <t xml:space="preserve">1.25545120239258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28717732429504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3089325428009</t>
+    <t xml:space="preserve">1.28717744350433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30893242359161</t>
   </si>
   <si>
     <t xml:space="preserve">1.30530667304993</t>
@@ -578,34 +578,34 @@
     <t xml:space="preserve">1.35244274139404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35697495937347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35969460010529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34065878391266</t>
+    <t xml:space="preserve">1.35697507858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35969436168671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34065866470337</t>
   </si>
   <si>
     <t xml:space="preserve">1.32343590259552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35062980651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32887446880341</t>
+    <t xml:space="preserve">1.35062968730927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3288745880127</t>
   </si>
   <si>
     <t xml:space="preserve">1.26995456218719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1947181224823</t>
+    <t xml:space="preserve">1.19471824169159</t>
   </si>
   <si>
     <t xml:space="preserve">1.14395606517792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2454799413681</t>
+    <t xml:space="preserve">1.24548006057739</t>
   </si>
   <si>
     <t xml:space="preserve">1.25001227855682</t>
@@ -614,40 +614,40 @@
     <t xml:space="preserve">1.26814162731171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23278951644897</t>
+    <t xml:space="preserve">1.23278939723969</t>
   </si>
   <si>
     <t xml:space="preserve">1.24185431003571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28173840045929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26451551914215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28264486789703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25091874599457</t>
+    <t xml:space="preserve">1.28173863887787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26451575756073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28264510631561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25091862678528</t>
   </si>
   <si>
     <t xml:space="preserve">1.26904821395874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33159399032593</t>
+    <t xml:space="preserve">1.33159387111664</t>
   </si>
   <si>
     <t xml:space="preserve">1.2962418794632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28536438941956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31437122821808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30983901023865</t>
+    <t xml:space="preserve">1.28536450862885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31437134742737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30983889102936</t>
   </si>
   <si>
     <t xml:space="preserve">1.31799697875977</t>
@@ -659,40 +659,40 @@
     <t xml:space="preserve">1.37782371044159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3352198600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2617963552475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31074523925781</t>
+    <t xml:space="preserve">1.33521997928619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26179623603821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31074547767639</t>
   </si>
   <si>
     <t xml:space="preserve">1.30711936950684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34247136116028</t>
+    <t xml:space="preserve">1.34247159957886</t>
   </si>
   <si>
     <t xml:space="preserve">1.294429063797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32434225082397</t>
+    <t xml:space="preserve">1.32434237003326</t>
   </si>
   <si>
     <t xml:space="preserve">1.33884572982788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31165194511414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27992570400238</t>
+    <t xml:space="preserve">1.31165206432343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27992558479309</t>
   </si>
   <si>
     <t xml:space="preserve">1.30621302127838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31618428230286</t>
+    <t xml:space="preserve">1.31618404388428</t>
   </si>
   <si>
     <t xml:space="preserve">1.30349361896515</t>
@@ -701,43 +701,43 @@
     <t xml:space="preserve">1.27720642089844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26632881164551</t>
+    <t xml:space="preserve">1.26632869243622</t>
   </si>
   <si>
     <t xml:space="preserve">1.28355145454407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25907707214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24910593032837</t>
+    <t xml:space="preserve">1.25907695293427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24910581111908</t>
   </si>
   <si>
     <t xml:space="preserve">1.27539324760437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25273168087006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34700381755829</t>
+    <t xml:space="preserve">1.25273191928864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34700393676758</t>
   </si>
   <si>
     <t xml:space="preserve">1.34972321987152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29261612892151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32978117465973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23369610309601</t>
+    <t xml:space="preserve">1.29261600971222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32978093624115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23369598388672</t>
   </si>
   <si>
     <t xml:space="preserve">1.22372496128082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22916352748871</t>
+    <t xml:space="preserve">1.22916376590729</t>
   </si>
   <si>
     <t xml:space="preserve">1.2046891450882</t>
@@ -755,28 +755,28 @@
     <t xml:space="preserve">1.21828603744507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22463142871857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21012806892395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1865599155426</t>
+    <t xml:space="preserve">1.22463130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21012794971466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18656003475189</t>
   </si>
   <si>
     <t xml:space="preserve">1.17477595806122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17840182781219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15211451053619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15845966339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08594238758087</t>
+    <t xml:space="preserve">1.17840170860291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1521143913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15845954418182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08594250679016</t>
   </si>
   <si>
     <t xml:space="preserve">1.10588479042053</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">1.07959735393524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10679125785828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13217198848724</t>
+    <t xml:space="preserve">1.10679113864899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13217210769653</t>
   </si>
   <si>
     <t xml:space="preserve">1.16933727264404</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">1.22644424438477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23822844028473</t>
+    <t xml:space="preserve">1.23822832107544</t>
   </si>
   <si>
     <t xml:space="preserve">1.24457359313965</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">1.25182545185089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24004125595093</t>
+    <t xml:space="preserve">1.24004137516022</t>
   </si>
   <si>
     <t xml:space="preserve">1.20378267765045</t>
@@ -815,31 +815,31 @@
     <t xml:space="preserve">1.20650219917297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24094784259796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23097681999207</t>
+    <t xml:space="preserve">1.24094772338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23097658157349</t>
   </si>
   <si>
     <t xml:space="preserve">1.21194100379944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23460245132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24638628959656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2762998342514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27086091041565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29805505275726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22553777694702</t>
+    <t xml:space="preserve">1.23460233211517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24638652801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27629971504211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27086102962494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29805493354797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22553789615631</t>
   </si>
   <si>
     <t xml:space="preserve">1.15574026107788</t>
@@ -848,88 +848,88 @@
     <t xml:space="preserve">1.11857509613037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16027271747589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16661787033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16480457782745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18112123012543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19925045967102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11676251888275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09319424629211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09772658348083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17658889293671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17930829524994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21375393867493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21556675434113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2862708568573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28989660739899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2844580411911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38960754871368</t>
+    <t xml:space="preserve">1.16027247905731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16661763191223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16480469703674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18112111091614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19925034046173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11676228046417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0931943655014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09772670269012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17658877372742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17930817604065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21375381946564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21556663513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28627097606659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28989672660828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28445792198181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38960766792297</t>
   </si>
   <si>
     <t xml:space="preserve">1.4004852771759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4140819311142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38235580921173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37057185173035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32796835899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36513328552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35516214370728</t>
+    <t xml:space="preserve">1.41408216953278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38235604763031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37057197093964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32796823978424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36513316631317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35516226291656</t>
   </si>
   <si>
     <t xml:space="preserve">1.38416886329651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42224037647247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38054311275482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38870096206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36694610118866</t>
+    <t xml:space="preserve">1.42224025726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38054299354553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38870120048523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36694598197937</t>
   </si>
   <si>
     <t xml:space="preserve">1.40773677825928</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">1.38326239585876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38688814640045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50926089286804</t>
+    <t xml:space="preserve">1.38688826560974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50926077365875</t>
   </si>
   <si>
     <t xml:space="preserve">1.57724547386169</t>
@@ -962,16 +962,16 @@
     <t xml:space="preserve">1.55005156993866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51379287242889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48659908771515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44580829143524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48206675052643</t>
+    <t xml:space="preserve">1.51379311084747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48659932613373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44580841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48206686973572</t>
   </si>
   <si>
     <t xml:space="preserve">1.43221127986908</t>
@@ -986,49 +986,49 @@
     <t xml:space="preserve">1.52739000320435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37329137325287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39142060279846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34609723091125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29170966148376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31890368461609</t>
+    <t xml:space="preserve">1.37329125404358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39142048358917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34609735012054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29170954227448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3189035654068</t>
   </si>
   <si>
     <t xml:space="preserve">1.33703279495239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27358043193817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39595282077789</t>
+    <t xml:space="preserve">1.27358019351959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39595293998718</t>
   </si>
   <si>
     <t xml:space="preserve">1.30077421665192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33341014385223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3147611618042</t>
+    <t xml:space="preserve">1.33341026306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31476104259491</t>
   </si>
   <si>
     <t xml:space="preserve">1.30543661117554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31942319869995</t>
+    <t xml:space="preserve">1.31942343711853</t>
   </si>
   <si>
     <t xml:space="preserve">1.24482703208923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24948942661285</t>
+    <t xml:space="preserve">1.24948930740356</t>
   </si>
   <si>
     <t xml:space="preserve">1.23084020614624</t>
@@ -1040,10 +1040,10 @@
     <t xml:space="preserve">1.2541515827179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23550260066986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2261780500412</t>
+    <t xml:space="preserve">1.23550248146057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22617793083191</t>
   </si>
   <si>
     <t xml:space="preserve">1.19354212284088</t>
@@ -1058,34 +1058,34 @@
     <t xml:space="preserve">1.27280068397522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29611206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31009888648987</t>
+    <t xml:space="preserve">1.29611217975616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31009900569916</t>
   </si>
   <si>
     <t xml:space="preserve">1.32874798774719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28212511539459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26813840866089</t>
+    <t xml:space="preserve">1.28212523460388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26813852787018</t>
   </si>
   <si>
     <t xml:space="preserve">1.21685326099396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18887984752655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16556835174561</t>
+    <t xml:space="preserve">1.18887972831726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1655684709549</t>
   </si>
   <si>
     <t xml:space="preserve">1.20286655426025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17489314079285</t>
+    <t xml:space="preserve">1.17489302158356</t>
   </si>
   <si>
     <t xml:space="preserve">1.1795551776886</t>
@@ -1094,34 +1094,34 @@
     <t xml:space="preserve">1.20752882957458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32408571243286</t>
+    <t xml:space="preserve">1.32408559322357</t>
   </si>
   <si>
     <t xml:space="preserve">1.34739708900452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17023062705994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14691925048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13293266296387</t>
+    <t xml:space="preserve">1.17023050785065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14691936969757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13293242454529</t>
   </si>
   <si>
     <t xml:space="preserve">1.25881385803223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27746295928955</t>
+    <t xml:space="preserve">1.27746284008026</t>
   </si>
   <si>
     <t xml:space="preserve">1.22151553630829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15624392032623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18421733379364</t>
+    <t xml:space="preserve">1.15624368190765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18421745300293</t>
   </si>
   <si>
     <t xml:space="preserve">1.28678739070892</t>
@@ -1133,31 +1133,31 @@
     <t xml:space="preserve">1.1515816450119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13759469985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36138391494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29144990444183</t>
+    <t xml:space="preserve">1.13759481906891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36138379573822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29144978523254</t>
   </si>
   <si>
     <t xml:space="preserve">1.34273481369019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33807241916656</t>
+    <t xml:space="preserve">1.33807253837585</t>
   </si>
   <si>
     <t xml:space="preserve">1.11428332328796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1049587726593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14225709438324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27810597419739</t>
+    <t xml:space="preserve">1.10495865345001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14225697517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27810621261597</t>
   </si>
   <si>
     <t xml:space="preserve">1.29230725765228</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">1.37278068065643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34437811374664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32544338703156</t>
+    <t xml:space="preserve">1.34437823295593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32544326782227</t>
   </si>
   <si>
     <t xml:space="preserve">1.30177462100983</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">1.41065037250519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31124210357666</t>
+    <t xml:space="preserve">1.31124222278595</t>
   </si>
   <si>
     <t xml:space="preserve">1.31597578525543</t>
@@ -1190,40 +1190,40 @@
     <t xml:space="preserve">1.28757357597351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3065083026886</t>
+    <t xml:space="preserve">1.30650842189789</t>
   </si>
   <si>
     <t xml:space="preserve">1.33964455127716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42011797428131</t>
+    <t xml:space="preserve">1.42011785507202</t>
   </si>
   <si>
     <t xml:space="preserve">1.40591669082642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35384559631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39644908905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3207094669342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3349107503891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28283977508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27337229251862</t>
+    <t xml:space="preserve">1.35384571552277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39644920825958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32070958614349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33491086959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28283989429474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27337241172791</t>
   </si>
   <si>
     <t xml:space="preserve">1.26390469074249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25917112827301</t>
+    <t xml:space="preserve">1.25917100906372</t>
   </si>
   <si>
     <t xml:space="preserve">1.29704105854034</t>
@@ -1232,16 +1232,16 @@
     <t xml:space="preserve">1.2449699640274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23076856136322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22130119800568</t>
+    <t xml:space="preserve">1.23076868057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22130131721497</t>
   </si>
   <si>
     <t xml:space="preserve">1.2165675163269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22603487968445</t>
+    <t xml:space="preserve">1.22603499889374</t>
   </si>
   <si>
     <t xml:space="preserve">1.24023616313934</t>
@@ -1250,34 +1250,34 @@
     <t xml:space="preserve">1.21183383464813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26863861083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20710015296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24970364570618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25443756580353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23550248146057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16923034191132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18343138694763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2023663520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1408280134201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12189316749573</t>
+    <t xml:space="preserve">1.26863849163055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20710003376007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24970352649689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25443744659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23550236225128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16923022270203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18343150615692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20236623287201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14082789421082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12189304828644</t>
   </si>
   <si>
     <t xml:space="preserve">1.11715936660767</t>
@@ -1286,16 +1286,16 @@
     <t xml:space="preserve">1.10295820236206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06982207298279</t>
+    <t xml:space="preserve">1.0698219537735</t>
   </si>
   <si>
     <t xml:space="preserve">1.01775109767914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989348709583282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979881167411804</t>
+    <t xml:space="preserve">0.989348649978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979881286621094</t>
   </si>
   <si>
     <t xml:space="preserve">0.965680062770844</t>
@@ -1307,10 +1307,10 @@
     <t xml:space="preserve">0.937277793884277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92023640871048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880473077297211</t>
+    <t xml:space="preserve">0.920236349105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880473017692566</t>
   </si>
   <si>
     <t xml:space="preserve">0.927810251712799</t>
@@ -1319,25 +1319,25 @@
     <t xml:space="preserve">0.946745216846466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.956212639808655</t>
+    <t xml:space="preserve">0.95621258020401</t>
   </si>
   <si>
     <t xml:space="preserve">1.02248477935791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07928955554962</t>
+    <t xml:space="preserve">1.07928943634033</t>
   </si>
   <si>
     <t xml:space="preserve">1.10769188404083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13609433174133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05562078952789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09349071979523</t>
+    <t xml:space="preserve">1.13609421253204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05562090873718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09349060058594</t>
   </si>
   <si>
     <t xml:space="preserve">1.06035459041595</t>
@@ -1346,10 +1346,10 @@
     <t xml:space="preserve">1.06508839130402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07455587387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04615354537964</t>
+    <t xml:space="preserve">1.07455575466156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04615342617035</t>
   </si>
   <si>
     <t xml:space="preserve">1.03668606281281</t>
@@ -1358,25 +1358,25 @@
     <t xml:space="preserve">1.04141974449158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1124255657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12662696838379</t>
+    <t xml:space="preserve">1.11242544651031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12662672996521</t>
   </si>
   <si>
     <t xml:space="preserve">1.08875703811646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09822428226471</t>
+    <t xml:space="preserve">1.098224401474</t>
   </si>
   <si>
     <t xml:space="preserve">1.05088722705841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03195238113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02721858024597</t>
+    <t xml:space="preserve">1.03195226192474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02721846103668</t>
   </si>
   <si>
     <t xml:space="preserve">1.17869770526886</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">1.15976285934448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15029549598694</t>
+    <t xml:space="preserve">1.15029537677765</t>
   </si>
   <si>
     <t xml:space="preserve">1.16449666023254</t>
@@ -1394,37 +1394,37 @@
     <t xml:space="preserve">1.15502917766571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14556169509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1739639043808</t>
+    <t xml:space="preserve">1.14556157588959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17396402359009</t>
   </si>
   <si>
     <t xml:space="preserve">1.13136053085327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08402335643768</t>
+    <t xml:space="preserve">1.0840231180191</t>
   </si>
   <si>
     <t xml:space="preserve">1.00828373432159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98461502790451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994082450866699</t>
+    <t xml:space="preserve">0.984615087509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994082391262054</t>
   </si>
   <si>
     <t xml:space="preserve">1.01301729679108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1881650686264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33017706871033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40118300914764</t>
+    <t xml:space="preserve">1.18816518783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33017694950104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40118312835693</t>
   </si>
   <si>
     <t xml:space="preserve">1.3633131980896</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">1.33981597423553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33504796028137</t>
+    <t xml:space="preserve">1.33504784107208</t>
   </si>
   <si>
     <t xml:space="preserve">1.36365604400635</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">1.32074379920959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35411989688873</t>
+    <t xml:space="preserve">1.35412001609802</t>
   </si>
   <si>
     <t xml:space="preserve">1.3445839881897</t>
@@ -1466,13 +1466,13 @@
     <t xml:space="preserve">1.34935212135315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3588879108429</t>
+    <t xml:space="preserve">1.35888803005219</t>
   </si>
   <si>
     <t xml:space="preserve">1.30167174339294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3922643661499</t>
+    <t xml:space="preserve">1.39226424694061</t>
   </si>
   <si>
     <t xml:space="preserve">1.38272833824158</t>
@@ -1481,16 +1481,16 @@
     <t xml:space="preserve">1.41133642196655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38749635219574</t>
+    <t xml:space="preserve">1.38749623298645</t>
   </si>
   <si>
     <t xml:space="preserve">1.37319219112396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43040859699249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47808885574341</t>
+    <t xml:space="preserve">1.4304084777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47808873653412</t>
   </si>
   <si>
     <t xml:space="preserve">1.44471251964569</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">1.4065682888031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42087244987488</t>
+    <t xml:space="preserve">1.42087233066559</t>
   </si>
   <si>
     <t xml:space="preserve">1.43517661094666</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">1.45901668071747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43994450569153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41610443592072</t>
+    <t xml:space="preserve">1.43994462490082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41610431671143</t>
   </si>
   <si>
     <t xml:space="preserve">1.516233086586</t>
@@ -1520,13 +1520,13 @@
     <t xml:space="preserve">1.50669693946838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53530502319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54484117031097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54007303714752</t>
+    <t xml:space="preserve">1.53530514240265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54484128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54007315635681</t>
   </si>
   <si>
     <t xml:space="preserve">1.58298528194427</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">1.65450572967529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70695412158966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76417052745819</t>
+    <t xml:space="preserve">1.70695400238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7641704082489</t>
   </si>
   <si>
     <t xml:space="preserve">1.74509835243225</t>
@@ -1571,19 +1571,19 @@
     <t xml:space="preserve">1.60682547092438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64973783493042</t>
+    <t xml:space="preserve">1.64973795413971</t>
   </si>
   <si>
     <t xml:space="preserve">1.71172213554382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64496970176697</t>
+    <t xml:space="preserve">1.64496982097626</t>
   </si>
   <si>
     <t xml:space="preserve">1.6163614988327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62112963199615</t>
+    <t xml:space="preserve">1.62112975120544</t>
   </si>
   <si>
     <t xml:space="preserve">1.63066565990448</t>
@@ -1595,10 +1595,10 @@
     <t xml:space="preserve">1.77847456932068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75940251350403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68311405181885</t>
+    <t xml:space="preserve">1.75940239429474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68311393260956</t>
   </si>
   <si>
     <t xml:space="preserve">1.71649014949799</t>
@@ -1613,10 +1613,10 @@
     <t xml:space="preserve">1.82615482807159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79754674434662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.788010597229</t>
+    <t xml:space="preserve">1.79754662513733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78801047801971</t>
   </si>
   <si>
     <t xml:space="preserve">1.81661880016327</t>
@@ -1628,13 +1628,13 @@
     <t xml:space="preserve">1.80708277225494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76893866062164</t>
+    <t xml:space="preserve">1.76893854141235</t>
   </si>
   <si>
     <t xml:space="preserve">1.73556232452393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73079431056976</t>
+    <t xml:space="preserve">1.73079442977905</t>
   </si>
   <si>
     <t xml:space="preserve">1.74033033847809</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">1.74986636638641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67834603786469</t>
+    <t xml:space="preserve">1.6783459186554</t>
   </si>
   <si>
     <t xml:space="preserve">1.66404187679291</t>
@@ -1664,10 +1664,10 @@
     <t xml:space="preserve">1.75463449954987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79277861118317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5686811208725</t>
+    <t xml:space="preserve">1.79277849197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56868124008179</t>
   </si>
   <si>
     <t xml:space="preserve">1.65927374362946</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">1.59252142906189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52576887607574</t>
+    <t xml:space="preserve">1.52576899528503</t>
   </si>
   <si>
     <t xml:space="preserve">1.59728944301605</t>
@@ -1685,10 +1685,10 @@
     <t xml:space="preserve">1.70218598842621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85953104496002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89767515659332</t>
+    <t xml:space="preserve">1.85953116416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89767527580261</t>
   </si>
   <si>
     <t xml:space="preserve">1.92628335952759</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">1.86429905891418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90721130371094</t>
+    <t xml:space="preserve">1.90721142292023</t>
   </si>
   <si>
     <t xml:space="preserve">1.94535541534424</t>
@@ -1721,22 +1721,22 @@
     <t xml:space="preserve">2.07886052131653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12654042243958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1074686050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08839654922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09793257713318</t>
+    <t xml:space="preserve">2.12654066085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10746836662292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08839631080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0979323387146</t>
   </si>
   <si>
     <t xml:space="preserve">2.1456127166748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27911758422852</t>
+    <t xml:space="preserve">2.27911734580994</t>
   </si>
   <si>
     <t xml:space="preserve">2.19329309463501</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">2.22190117835999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25050950050354</t>
+    <t xml:space="preserve">2.25050926208496</t>
   </si>
   <si>
     <t xml:space="preserve">2.02164387702942</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">2.01210808753967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97396349906921</t>
+    <t xml:space="preserve">1.97396373748779</t>
   </si>
   <si>
     <t xml:space="preserve">1.98349976539612</t>
@@ -68605,7 +68605,7 @@
     </row>
     <row r="2531">
       <c r="A2531" s="1" t="n">
-        <v>46002.6586458333</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B2531" t="n">
         <v>13500</v>
@@ -68626,6 +68626,32 @@
         <v>798</v>
       </c>
       <c r="H2531" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" s="1" t="n">
+        <v>46003.6766203704</v>
+      </c>
+      <c r="B2532" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C2532" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2532" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="E2532" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2532" t="n">
+        <v>1.96000003814697</v>
+      </c>
+      <c r="G2532" t="s">
+        <v>814</v>
+      </c>
+      <c r="H2532" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DGT.MI.xlsx
+++ b/data/DGT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08123874664307</t>
+    <t xml:space="preserve">2.08123898506165</t>
   </si>
   <si>
     <t xml:space="preserve">DGT.MI</t>
@@ -50,49 +50,49 @@
     <t xml:space="preserve">2.03047680854797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96702480316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00509595870972</t>
+    <t xml:space="preserve">1.96702456474304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00509572029114</t>
   </si>
   <si>
     <t xml:space="preserve">2.04860639572144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99421846866608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94889521598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88544285297394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91444945335388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89632022380829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8763781785965</t>
+    <t xml:space="preserve">1.99421834945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971510887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94889557361603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88544297218323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91444957256317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89632046222687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87637829780579</t>
   </si>
   <si>
     <t xml:space="preserve">1.97065031528473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92714011669159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93076622486115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85824918746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80839359760284</t>
+    <t xml:space="preserve">1.92714023590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93076598644257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85824882984161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80839335918427</t>
   </si>
   <si>
     <t xml:space="preserve">1.8256162405014</t>
@@ -101,67 +101,67 @@
     <t xml:space="preserve">1.75128638744354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64704298973083</t>
+    <t xml:space="preserve">1.64704322814941</t>
   </si>
   <si>
     <t xml:space="preserve">1.75581872463226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71321475505829</t>
+    <t xml:space="preserve">1.71321499347687</t>
   </si>
   <si>
     <t xml:space="preserve">1.68964672088623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73134434223175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76760256290436</t>
+    <t xml:space="preserve">1.73134410381317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76760268211365</t>
   </si>
   <si>
     <t xml:space="preserve">1.72862458229065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7585381269455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81292581558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83105516433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76850926876068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67514336109161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74947345256805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69871163368225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74766039848328</t>
+    <t xml:space="preserve">1.75853800773621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81292593479156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83105504512787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76850914955139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6751434803009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74947321414948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69871139526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74766063690186</t>
   </si>
   <si>
     <t xml:space="preserve">1.70777606964111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70868265628815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6950855255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77666735649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7014307975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69055342674255</t>
+    <t xml:space="preserve">1.70868241786957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69508576393127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77666747570038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70143103599548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69055330753326</t>
   </si>
   <si>
     <t xml:space="preserve">1.73496997356415</t>
@@ -170,16 +170,16 @@
     <t xml:space="preserve">1.64069783687592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62982034683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63163328170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68692755699158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68602097034454</t>
+    <t xml:space="preserve">1.62982022762299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63163316249847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68692743778229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68602120876312</t>
   </si>
   <si>
     <t xml:space="preserve">1.67333054542542</t>
@@ -188,22 +188,22 @@
     <t xml:space="preserve">1.74040865898132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70415043830872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75672519207001</t>
+    <t xml:space="preserve">1.70415019989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75672507286072</t>
   </si>
   <si>
     <t xml:space="preserve">1.68783390522003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64885604381561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64794969558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68420803546906</t>
+    <t xml:space="preserve">1.64885592460632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64794957637787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68420827388763</t>
   </si>
   <si>
     <t xml:space="preserve">1.72137308120728</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">1.72227954864502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67786276340485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6325398683548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66335928440094</t>
+    <t xml:space="preserve">1.67786288261414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63253962993622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66335952281952</t>
   </si>
   <si>
     <t xml:space="preserve">1.66517245769501</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">1.78754484653473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78935766220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66154658794403</t>
+    <t xml:space="preserve">1.78935778141022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66154646873474</t>
   </si>
   <si>
     <t xml:space="preserve">1.69961786270142</t>
@@ -254,43 +254,43 @@
     <t xml:space="preserve">1.65882706642151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60353302955627</t>
+    <t xml:space="preserve">1.60353291034698</t>
   </si>
   <si>
     <t xml:space="preserve">1.569087266922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58902955055237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48297321796417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49566400051117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49203789234161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53192222118378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4838799238205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45215368270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48569273948669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42858564853668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45940518379211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49294424057007</t>
+    <t xml:space="preserve">1.58902943134308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48297345638275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49566376209259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49203777313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53192234039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48387968540192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45215356349945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48569285869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42858576774597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45940506458282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49294435977936</t>
   </si>
   <si>
     <t xml:space="preserve">1.46031177043915</t>
@@ -302,31 +302,31 @@
     <t xml:space="preserve">1.45034062862396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46846997737885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42586624622345</t>
+    <t xml:space="preserve">1.46847009658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42586600780487</t>
   </si>
   <si>
     <t xml:space="preserve">1.31255829334259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36422681808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3415652513504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36875903606415</t>
+    <t xml:space="preserve">1.36422657966614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34156501293182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36875915527344</t>
   </si>
   <si>
     <t xml:space="preserve">1.33250045776367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2781126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1965309381485</t>
+    <t xml:space="preserve">1.27811288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19653129577637</t>
   </si>
   <si>
     <t xml:space="preserve">1.17296290397644</t>
@@ -335,46 +335,46 @@
     <t xml:space="preserve">1.18746650218964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17568254470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15483367443085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09863305091858</t>
+    <t xml:space="preserve">1.17568242549896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15483391284943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09863317012787</t>
   </si>
   <si>
     <t xml:space="preserve">1.12401401996613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13307869434357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1258270740509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1131364107132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06962621212006</t>
+    <t xml:space="preserve">1.13307857513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12582671642303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11313652992249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06962645053864</t>
   </si>
   <si>
     <t xml:space="preserve">1.08684909343719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0950071811676</t>
+    <t xml:space="preserve">1.09500730037689</t>
   </si>
   <si>
     <t xml:space="preserve">1.09410071372986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12038803100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09228777885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10769760608673</t>
+    <t xml:space="preserve">1.12038815021515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09228789806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10769772529602</t>
   </si>
   <si>
     <t xml:space="preserve">1.10951054096222</t>
@@ -386,46 +386,46 @@
     <t xml:space="preserve">1.09682011604309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08956837654114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0886617898941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07234561443329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05149698257446</t>
+    <t xml:space="preserve">1.08956849575043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08866202831268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.072345495224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05149674415588</t>
   </si>
   <si>
     <t xml:space="preserve">1.12310743331909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10135245323181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08322334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08775568008423</t>
+    <t xml:space="preserve">1.10135233402252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08322322368622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08775556087494</t>
   </si>
   <si>
     <t xml:space="preserve">1.11404287815094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15120792388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21466040611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18474698066711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14576935768127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12220132350922</t>
+    <t xml:space="preserve">1.15120780467987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21466016769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18474686145782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14576923847198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12220108509064</t>
   </si>
   <si>
     <t xml:space="preserve">1.06237459182739</t>
@@ -434,16 +434,16 @@
     <t xml:space="preserve">1.03336775302887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.934563338756561</t>
+    <t xml:space="preserve">0.934563219547272</t>
   </si>
   <si>
     <t xml:space="preserve">0.945440769195557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977166950702667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956318199634552</t>
+    <t xml:space="preserve">0.977166891098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956318259239197</t>
   </si>
   <si>
     <t xml:space="preserve">0.933656811714172</t>
@@ -452,43 +452,43 @@
     <t xml:space="preserve">1.01523840427399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04877758026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0360871553421</t>
+    <t xml:space="preserve">1.04877769947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03608703613281</t>
   </si>
   <si>
     <t xml:space="preserve">1.02430319786072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990764081478119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05059051513672</t>
+    <t xml:space="preserve">0.990764141082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05059063434601</t>
   </si>
   <si>
     <t xml:space="preserve">1.11494934558868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12854635715485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07506513595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06418752670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02067720890045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997109234333038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00617372989655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988044500350952</t>
+    <t xml:space="preserve">1.12854647636414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07506501674652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06418740749359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02067756652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997109174728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00617384910583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988044738769531</t>
   </si>
   <si>
     <t xml:space="preserve">1.03880643844604</t>
@@ -497,22 +497,22 @@
     <t xml:space="preserve">1.05965518951416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04243230819702</t>
+    <t xml:space="preserve">1.04243218898773</t>
   </si>
   <si>
     <t xml:space="preserve">1.06328105926514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05693578720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10407173633575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10497832298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07597160339355</t>
+    <t xml:space="preserve">1.05693566799164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10407185554504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1049782037735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07597148418427</t>
   </si>
   <si>
     <t xml:space="preserve">1.12492048740387</t>
@@ -521,40 +521,40 @@
     <t xml:space="preserve">1.1031653881073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21103453636169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19562458992004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2128472328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14667558670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1539272069931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20559573173523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20196986198425</t>
+    <t xml:space="preserve">1.21103429794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19562470912933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21284747123718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14667546749115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15392732620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20559561252594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20196974277496</t>
   </si>
   <si>
     <t xml:space="preserve">1.23188304901123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25363838672638</t>
+    <t xml:space="preserve">1.25363826751709</t>
   </si>
   <si>
     <t xml:space="preserve">1.25817048549652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26088988780975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25545108318329</t>
+    <t xml:space="preserve">1.26089000701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25545120239258</t>
   </si>
   <si>
     <t xml:space="preserve">1.28717732429504</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">1.30530655384064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41226935386658</t>
+    <t xml:space="preserve">1.412269115448</t>
   </si>
   <si>
     <t xml:space="preserve">1.37963652610779</t>
@@ -575,16 +575,16 @@
     <t xml:space="preserve">1.40320456027985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35244286060333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35697495937347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35969436168671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34065854549408</t>
+    <t xml:space="preserve">1.35244274139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35697507858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35969424247742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34065866470337</t>
   </si>
   <si>
     <t xml:space="preserve">1.32343590259552</t>
@@ -593,43 +593,43 @@
     <t xml:space="preserve">1.35062968730927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3288745880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26995468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19471824169159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1439563035965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24548017978668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25001227855682</t>
+    <t xml:space="preserve">1.32887470722198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26995456218719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1947181224823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14395618438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24548006057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25001239776611</t>
   </si>
   <si>
     <t xml:space="preserve">1.26814162731171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23278951644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24185419082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28173851966858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26451599597931</t>
+    <t xml:space="preserve">1.23278963565826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24185407161713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28173863887787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26451575756073</t>
   </si>
   <si>
     <t xml:space="preserve">1.28264498710632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25091874599457</t>
+    <t xml:space="preserve">1.25091862678528</t>
   </si>
   <si>
     <t xml:space="preserve">1.26904809474945</t>
@@ -638,19 +638,19 @@
     <t xml:space="preserve">1.33159399032593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2962418794632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28536427021027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31437122821808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30983901023865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31799721717834</t>
+    <t xml:space="preserve">1.29624199867249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28536438941956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31437134742737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30983877182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31799709796906</t>
   </si>
   <si>
     <t xml:space="preserve">1.29896140098572</t>
@@ -659,37 +659,37 @@
     <t xml:space="preserve">1.37782371044159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3352198600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26179623603821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3107453584671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30711948871613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34247159957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29442918300629</t>
+    <t xml:space="preserve">1.33521997928619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2617963552475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31074547767639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3071197271347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34247136116028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.294429063797</t>
   </si>
   <si>
     <t xml:space="preserve">1.32434237003326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33884572982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31165182590485</t>
+    <t xml:space="preserve">1.33884584903717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31165170669556</t>
   </si>
   <si>
     <t xml:space="preserve">1.27992558479309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30621314048767</t>
+    <t xml:space="preserve">1.30621302127838</t>
   </si>
   <si>
     <t xml:space="preserve">1.31618416309357</t>
@@ -698,25 +698,25 @@
     <t xml:space="preserve">1.30349373817444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27720630168915</t>
+    <t xml:space="preserve">1.27720642089844</t>
   </si>
   <si>
     <t xml:space="preserve">1.26632857322693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28355157375336</t>
+    <t xml:space="preserve">1.28355133533478</t>
   </si>
   <si>
     <t xml:space="preserve">1.25907719135284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24910593032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27539324760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25273168087006</t>
+    <t xml:space="preserve">1.24910604953766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27539336681366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25273180007935</t>
   </si>
   <si>
     <t xml:space="preserve">1.34700393676758</t>
@@ -725,40 +725,40 @@
     <t xml:space="preserve">1.34972321987152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29261612892151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32978117465973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23369610309601</t>
+    <t xml:space="preserve">1.29261600971222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32978105545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23369586467743</t>
   </si>
   <si>
     <t xml:space="preserve">1.22372496128082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.229163646698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20468926429749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22191214561462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21919250488281</t>
+    <t xml:space="preserve">1.22916376590729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2046891450882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22191190719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21919286251068</t>
   </si>
   <si>
     <t xml:space="preserve">1.2210054397583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21828627586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22463119029999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21012818813324</t>
+    <t xml:space="preserve">1.21828603744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22463130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21012806892395</t>
   </si>
   <si>
     <t xml:space="preserve">1.18656003475189</t>
@@ -767,58 +767,58 @@
     <t xml:space="preserve">1.17477595806122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17840170860291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15211451053619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15845954418182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08594262599945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10588479042053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07959735393524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10679125785828</t>
+    <t xml:space="preserve">1.17840182781219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15211427211761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15845966339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08594250679016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10588490962982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07959747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10679113864899</t>
   </si>
   <si>
     <t xml:space="preserve">1.13217222690582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16933715343475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22644436359406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23822844028473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24457359313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2518253326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24004137516022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20378267765045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20650207996368</t>
+    <t xml:space="preserve">1.16933727264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22644424438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23822855949402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24457371234894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25182521343231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24004125595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20378279685974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20650231838226</t>
   </si>
   <si>
     <t xml:space="preserve">1.24094760417938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2309764623642</t>
+    <t xml:space="preserve">1.23097658157349</t>
   </si>
   <si>
     <t xml:space="preserve">1.21194100379944</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">1.23460245132446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24638640880585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27629995346069</t>
+    <t xml:space="preserve">1.24638652801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27629971504211</t>
   </si>
   <si>
     <t xml:space="preserve">1.27086102962494</t>
@@ -839,25 +839,25 @@
     <t xml:space="preserve">1.29805505275726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22553789615631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15574026107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11857521533966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1602725982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16661763191223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16480481624603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18112111091614</t>
+    <t xml:space="preserve">1.22553777694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15574014186859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11857509613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16027247905731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16661775112152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16480469703674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18112099170685</t>
   </si>
   <si>
     <t xml:space="preserve">1.19925045967102</t>
@@ -866,16 +866,16 @@
     <t xml:space="preserve">1.11676239967346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0931943655014</t>
+    <t xml:space="preserve">1.09319400787354</t>
   </si>
   <si>
     <t xml:space="preserve">1.09772658348083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.176589012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17930829524994</t>
+    <t xml:space="preserve">1.17658877372742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17930817604065</t>
   </si>
   <si>
     <t xml:space="preserve">1.21375381946564</t>
@@ -884,49 +884,49 @@
     <t xml:space="preserve">1.21556675434113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28627097606659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28989660739899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28445816040039</t>
+    <t xml:space="preserve">1.28627109527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28989672660828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28445792198181</t>
   </si>
   <si>
     <t xml:space="preserve">1.38960766792297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40048515796661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41408216953278</t>
+    <t xml:space="preserve">1.40048503875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41408205032349</t>
   </si>
   <si>
     <t xml:space="preserve">1.38235604763031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37057197093964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32796823978424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36513316631317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3551619052887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38416886329651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42224037647247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38054311275482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38870096206665</t>
+    <t xml:space="preserve">1.37057185173035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32796835899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36513328552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35516202449799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38416862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42224025726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38054287433624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38870120048523</t>
   </si>
   <si>
     <t xml:space="preserve">1.36694598197937</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">1.40773701667786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39957880973816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39685928821564</t>
+    <t xml:space="preserve">1.39957869052887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39685940742493</t>
   </si>
   <si>
     <t xml:space="preserve">1.38326227664948</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">1.38688826560974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50926065444946</t>
+    <t xml:space="preserve">1.50926053524017</t>
   </si>
   <si>
     <t xml:space="preserve">1.57724559307098</t>
@@ -956,40 +956,40 @@
     <t xml:space="preserve">1.57271325588226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54551923274994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55005180835724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51379311084747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48659908771515</t>
+    <t xml:space="preserve">1.54551935195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55005145072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51379299163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48659920692444</t>
   </si>
   <si>
     <t xml:space="preserve">1.44580841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48206675052643</t>
+    <t xml:space="preserve">1.48206686973572</t>
   </si>
   <si>
     <t xml:space="preserve">1.43221139907837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54098689556122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52285766601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52738988399506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37329113483429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39142060279846</t>
+    <t xml:space="preserve">1.54098701477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52285778522491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52739000320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37329137325287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39142036437988</t>
   </si>
   <si>
     <t xml:space="preserve">1.34609746932983</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">1.27358031272888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39595305919647</t>
+    <t xml:space="preserve">1.39595293998718</t>
   </si>
   <si>
     <t xml:space="preserve">1.30077409744263</t>
@@ -1019,28 +1019,28 @@
     <t xml:space="preserve">1.3147611618042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30543661117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31942343711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24482715129852</t>
+    <t xml:space="preserve">1.30543649196625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31942331790924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24482727050781</t>
   </si>
   <si>
     <t xml:space="preserve">1.24948942661285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23084020614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21219110488892</t>
+    <t xml:space="preserve">1.23084032535553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21219098567963</t>
   </si>
   <si>
     <t xml:space="preserve">1.2541515827179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23550260066986</t>
+    <t xml:space="preserve">1.23550248146057</t>
   </si>
   <si>
     <t xml:space="preserve">1.22617793083191</t>
@@ -1049,49 +1049,49 @@
     <t xml:space="preserve">1.19354200363159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19820439815521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24016463756561</t>
+    <t xml:space="preserve">1.19820427894592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2401647567749</t>
   </si>
   <si>
     <t xml:space="preserve">1.27280068397522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29611194133759</t>
+    <t xml:space="preserve">1.29611217975616</t>
   </si>
   <si>
     <t xml:space="preserve">1.31009888648987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32874810695648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28212535381317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26813840866089</t>
+    <t xml:space="preserve">1.3287478685379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28212523460388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26813852787018</t>
   </si>
   <si>
     <t xml:space="preserve">1.30077421665192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21685326099396</t>
+    <t xml:space="preserve">1.21685338020325</t>
   </si>
   <si>
     <t xml:space="preserve">1.18887972831726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1655684709549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20286655426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17489302158356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17955505847931</t>
+    <t xml:space="preserve">1.16556835174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20286667346954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17489278316498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1795551776886</t>
   </si>
   <si>
     <t xml:space="preserve">1.20752882957458</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">1.14691925048828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13293254375458</t>
+    <t xml:space="preserve">1.13293242454529</t>
   </si>
   <si>
     <t xml:space="preserve">1.25881385803223</t>
@@ -1118,37 +1118,37 @@
     <t xml:space="preserve">1.27746295928955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22151577472687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15624380111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18421757221222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28678750991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16090631484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15158140659332</t>
+    <t xml:space="preserve">1.22151553630829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15624392032623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18421745300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28678739070892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16090607643127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1515816450119</t>
   </si>
   <si>
     <t xml:space="preserve">1.13759481906891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36138391494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29144966602325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34273493289948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33807241916656</t>
+    <t xml:space="preserve">1.3613840341568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29144990444183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34273481369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33807265758514</t>
   </si>
   <si>
     <t xml:space="preserve">1.11428344249725</t>
@@ -1157,16 +1157,16 @@
     <t xml:space="preserve">1.1049587726593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14225697517395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27810597419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29230725765228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37278044223785</t>
+    <t xml:space="preserve">1.14225709438324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27810609340668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29230737686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37278068065643</t>
   </si>
   <si>
     <t xml:space="preserve">1.34437811374664</t>
@@ -1175,31 +1175,31 @@
     <t xml:space="preserve">1.32544326782227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30177474021912</t>
+    <t xml:space="preserve">1.30177450180054</t>
   </si>
   <si>
     <t xml:space="preserve">1.55266213417053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41065037250519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31124198436737</t>
+    <t xml:space="preserve">1.4106502532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31124210357666</t>
   </si>
   <si>
     <t xml:space="preserve">1.31597578525543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28757345676422</t>
+    <t xml:space="preserve">1.28757357597351</t>
   </si>
   <si>
     <t xml:space="preserve">1.30650842189789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33964443206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42011785507202</t>
+    <t xml:space="preserve">1.33964431285858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42011773586273</t>
   </si>
   <si>
     <t xml:space="preserve">1.40591669082642</t>
@@ -1208,28 +1208,28 @@
     <t xml:space="preserve">1.35384559631348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39644908905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3207094669342</t>
+    <t xml:space="preserve">1.39644920825958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32070958614349</t>
   </si>
   <si>
     <t xml:space="preserve">1.3349107503891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28283965587616</t>
+    <t xml:space="preserve">1.28283977508545</t>
   </si>
   <si>
     <t xml:space="preserve">1.27337229251862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26390492916107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25917100906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29704093933105</t>
+    <t xml:space="preserve">1.26390480995178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25917112827301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29704082012177</t>
   </si>
   <si>
     <t xml:space="preserve">1.2449699640274</t>
@@ -1238,28 +1238,28 @@
     <t xml:space="preserve">1.2307687997818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22130131721497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21656763553619</t>
+    <t xml:space="preserve">1.22130119800568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2165675163269</t>
   </si>
   <si>
     <t xml:space="preserve">1.22603499889374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24023628234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21183383464813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26863873004913</t>
+    <t xml:space="preserve">1.24023604393005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21183395385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26863861083984</t>
   </si>
   <si>
     <t xml:space="preserve">1.20710015296936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24970364570618</t>
+    <t xml:space="preserve">1.24970376491547</t>
   </si>
   <si>
     <t xml:space="preserve">1.25443744659424</t>
@@ -1268,13 +1268,13 @@
     <t xml:space="preserve">1.23550236225128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16923022270203</t>
+    <t xml:space="preserve">1.16923034191132</t>
   </si>
   <si>
     <t xml:space="preserve">1.18343162536621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20236647129059</t>
+    <t xml:space="preserve">1.2023663520813</t>
   </si>
   <si>
     <t xml:space="preserve">1.1408280134201</t>
@@ -1289,25 +1289,25 @@
     <t xml:space="preserve">1.10295820236206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06982219219208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01775109767914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989348709583282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979881227016449</t>
+    <t xml:space="preserve">1.06982207298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01775097846985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989348649978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979881286621094</t>
   </si>
   <si>
     <t xml:space="preserve">0.965680122375488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.914555847644806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937277734279633</t>
+    <t xml:space="preserve">0.914555907249451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937277853488922</t>
   </si>
   <si>
     <t xml:space="preserve">0.920236349105835</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">0.880473077297211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927810370922089</t>
+    <t xml:space="preserve">0.927810251712799</t>
   </si>
   <si>
     <t xml:space="preserve">0.946745216846466</t>
@@ -1325,16 +1325,16 @@
     <t xml:space="preserve">0.956212639808655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0224848985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07928943634033</t>
+    <t xml:space="preserve">1.02248501777649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07928955554962</t>
   </si>
   <si>
     <t xml:space="preserve">1.10769188404083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13609421253204</t>
+    <t xml:space="preserve">1.13609433174133</t>
   </si>
   <si>
     <t xml:space="preserve">1.05562090873718</t>
@@ -1346,10 +1346,10 @@
     <t xml:space="preserve">1.06035470962524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06508839130402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07455575466156</t>
+    <t xml:space="preserve">1.06508851051331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07455563545227</t>
   </si>
   <si>
     <t xml:space="preserve">1.04615342617035</t>
@@ -1358,37 +1358,37 @@
     <t xml:space="preserve">1.03668606281281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04141974449158</t>
+    <t xml:space="preserve">1.04141986370087</t>
   </si>
   <si>
     <t xml:space="preserve">1.11242544651031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12662672996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08875703811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.098224401474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05088698863983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03195238113403</t>
+    <t xml:space="preserve">1.1266268491745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08875691890717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09822452068329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05088710784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03195226192474</t>
   </si>
   <si>
     <t xml:space="preserve">1.02721858024597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17869794368744</t>
+    <t xml:space="preserve">1.17869782447815</t>
   </si>
   <si>
     <t xml:space="preserve">1.15976285934448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15029549598694</t>
+    <t xml:space="preserve">1.15029537677765</t>
   </si>
   <si>
     <t xml:space="preserve">1.16449654102325</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">1.14556181430817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17396402359009</t>
+    <t xml:space="preserve">1.17396414279938</t>
   </si>
   <si>
     <t xml:space="preserve">1.13136053085327</t>
@@ -1412,28 +1412,28 @@
     <t xml:space="preserve">1.00828373432159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984614968299866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994082510471344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01301729679108</t>
+    <t xml:space="preserve">0.98461502790451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994082391262054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01301741600037</t>
   </si>
   <si>
     <t xml:space="preserve">1.18816518783569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33017706871033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40118288993835</t>
+    <t xml:space="preserve">1.33017694950104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40118300914764</t>
   </si>
   <si>
     <t xml:space="preserve">1.3633131980896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33027982711792</t>
+    <t xml:space="preserve">1.33027994632721</t>
   </si>
   <si>
     <t xml:space="preserve">1.32551181316376</t>
@@ -1445,13 +1445,13 @@
     <t xml:space="preserve">1.33504784107208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36365616321564</t>
+    <t xml:space="preserve">1.36365604400635</t>
   </si>
   <si>
     <t xml:space="preserve">1.32074379920959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35412001609802</t>
+    <t xml:space="preserve">1.35411989688873</t>
   </si>
   <si>
     <t xml:space="preserve">1.3445839881897</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">1.36842405796051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34935200214386</t>
+    <t xml:space="preserve">1.34935212135315</t>
   </si>
   <si>
     <t xml:space="preserve">1.35888803005219</t>
@@ -1475,28 +1475,28 @@
     <t xml:space="preserve">1.3922643661499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38272821903229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41133642196655</t>
+    <t xml:space="preserve">1.38272833824158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41133630275726</t>
   </si>
   <si>
     <t xml:space="preserve">1.38749623298645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37319231033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43040859699249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47808885574341</t>
+    <t xml:space="preserve">1.37319219112396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4304084777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47808873653412</t>
   </si>
   <si>
     <t xml:space="preserve">1.44471251964569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40656840801239</t>
+    <t xml:space="preserve">1.4065682888031</t>
   </si>
   <si>
     <t xml:space="preserve">1.42087244987488</t>
@@ -1505,10 +1505,10 @@
     <t xml:space="preserve">1.43517661094666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45901668071747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43994462490082</t>
+    <t xml:space="preserve">1.45901656150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43994450569153</t>
   </si>
   <si>
     <t xml:space="preserve">1.41610443592072</t>
@@ -1517,22 +1517,22 @@
     <t xml:space="preserve">1.51623296737671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50669705867767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53530514240265</t>
+    <t xml:space="preserve">1.50669693946838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53530502319336</t>
   </si>
   <si>
     <t xml:space="preserve">1.54484117031097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54007303714752</t>
+    <t xml:space="preserve">1.54007315635681</t>
   </si>
   <si>
     <t xml:space="preserve">1.58298540115356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57344937324524</t>
+    <t xml:space="preserve">1.57344925403595</t>
   </si>
   <si>
     <t xml:space="preserve">1.68788206577301</t>
@@ -1541,25 +1541,25 @@
     <t xml:space="preserve">1.65450572967529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70695424079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7641704082489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74509835243225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72602617740631</t>
+    <t xml:space="preserve">1.70695412158966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76417052745819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74509847164154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7260262966156</t>
   </si>
   <si>
     <t xml:space="preserve">1.69741797447205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66880977153778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67357778549194</t>
+    <t xml:space="preserve">1.66881000995636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67357802391052</t>
   </si>
   <si>
     <t xml:space="preserve">1.64020168781281</t>
@@ -1574,31 +1574,31 @@
     <t xml:space="preserve">1.64973783493042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71172201633453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64496982097626</t>
+    <t xml:space="preserve">1.71172213554382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64496970176697</t>
   </si>
   <si>
     <t xml:space="preserve">1.61636161804199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62112975120544</t>
+    <t xml:space="preserve">1.62112951278687</t>
   </si>
   <si>
     <t xml:space="preserve">1.63066565990448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63543367385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77847456932068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75940239429474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68311393260956</t>
+    <t xml:space="preserve">1.63543379306793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77847468852997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75940251350403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68311405181885</t>
   </si>
   <si>
     <t xml:space="preserve">1.71649014949799</t>
@@ -1607,40 +1607,40 @@
     <t xml:space="preserve">1.77370655536652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81185066699982</t>
+    <t xml:space="preserve">1.81185078620911</t>
   </si>
   <si>
     <t xml:space="preserve">1.8261547088623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79754650592804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78801047801971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81661880016327</t>
+    <t xml:space="preserve">1.79754674434662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.788010597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81661891937256</t>
   </si>
   <si>
     <t xml:space="preserve">1.83092284202576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80708265304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76893842220306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73556232452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73079419136047</t>
+    <t xml:space="preserve">1.80708277225494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76893854141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73556244373322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73079431056976</t>
   </si>
   <si>
     <t xml:space="preserve">1.74033033847809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72125816345215</t>
+    <t xml:space="preserve">1.72125828266144</t>
   </si>
   <si>
     <t xml:space="preserve">1.78324246406555</t>
@@ -1652,52 +1652,52 @@
     <t xml:space="preserve">1.67834603786469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66404187679291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69264996051788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80231475830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75463438034058</t>
+    <t xml:space="preserve">1.66404175758362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69265007972717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80231463909149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75463449954987</t>
   </si>
   <si>
     <t xml:space="preserve">1.79277861118317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56868124008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65927386283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59252154827118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52576911449432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59728932380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70218598842621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85953104496002</t>
+    <t xml:space="preserve">1.5686811208725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65927374362946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5925213098526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52576899528503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59728944301605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7021861076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85953116416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.89767527580261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92628347873688</t>
+    <t xml:space="preserve">1.92628335952759</t>
   </si>
   <si>
     <t xml:space="preserve">1.82138681411743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83569097518921</t>
+    <t xml:space="preserve">1.83569073677063</t>
   </si>
   <si>
     <t xml:space="preserve">1.86429917812347</t>
@@ -1706,25 +1706,25 @@
     <t xml:space="preserve">1.90721130371094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94535541534424</t>
+    <t xml:space="preserve">1.94535565376282</t>
   </si>
   <si>
     <t xml:space="preserve">1.99303579330444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05978846549988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00257205963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07886028289795</t>
+    <t xml:space="preserve">2.0597882270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00257182121277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07886052131653</t>
   </si>
   <si>
     <t xml:space="preserve">2.12654066085815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1074686050415</t>
+    <t xml:space="preserve">2.10746836662292</t>
   </si>
   <si>
     <t xml:space="preserve">2.08839654922485</t>
@@ -1733,16 +1733,16 @@
     <t xml:space="preserve">2.0979323387146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14561295509338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27911758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19329309463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22190117835999</t>
+    <t xml:space="preserve">2.1456127166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27911734580994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19329285621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22190093994141</t>
   </si>
   <si>
     <t xml:space="preserve">2.25050926208496</t>
@@ -1754,88 +1754,91 @@
     <t xml:space="preserve">2.01210784912109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97396349906921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98349964618683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0311803817749</t>
+    <t xml:space="preserve">1.97396373748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98349976539612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03117990493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04071617126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09847211837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08884620666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10809803009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00221180915833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95408177375793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03108978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02146410942078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05996799468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94445586204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97333383560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93482995033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85782170295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83856964111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82894361019135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86744773387909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88669979572296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707364559174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89632570743561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92520391941071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99258589744568</t>
   </si>
   <si>
     <t xml:space="preserve">2.04071593284607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09847211837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08884644508362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10809826850891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00221180915833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95408177375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03109002113342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02146410942078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05996799468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94445586204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9733339548111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93482983112335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85782170295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83856964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82894361019135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86744773387909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88669979572296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707376480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89632570743561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92520380020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99258577823639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05034232139587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11772418022156</t>
+    <t xml:space="preserve">2.05034208297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11772441864014</t>
   </si>
   <si>
     <t xml:space="preserve">2.1562283039093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20435857772827</t>
+    <t xml:space="preserve">2.20435833930969</t>
   </si>
   <si>
     <t xml:space="preserve">2.16585445404053</t>
@@ -1844,7 +1847,7 @@
     <t xml:space="preserve">2.14660239219666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07922029495239</t>
+    <t xml:space="preserve">2.07922005653381</t>
   </si>
   <si>
     <t xml:space="preserve">2.24286246299744</t>
@@ -1859,19 +1862,19 @@
     <t xml:space="preserve">2.30061864852905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28136658668518</t>
+    <t xml:space="preserve">2.2813663482666</t>
   </si>
   <si>
     <t xml:space="preserve">2.18510627746582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19473218917847</t>
+    <t xml:space="preserve">2.19473242759705</t>
   </si>
   <si>
     <t xml:space="preserve">2.12735033035278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13697600364685</t>
+    <t xml:space="preserve">2.13697624206543</t>
   </si>
   <si>
     <t xml:space="preserve">2.01183795928955</t>
@@ -1880,7 +1883,7 @@
     <t xml:space="preserve">1.8722608089447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96370780467987</t>
+    <t xml:space="preserve">1.96370792388916</t>
   </si>
   <si>
     <t xml:space="preserve">2.06959414482117</t>
@@ -1898,7 +1901,7 @@
     <t xml:space="preserve">2.35837483406067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42575669288635</t>
+    <t xml:space="preserve">2.42575693130493</t>
   </si>
   <si>
     <t xml:space="preserve">2.39687895774841</t>
@@ -1913,7 +1916,7 @@
     <t xml:space="preserve">2.41613078117371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37762665748596</t>
+    <t xml:space="preserve">2.37762689590454</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874868392944</t>
@@ -1922,10 +1925,10 @@
     <t xml:space="preserve">2.29099249839783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36800050735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38725256919861</t>
+    <t xml:space="preserve">2.36800074577332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38725280761719</t>
   </si>
   <si>
     <t xml:space="preserve">2.21398448944092</t>
@@ -1934,7 +1937,7 @@
     <t xml:space="preserve">2.31987071037292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44500875473022</t>
+    <t xml:space="preserve">2.4450089931488</t>
   </si>
   <si>
     <t xml:space="preserve">2.45463490486145</t>
@@ -1949,7 +1952,7 @@
     <t xml:space="preserve">2.52201700210571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50276470184326</t>
+    <t xml:space="preserve">2.50276494026184</t>
   </si>
   <si>
     <t xml:space="preserve">2.59902501106262</t>
@@ -1970,13 +1973,13 @@
     <t xml:space="preserve">2.48351287841797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53164315223694</t>
+    <t xml:space="preserve">2.53164291381836</t>
   </si>
   <si>
     <t xml:space="preserve">2.63752913475037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6952850818634</t>
+    <t xml:space="preserve">2.69528532028198</t>
   </si>
   <si>
     <t xml:space="preserve">2.82042360305786</t>
@@ -1985,7 +1988,7 @@
     <t xml:space="preserve">2.71453738212585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67603325843811</t>
+    <t xml:space="preserve">2.67603349685669</t>
   </si>
   <si>
     <t xml:space="preserve">2.60865116119385</t>
@@ -1997,13 +2000,13 @@
     <t xml:space="preserve">2.5701470375061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58939933776855</t>
+    <t xml:space="preserve">2.58939909934998</t>
   </si>
   <si>
     <t xml:space="preserve">2.56052088737488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62790322303772</t>
+    <t xml:space="preserve">2.6279034614563</t>
   </si>
   <si>
     <t xml:space="preserve">2.55089521408081</t>
@@ -2012,7 +2015,7 @@
     <t xml:space="preserve">2.57977318763733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38258814811707</t>
+    <t xml:space="preserve">2.38258790969849</t>
   </si>
   <si>
     <t xml:space="preserve">2.29506421089172</t>
@@ -2021,13 +2024,13 @@
     <t xml:space="preserve">2.28533935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32423901557922</t>
+    <t xml:space="preserve">2.32423877716064</t>
   </si>
   <si>
     <t xml:space="preserve">2.25616478919983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23671507835388</t>
+    <t xml:space="preserve">2.23671531677246</t>
   </si>
   <si>
     <t xml:space="preserve">2.21726560592651</t>
@@ -2039,16 +2042,16 @@
     <t xml:space="preserve">2.34368872642517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2658896446228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30478882789612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24644017219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11029243469238</t>
+    <t xml:space="preserve">2.26588988304138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3047890663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24643993377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1102921962738</t>
   </si>
   <si>
     <t xml:space="preserve">2.15891647338867</t>
@@ -2066,7 +2069,7 @@
     <t xml:space="preserve">2.19781565666199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16864109039307</t>
+    <t xml:space="preserve">2.16864132881165</t>
   </si>
   <si>
     <t xml:space="preserve">2.18809103965759</t>
@@ -2078,16 +2081,16 @@
     <t xml:space="preserve">2.13946676254272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09084248542786</t>
+    <t xml:space="preserve">2.09084272384644</t>
   </si>
   <si>
     <t xml:space="preserve">2.10056734085083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27561473846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08111786842346</t>
+    <t xml:space="preserve">2.27561450004578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08111763000488</t>
   </si>
   <si>
     <t xml:space="preserve">1.97414433956146</t>
@@ -2099,7 +2102,7 @@
     <t xml:space="preserve">1.98386907577515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96441948413849</t>
+    <t xml:space="preserve">1.9644193649292</t>
   </si>
   <si>
     <t xml:space="preserve">1.94496977329254</t>
@@ -2114,13 +2117,13 @@
     <t xml:space="preserve">2.02276849746704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03249311447144</t>
+    <t xml:space="preserve">2.03249335289001</t>
   </si>
   <si>
     <t xml:space="preserve">2.01304364204407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07139301300049</t>
+    <t xml:space="preserve">2.07139277458191</t>
   </si>
   <si>
     <t xml:space="preserve">2.04221820831299</t>
@@ -2132,7 +2135,7 @@
     <t xml:space="preserve">1.93524491786957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95469450950623</t>
+    <t xml:space="preserve">1.95469462871552</t>
   </si>
   <si>
     <t xml:space="preserve">1.91579520702362</t>
@@ -2141,10 +2144,10 @@
     <t xml:space="preserve">1.93038249015808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06166768074036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91093277931213</t>
+    <t xml:space="preserve">2.06166791915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91093289852142</t>
   </si>
   <si>
     <t xml:space="preserve">2.1491916179657</t>
@@ -2159,16 +2162,16 @@
     <t xml:space="preserve">1.92552006244659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81854665279388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84772121906281</t>
+    <t xml:space="preserve">1.81854677200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84772133827209</t>
   </si>
   <si>
     <t xml:space="preserve">1.8866206407547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83313393592834</t>
+    <t xml:space="preserve">1.83313405513763</t>
   </si>
   <si>
     <t xml:space="preserve">1.85258364677429</t>
@@ -2202,9 +2205,6 @@
   </si>
   <si>
     <t xml:space="preserve">1.97931289672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95469462871552</t>
   </si>
   <si>
     <t xml:space="preserve">1.9497709274292</t>
@@ -46422,7 +46422,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1677" t="s">
-        <v>583</v>
+        <v>604</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46448,7 +46448,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1678" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46500,7 +46500,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1680" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46526,7 +46526,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1681" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46552,7 +46552,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1682" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -46578,7 +46578,7 @@
         <v>2.25</v>
       </c>
       <c r="G1683" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46604,7 +46604,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1684" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46630,7 +46630,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1685" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46656,7 +46656,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1686" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46682,7 +46682,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1687" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46708,7 +46708,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1688" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46734,7 +46734,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1689" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46760,7 +46760,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1690" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46786,7 +46786,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1691" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46812,7 +46812,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1692" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46838,7 +46838,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1693" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46890,7 +46890,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1695" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46942,7 +46942,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1697" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46968,7 +46968,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1698" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46994,7 +46994,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1699" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -47020,7 +47020,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1700" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -47046,7 +47046,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1701" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -47072,7 +47072,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1702" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -47098,7 +47098,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1703" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -47124,7 +47124,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1704" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -47150,7 +47150,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1705" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -47176,7 +47176,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1706" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -47202,7 +47202,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -47228,7 +47228,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1708" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -47254,7 +47254,7 @@
         <v>2.25</v>
       </c>
       <c r="G1709" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -47280,7 +47280,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1710" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -47306,7 +47306,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1711" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -47332,7 +47332,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1712" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47384,7 +47384,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1714" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47410,7 +47410,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1715" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47514,7 +47514,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1719" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47618,7 +47618,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1723" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47670,7 +47670,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1725" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47696,7 +47696,7 @@
         <v>2.25</v>
       </c>
       <c r="G1726" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47722,7 +47722,7 @@
         <v>2.25</v>
       </c>
       <c r="G1727" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47748,7 +47748,7 @@
         <v>2.25</v>
       </c>
       <c r="G1728" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47774,7 +47774,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1729" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47800,7 +47800,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1730" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47826,7 +47826,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1731" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47852,7 +47852,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1732" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47878,7 +47878,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1733" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47904,7 +47904,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1734" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47930,7 +47930,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1735" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47956,7 +47956,7 @@
         <v>2.5</v>
       </c>
       <c r="G1736" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47982,7 +47982,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1737" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -48008,7 +48008,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1738" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -48034,7 +48034,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1739" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -48060,7 +48060,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1740" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -48086,7 +48086,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1741" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -48112,7 +48112,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1742" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -48138,7 +48138,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1743" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -48164,7 +48164,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1744" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -48190,7 +48190,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1745" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -48216,7 +48216,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1746" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -48242,7 +48242,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1747" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -48268,7 +48268,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1748" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -48294,7 +48294,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1749" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -48320,7 +48320,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1750" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -48346,7 +48346,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1751" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48372,7 +48372,7 @@
         <v>2.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48398,7 +48398,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1753" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48424,7 +48424,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1754" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48450,7 +48450,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1755" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48476,7 +48476,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1756" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48502,7 +48502,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1757" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48528,7 +48528,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1758" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48554,7 +48554,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1759" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48580,7 +48580,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1760" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48606,7 +48606,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1761" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48632,7 +48632,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1762" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48658,7 +48658,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1763" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48684,7 +48684,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1764" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48710,7 +48710,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1765" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48736,7 +48736,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1766" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48762,7 +48762,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1767" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48866,7 +48866,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1771" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48918,7 +48918,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48944,7 +48944,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1774" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -49022,7 +49022,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1777" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -49048,7 +49048,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1778" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -49074,7 +49074,7 @@
         <v>2.25</v>
       </c>
       <c r="G1779" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -49100,7 +49100,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1780" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -49126,7 +49126,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1781" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -49152,7 +49152,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1782" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -49178,7 +49178,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1783" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -49204,7 +49204,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1784" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -49230,7 +49230,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1785" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -49256,7 +49256,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1786" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -49282,7 +49282,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1787" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -49308,7 +49308,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1788" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -49334,7 +49334,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1789" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49360,7 +49360,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1790" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49386,7 +49386,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1791" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49412,7 +49412,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1792" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49438,7 +49438,7 @@
         <v>2.5</v>
       </c>
       <c r="G1793" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49464,7 +49464,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1794" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49490,7 +49490,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1795" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49516,7 +49516,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1796" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49542,7 +49542,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1797" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49568,7 +49568,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1798" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49594,7 +49594,7 @@
         <v>2.5</v>
       </c>
       <c r="G1799" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49620,7 +49620,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1800" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49646,7 +49646,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1801" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -49672,7 +49672,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1802" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49698,7 +49698,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1803" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49724,7 +49724,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1804" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49750,7 +49750,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1805" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49776,7 +49776,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1806" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49802,7 +49802,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1807" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49828,7 +49828,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1808" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49854,7 +49854,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1809" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49880,7 +49880,7 @@
         <v>2.75</v>
       </c>
       <c r="G1810" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49906,7 +49906,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1811" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49932,7 +49932,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1812" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49958,7 +49958,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1813" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49984,7 +49984,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1814" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -50010,7 +50010,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1815" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -50036,7 +50036,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1816" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -50062,7 +50062,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1817" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -50088,7 +50088,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1818" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -50114,7 +50114,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1819" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -50140,7 +50140,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1820" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -50166,7 +50166,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1821" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -50192,7 +50192,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1822" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -50218,7 +50218,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1823" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -50244,7 +50244,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1824" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -50270,7 +50270,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1825" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -50296,7 +50296,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1826" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -50322,7 +50322,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1827" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50348,7 +50348,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1828" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50374,7 +50374,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1829" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -50400,7 +50400,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1830" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50426,7 +50426,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1831" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50452,7 +50452,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1832" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50478,7 +50478,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1833" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50504,7 +50504,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1834" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50530,7 +50530,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1835" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50556,7 +50556,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1836" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50582,7 +50582,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1837" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50608,7 +50608,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1838" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50634,7 +50634,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50660,7 +50660,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1840" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50686,7 +50686,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1841" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50712,7 +50712,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1842" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50738,7 +50738,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1843" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50764,7 +50764,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1844" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50790,7 +50790,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1845" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50816,7 +50816,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1846" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50842,7 +50842,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1847" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50868,7 +50868,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1848" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50894,7 +50894,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1849" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50920,7 +50920,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1850" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50946,7 +50946,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1851" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50972,7 +50972,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1852" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50998,7 +50998,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1853" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -51024,7 +51024,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1854" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -51050,7 +51050,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1855" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -51076,7 +51076,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -51102,7 +51102,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1857" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -51128,7 +51128,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1858" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -51154,7 +51154,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1859" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -51180,7 +51180,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1860" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -51206,7 +51206,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1861" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -51232,7 +51232,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1862" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51258,7 +51258,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1863" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -51284,7 +51284,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1864" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -51310,7 +51310,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1865" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -51336,7 +51336,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1866" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51362,7 +51362,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1867" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51388,7 +51388,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1868" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51414,7 +51414,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1869" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51440,7 +51440,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1870" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51466,7 +51466,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1871" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51492,7 +51492,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1872" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51518,7 +51518,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1873" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51544,7 +51544,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1874" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51570,7 +51570,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1875" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51596,7 +51596,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1876" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51622,7 +51622,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1877" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51648,7 +51648,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1878" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51674,7 +51674,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1879" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51700,7 +51700,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1880" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51726,7 +51726,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1881" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51752,7 +51752,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51778,7 +51778,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1883" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51804,7 +51804,7 @@
         <v>2.5</v>
       </c>
       <c r="G1884" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51830,7 +51830,7 @@
         <v>2.5</v>
       </c>
       <c r="G1885" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51856,7 +51856,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1886" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51882,7 +51882,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1887" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51908,7 +51908,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1888" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51934,7 +51934,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1889" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51960,7 +51960,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1890" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51986,7 +51986,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1891" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52012,7 +52012,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1892" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52038,7 +52038,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1893" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52064,7 +52064,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1894" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52090,7 +52090,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1895" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52116,7 +52116,7 @@
         <v>2.5</v>
       </c>
       <c r="G1896" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52142,7 +52142,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1897" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52168,7 +52168,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1898" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52194,7 +52194,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1899" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52220,7 +52220,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1900" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52246,7 +52246,7 @@
         <v>2.5</v>
       </c>
       <c r="G1901" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52272,7 +52272,7 @@
         <v>2.5</v>
       </c>
       <c r="G1902" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52298,7 +52298,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1903" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52324,7 +52324,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52350,7 +52350,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1905" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52376,7 +52376,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1906" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52402,7 +52402,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1907" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52428,7 +52428,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1908" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52454,7 +52454,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1909" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52480,7 +52480,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1910" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52506,7 +52506,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1911" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52532,7 +52532,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1912" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52558,7 +52558,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1913" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52584,7 +52584,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1914" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52610,7 +52610,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1915" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52636,7 +52636,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1916" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52662,7 +52662,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1917" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52688,7 +52688,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1918" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52714,7 +52714,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1919" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52740,7 +52740,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1920" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52766,7 +52766,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1921" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52792,7 +52792,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1922" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52818,7 +52818,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1923" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52844,7 +52844,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1924" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52870,7 +52870,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1925" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52896,7 +52896,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1926" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52922,7 +52922,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1927" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52948,7 +52948,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1928" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52974,7 +52974,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1929" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53000,7 +53000,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1930" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -53026,7 +53026,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1931" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53052,7 +53052,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1932" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53078,7 +53078,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1933" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53104,7 +53104,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1934" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53130,7 +53130,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1935" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53156,7 +53156,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1936" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53182,7 +53182,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53208,7 +53208,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1938" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53234,7 +53234,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1939" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53260,7 +53260,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1940" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53286,7 +53286,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1941" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53312,7 +53312,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1942" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53338,7 +53338,7 @@
         <v>2.25</v>
       </c>
       <c r="G1943" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53364,7 +53364,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1944" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53390,7 +53390,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1945" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53416,7 +53416,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1946" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53442,7 +53442,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1947" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53468,7 +53468,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1948" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53494,7 +53494,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1949" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53520,7 +53520,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1950" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53546,7 +53546,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1951" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53572,7 +53572,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1952" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53598,7 +53598,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1953" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53624,7 +53624,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1954" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53650,7 +53650,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1955" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53676,7 +53676,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1956" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53702,7 +53702,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1957" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53728,7 +53728,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1958" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53754,7 +53754,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1959" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53780,7 +53780,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1960" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53806,7 +53806,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1961" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53832,7 +53832,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1962" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53858,7 +53858,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1963" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53884,7 +53884,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1964" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53910,7 +53910,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1965" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53936,7 +53936,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1966" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53962,7 +53962,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1967" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53988,7 +53988,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1968" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54014,7 +54014,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1969" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54040,7 +54040,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1970" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54066,7 +54066,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1971" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54092,7 +54092,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1972" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54118,7 +54118,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1973" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54144,7 +54144,7 @@
         <v>2</v>
       </c>
       <c r="G1974" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54170,7 +54170,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1975" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54196,7 +54196,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1976" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54222,7 +54222,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1977" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54248,7 +54248,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1978" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54274,7 +54274,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1979" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54300,7 +54300,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1980" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54326,7 +54326,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1981" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54352,7 +54352,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1982" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54378,7 +54378,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1983" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54404,7 +54404,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1984" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54430,7 +54430,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1985" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54456,7 +54456,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1986" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54482,7 +54482,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1987" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54508,7 +54508,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1988" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54534,7 +54534,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1989" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54560,7 +54560,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1990" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54586,7 +54586,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1991" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54612,7 +54612,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1992" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54638,7 +54638,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1993" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54664,7 +54664,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1994" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54690,7 +54690,7 @@
         <v>2</v>
       </c>
       <c r="G1995" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54716,7 +54716,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1996" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54742,7 +54742,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1997" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54768,7 +54768,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1998" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54794,7 +54794,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1999" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54820,7 +54820,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2000" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54846,7 +54846,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2001" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54872,7 +54872,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2002" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54898,7 +54898,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2003" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54924,7 +54924,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2004" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54950,7 +54950,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2005" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54976,7 +54976,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2006" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55002,7 +55002,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2007" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55028,7 +55028,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2008" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55054,7 +55054,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2009" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55080,7 +55080,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2010" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55106,7 +55106,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2011" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55132,7 +55132,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2012" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55158,7 +55158,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2013" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55184,7 +55184,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2014" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55210,7 +55210,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2015" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55236,7 +55236,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2016" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55262,7 +55262,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2017" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55288,7 +55288,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2018" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55314,7 +55314,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2019" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55340,7 +55340,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2020" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55366,7 +55366,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2021" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55392,7 +55392,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2022" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55418,7 +55418,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2023" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55444,7 +55444,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2024" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55470,7 +55470,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2025" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -55496,7 +55496,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2026" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55522,7 +55522,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2027" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55548,7 +55548,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2028" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55574,7 +55574,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2029" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55600,7 +55600,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2030" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55626,7 +55626,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2031" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55652,7 +55652,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2032" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55678,7 +55678,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2033" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55704,7 +55704,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2034" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55730,7 +55730,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2035" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55756,7 +55756,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2036" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55782,7 +55782,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2037" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55808,7 +55808,7 @@
         <v>2.25</v>
       </c>
       <c r="G2038" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55834,7 +55834,7 @@
         <v>2.25</v>
       </c>
       <c r="G2039" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55860,7 +55860,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2040" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55886,7 +55886,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2041" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55912,7 +55912,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2042" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55938,7 +55938,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2043" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55964,7 +55964,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2044" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55990,7 +55990,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2045" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56016,7 +56016,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2046" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56042,7 +56042,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2047" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56068,7 +56068,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2048" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56094,7 +56094,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2049" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56120,7 +56120,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2050" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56146,7 +56146,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2051" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56172,7 +56172,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G2052" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56198,7 +56198,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2053" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56224,7 +56224,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G2054" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56250,7 +56250,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G2055" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56276,7 +56276,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G2056" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56302,7 +56302,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2057" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56328,7 +56328,7 @@
         <v>2.25</v>
       </c>
       <c r="G2058" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56354,7 +56354,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2059" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56380,7 +56380,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G2060" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56406,7 +56406,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2061" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56432,7 +56432,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2062" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56458,7 +56458,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2063" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -56484,7 +56484,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2064" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -56510,7 +56510,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2065" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -56536,7 +56536,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2066" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -56562,7 +56562,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2067" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -56588,7 +56588,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2068" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -56614,7 +56614,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2069" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -56640,7 +56640,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2070" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -56666,7 +56666,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2071" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -56692,7 +56692,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2072" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56718,7 +56718,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2073" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56744,7 +56744,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2074" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56770,7 +56770,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2075" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56796,7 +56796,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2076" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56822,7 +56822,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2077" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56848,7 +56848,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2078" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56874,7 +56874,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2079" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56900,7 +56900,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2080" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56926,7 +56926,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2081" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56952,7 +56952,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2082" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56978,7 +56978,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2083" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57004,7 +57004,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2084" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57030,7 +57030,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2085" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57056,7 +57056,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2086" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57082,7 +57082,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2087" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57108,7 +57108,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2088" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57134,7 +57134,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2089" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57160,7 +57160,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2090" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57186,7 +57186,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2091" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57212,7 +57212,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2092" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -57238,7 +57238,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2093" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57264,7 +57264,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2094" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57290,7 +57290,7 @@
         <v>2</v>
       </c>
       <c r="G2095" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -57316,7 +57316,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2096" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -57342,7 +57342,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2097" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57368,7 +57368,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57394,7 +57394,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2099" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57420,7 +57420,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2100" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57446,7 +57446,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2101" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57472,7 +57472,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2102" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -57498,7 +57498,7 @@
         <v>2</v>
       </c>
       <c r="G2103" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -57524,7 +57524,7 @@
         <v>2</v>
       </c>
       <c r="G2104" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57550,7 +57550,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2105" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -57576,7 +57576,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2106" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -57602,7 +57602,7 @@
         <v>2</v>
       </c>
       <c r="G2107" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -57628,7 +57628,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2108" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -57654,7 +57654,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2109" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -57680,7 +57680,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2110" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -57706,7 +57706,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2111" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57732,7 +57732,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2112" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57758,7 +57758,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2113" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57784,7 +57784,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2114" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57810,7 +57810,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2115" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57836,7 +57836,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2116" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57862,7 +57862,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2117" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57888,7 +57888,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2118" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57914,7 +57914,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2119" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57940,7 +57940,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2120" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57966,7 +57966,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2121" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57992,7 +57992,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2122" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58018,7 +58018,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2123" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58044,7 +58044,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2124" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58070,7 +58070,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2125" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58096,7 +58096,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2126" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58122,7 +58122,7 @@
         <v>2</v>
       </c>
       <c r="G2127" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58148,7 +58148,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2128" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58174,7 +58174,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2129" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58200,7 +58200,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2130" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58226,7 +58226,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2131" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58252,7 +58252,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2132" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58278,7 +58278,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2133" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58304,7 +58304,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2134" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -58330,7 +58330,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2135" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -58356,7 +58356,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2136" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -58382,7 +58382,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2137" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -58408,7 +58408,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2138" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -58434,7 +58434,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2139" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -58460,7 +58460,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2140" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -58486,7 +58486,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2141" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -58512,7 +58512,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2142" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -58538,7 +58538,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2143" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -58564,7 +58564,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2144" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -58590,7 +58590,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2145" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -58616,7 +58616,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2146" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -58642,7 +58642,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2147" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -58668,7 +58668,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2148" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -58694,7 +58694,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G2149" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -58720,7 +58720,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2150" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -58746,7 +58746,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2151" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -58772,7 +58772,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2152" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58798,7 +58798,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2153" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58824,7 +58824,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2154" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58850,7 +58850,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2155" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58876,7 +58876,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2156" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58902,7 +58902,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2157" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58928,7 +58928,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2158" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58954,7 +58954,7 @@
         <v>2</v>
       </c>
       <c r="G2159" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58980,7 +58980,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2160" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59006,7 +59006,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2161" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59032,7 +59032,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2162" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59058,7 +59058,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2163" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59084,7 +59084,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2164" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59110,7 +59110,7 @@
         <v>2</v>
       </c>
       <c r="G2165" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59136,7 +59136,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2166" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59162,7 +59162,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2167" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59188,7 +59188,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2168" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59214,7 +59214,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2169" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59240,7 +59240,7 @@
         <v>2</v>
       </c>
       <c r="G2170" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59266,7 +59266,7 @@
         <v>2</v>
       </c>
       <c r="G2171" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59292,7 +59292,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2172" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59318,7 +59318,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2173" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59344,7 +59344,7 @@
         <v>2</v>
       </c>
       <c r="G2174" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -59370,7 +59370,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2175" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59396,7 +59396,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2176" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59422,7 +59422,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2177" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59448,7 +59448,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2178" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59474,7 +59474,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2179" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -59500,7 +59500,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2180" t="s">
-        <v>730</v>
+        <v>707</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -59604,7 +59604,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2184" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -59630,7 +59630,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2185" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -59656,7 +59656,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2186" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -59864,7 +59864,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2194" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59890,7 +59890,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2195" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59916,7 +59916,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2196" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59942,7 +59942,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2197" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59968,7 +59968,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2198" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59994,7 +59994,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2199" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60020,7 +60020,7 @@
         <v>2</v>
       </c>
       <c r="G2200" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60046,7 +60046,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2201" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60072,7 +60072,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2202" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60098,7 +60098,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2203" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60124,7 +60124,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2204" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60176,7 +60176,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2206" t="s">
-        <v>730</v>
+        <v>707</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60254,7 +60254,7 @@
         <v>2</v>
       </c>
       <c r="G2209" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60332,7 +60332,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2212" t="s">
-        <v>730</v>
+        <v>707</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60358,7 +60358,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2213" t="s">
-        <v>730</v>
+        <v>707</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60410,7 +60410,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2215" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60436,7 +60436,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2216" t="s">
-        <v>730</v>
+        <v>707</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60462,7 +60462,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2217" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -60488,7 +60488,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2218" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -60514,7 +60514,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2219" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -60540,7 +60540,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2220" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -60566,7 +60566,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2221" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -60618,7 +60618,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2223" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -60644,7 +60644,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2224" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -60722,7 +60722,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2227" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -60748,7 +60748,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2228" t="s">
-        <v>730</v>
+        <v>707</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61398,7 +61398,7 @@
         <v>2</v>
       </c>
       <c r="G2253" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61424,7 +61424,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2254" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61450,7 +61450,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2255" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61528,7 +61528,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2258" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -61684,7 +61684,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2264" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -61762,7 +61762,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2267" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -61788,7 +61788,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2268" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61814,7 +61814,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2269" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61840,7 +61840,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2270" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -65402,7 +65402,7 @@
         <v>2</v>
       </c>
       <c r="G2407" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68712,7 +68712,7 @@
     </row>
     <row r="2535">
       <c r="A2535" s="1" t="n">
-        <v>46008.6782638889</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B2535" t="n">
         <v>14000</v>
@@ -68733,6 +68733,32 @@
         <v>822</v>
       </c>
       <c r="H2535" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" s="1" t="n">
+        <v>46009.6768981481</v>
+      </c>
+      <c r="B2536" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C2536" t="n">
+        <v>1.99500000476837</v>
+      </c>
+      <c r="D2536" t="n">
+        <v>1.95000004768372</v>
+      </c>
+      <c r="E2536" t="n">
+        <v>1.95000004768372</v>
+      </c>
+      <c r="F2536" t="n">
+        <v>1.99500000476837</v>
+      </c>
+      <c r="G2536" t="s">
+        <v>820</v>
+      </c>
+      <c r="H2536" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DGT.MI.xlsx
+++ b/data/DGT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="825">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="826">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08123874664307</t>
+    <t xml:space="preserve">2.08123898506165</t>
   </si>
   <si>
     <t xml:space="preserve">DGT.MI</t>
@@ -50,19 +50,19 @@
     <t xml:space="preserve">2.03047704696655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96702468395233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00509572029114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04860639572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99421858787537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971487045288</t>
+    <t xml:space="preserve">1.96702456474304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00509595870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04860615730286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99421846866608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971498966217</t>
   </si>
   <si>
     <t xml:space="preserve">1.94889557361603</t>
@@ -71,28 +71,28 @@
     <t xml:space="preserve">1.88544285297394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91444957256317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89632046222687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87637805938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97065055370331</t>
+    <t xml:space="preserve">1.91444969177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89632070064545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87637829780579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97065019607544</t>
   </si>
   <si>
     <t xml:space="preserve">1.92714011669159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93076622486115</t>
+    <t xml:space="preserve">1.93076586723328</t>
   </si>
   <si>
     <t xml:space="preserve">1.8582489490509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80839359760284</t>
+    <t xml:space="preserve">1.80839347839355</t>
   </si>
   <si>
     <t xml:space="preserve">1.82561635971069</t>
@@ -104,19 +104,19 @@
     <t xml:space="preserve">1.64704322814941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75581872463226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71321487426758</t>
+    <t xml:space="preserve">1.75581884384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71321499347687</t>
   </si>
   <si>
     <t xml:space="preserve">1.68964684009552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73134422302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76760268211365</t>
+    <t xml:space="preserve">1.73134410381317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76760280132294</t>
   </si>
   <si>
     <t xml:space="preserve">1.72862470149994</t>
@@ -128,37 +128,37 @@
     <t xml:space="preserve">1.81292581558228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83105528354645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7685090303421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67514336109161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74947333335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69871151447296</t>
+    <t xml:space="preserve">1.83105504512787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76850926876068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6751434803009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74947321414948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69871127605438</t>
   </si>
   <si>
     <t xml:space="preserve">1.74766051769257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7077761888504</t>
+    <t xml:space="preserve">1.70777606964111</t>
   </si>
   <si>
     <t xml:space="preserve">1.70868253707886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69508576393127</t>
+    <t xml:space="preserve">1.69508564472198</t>
   </si>
   <si>
     <t xml:space="preserve">1.77666735649109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70143067836761</t>
+    <t xml:space="preserve">1.70143091678619</t>
   </si>
   <si>
     <t xml:space="preserve">1.69055342674255</t>
@@ -167,22 +167,22 @@
     <t xml:space="preserve">1.73496997356415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64069771766663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62982022762299</t>
+    <t xml:space="preserve">1.64069783687592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6298201084137</t>
   </si>
   <si>
     <t xml:space="preserve">1.63163316249847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68692755699158</t>
+    <t xml:space="preserve">1.68692743778229</t>
   </si>
   <si>
     <t xml:space="preserve">1.68602108955383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6733306646347</t>
+    <t xml:space="preserve">1.67333054542542</t>
   </si>
   <si>
     <t xml:space="preserve">1.74040877819061</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">1.70415008068085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75672495365143</t>
+    <t xml:space="preserve">1.75672507286072</t>
   </si>
   <si>
     <t xml:space="preserve">1.68783390522003</t>
@@ -209,58 +209,58 @@
     <t xml:space="preserve">1.72137308120728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72227954864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67786276340485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63253962993622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66335952281952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66517233848572</t>
+    <t xml:space="preserve">1.72227942943573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67786300182343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63253974914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66335964202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66517245769501</t>
   </si>
   <si>
     <t xml:space="preserve">1.65429484844208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8111127614975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79026436805725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78754472732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78935790061951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66154658794403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69961810112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6624528169632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68330156803131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6588271856308</t>
+    <t xml:space="preserve">1.81111299991608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79026424884796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78754484653473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78935778141022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66154646873474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69961786270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66245293617249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6833016872406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65882706642151</t>
   </si>
   <si>
     <t xml:space="preserve">1.60353291034698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56908738613129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58902943134308</t>
+    <t xml:space="preserve">1.56908714771271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58902955055237</t>
   </si>
   <si>
     <t xml:space="preserve">1.48297345638275</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">1.49566376209259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4920380115509</t>
+    <t xml:space="preserve">1.49203789234161</t>
   </si>
   <si>
     <t xml:space="preserve">1.53192234039307</t>
@@ -278,43 +278,43 @@
     <t xml:space="preserve">1.48387968540192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45215356349945</t>
+    <t xml:space="preserve">1.45215368270874</t>
   </si>
   <si>
     <t xml:space="preserve">1.48569273948669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42858552932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45940542221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49294447898865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46031153202057</t>
+    <t xml:space="preserve">1.42858564853668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4594053030014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49294424057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46031165122986</t>
   </si>
   <si>
     <t xml:space="preserve">1.44127595424652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45034050941467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46846985816956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42586624622345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31255853176117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36422669887543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34156537055969</t>
+    <t xml:space="preserve">1.45034062862396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46846997737885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42586600780487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31255829334259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36422657966614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34156513214111</t>
   </si>
   <si>
     <t xml:space="preserve">1.36875903606415</t>
@@ -329,25 +329,25 @@
     <t xml:space="preserve">1.19653105735779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17296290397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18746638298035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17568242549896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15483367443085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09863328933716</t>
+    <t xml:space="preserve">1.17296278476715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18746626377106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17568254470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15483379364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09863317012787</t>
   </si>
   <si>
     <t xml:space="preserve">1.12401413917542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13307857513428</t>
+    <t xml:space="preserve">1.13307881355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.12582695484161</t>
@@ -356,25 +356,25 @@
     <t xml:space="preserve">1.11313652992249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06962621212006</t>
+    <t xml:space="preserve">1.06962633132935</t>
   </si>
   <si>
     <t xml:space="preserve">1.08684897422791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09500706195831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09410071372986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12038803100586</t>
+    <t xml:space="preserve">1.0950071811676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09410059452057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12038815021515</t>
   </si>
   <si>
     <t xml:space="preserve">1.09228777885437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10769772529602</t>
+    <t xml:space="preserve">1.10769784450531</t>
   </si>
   <si>
     <t xml:space="preserve">1.10951054096222</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">1.12129461765289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09682011604309</t>
+    <t xml:space="preserve">1.09682023525238</t>
   </si>
   <si>
     <t xml:space="preserve">1.08956849575043</t>
@@ -392,10 +392,10 @@
     <t xml:space="preserve">1.08866190910339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07234573364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05149710178375</t>
+    <t xml:space="preserve">1.072345495224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05149686336517</t>
   </si>
   <si>
     <t xml:space="preserve">1.12310755252838</t>
@@ -404,31 +404,31 @@
     <t xml:space="preserve">1.10135245323181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08322310447693</t>
+    <t xml:space="preserve">1.08322322368622</t>
   </si>
   <si>
     <t xml:space="preserve">1.08775556087494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11404287815094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15120792388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21466040611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1847470998764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14576923847198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12220120429993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06237471103668</t>
+    <t xml:space="preserve">1.11404275894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15120780467987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21466016769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18474698066711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1457691192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12220108509064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0623744726181</t>
   </si>
   <si>
     <t xml:space="preserve">1.03336775302887</t>
@@ -446,55 +446,55 @@
     <t xml:space="preserve">0.956318259239197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933656752109528</t>
+    <t xml:space="preserve">0.933656811714172</t>
   </si>
   <si>
     <t xml:space="preserve">1.01523852348328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04877758026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0360871553421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02430319786072</t>
+    <t xml:space="preserve">1.04877769947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03608691692352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02430307865143</t>
   </si>
   <si>
     <t xml:space="preserve">0.990764081478119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05059051513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11494958400726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12854611873627</t>
+    <t xml:space="preserve">1.05059063434601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11494934558868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12854647636414</t>
   </si>
   <si>
     <t xml:space="preserve">1.07506501674652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06418740749359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02067732810974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997109293937683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00617372989655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988044559955597</t>
+    <t xml:space="preserve">1.06418752670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02067744731903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997109234333038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00617396831512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988044619560242</t>
   </si>
   <si>
     <t xml:space="preserve">1.03880655765533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05965518951416</t>
+    <t xml:space="preserve">1.05965507030487</t>
   </si>
   <si>
     <t xml:space="preserve">1.04243230819702</t>
@@ -512,43 +512,43 @@
     <t xml:space="preserve">1.1049782037735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07597148418427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12492060661316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1031653881073</t>
+    <t xml:space="preserve">1.07597160339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12492048740387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10316550731659</t>
   </si>
   <si>
     <t xml:space="preserve">1.2110344171524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19562470912933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21284747123718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14667546749115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1539272069931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20559585094452</t>
+    <t xml:space="preserve">1.19562458992004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21284735202789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14667558670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15392744541168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20559561252594</t>
   </si>
   <si>
     <t xml:space="preserve">1.20196974277496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23188316822052</t>
+    <t xml:space="preserve">1.23188304901123</t>
   </si>
   <si>
     <t xml:space="preserve">1.25363826751709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25817060470581</t>
+    <t xml:space="preserve">1.25817048549652</t>
   </si>
   <si>
     <t xml:space="preserve">1.26089000701904</t>
@@ -560,16 +560,16 @@
     <t xml:space="preserve">1.28717744350433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30893242359161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30530667304993</t>
+    <t xml:space="preserve">1.3089325428009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30530655384064</t>
   </si>
   <si>
     <t xml:space="preserve">1.41226923465729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37963652610779</t>
+    <t xml:space="preserve">1.3796364068985</t>
   </si>
   <si>
     <t xml:space="preserve">1.40320456027985</t>
@@ -578,28 +578,28 @@
     <t xml:space="preserve">1.35244262218475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35697507858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.359694480896</t>
+    <t xml:space="preserve">1.35697519779205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35969424247742</t>
   </si>
   <si>
     <t xml:space="preserve">1.34065854549408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32343602180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35062980651855</t>
+    <t xml:space="preserve">1.32343590259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35062968730927</t>
   </si>
   <si>
     <t xml:space="preserve">1.32887470722198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26995468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1947181224823</t>
+    <t xml:space="preserve">1.26995456218719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19471800327301</t>
   </si>
   <si>
     <t xml:space="preserve">1.14395618438721</t>
@@ -608,31 +608,31 @@
     <t xml:space="preserve">1.2454799413681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25001227855682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26814186573029</t>
+    <t xml:space="preserve">1.25001239776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26814162731171</t>
   </si>
   <si>
     <t xml:space="preserve">1.23278963565826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24185419082642</t>
+    <t xml:space="preserve">1.24185407161713</t>
   </si>
   <si>
     <t xml:space="preserve">1.28173863887787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26451563835144</t>
+    <t xml:space="preserve">1.26451575756073</t>
   </si>
   <si>
     <t xml:space="preserve">1.28264498710632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25091886520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26904797554016</t>
+    <t xml:space="preserve">1.25091874599457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26904809474945</t>
   </si>
   <si>
     <t xml:space="preserve">1.33159410953522</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">1.29624199867249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28536438941956</t>
+    <t xml:space="preserve">1.28536427021027</t>
   </si>
   <si>
     <t xml:space="preserve">1.31437122821808</t>
@@ -653,13 +653,13 @@
     <t xml:space="preserve">1.31799709796906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29896116256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3778235912323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3352198600769</t>
+    <t xml:space="preserve">1.29896152019501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37782371044159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33521997928619</t>
   </si>
   <si>
     <t xml:space="preserve">1.2617963552475</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">1.3107453584671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30711936950684</t>
+    <t xml:space="preserve">1.3071197271347</t>
   </si>
   <si>
     <t xml:space="preserve">1.34247148036957</t>
@@ -677,25 +677,25 @@
     <t xml:space="preserve">1.294429063797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32434213161469</t>
+    <t xml:space="preserve">1.32434237003326</t>
   </si>
   <si>
     <t xml:space="preserve">1.33884584903717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31165182590485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2799254655838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30621302127838</t>
+    <t xml:space="preserve">1.31165194511414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27992558479309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30621325969696</t>
   </si>
   <si>
     <t xml:space="preserve">1.31618416309357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30349385738373</t>
+    <t xml:space="preserve">1.30349361896515</t>
   </si>
   <si>
     <t xml:space="preserve">1.27720642089844</t>
@@ -704,19 +704,19 @@
     <t xml:space="preserve">1.26632869243622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28355133533478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25907707214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24910593032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27539324760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25273156166077</t>
+    <t xml:space="preserve">1.28355157375336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25907719135284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24910604953766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27539336681366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25273168087006</t>
   </si>
   <si>
     <t xml:space="preserve">1.34700381755829</t>
@@ -725,34 +725,34 @@
     <t xml:space="preserve">1.34972333908081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29261612892151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32978105545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23369598388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22372508049011</t>
+    <t xml:space="preserve">1.29261600971222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32978117465973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23369610309601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22372496128082</t>
   </si>
   <si>
     <t xml:space="preserve">1.22916376590729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20468902587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22191214561462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21919250488281</t>
+    <t xml:space="preserve">1.20468926429749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22191190719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21919274330139</t>
   </si>
   <si>
     <t xml:space="preserve">1.22100555896759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21828615665436</t>
+    <t xml:space="preserve">1.21828603744507</t>
   </si>
   <si>
     <t xml:space="preserve">1.22463142871857</t>
@@ -773,46 +773,46 @@
     <t xml:space="preserve">1.15211427211761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15845954418182</t>
+    <t xml:space="preserve">1.1584597826004</t>
   </si>
   <si>
     <t xml:space="preserve">1.08594250679016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10588467121124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07959747314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10679125785828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13217210769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16933727264404</t>
+    <t xml:space="preserve">1.10588490962982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07959735393524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10679113864899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13217222690582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16933715343475</t>
   </si>
   <si>
     <t xml:space="preserve">1.22644436359406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23822820186615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24457359313965</t>
+    <t xml:space="preserve">1.23822832107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24457371234894</t>
   </si>
   <si>
     <t xml:space="preserve">1.2518253326416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24004137516022</t>
+    <t xml:space="preserve">1.24004125595093</t>
   </si>
   <si>
     <t xml:space="preserve">1.20378267765045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20650219917297</t>
+    <t xml:space="preserve">1.20650231838226</t>
   </si>
   <si>
     <t xml:space="preserve">1.24094772338867</t>
@@ -827,40 +827,40 @@
     <t xml:space="preserve">1.23460245132446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24638640880585</t>
+    <t xml:space="preserve">1.24638652801514</t>
   </si>
   <si>
     <t xml:space="preserve">1.2762998342514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27086102962494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29805481433868</t>
+    <t xml:space="preserve">1.27086079120636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29805493354797</t>
   </si>
   <si>
     <t xml:space="preserve">1.22553777694702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15574014186859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11857509613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1602725982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16661763191223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16480481624603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18112099170685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19925034046173</t>
+    <t xml:space="preserve">1.15574026107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11857521533966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16027235984802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16661775112152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16480469703674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18112111091614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19925045967102</t>
   </si>
   <si>
     <t xml:space="preserve">1.11676239967346</t>
@@ -869,22 +869,22 @@
     <t xml:space="preserve">1.09319424629211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09772658348083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17658889293671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17930841445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21375393867493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21556675434113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2862708568573</t>
+    <t xml:space="preserve">1.09772646427155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17658877372742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17930829524994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21375381946564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21556663513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28627109527588</t>
   </si>
   <si>
     <t xml:space="preserve">1.28989672660828</t>
@@ -893,70 +893,70 @@
     <t xml:space="preserve">1.2844580411911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38960766792297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40048515796661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41408205032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38235580921173</t>
+    <t xml:space="preserve">1.38960754871368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40048503875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41408216953278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38235592842102</t>
   </si>
   <si>
     <t xml:space="preserve">1.37057185173035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32796812057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36513340473175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35516202449799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3841689825058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42224037647247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38054299354553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38870108127594</t>
+    <t xml:space="preserve">1.32796835899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36513328552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35516214370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38416874408722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42224013805389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38054287433624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38870120048523</t>
   </si>
   <si>
     <t xml:space="preserve">1.36694610118866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40773677825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39957880973816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39685928821564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38326251506805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38688814640045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50926077365875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57724547386169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57271313667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54551947116852</t>
+    <t xml:space="preserve">1.40773701667786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39957869052887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39685940742493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38326239585876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38688838481903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50926065444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57724571228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57271325588226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54551935195923</t>
   </si>
   <si>
     <t xml:space="preserve">1.55005156993866</t>
@@ -968,16 +968,16 @@
     <t xml:space="preserve">1.48659920692444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44580841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48206686973572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43221127986908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54098701477051</t>
+    <t xml:space="preserve">1.44580829143524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48206698894501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43221151828766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5409871339798</t>
   </si>
   <si>
     <t xml:space="preserve">1.52285766601562</t>
@@ -986,10 +986,10 @@
     <t xml:space="preserve">1.52739000320435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37329137325287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39142060279846</t>
+    <t xml:space="preserve">1.37329125404358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39142036437988</t>
   </si>
   <si>
     <t xml:space="preserve">1.34609746932983</t>
@@ -998,37 +998,37 @@
     <t xml:space="preserve">1.29170966148376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3189035654068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33703279495239</t>
+    <t xml:space="preserve">1.31890380382538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33703291416168</t>
   </si>
   <si>
     <t xml:space="preserve">1.27358043193817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3959527015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30077433586121</t>
+    <t xml:space="preserve">1.39595282077789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30077409744263</t>
   </si>
   <si>
     <t xml:space="preserve">1.33341014385223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31476104259491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30543649196625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31942331790924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24482715129852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24948942661285</t>
+    <t xml:space="preserve">1.3147611618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30543661117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31942343711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24482727050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24948930740356</t>
   </si>
   <si>
     <t xml:space="preserve">1.23084020614624</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">1.21219110488892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25415146350861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23550271987915</t>
+    <t xml:space="preserve">1.2541515827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23550260066986</t>
   </si>
   <si>
     <t xml:space="preserve">1.22617793083191</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">1.29611206054688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31009888648987</t>
+    <t xml:space="preserve">1.31009876728058</t>
   </si>
   <si>
     <t xml:space="preserve">1.32874798774719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28212511539459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26813840866089</t>
+    <t xml:space="preserve">1.28212523460388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26813852787018</t>
   </si>
   <si>
     <t xml:space="preserve">1.30077421665192</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">1.21685326099396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18887972831726</t>
+    <t xml:space="preserve">1.18887984752655</t>
   </si>
   <si>
     <t xml:space="preserve">1.16556835174561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20286667346954</t>
+    <t xml:space="preserve">1.20286655426025</t>
   </si>
   <si>
     <t xml:space="preserve">1.17489290237427</t>
@@ -1094,16 +1094,16 @@
     <t xml:space="preserve">1.1795551776886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2075287103653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32408571243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34739708900452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17023074626923</t>
+    <t xml:space="preserve">1.20752882957458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32408559322357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34739696979523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17023062705994</t>
   </si>
   <si>
     <t xml:space="preserve">1.14691936969757</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">1.13293254375458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25881397724152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746284008026</t>
+    <t xml:space="preserve">1.25881385803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746295928955</t>
   </si>
   <si>
     <t xml:space="preserve">1.22151565551758</t>
@@ -1130,34 +1130,34 @@
     <t xml:space="preserve">1.28678750991821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16090595722198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1515816450119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13759458065033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3613840341568</t>
+    <t xml:space="preserve">1.16090607643127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15158152580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13759481906891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36138391494751</t>
   </si>
   <si>
     <t xml:space="preserve">1.29144990444183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3427346944809</t>
+    <t xml:space="preserve">1.34273481369019</t>
   </si>
   <si>
     <t xml:space="preserve">1.33807253837585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11428332328796</t>
+    <t xml:space="preserve">1.11428344249725</t>
   </si>
   <si>
     <t xml:space="preserve">1.1049587726593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14225709438324</t>
+    <t xml:space="preserve">1.14225697517395</t>
   </si>
   <si>
     <t xml:space="preserve">1.27810597419739</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">1.37278056144714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34437823295593</t>
+    <t xml:space="preserve">1.34437811374664</t>
   </si>
   <si>
     <t xml:space="preserve">1.32544338703156</t>
@@ -1190,13 +1190,13 @@
     <t xml:space="preserve">1.31597578525543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28757345676422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30650842189789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33964443206787</t>
+    <t xml:space="preserve">1.28757357597351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3065083026886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33964431285858</t>
   </si>
   <si>
     <t xml:space="preserve">1.42011785507202</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">1.39644920825958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3207094669342</t>
+    <t xml:space="preserve">1.32070958614349</t>
   </si>
   <si>
     <t xml:space="preserve">1.3349107503891</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">1.28283977508545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27337241172791</t>
+    <t xml:space="preserve">1.27337229251862</t>
   </si>
   <si>
     <t xml:space="preserve">1.26390480995178</t>
@@ -1229,46 +1229,46 @@
     <t xml:space="preserve">1.25917112827301</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29704093933105</t>
+    <t xml:space="preserve">1.29704105854034</t>
   </si>
   <si>
     <t xml:space="preserve">1.2449699640274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23076856136322</t>
+    <t xml:space="preserve">1.23076868057251</t>
   </si>
   <si>
     <t xml:space="preserve">1.22130131721497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2165675163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22603499889374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24023604393005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21183371543884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26863861083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20710015296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24970364570618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25443744659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23550260066986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16923022270203</t>
+    <t xml:space="preserve">1.21656763553619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22603487968445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24023616313934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21183395385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26863873004913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20710003376007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24970388412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25443756580353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23550248146057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16923046112061</t>
   </si>
   <si>
     <t xml:space="preserve">1.18343150615692</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">1.12189304828644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11715924739838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10295820236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0698219537735</t>
+    <t xml:space="preserve">1.11715936660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10295808315277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06982219219208</t>
   </si>
   <si>
     <t xml:space="preserve">1.01775121688843</t>
@@ -1301,22 +1301,22 @@
     <t xml:space="preserve">0.979881227016449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965680062770844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914555907249451</t>
+    <t xml:space="preserve">0.965680241584778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914555847644806</t>
   </si>
   <si>
     <t xml:space="preserve">0.937277734279633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92023640871048</t>
+    <t xml:space="preserve">0.920236349105835</t>
   </si>
   <si>
     <t xml:space="preserve">0.880473077297211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927810370922089</t>
+    <t xml:space="preserve">0.927810311317444</t>
   </si>
   <si>
     <t xml:space="preserve">0.946745216846466</t>
@@ -1331,46 +1331,46 @@
     <t xml:space="preserve">1.07928955554962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10769188404083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13609433174133</t>
+    <t xml:space="preserve">1.10769176483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13609445095062</t>
   </si>
   <si>
     <t xml:space="preserve">1.05562090873718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09349060058594</t>
+    <t xml:space="preserve">1.09349071979523</t>
   </si>
   <si>
     <t xml:space="preserve">1.06035459041595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06508851051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07455587387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04615354537964</t>
+    <t xml:space="preserve">1.06508839130402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07455563545227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04615342617035</t>
   </si>
   <si>
     <t xml:space="preserve">1.03668606281281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04141962528229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11242544651031</t>
+    <t xml:space="preserve">1.04141986370087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1124255657196</t>
   </si>
   <si>
     <t xml:space="preserve">1.1266268491745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08875703811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09822428226471</t>
+    <t xml:space="preserve">1.08875691890717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09822452068329</t>
   </si>
   <si>
     <t xml:space="preserve">1.05088722705841</t>
@@ -1388,13 +1388,13 @@
     <t xml:space="preserve">1.15976285934448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15029549598694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16449677944183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15502905845642</t>
+    <t xml:space="preserve">1.15029537677765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16449666023254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15502917766571</t>
   </si>
   <si>
     <t xml:space="preserve">1.14556169509888</t>
@@ -1403,22 +1403,22 @@
     <t xml:space="preserve">1.17396402359009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13136041164398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08402323722839</t>
+    <t xml:space="preserve">1.13136053085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08402335643768</t>
   </si>
   <si>
     <t xml:space="preserve">1.00828373432159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984614968299866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994082450866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01301729679108</t>
+    <t xml:space="preserve">0.984615087509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99408233165741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01301753520966</t>
   </si>
   <si>
     <t xml:space="preserve">1.18816518783569</t>
@@ -1436,16 +1436,16 @@
     <t xml:space="preserve">1.33027982711792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32551181316376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33981585502625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33504796028137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36365616321564</t>
+    <t xml:space="preserve">1.32551193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33981597423553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33504784107208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36365604400635</t>
   </si>
   <si>
     <t xml:space="preserve">1.32074379920959</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">1.35412001609802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3445839881897</t>
+    <t xml:space="preserve">1.34458410739899</t>
   </si>
   <si>
     <t xml:space="preserve">1.40180039405823</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">1.3588879108429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30167174339294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3922643661499</t>
+    <t xml:space="preserve">1.30167162418365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39226424694061</t>
   </si>
   <si>
     <t xml:space="preserve">1.38272821903229</t>
@@ -1499,43 +1499,43 @@
     <t xml:space="preserve">1.40656840801239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42087244987488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43517649173737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45901656150818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43994450569153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41610443592072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.516233086586</t>
+    <t xml:space="preserve">1.42087233066559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43517661094666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45901668071747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43994462490082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41610431671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51623296737671</t>
   </si>
   <si>
     <t xml:space="preserve">1.50669693946838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53530514240265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54484117031097</t>
+    <t xml:space="preserve">1.53530502319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54484105110168</t>
   </si>
   <si>
     <t xml:space="preserve">1.54007303714752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58298528194427</t>
+    <t xml:space="preserve">1.58298540115356</t>
   </si>
   <si>
     <t xml:space="preserve">1.57344937324524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68788194656372</t>
+    <t xml:space="preserve">1.68788206577301</t>
   </si>
   <si>
     <t xml:space="preserve">1.65450572967529</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">1.70695412158966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7641704082489</t>
+    <t xml:space="preserve">1.76417028903961</t>
   </si>
   <si>
     <t xml:space="preserve">1.74509835243225</t>
@@ -1553,34 +1553,34 @@
     <t xml:space="preserve">1.72602617740631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69741797447205</t>
+    <t xml:space="preserve">1.69741809368134</t>
   </si>
   <si>
     <t xml:space="preserve">1.66880977153778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67357790470123</t>
+    <t xml:space="preserve">1.67357778549194</t>
   </si>
   <si>
     <t xml:space="preserve">1.64020180702209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61159360408783</t>
+    <t xml:space="preserve">1.61159348487854</t>
   </si>
   <si>
     <t xml:space="preserve">1.60682547092438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64973783493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71172213554382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64496970176697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6163614988327</t>
+    <t xml:space="preserve">1.64973771572113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71172201633453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64496982097626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61636161804199</t>
   </si>
   <si>
     <t xml:space="preserve">1.62112975120544</t>
@@ -1589,19 +1589,19 @@
     <t xml:space="preserve">1.63066565990448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63543379306793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77847445011139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75940239429474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68311393260956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7164900302887</t>
+    <t xml:space="preserve">1.63543367385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77847456932068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75940251350403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68311405181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71649014949799</t>
   </si>
   <si>
     <t xml:space="preserve">1.77370655536652</t>
@@ -1619,64 +1619,64 @@
     <t xml:space="preserve">1.788010597229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81661868095398</t>
+    <t xml:space="preserve">1.81661880016327</t>
   </si>
   <si>
     <t xml:space="preserve">1.83092284202576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80708265304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76893842220306</t>
+    <t xml:space="preserve">1.80708277225494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76893854141235</t>
   </si>
   <si>
     <t xml:space="preserve">1.73556232452393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73079431056976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74033033847809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72125828266144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78324258327484</t>
+    <t xml:space="preserve">1.73079419136047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74033045768738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72125816345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78324246406555</t>
   </si>
   <si>
     <t xml:space="preserve">1.7498664855957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6783459186554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6640419960022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69265007972717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80231463909149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75463438034058</t>
+    <t xml:space="preserve">1.67834603786469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66404187679291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69264996051788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80231475830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75463449954987</t>
   </si>
   <si>
     <t xml:space="preserve">1.79277861118317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5686811208725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65927374362946</t>
+    <t xml:space="preserve">1.56868135929108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65927386283875</t>
   </si>
   <si>
     <t xml:space="preserve">1.59252142906189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52576899528503</t>
+    <t xml:space="preserve">1.52576911449432</t>
   </si>
   <si>
     <t xml:space="preserve">1.59728932380676</t>
@@ -1685,22 +1685,22 @@
     <t xml:space="preserve">1.7021861076355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85953116416931</t>
+    <t xml:space="preserve">1.85953104496002</t>
   </si>
   <si>
     <t xml:space="preserve">1.89767527580261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92628335952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82138681411743</t>
+    <t xml:space="preserve">1.92628347873688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82138669490814</t>
   </si>
   <si>
     <t xml:space="preserve">1.83569085597992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86429905891418</t>
+    <t xml:space="preserve">1.86429917812347</t>
   </si>
   <si>
     <t xml:space="preserve">1.90721130371094</t>
@@ -1712,10 +1712,10 @@
     <t xml:space="preserve">1.99303579330444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0597882270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00257182121277</t>
+    <t xml:space="preserve">2.05978846549988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00257205963135</t>
   </si>
   <si>
     <t xml:space="preserve">2.07886028289795</t>
@@ -1727,16 +1727,16 @@
     <t xml:space="preserve">2.1074686050415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08839654922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0979323387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14561295509338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27911734580994</t>
+    <t xml:space="preserve">2.08839631080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09793257713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1456127166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27911758422852</t>
   </si>
   <si>
     <t xml:space="preserve">2.19329309463501</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">2.22190117835999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25050926208496</t>
+    <t xml:space="preserve">2.25050950050354</t>
   </si>
   <si>
     <t xml:space="preserve">2.02164387702942</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">2.09847211837769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08884620666504</t>
+    <t xml:space="preserve">2.08884644508362</t>
   </si>
   <si>
     <t xml:space="preserve">2.10809826850891</t>
@@ -1778,19 +1778,19 @@
     <t xml:space="preserve">2.00221180915833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95408189296722</t>
+    <t xml:space="preserve">1.95408177375793</t>
   </si>
   <si>
     <t xml:space="preserve">2.03109002113342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0214638710022</t>
+    <t xml:space="preserve">2.02146410942078</t>
   </si>
   <si>
     <t xml:space="preserve">2.05996799468994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.944455742836</t>
+    <t xml:space="preserve">1.94445586204529</t>
   </si>
   <si>
     <t xml:space="preserve">1.9733339548111</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">1.83856964111328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82894372940063</t>
+    <t xml:space="preserve">1.82894361019135</t>
   </si>
   <si>
     <t xml:space="preserve">1.86744773387909</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">1.88669979572296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87707388401031</t>
+    <t xml:space="preserve">1.87707376480103</t>
   </si>
   <si>
     <t xml:space="preserve">1.89632570743561</t>
@@ -1823,10 +1823,10 @@
     <t xml:space="preserve">1.92520380020142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99258589744568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05034208297729</t>
+    <t xml:space="preserve">1.99258577823639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05034232139587</t>
   </si>
   <si>
     <t xml:space="preserve">2.11772418022156</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">2.1562283039093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20435833930969</t>
+    <t xml:space="preserve">2.20435857772827</t>
   </si>
   <si>
     <t xml:space="preserve">2.16585445404053</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">2.14660239219666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07922005653381</t>
+    <t xml:space="preserve">2.07922029495239</t>
   </si>
   <si>
     <t xml:space="preserve">2.24286246299744</t>
@@ -1856,52 +1856,52 @@
     <t xml:space="preserve">2.27174043655396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30061841011047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2813663482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1851065158844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19473242759705</t>
+    <t xml:space="preserve">2.30061864852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28136658668518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18510627746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19473218917847</t>
   </si>
   <si>
     <t xml:space="preserve">2.12735033035278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13697624206543</t>
+    <t xml:space="preserve">2.13697600364685</t>
   </si>
   <si>
     <t xml:space="preserve">2.01183795928955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87226068973541</t>
+    <t xml:space="preserve">1.8722608089447</t>
   </si>
   <si>
     <t xml:space="preserve">1.96370780467987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06959438323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17548012733459</t>
+    <t xml:space="preserve">2.06959414482117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17548036575317</t>
   </si>
   <si>
     <t xml:space="preserve">2.23323631286621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31024479866028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35837459564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42575693130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39687871932983</t>
+    <t xml:space="preserve">2.3102445602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35837483406067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42575669288635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39687895774841</t>
   </si>
   <si>
     <t xml:space="preserve">2.40650486946106</t>
@@ -1919,13 +1919,13 @@
     <t xml:space="preserve">2.34874868392944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29099273681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36800098419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38725280761719</t>
+    <t xml:space="preserve">2.29099249839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36800050735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38725256919861</t>
   </si>
   <si>
     <t xml:space="preserve">2.21398448944092</t>
@@ -1943,10 +1943,10 @@
     <t xml:space="preserve">2.4642608165741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49313902854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52201676368713</t>
+    <t xml:space="preserve">2.49313879013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52201700210571</t>
   </si>
   <si>
     <t xml:space="preserve">2.50276470184326</t>
@@ -1961,10 +1961,10 @@
     <t xml:space="preserve">2.54126906394958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51239109039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47388672828674</t>
+    <t xml:space="preserve">2.51239085197449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47388696670532</t>
   </si>
   <si>
     <t xml:space="preserve">2.48351287841797</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">2.53164315223694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63752937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69528532028198</t>
+    <t xml:space="preserve">2.63752913475037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6952850818634</t>
   </si>
   <si>
     <t xml:space="preserve">2.82042360305786</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">2.67603325843811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60865139961243</t>
+    <t xml:space="preserve">2.60865116119385</t>
   </si>
   <si>
     <t xml:space="preserve">2.66640734672546</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">2.58939933776855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56052112579346</t>
+    <t xml:space="preserve">2.56052088737488</t>
   </si>
   <si>
     <t xml:space="preserve">2.62790322303772</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">2.57977318763733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38258790969849</t>
+    <t xml:space="preserve">2.38258814811707</t>
   </si>
   <si>
     <t xml:space="preserve">2.29506421089172</t>
@@ -2021,13 +2021,13 @@
     <t xml:space="preserve">2.28533935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32423877716064</t>
+    <t xml:space="preserve">2.32423901557922</t>
   </si>
   <si>
     <t xml:space="preserve">2.25616478919983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23671531677246</t>
+    <t xml:space="preserve">2.23671507835388</t>
   </si>
   <si>
     <t xml:space="preserve">2.21726560592651</t>
@@ -2039,16 +2039,16 @@
     <t xml:space="preserve">2.34368872642517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26588988304138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3047890663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24643993377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1102921962738</t>
+    <t xml:space="preserve">2.2658896446228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30478882789612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24644017219543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11029243469238</t>
   </si>
   <si>
     <t xml:space="preserve">2.15891647338867</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">2.19781565666199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16864132881165</t>
+    <t xml:space="preserve">2.16864109039307</t>
   </si>
   <si>
     <t xml:space="preserve">2.18809103965759</t>
@@ -2078,16 +2078,16 @@
     <t xml:space="preserve">2.13946676254272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09084272384644</t>
+    <t xml:space="preserve">2.09084248542786</t>
   </si>
   <si>
     <t xml:space="preserve">2.10056734085083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27561450004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08111763000488</t>
+    <t xml:space="preserve">2.27561473846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08111786842346</t>
   </si>
   <si>
     <t xml:space="preserve">1.97414433956146</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">1.98386907577515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9644193649292</t>
+    <t xml:space="preserve">1.96441948413849</t>
   </si>
   <si>
     <t xml:space="preserve">1.94496977329254</t>
@@ -2114,13 +2114,13 @@
     <t xml:space="preserve">2.02276849746704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03249335289001</t>
+    <t xml:space="preserve">2.03249311447144</t>
   </si>
   <si>
     <t xml:space="preserve">2.01304364204407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07139277458191</t>
+    <t xml:space="preserve">2.07139301300049</t>
   </si>
   <si>
     <t xml:space="preserve">2.04221820831299</t>
@@ -2132,76 +2132,79 @@
     <t xml:space="preserve">1.93524491786957</t>
   </si>
   <si>
+    <t xml:space="preserve">1.95469450950623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91579520702362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93038249015808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06166768074036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91093277931213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1491916179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00331878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86717092990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92552006244659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81854665279388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84772121906281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8866206407547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83313393592834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85258364677429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89634561538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92065763473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95961833000183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96946561336517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01870226860046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96454191207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98916029930115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00885486602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99900758266449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97931289672852</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.95469462871552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91579520702362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93038249015808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06166791915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91093289852142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1491916179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00331878662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86717092990875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92552006244659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81854677200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84772133827209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8866206407547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83313405513763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85258364677429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89634561538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92065763473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95961833000183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96946561336517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01870226860046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96454191207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98916029930115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00885486602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99900758266449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97931289672852</t>
   </si>
   <si>
     <t xml:space="preserve">1.9497709274292</t>
@@ -59497,7 +59500,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2180" t="s">
-        <v>706</v>
+        <v>730</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -59523,7 +59526,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2181" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59549,7 +59552,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2182" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59575,7 +59578,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2183" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59679,7 +59682,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2187" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59705,7 +59708,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2188" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59731,7 +59734,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2189" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59757,7 +59760,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2190" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59783,7 +59786,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2191" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59809,7 +59812,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2192" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59835,7 +59838,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2193" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60147,7 +60150,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2205" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60173,7 +60176,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2206" t="s">
-        <v>706</v>
+        <v>730</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60199,7 +60202,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2207" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60225,7 +60228,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2208" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60277,7 +60280,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2210" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60303,7 +60306,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2211" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60329,7 +60332,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2212" t="s">
-        <v>706</v>
+        <v>730</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60355,7 +60358,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2213" t="s">
-        <v>706</v>
+        <v>730</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60381,7 +60384,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2214" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60433,7 +60436,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2216" t="s">
-        <v>706</v>
+        <v>730</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60589,7 +60592,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60667,7 +60670,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2225" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60693,7 +60696,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2226" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60745,7 +60748,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2228" t="s">
-        <v>706</v>
+        <v>730</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60771,7 +60774,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2229" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60797,7 +60800,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2230" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60823,7 +60826,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2231" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60849,7 +60852,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2232" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60875,7 +60878,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2233" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60901,7 +60904,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2234" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60927,7 +60930,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2235" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60953,7 +60956,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2236" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60979,7 +60982,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2237" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61005,7 +61008,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2238" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61031,7 +61034,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2239" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61057,7 +61060,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2240" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61083,7 +61086,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G2241" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61109,7 +61112,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2242" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61135,7 +61138,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2243" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61161,7 +61164,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G2244" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61187,7 +61190,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2245" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61213,7 +61216,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2246" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61239,7 +61242,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2247" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61265,7 +61268,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2248" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61291,7 +61294,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2249" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61317,7 +61320,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2250" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61343,7 +61346,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2251" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61369,7 +61372,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2252" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61473,7 +61476,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2256" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -61499,7 +61502,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2257" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -61551,7 +61554,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2259" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -61577,7 +61580,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2260" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -61603,7 +61606,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2261" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -61629,7 +61632,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -61655,7 +61658,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2263" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -61707,7 +61710,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2265" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61733,7 +61736,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2266" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61863,7 +61866,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2271" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61889,7 +61892,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2272" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61915,7 +61918,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2273" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61941,7 +61944,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2274" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61967,7 +61970,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2275" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61993,7 +61996,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2276" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62019,7 +62022,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2277" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62045,7 +62048,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2278" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62071,7 +62074,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2279" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62097,7 +62100,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2280" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62123,7 +62126,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2281" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62149,7 +62152,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2282" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62175,7 +62178,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2283" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62201,7 +62204,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2284" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62227,7 +62230,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2285" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62253,7 +62256,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2286" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62279,7 +62282,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2287" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62305,7 +62308,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2288" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62331,7 +62334,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2289" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62357,7 +62360,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2290" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62383,7 +62386,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2291" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62409,7 +62412,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2292" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62435,7 +62438,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2293" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62461,7 +62464,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2294" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -62487,7 +62490,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2295" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -62513,7 +62516,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2296" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -62539,7 +62542,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2297" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -62565,7 +62568,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2298" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -62591,7 +62594,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2299" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -62617,7 +62620,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2300" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -62643,7 +62646,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2301" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -62669,7 +62672,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2302" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -62695,7 +62698,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2303" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62721,7 +62724,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2304" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62747,7 +62750,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62773,7 +62776,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2306" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62799,7 +62802,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G2307" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62825,7 +62828,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2308" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62851,7 +62854,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2309" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62877,7 +62880,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2310" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62903,7 +62906,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2311" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62929,7 +62932,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2312" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62955,7 +62958,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2313" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62981,7 +62984,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2314" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63007,7 +63010,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2315" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63033,7 +63036,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2316" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63059,7 +63062,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2317" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63085,7 +63088,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2318" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63111,7 +63114,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2319" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63137,7 +63140,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2320" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63163,7 +63166,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2321" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63189,7 +63192,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2322" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63215,7 +63218,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2323" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63241,7 +63244,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2324" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63267,7 +63270,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2325" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63293,7 +63296,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2326" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63319,7 +63322,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2327" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63345,7 +63348,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2328" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63371,7 +63374,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2329" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63397,7 +63400,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2330" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63423,7 +63426,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2331" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63449,7 +63452,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2332" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63475,7 +63478,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2333" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -63501,7 +63504,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2334" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -63527,7 +63530,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2335" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -63553,7 +63556,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2336" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -63579,7 +63582,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2337" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -63605,7 +63608,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2338" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -63631,7 +63634,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2339" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -63657,7 +63660,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G2340" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -63683,7 +63686,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2341" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63709,7 +63712,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2342" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63735,7 +63738,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63761,7 +63764,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2344" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63787,7 +63790,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2345" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63813,7 +63816,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2346" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63839,7 +63842,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2347" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63865,7 +63868,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63891,7 +63894,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63917,7 +63920,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2350" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63943,7 +63946,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2351" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63969,7 +63972,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G2352" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63995,7 +63998,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2353" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64021,7 +64024,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2354" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64047,7 +64050,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2355" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64073,7 +64076,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2356" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64099,7 +64102,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G2357" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64125,7 +64128,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2358" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64151,7 +64154,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G2359" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64177,7 +64180,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G2360" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64203,7 +64206,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2361" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64229,7 +64232,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2362" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64255,7 +64258,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2363" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64281,7 +64284,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G2364" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64307,7 +64310,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2365" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64333,7 +64336,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64359,7 +64362,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G2367" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64385,7 +64388,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2368" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64411,7 +64414,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2369" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64437,7 +64440,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2370" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64463,7 +64466,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2371" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64489,7 +64492,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2372" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -64515,7 +64518,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2373" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -64541,7 +64544,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G2374" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -64567,7 +64570,7 @@
         <v>1.625</v>
       </c>
       <c r="G2375" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -64593,7 +64596,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G2376" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -64619,7 +64622,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G2377" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -64645,7 +64648,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2378" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -64671,7 +64674,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G2379" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -64697,7 +64700,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2380" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64723,7 +64726,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2381" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64749,7 +64752,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2382" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64775,7 +64778,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G2383" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64801,7 +64804,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2384" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64827,7 +64830,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2385" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64853,7 +64856,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64879,7 +64882,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2387" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64905,7 +64908,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2388" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64931,7 +64934,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64957,7 +64960,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2390" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64983,7 +64986,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2391" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65009,7 +65012,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2392" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65035,7 +65038,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G2393" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65061,7 +65064,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G2394" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65087,7 +65090,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2395" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65113,7 +65116,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2396" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65139,7 +65142,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2397" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65165,7 +65168,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2398" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65191,7 +65194,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2399" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65217,7 +65220,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2400" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65243,7 +65246,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2401" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65269,7 +65272,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2402" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65295,7 +65298,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2403" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65321,7 +65324,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2404" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65347,7 +65350,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2405" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65373,7 +65376,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2406" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65425,7 +65428,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2408" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65451,7 +65454,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2409" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65477,7 +65480,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2410" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -65503,7 +65506,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2411" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65529,7 +65532,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2412" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65555,7 +65558,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2413" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65581,7 +65584,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2414" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65607,7 +65610,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2415" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65633,7 +65636,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2416" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65659,7 +65662,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2417" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65685,7 +65688,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2418" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65711,7 +65714,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2419" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65737,7 +65740,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2420" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65763,7 +65766,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2421" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65789,7 +65792,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65815,7 +65818,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2423" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65841,7 +65844,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2424" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65867,7 +65870,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2425" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65893,7 +65896,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2426" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65919,7 +65922,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2427" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65945,7 +65948,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2428" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65971,7 +65974,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2429" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65997,7 +66000,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2430" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66023,7 +66026,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2431" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66049,7 +66052,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2432" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66075,7 +66078,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2433" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66101,7 +66104,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2434" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66127,7 +66130,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2435" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66153,7 +66156,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2436" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66179,7 +66182,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2437" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66205,7 +66208,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2438" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66231,7 +66234,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2439" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66257,7 +66260,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2440" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66283,7 +66286,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2441" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66309,7 +66312,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2442" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66335,7 +66338,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2443" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66361,7 +66364,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2444" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66387,7 +66390,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2445" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66413,7 +66416,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2446" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66439,7 +66442,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2447" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66465,7 +66468,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2448" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -66491,7 +66494,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2449" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -66517,7 +66520,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2450" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66543,7 +66546,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2451" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66569,7 +66572,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2452" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66595,7 +66598,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2453" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66621,7 +66624,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2454" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66647,7 +66650,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2455" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66673,7 +66676,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2456" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66699,7 +66702,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2457" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66725,7 +66728,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2458" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66751,7 +66754,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2459" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66777,7 +66780,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2460" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66803,7 +66806,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2461" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66829,7 +66832,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2462" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66855,7 +66858,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2463" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66881,7 +66884,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2464" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66907,7 +66910,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2465" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66933,7 +66936,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2466" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66959,7 +66962,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2467" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66985,7 +66988,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2468" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67011,7 +67014,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2469" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67037,7 +67040,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2470" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67063,7 +67066,7 @@
         <v>2</v>
       </c>
       <c r="G2471" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67089,7 +67092,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2472" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67115,7 +67118,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2473" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67141,7 +67144,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2474" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67167,7 +67170,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2475" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67193,7 +67196,7 @@
         <v>2</v>
       </c>
       <c r="G2476" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67219,7 +67222,7 @@
         <v>2</v>
       </c>
       <c r="G2477" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67245,7 +67248,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2478" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67271,7 +67274,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2479" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67297,7 +67300,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2480" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67323,7 +67326,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2481" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67349,7 +67352,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2482" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67375,7 +67378,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2483" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67401,7 +67404,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2484" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67427,7 +67430,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2485" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67453,7 +67456,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2486" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67479,7 +67482,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2487" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -67505,7 +67508,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2488" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67531,7 +67534,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2489" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67557,7 +67560,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2490" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67583,7 +67586,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2491" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67609,7 +67612,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2492" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67635,7 +67638,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2493" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67661,7 +67664,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2494" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67687,7 +67690,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2495" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67713,7 +67716,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2496" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67739,7 +67742,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2497" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67765,7 +67768,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2498" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67791,7 +67794,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2499" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67817,7 +67820,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2500" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67843,7 +67846,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2501" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67869,7 +67872,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2502" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -67895,7 +67898,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2503" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -67921,7 +67924,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2504" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67947,7 +67950,7 @@
         <v>2</v>
       </c>
       <c r="G2505" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67973,7 +67976,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2506" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -67999,7 +68002,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2507" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68025,7 +68028,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2508" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68051,7 +68054,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2509" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68077,7 +68080,7 @@
         <v>2</v>
       </c>
       <c r="G2510" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68103,7 +68106,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2511" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68129,7 +68132,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2512" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68155,7 +68158,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2513" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -68181,7 +68184,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2514" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -68207,7 +68210,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2515" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -68233,7 +68236,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2516" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -68259,7 +68262,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2517" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -68285,7 +68288,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2518" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -68311,7 +68314,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2519" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -68337,7 +68340,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2520" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -68363,7 +68366,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2521" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -68389,7 +68392,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2522" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -68415,7 +68418,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2523" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -68441,7 +68444,7 @@
         <v>2</v>
       </c>
       <c r="G2524" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -68467,7 +68470,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2525" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -68493,7 +68496,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2526" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -68519,7 +68522,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2527" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -68545,7 +68548,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2528" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -68571,7 +68574,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2529" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -68597,7 +68600,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2530" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -68623,7 +68626,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2531" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -68649,7 +68652,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2532" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -68675,7 +68678,7 @@
         <v>2</v>
       </c>
       <c r="G2533" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -68701,7 +68704,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2534" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -68727,7 +68730,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2535" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -68753,7 +68756,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2536" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -68761,7 +68764,7 @@
     </row>
     <row r="2537">
       <c r="A2537" s="1" t="n">
-        <v>46010.5094444444</v>
+        <v>46010.3333333333</v>
       </c>
       <c r="B2537" t="n">
         <v>5000</v>
@@ -68779,9 +68782,35 @@
         <v>2</v>
       </c>
       <c r="G2537" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2537" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" s="1" t="n">
+        <v>46013.6526157407</v>
+      </c>
+      <c r="B2538" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C2538" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="D2538" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="E2538" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="F2538" t="n">
+        <v>1.98000001907349</v>
+      </c>
+      <c r="G2538" t="s">
+        <v>814</v>
+      </c>
+      <c r="H2538" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DGT.MI.xlsx
+++ b/data/DGT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="826">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08123898506165</t>
+    <t xml:space="preserve">2.08123874664307</t>
   </si>
   <si>
     <t xml:space="preserve">DGT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05767059326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03047704696655</t>
+    <t xml:space="preserve">2.05767035484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03047680854797</t>
   </si>
   <si>
     <t xml:space="preserve">1.96702456474304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0050961971283</t>
+    <t xml:space="preserve">2.00509572029114</t>
   </si>
   <si>
     <t xml:space="preserve">2.04860615730286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99421846866608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971522808075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94889557361603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88544273376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91444969177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89632058143616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8763781785965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97065043449402</t>
+    <t xml:space="preserve">1.99421858787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971487045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94889521598816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88544285297394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91444957256317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89632070064545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87637829780579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97065007686615</t>
   </si>
   <si>
     <t xml:space="preserve">1.92714011669159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93076610565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85824906826019</t>
+    <t xml:space="preserve">1.93076598644257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85824882984161</t>
   </si>
   <si>
     <t xml:space="preserve">1.80839359760284</t>
@@ -98,49 +98,49 @@
     <t xml:space="preserve">1.8256162405014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75128638744354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64704322814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75581884384155</t>
+    <t xml:space="preserve">1.75128626823425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64704310894012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75581860542297</t>
   </si>
   <si>
     <t xml:space="preserve">1.71321487426758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68964672088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73134398460388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76760268211365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72862482070923</t>
+    <t xml:space="preserve">1.68964684009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73134434223175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76760280132294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72862470149994</t>
   </si>
   <si>
     <t xml:space="preserve">1.7585381269455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81292581558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83105504512787</t>
+    <t xml:space="preserve">1.81292593479156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83105516433716</t>
   </si>
   <si>
     <t xml:space="preserve">1.76850914955139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67514359951019</t>
+    <t xml:space="preserve">1.67514336109161</t>
   </si>
   <si>
     <t xml:space="preserve">1.74947345256805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69871139526367</t>
+    <t xml:space="preserve">1.69871151447296</t>
   </si>
   <si>
     <t xml:space="preserve">1.74766051769257</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">1.70777606964111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70868253707886</t>
+    <t xml:space="preserve">1.70868265628815</t>
   </si>
   <si>
     <t xml:space="preserve">1.69508564472198</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">1.77666735649109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70143091678619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69055342674255</t>
+    <t xml:space="preserve">1.7014307975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69055354595184</t>
   </si>
   <si>
     <t xml:space="preserve">1.73496997356415</t>
@@ -176,22 +176,22 @@
     <t xml:space="preserve">1.63163316249847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68692743778229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68602097034454</t>
+    <t xml:space="preserve">1.686927318573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68602120876312</t>
   </si>
   <si>
     <t xml:space="preserve">1.67333054542542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7404088973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70415008068085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75672507286072</t>
+    <t xml:space="preserve">1.74040877819061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70415031909943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75672519207001</t>
   </si>
   <si>
     <t xml:space="preserve">1.68783390522003</t>
@@ -206,22 +206,22 @@
     <t xml:space="preserve">1.68420815467834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72137331962585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72227942943573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67786300182343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63253974914551</t>
+    <t xml:space="preserve">1.72137320041656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72227954864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67786276340485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63253962993622</t>
   </si>
   <si>
     <t xml:space="preserve">1.66335952281952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66517245769501</t>
+    <t xml:space="preserve">1.66517233848572</t>
   </si>
   <si>
     <t xml:space="preserve">1.65429496765137</t>
@@ -230,28 +230,28 @@
     <t xml:space="preserve">1.81111299991608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79026424884796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78754472732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78935778141022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66154646873474</t>
+    <t xml:space="preserve">1.79026436805725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78754496574402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78935766220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66154634952545</t>
   </si>
   <si>
     <t xml:space="preserve">1.69961798191071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66245293617249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68330180644989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6588271856308</t>
+    <t xml:space="preserve">1.66245305538177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6833016872406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65882730484009</t>
   </si>
   <si>
     <t xml:space="preserve">1.60353291034698</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">1.58902943134308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48297357559204</t>
+    <t xml:space="preserve">1.48297345638275</t>
   </si>
   <si>
     <t xml:space="preserve">1.49566376209259</t>
@@ -275,34 +275,34 @@
     <t xml:space="preserve">1.53192222118378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48387980461121</t>
+    <t xml:space="preserve">1.48387968540192</t>
   </si>
   <si>
     <t xml:space="preserve">1.45215356349945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4856926202774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42858552932739</t>
+    <t xml:space="preserve">1.48569273948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42858564853668</t>
   </si>
   <si>
     <t xml:space="preserve">1.4594053030014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49294435977936</t>
+    <t xml:space="preserve">1.49294447898865</t>
   </si>
   <si>
     <t xml:space="preserve">1.46031165122986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44127607345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45034074783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46846997737885</t>
+    <t xml:space="preserve">1.44127595424652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45034062862396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46846973896027</t>
   </si>
   <si>
     <t xml:space="preserve">1.42586612701416</t>
@@ -314,88 +314,88 @@
     <t xml:space="preserve">1.36422669887543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3415652513504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36875891685486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33250045776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27811253070831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19653105735779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17296278476715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18746626377106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17568254470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15483379364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09863305091858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12401413917542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13307881355286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12582695484161</t>
+    <t xml:space="preserve">1.34156513214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36875903606415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33250057697296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2781126499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19653117656708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17296314239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18746650218964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17568242549896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15483391284943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09863317012787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12401390075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13307869434357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1258270740509</t>
   </si>
   <si>
     <t xml:space="preserve">1.11313652992249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06962621212006</t>
+    <t xml:space="preserve">1.06962609291077</t>
   </si>
   <si>
     <t xml:space="preserve">1.08684897422791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0950071811676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09410059452057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12038815021515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09228789806366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10769760608673</t>
+    <t xml:space="preserve">1.09500706195831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09410071372986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12038791179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09228777885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10769772529602</t>
   </si>
   <si>
     <t xml:space="preserve">1.10951066017151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12129461765289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09682023525238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08956849575043</t>
+    <t xml:space="preserve">1.12129473686218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09682011604309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08956861495972</t>
   </si>
   <si>
     <t xml:space="preserve">1.08866190910339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.072345495224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05149698257446</t>
+    <t xml:space="preserve">1.07234561443329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05149686336517</t>
   </si>
   <si>
     <t xml:space="preserve">1.12310755252838</t>
@@ -413,61 +413,61 @@
     <t xml:space="preserve">1.11404287815094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15120780467987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21466016769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18474698066711</t>
+    <t xml:space="preserve">1.15120804309845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21466028690338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1847470998764</t>
   </si>
   <si>
     <t xml:space="preserve">1.1457691192627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12220108509064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0623744726181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03336775302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934563279151917</t>
+    <t xml:space="preserve">1.12220096588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06237471103668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03336763381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934563338756561</t>
   </si>
   <si>
     <t xml:space="preserve">0.945440828800201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977166891098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956318259239197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933656692504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01523852348328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04877758026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03608703613281</t>
+    <t xml:space="preserve">0.977167010307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956318318843842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933656811714172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01523840427399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04877746105194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0360871553421</t>
   </si>
   <si>
     <t xml:space="preserve">1.02430307865143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990763962268829</t>
+    <t xml:space="preserve">0.990764021873474</t>
   </si>
   <si>
     <t xml:space="preserve">1.05059051513672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11494946479797</t>
+    <t xml:space="preserve">1.11494934558868</t>
   </si>
   <si>
     <t xml:space="preserve">1.12854635715485</t>
@@ -476,28 +476,28 @@
     <t xml:space="preserve">1.07506501674652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06418764591217</t>
+    <t xml:space="preserve">1.06418752670288</t>
   </si>
   <si>
     <t xml:space="preserve">1.02067732810974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997109234333038</t>
+    <t xml:space="preserve">0.997109293937683</t>
   </si>
   <si>
     <t xml:space="preserve">1.00617396831512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988044619560242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03880655765533</t>
+    <t xml:space="preserve">0.988044559955597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03880631923676</t>
   </si>
   <si>
     <t xml:space="preserve">1.05965518951416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04243230819702</t>
+    <t xml:space="preserve">1.04243242740631</t>
   </si>
   <si>
     <t xml:space="preserve">1.06328105926514</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">1.05693566799164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10407197475433</t>
+    <t xml:space="preserve">1.10407185554504</t>
   </si>
   <si>
     <t xml:space="preserve">1.1049782037735</t>
@@ -515,10 +515,10 @@
     <t xml:space="preserve">1.07597160339355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12492048740387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10316550731659</t>
+    <t xml:space="preserve">1.12492060661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1031653881073</t>
   </si>
   <si>
     <t xml:space="preserve">1.2110344171524</t>
@@ -527,19 +527,19 @@
     <t xml:space="preserve">1.19562458992004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21284747123718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14667558670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15392744541168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20559561252594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20196974277496</t>
+    <t xml:space="preserve">1.21284735202789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14667570590973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15392732620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20559573173523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20196986198425</t>
   </si>
   <si>
     <t xml:space="preserve">1.23188304901123</t>
@@ -548,22 +548,22 @@
     <t xml:space="preserve">1.25363826751709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25817036628723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26088988780975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25545120239258</t>
+    <t xml:space="preserve">1.25817060470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26089000701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25545108318329</t>
   </si>
   <si>
     <t xml:space="preserve">1.28717732429504</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30893242359161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30530655384064</t>
+    <t xml:space="preserve">1.3089325428009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30530667304993</t>
   </si>
   <si>
     <t xml:space="preserve">1.41226923465729</t>
@@ -572,52 +572,52 @@
     <t xml:space="preserve">1.3796364068985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40320467948914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35244262218475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35697507858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35969424247742</t>
+    <t xml:space="preserve">1.40320456027985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35244274139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35697495937347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35969436168671</t>
   </si>
   <si>
     <t xml:space="preserve">1.34065866470337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32343578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35062968730927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3288745880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26995456218719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19471800327301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14395618438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24548006057739</t>
+    <t xml:space="preserve">1.32343590259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35062980651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32887470722198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26995444297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1947181224823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1439563035965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2454799413681</t>
   </si>
   <si>
     <t xml:space="preserve">1.25001239776611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.268141746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23278951644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24185419082642</t>
+    <t xml:space="preserve">1.26814150810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23278963565826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24185431003571</t>
   </si>
   <si>
     <t xml:space="preserve">1.28173863887787</t>
@@ -629,28 +629,28 @@
     <t xml:space="preserve">1.28264498710632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25091874599457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26904809474945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33159410953522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29624211788177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28536427021027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31437134742737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30983901023865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31799721717834</t>
+    <t xml:space="preserve">1.25091886520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26904821395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33159387111664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29624199867249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28536450862885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31437146663666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30983889102936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31799697875977</t>
   </si>
   <si>
     <t xml:space="preserve">1.29896140098572</t>
@@ -674,25 +674,25 @@
     <t xml:space="preserve">1.34247159957886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29442894458771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32434248924255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33884596824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31165194511414</t>
+    <t xml:space="preserve">1.294429063797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32434225082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33884572982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31165182590485</t>
   </si>
   <si>
     <t xml:space="preserve">1.2799254655838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30621314048767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31618416309357</t>
+    <t xml:space="preserve">1.30621290206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31618404388428</t>
   </si>
   <si>
     <t xml:space="preserve">1.30349361896515</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">1.26632857322693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28355157375336</t>
+    <t xml:space="preserve">1.28355169296265</t>
   </si>
   <si>
     <t xml:space="preserve">1.25907707214355</t>
@@ -713,28 +713,28 @@
     <t xml:space="preserve">1.24910593032837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27539336681366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25273168087006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34700393676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34972333908081</t>
+    <t xml:space="preserve">1.27539324760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25273156166077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34700381755829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34972321987152</t>
   </si>
   <si>
     <t xml:space="preserve">1.29261612892151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32978129386902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23369610309601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22372496128082</t>
+    <t xml:space="preserve">1.32978117465973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23369598388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22372508049011</t>
   </si>
   <si>
     <t xml:space="preserve">1.229163646698</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">1.20468926429749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22191202640533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2191926240921</t>
+    <t xml:space="preserve">1.22191190719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21919274330139</t>
   </si>
   <si>
     <t xml:space="preserve">1.22100555896759</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">1.21828615665436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22463142871857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21012794971466</t>
+    <t xml:space="preserve">1.22463119029999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21012806892395</t>
   </si>
   <si>
     <t xml:space="preserve">1.1865599155426</t>
@@ -767,145 +767,145 @@
     <t xml:space="preserve">1.17477595806122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17840170860291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1521143913269</t>
+    <t xml:space="preserve">1.17840182781219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15211451053619</t>
   </si>
   <si>
     <t xml:space="preserve">1.15845954418182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08594262599945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10588490962982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07959711551666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1067910194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13217222690582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16933703422546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22644436359406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23822832107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24457371234894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2518253326416</t>
+    <t xml:space="preserve">1.08594250679016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10588479042053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07959735393524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10679125785828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13217210769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16933715343475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22644424438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23822855949402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24457359313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25182545185089</t>
   </si>
   <si>
     <t xml:space="preserve">1.24004137516022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20378267765045</t>
+    <t xml:space="preserve">1.20378255844116</t>
   </si>
   <si>
     <t xml:space="preserve">1.20650219917297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24094784259796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23097670078278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21194100379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23460245132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24638664722443</t>
+    <t xml:space="preserve">1.24094760417938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23097681999207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21194088459015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23460233211517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24638652801514</t>
   </si>
   <si>
     <t xml:space="preserve">1.2762998342514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27086079120636</t>
+    <t xml:space="preserve">1.27086102962494</t>
   </si>
   <si>
     <t xml:space="preserve">1.29805481433868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22553777694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15574026107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11857521533966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16027247905731</t>
+    <t xml:space="preserve">1.22553789615631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15574014186859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11857533454895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1602725982666</t>
   </si>
   <si>
     <t xml:space="preserve">1.16661787033081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16480469703674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18112123012543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19925045967102</t>
+    <t xml:space="preserve">1.16480493545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18112111091614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19925022125244</t>
   </si>
   <si>
     <t xml:space="preserve">1.11676239967346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09319424629211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09772646427155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17658889293671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17930817604065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21375393867493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21556651592255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28627097606659</t>
+    <t xml:space="preserve">1.09319412708282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09772670269012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17658877372742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17930829524994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21375381946564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21556675434113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2862708568573</t>
   </si>
   <si>
     <t xml:space="preserve">1.28989672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2844580411911</t>
+    <t xml:space="preserve">1.28445792198181</t>
   </si>
   <si>
     <t xml:space="preserve">1.38960766792297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40048503875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41408216953278</t>
+    <t xml:space="preserve">1.40048515796661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41408205032349</t>
   </si>
   <si>
     <t xml:space="preserve">1.38235592842102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37057197093964</t>
+    <t xml:space="preserve">1.37057185173035</t>
   </si>
   <si>
     <t xml:space="preserve">1.32796823978424</t>
@@ -914,46 +914,46 @@
     <t xml:space="preserve">1.36513328552246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35516214370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38416874408722</t>
+    <t xml:space="preserve">1.35516202449799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38416886329651</t>
   </si>
   <si>
     <t xml:space="preserve">1.42224025726318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38054299354553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38870120048523</t>
+    <t xml:space="preserve">1.38054311275482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38870096206665</t>
   </si>
   <si>
     <t xml:space="preserve">1.36694610118866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40773689746857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39957880973816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39685940742493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38326239585876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38688826560974</t>
+    <t xml:space="preserve">1.40773677825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39957869052887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39685928821564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38326263427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38688802719116</t>
   </si>
   <si>
     <t xml:space="preserve">1.50926065444946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57724571228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57271313667297</t>
+    <t xml:space="preserve">1.5772453546524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57271301746368</t>
   </si>
   <si>
     <t xml:space="preserve">1.54551935195923</t>
@@ -962,22 +962,22 @@
     <t xml:space="preserve">1.55005156993866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51379311084747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48659908771515</t>
+    <t xml:space="preserve">1.51379287242889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48659896850586</t>
   </si>
   <si>
     <t xml:space="preserve">1.44580829143524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48206698894501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43221163749695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5409871339798</t>
+    <t xml:space="preserve">1.48206686973572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43221127986908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54098689556122</t>
   </si>
   <si>
     <t xml:space="preserve">1.52285766601562</t>
@@ -986,40 +986,40 @@
     <t xml:space="preserve">1.52738988399506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37329125404358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39142036437988</t>
+    <t xml:space="preserve">1.37329137325287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39142048358917</t>
   </si>
   <si>
     <t xml:space="preserve">1.34609746932983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29170978069305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31890380382538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33703279495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27358043193817</t>
+    <t xml:space="preserve">1.29170966148376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31890368461609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33703291416168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27358055114746</t>
   </si>
   <si>
     <t xml:space="preserve">1.39595282077789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30077409744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33341026306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31476104259491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30543673038483</t>
+    <t xml:space="preserve">1.30077421665192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33341014385223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3147611618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30543661117554</t>
   </si>
   <si>
     <t xml:space="preserve">1.31942343711853</t>
@@ -1028,28 +1028,28 @@
     <t xml:space="preserve">1.24482703208923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24948930740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23084008693695</t>
+    <t xml:space="preserve">1.24948942661285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23084032535553</t>
   </si>
   <si>
     <t xml:space="preserve">1.21219110488892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25415170192719</t>
+    <t xml:space="preserve">1.2541515827179</t>
   </si>
   <si>
     <t xml:space="preserve">1.23550260066986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22617793083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19354200363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19820439815521</t>
+    <t xml:space="preserve">1.22617816925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19354212284088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19820427894592</t>
   </si>
   <si>
     <t xml:space="preserve">1.2401647567749</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">1.27280068397522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29611206054688</t>
+    <t xml:space="preserve">1.29611194133759</t>
   </si>
   <si>
     <t xml:space="preserve">1.31009888648987</t>
@@ -1070,19 +1070,19 @@
     <t xml:space="preserve">1.28212523460388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26813840866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30077421665192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21685338020325</t>
+    <t xml:space="preserve">1.26813852787018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30077433586121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21685326099396</t>
   </si>
   <si>
     <t xml:space="preserve">1.18887984752655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1655684709549</t>
+    <t xml:space="preserve">1.16556823253632</t>
   </si>
   <si>
     <t xml:space="preserve">1.20286655426025</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">1.17489302158356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1795551776886</t>
+    <t xml:space="preserve">1.17955529689789</t>
   </si>
   <si>
     <t xml:space="preserve">1.20752882957458</t>
@@ -1106,40 +1106,40 @@
     <t xml:space="preserve">1.17023062705994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14691936969757</t>
+    <t xml:space="preserve">1.14691913127899</t>
   </si>
   <si>
     <t xml:space="preserve">1.13293254375458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25881373882294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746295928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22151577472687</t>
+    <t xml:space="preserve">1.25881397724152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746307849884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22151565551758</t>
   </si>
   <si>
     <t xml:space="preserve">1.15624380111694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18421745300293</t>
+    <t xml:space="preserve">1.18421757221222</t>
   </si>
   <si>
     <t xml:space="preserve">1.28678739070892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16090619564056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15158152580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13759481906891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36138391494751</t>
+    <t xml:space="preserve">1.16090595722198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1515816450119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13759469985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3613840341568</t>
   </si>
   <si>
     <t xml:space="preserve">1.29144978523254</t>
@@ -1151,22 +1151,22 @@
     <t xml:space="preserve">1.33807241916656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11428344249725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10495889186859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14225697517395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27810597419739</t>
+    <t xml:space="preserve">1.11428332328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1049587726593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14225709438324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27810609340668</t>
   </si>
   <si>
     <t xml:space="preserve">1.29230725765228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37278056144714</t>
+    <t xml:space="preserve">1.37278068065643</t>
   </si>
   <si>
     <t xml:space="preserve">1.34437811374664</t>
@@ -1187,16 +1187,16 @@
     <t xml:space="preserve">1.31124210357666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31597590446472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28757357597351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3065083026886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33964431285858</t>
+    <t xml:space="preserve">1.31597578525543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2875736951828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30650842189789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33964455127716</t>
   </si>
   <si>
     <t xml:space="preserve">1.42011785507202</t>
@@ -1205,16 +1205,16 @@
     <t xml:space="preserve">1.40591669082642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35384571552277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39644920825958</t>
+    <t xml:space="preserve">1.35384559631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39644908905029</t>
   </si>
   <si>
     <t xml:space="preserve">1.32070958614349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33491086959839</t>
+    <t xml:space="preserve">1.3349107503891</t>
   </si>
   <si>
     <t xml:space="preserve">1.28283977508545</t>
@@ -1229,16 +1229,16 @@
     <t xml:space="preserve">1.25917112827301</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29704093933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2449699640274</t>
+    <t xml:space="preserve">1.29704105854034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24497008323669</t>
   </si>
   <si>
     <t xml:space="preserve">1.23076868057251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22130131721497</t>
+    <t xml:space="preserve">1.22130119800568</t>
   </si>
   <si>
     <t xml:space="preserve">1.21656763553619</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">1.22603499889374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24023628234863</t>
+    <t xml:space="preserve">1.24023616313934</t>
   </si>
   <si>
     <t xml:space="preserve">1.21183395385742</t>
@@ -1256,22 +1256,22 @@
     <t xml:space="preserve">1.26863861083984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20710003376007</t>
+    <t xml:space="preserve">1.20710015296936</t>
   </si>
   <si>
     <t xml:space="preserve">1.24970376491547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25443768501282</t>
+    <t xml:space="preserve">1.25443756580353</t>
   </si>
   <si>
     <t xml:space="preserve">1.23550248146057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16923046112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18343162536621</t>
+    <t xml:space="preserve">1.16923034191132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18343138694763</t>
   </si>
   <si>
     <t xml:space="preserve">1.20236647129059</t>
@@ -1289,25 +1289,25 @@
     <t xml:space="preserve">1.10295808315277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06982219219208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01775121688843</t>
+    <t xml:space="preserve">1.06982207298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01775109767914</t>
   </si>
   <si>
     <t xml:space="preserve">0.989348709583282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979881227016449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965680122375488</t>
+    <t xml:space="preserve">0.979881286621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965680181980133</t>
   </si>
   <si>
     <t xml:space="preserve">0.914555847644806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937277734279633</t>
+    <t xml:space="preserve">0.937277793884277</t>
   </si>
   <si>
     <t xml:space="preserve">0.920236349105835</t>
@@ -1328,19 +1328,19 @@
     <t xml:space="preserve">1.02248477935791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07928955554962</t>
+    <t xml:space="preserve">1.07928943634033</t>
   </si>
   <si>
     <t xml:space="preserve">1.10769188404083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13609445095062</t>
+    <t xml:space="preserve">1.13609409332275</t>
   </si>
   <si>
     <t xml:space="preserve">1.05562090873718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09349071979523</t>
+    <t xml:space="preserve">1.09349048137665</t>
   </si>
   <si>
     <t xml:space="preserve">1.06035447120667</t>
@@ -1349,70 +1349,70 @@
     <t xml:space="preserve">1.06508839130402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07455563545227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04615354537964</t>
+    <t xml:space="preserve">1.07455587387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04615342617035</t>
   </si>
   <si>
     <t xml:space="preserve">1.03668606281281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04141974449158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1124255657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1266268491745</t>
+    <t xml:space="preserve">1.04141962528229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11242544651031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12662696838379</t>
   </si>
   <si>
     <t xml:space="preserve">1.08875691890717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09822452068329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05088722705841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03195226192474</t>
+    <t xml:space="preserve">1.09822428226471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05088710784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03195238113403</t>
   </si>
   <si>
     <t xml:space="preserve">1.02721858024597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17869782447815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15976285934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15029549598694</t>
+    <t xml:space="preserve">1.17869770526886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15976297855377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15029537677765</t>
   </si>
   <si>
     <t xml:space="preserve">1.16449654102325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15502917766571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14556157588959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17396402359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13136053085327</t>
+    <t xml:space="preserve">1.15502905845642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14556169509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1739639043808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13136041164398</t>
   </si>
   <si>
     <t xml:space="preserve">1.08402335643768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00828373432159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984614968299866</t>
+    <t xml:space="preserve">1.0082836151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98461502790451</t>
   </si>
   <si>
     <t xml:space="preserve">0.994082450866699</t>
@@ -1433,13 +1433,10 @@
     <t xml:space="preserve">1.3633131980896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33027982711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31597578525543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32551193237305</t>
+    <t xml:space="preserve">1.33027994632721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32551181316376</t>
   </si>
   <si>
     <t xml:space="preserve">1.33981597423553</t>
@@ -1454,10 +1451,10 @@
     <t xml:space="preserve">1.32074379920959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35412001609802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34458410739899</t>
+    <t xml:space="preserve">1.35411989688873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3445839881897</t>
   </si>
   <si>
     <t xml:space="preserve">1.40180039405823</t>
@@ -1466,22 +1463,22 @@
     <t xml:space="preserve">1.36842405796051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34935200214386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3588879108429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30167162418365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39226424694061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38272821903229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41133642196655</t>
+    <t xml:space="preserve">1.34935212135315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35888803005219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30167174339294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3922643661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38272833824158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41133630275726</t>
   </si>
   <si>
     <t xml:space="preserve">1.38749623298645</t>
@@ -1499,22 +1496,22 @@
     <t xml:space="preserve">1.44471251964569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40656840801239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42087233066559</t>
+    <t xml:space="preserve">1.4065682888031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42087244987488</t>
   </si>
   <si>
     <t xml:space="preserve">1.43517661094666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45901668071747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43994462490082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41610431671143</t>
+    <t xml:space="preserve">1.45901656150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43994450569153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41610443592072</t>
   </si>
   <si>
     <t xml:space="preserve">1.51623296737671</t>
@@ -1526,16 +1523,16 @@
     <t xml:space="preserve">1.53530502319336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54484105110168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54007303714752</t>
+    <t xml:space="preserve">1.54484117031097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54007315635681</t>
   </si>
   <si>
     <t xml:space="preserve">1.58298540115356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57344937324524</t>
+    <t xml:space="preserve">1.57344925403595</t>
   </si>
   <si>
     <t xml:space="preserve">1.68788206577301</t>
@@ -1547,25 +1544,25 @@
     <t xml:space="preserve">1.70695412158966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76417028903961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74509835243225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72602617740631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69741809368134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66880977153778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67357778549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64020180702209</t>
+    <t xml:space="preserve">1.76417052745819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74509847164154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7260262966156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69741797447205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66881000995636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67357802391052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64020168781281</t>
   </si>
   <si>
     <t xml:space="preserve">1.61159348487854</t>
@@ -1574,28 +1571,28 @@
     <t xml:space="preserve">1.60682547092438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64973771572113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71172201633453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64496982097626</t>
+    <t xml:space="preserve">1.64973783493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71172213554382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64496970176697</t>
   </si>
   <si>
     <t xml:space="preserve">1.61636161804199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62112975120544</t>
+    <t xml:space="preserve">1.62112951278687</t>
   </si>
   <si>
     <t xml:space="preserve">1.63066565990448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63543367385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77847456932068</t>
+    <t xml:space="preserve">1.63543379306793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77847468852997</t>
   </si>
   <si>
     <t xml:space="preserve">1.75940251350403</t>
@@ -1616,13 +1613,13 @@
     <t xml:space="preserve">1.8261547088623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79754662513733</t>
+    <t xml:space="preserve">1.79754674434662</t>
   </si>
   <si>
     <t xml:space="preserve">1.788010597229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81661880016327</t>
+    <t xml:space="preserve">1.81661891937256</t>
   </si>
   <si>
     <t xml:space="preserve">1.83092284202576</t>
@@ -1634,34 +1631,34 @@
     <t xml:space="preserve">1.76893854141235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73556232452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73079419136047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74033045768738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72125816345215</t>
+    <t xml:space="preserve">1.73556244373322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73079431056976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74033033847809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72125828266144</t>
   </si>
   <si>
     <t xml:space="preserve">1.78324246406555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7498664855957</t>
+    <t xml:space="preserve">1.74986636638641</t>
   </si>
   <si>
     <t xml:space="preserve">1.67834603786469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66404187679291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69264996051788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80231475830078</t>
+    <t xml:space="preserve">1.66404175758362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69265007972717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80231463909149</t>
   </si>
   <si>
     <t xml:space="preserve">1.75463449954987</t>
@@ -1670,37 +1667,37 @@
     <t xml:space="preserve">1.79277861118317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56868135929108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65927386283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59252142906189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52576911449432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59728932380676</t>
+    <t xml:space="preserve">1.5686811208725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65927374362946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5925213098526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52576899528503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59728944301605</t>
   </si>
   <si>
     <t xml:space="preserve">1.7021861076355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85953104496002</t>
+    <t xml:space="preserve">1.85953116416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.89767527580261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92628347873688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82138669490814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83569085597992</t>
+    <t xml:space="preserve">1.92628335952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82138681411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83569073677063</t>
   </si>
   <si>
     <t xml:space="preserve">1.86429917812347</t>
@@ -1709,46 +1706,46 @@
     <t xml:space="preserve">1.90721130371094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94535541534424</t>
+    <t xml:space="preserve">1.94535565376282</t>
   </si>
   <si>
     <t xml:space="preserve">1.99303579330444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05978846549988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00257205963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07886028289795</t>
+    <t xml:space="preserve">2.0597882270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00257182121277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07886052131653</t>
   </si>
   <si>
     <t xml:space="preserve">2.12654066085815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1074686050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08839631080627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09793257713318</t>
+    <t xml:space="preserve">2.10746836662292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08839654922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0979323387146</t>
   </si>
   <si>
     <t xml:space="preserve">2.1456127166748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27911758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19329309463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22190117835999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25050950050354</t>
+    <t xml:space="preserve">2.27911734580994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19329285621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22190093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25050926208496</t>
   </si>
   <si>
     <t xml:space="preserve">2.02164387702942</t>
@@ -1757,88 +1754,91 @@
     <t xml:space="preserve">2.01210784912109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9739636182785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98349964618683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03118014335632</t>
+    <t xml:space="preserve">1.97396373748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98349976539612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03117990493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04071617126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09847211837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08884620666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10809803009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00221180915833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95408177375793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03108978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02146410942078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05996799468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94445586204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97333383560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93482995033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85782170295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83856964111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82894361019135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86744773387909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88669979572296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707364559174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89632570743561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92520391941071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99258589744568</t>
   </si>
   <si>
     <t xml:space="preserve">2.04071593284607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09847211837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08884644508362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10809826850891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00221180915833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95408177375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03109002113342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02146410942078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05996799468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94445586204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9733339548111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93482983112335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85782170295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83856964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82894361019135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86744773387909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88669979572296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707376480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89632570743561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92520380020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99258577823639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05034232139587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11772418022156</t>
+    <t xml:space="preserve">2.05034208297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11772441864014</t>
   </si>
   <si>
     <t xml:space="preserve">2.1562283039093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20435857772827</t>
+    <t xml:space="preserve">2.20435833930969</t>
   </si>
   <si>
     <t xml:space="preserve">2.16585445404053</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">2.14660239219666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07922029495239</t>
+    <t xml:space="preserve">2.07922005653381</t>
   </si>
   <si>
     <t xml:space="preserve">2.24286246299744</t>
@@ -1862,19 +1862,19 @@
     <t xml:space="preserve">2.30061864852905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28136658668518</t>
+    <t xml:space="preserve">2.2813663482666</t>
   </si>
   <si>
     <t xml:space="preserve">2.18510627746582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19473218917847</t>
+    <t xml:space="preserve">2.19473242759705</t>
   </si>
   <si>
     <t xml:space="preserve">2.12735033035278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13697600364685</t>
+    <t xml:space="preserve">2.13697624206543</t>
   </si>
   <si>
     <t xml:space="preserve">2.01183795928955</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">1.8722608089447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96370780467987</t>
+    <t xml:space="preserve">1.96370792388916</t>
   </si>
   <si>
     <t xml:space="preserve">2.06959414482117</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">2.35837483406067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42575669288635</t>
+    <t xml:space="preserve">2.42575693130493</t>
   </si>
   <si>
     <t xml:space="preserve">2.39687895774841</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">2.41613078117371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37762665748596</t>
+    <t xml:space="preserve">2.37762689590454</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874868392944</t>
@@ -1925,10 +1925,10 @@
     <t xml:space="preserve">2.29099249839783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36800050735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38725256919861</t>
+    <t xml:space="preserve">2.36800074577332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38725280761719</t>
   </si>
   <si>
     <t xml:space="preserve">2.21398448944092</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">2.31987071037292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44500875473022</t>
+    <t xml:space="preserve">2.4450089931488</t>
   </si>
   <si>
     <t xml:space="preserve">2.45463490486145</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">2.52201700210571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50276470184326</t>
+    <t xml:space="preserve">2.50276494026184</t>
   </si>
   <si>
     <t xml:space="preserve">2.59902501106262</t>
@@ -1973,13 +1973,13 @@
     <t xml:space="preserve">2.48351287841797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53164315223694</t>
+    <t xml:space="preserve">2.53164291381836</t>
   </si>
   <si>
     <t xml:space="preserve">2.63752913475037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6952850818634</t>
+    <t xml:space="preserve">2.69528532028198</t>
   </si>
   <si>
     <t xml:space="preserve">2.82042360305786</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">2.71453738212585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67603325843811</t>
+    <t xml:space="preserve">2.67603349685669</t>
   </si>
   <si>
     <t xml:space="preserve">2.60865116119385</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">2.5701470375061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58939933776855</t>
+    <t xml:space="preserve">2.58939909934998</t>
   </si>
   <si>
     <t xml:space="preserve">2.56052088737488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62790322303772</t>
+    <t xml:space="preserve">2.6279034614563</t>
   </si>
   <si>
     <t xml:space="preserve">2.55089521408081</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">2.57977318763733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38258814811707</t>
+    <t xml:space="preserve">2.38258790969849</t>
   </si>
   <si>
     <t xml:space="preserve">2.29506421089172</t>
@@ -2024,13 +2024,13 @@
     <t xml:space="preserve">2.28533935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32423901557922</t>
+    <t xml:space="preserve">2.32423877716064</t>
   </si>
   <si>
     <t xml:space="preserve">2.25616478919983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23671507835388</t>
+    <t xml:space="preserve">2.23671531677246</t>
   </si>
   <si>
     <t xml:space="preserve">2.21726560592651</t>
@@ -2042,16 +2042,16 @@
     <t xml:space="preserve">2.34368872642517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2658896446228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30478882789612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24644017219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11029243469238</t>
+    <t xml:space="preserve">2.26588988304138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3047890663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24643993377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1102921962738</t>
   </si>
   <si>
     <t xml:space="preserve">2.15891647338867</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">2.19781565666199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16864109039307</t>
+    <t xml:space="preserve">2.16864132881165</t>
   </si>
   <si>
     <t xml:space="preserve">2.18809103965759</t>
@@ -2081,16 +2081,16 @@
     <t xml:space="preserve">2.13946676254272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09084248542786</t>
+    <t xml:space="preserve">2.09084272384644</t>
   </si>
   <si>
     <t xml:space="preserve">2.10056734085083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27561473846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08111786842346</t>
+    <t xml:space="preserve">2.27561450004578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08111763000488</t>
   </si>
   <si>
     <t xml:space="preserve">1.97414433956146</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">1.98386907577515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96441948413849</t>
+    <t xml:space="preserve">1.9644193649292</t>
   </si>
   <si>
     <t xml:space="preserve">1.94496977329254</t>
@@ -2117,13 +2117,13 @@
     <t xml:space="preserve">2.02276849746704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03249311447144</t>
+    <t xml:space="preserve">2.03249335289001</t>
   </si>
   <si>
     <t xml:space="preserve">2.01304364204407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07139301300049</t>
+    <t xml:space="preserve">2.07139277458191</t>
   </si>
   <si>
     <t xml:space="preserve">2.04221820831299</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">1.93524491786957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95469450950623</t>
+    <t xml:space="preserve">1.95469462871552</t>
   </si>
   <si>
     <t xml:space="preserve">1.91579520702362</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">1.93038249015808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06166768074036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91093277931213</t>
+    <t xml:space="preserve">2.06166791915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91093289852142</t>
   </si>
   <si>
     <t xml:space="preserve">2.1491916179657</t>
@@ -2162,16 +2162,16 @@
     <t xml:space="preserve">1.92552006244659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81854665279388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84772121906281</t>
+    <t xml:space="preserve">1.81854677200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84772133827209</t>
   </si>
   <si>
     <t xml:space="preserve">1.8866206407547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83313393592834</t>
+    <t xml:space="preserve">1.83313405513763</t>
   </si>
   <si>
     <t xml:space="preserve">1.85258364677429</t>
@@ -2205,9 +2205,6 @@
   </si>
   <si>
     <t xml:space="preserve">1.97931289672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95469462871552</t>
   </si>
   <si>
     <t xml:space="preserve">1.9497709274292</t>
@@ -39093,7 +39090,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1395" t="s">
-        <v>474</v>
+        <v>391</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -39119,7 +39116,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1396" t="s">
-        <v>474</v>
+        <v>391</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -39145,7 +39142,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1397" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -39171,7 +39168,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1398" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -39197,7 +39194,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1399" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -39223,7 +39220,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1400" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -39249,7 +39246,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1401" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -39275,7 +39272,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1402" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39301,7 +39298,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1403" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39327,7 +39324,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1404" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39353,7 +39350,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1405" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39379,7 +39376,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1406" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39405,7 +39402,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1407" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39431,7 +39428,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1408" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39457,7 +39454,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1409" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39483,7 +39480,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1410" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39509,7 +39506,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1411" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39535,7 +39532,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1412" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39561,7 +39558,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1413" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39587,7 +39584,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1414" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39613,7 +39610,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1415" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39639,7 +39636,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1416" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39665,7 +39662,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1417" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39691,7 +39688,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1418" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39717,7 +39714,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1419" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39743,7 +39740,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1420" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39769,7 +39766,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1421" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39795,7 +39792,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1422" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39821,7 +39818,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1423" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39873,7 +39870,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1425" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39899,7 +39896,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1426" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39951,7 +39948,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1428" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39977,7 +39974,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1429" t="s">
-        <v>474</v>
+        <v>391</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -40003,7 +40000,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1430" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -40029,7 +40026,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1431" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -40055,7 +40052,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1432" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -40081,7 +40078,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1433" t="s">
-        <v>474</v>
+        <v>391</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -40107,7 +40104,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1434" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -40133,7 +40130,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1435" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -40159,7 +40156,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1436" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -40185,7 +40182,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1437" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -40211,7 +40208,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1438" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -40237,7 +40234,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1439" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -40263,7 +40260,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1440" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40289,7 +40286,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1441" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40315,7 +40312,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1442" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40341,7 +40338,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1443" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40367,7 +40364,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1444" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40393,7 +40390,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1445" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40419,7 +40416,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1446" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40445,7 +40442,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1447" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40471,7 +40468,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1448" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40497,7 +40494,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1449" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40523,7 +40520,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1450" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40549,7 +40546,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1451" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40575,7 +40572,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1452" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40601,7 +40598,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40627,7 +40624,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1454" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40653,7 +40650,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1455" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40679,7 +40676,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1456" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40705,7 +40702,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1457" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40731,7 +40728,7 @@
         <v>1.5</v>
       </c>
       <c r="G1458" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40757,7 +40754,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1459" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40783,7 +40780,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1460" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40809,7 +40806,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1461" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40835,7 +40832,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1462" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40861,7 +40858,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1463" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40887,7 +40884,7 @@
         <v>1.5</v>
       </c>
       <c r="G1464" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40913,7 +40910,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1465" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40939,7 +40936,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1466" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40965,7 +40962,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1467" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40991,7 +40988,7 @@
         <v>1.5</v>
       </c>
       <c r="G1468" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -41017,7 +41014,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1469" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -41043,7 +41040,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1470" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -41069,7 +41066,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1471" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -41095,7 +41092,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1472" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -41121,7 +41118,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1473" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -41147,7 +41144,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1474" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -41173,7 +41170,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1475" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -41199,7 +41196,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1476" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -41225,7 +41222,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1477" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -41251,7 +41248,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1478" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41277,7 +41274,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1479" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41303,7 +41300,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1480" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41329,7 +41326,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1481" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41355,7 +41352,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1482" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41381,7 +41378,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1483" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41407,7 +41404,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1484" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41433,7 +41430,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1485" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41459,7 +41456,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1486" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41485,7 +41482,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1487" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41511,7 +41508,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1488" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41537,7 +41534,7 @@
         <v>1.75</v>
       </c>
       <c r="G1489" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41563,7 +41560,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1490" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41589,7 +41586,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1491" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41615,7 +41612,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1492" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41641,7 +41638,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1493" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41667,7 +41664,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1494" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41693,7 +41690,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1495" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41719,7 +41716,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1496" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41745,7 +41742,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1497" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41771,7 +41768,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1498" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41797,7 +41794,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1499" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41823,7 +41820,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1500" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41849,7 +41846,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1501" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41875,7 +41872,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1502" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41901,7 +41898,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1503" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41927,7 +41924,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1504" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41953,7 +41950,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1505" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41979,7 +41976,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1506" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -42005,7 +42002,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1507" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -42031,7 +42028,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1508" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -42057,7 +42054,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1509" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -42083,7 +42080,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1510" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -42109,7 +42106,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1511" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -42135,7 +42132,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1512" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -42161,7 +42158,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1513" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -42187,7 +42184,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1514" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -42213,7 +42210,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1515" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -42239,7 +42236,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1516" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -42265,7 +42262,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1517" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42291,7 +42288,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1518" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42317,7 +42314,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1519" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42343,7 +42340,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1520" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42369,7 +42366,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1521" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42395,7 +42392,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1522" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42421,7 +42418,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1523" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42447,7 +42444,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1524" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42473,7 +42470,7 @@
         <v>1.875</v>
       </c>
       <c r="G1525" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42499,7 +42496,7 @@
         <v>1.875</v>
       </c>
       <c r="G1526" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42525,7 +42522,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1527" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42551,7 +42548,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1528" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42577,7 +42574,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1529" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42603,7 +42600,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1530" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42629,7 +42626,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1531" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42655,7 +42652,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1532" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42681,7 +42678,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1533" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42707,7 +42704,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1534" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42733,7 +42730,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1535" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42759,7 +42756,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1536" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42785,7 +42782,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1537" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42811,7 +42808,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1538" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42837,7 +42834,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1539" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42863,7 +42860,7 @@
         <v>1.875</v>
       </c>
       <c r="G1540" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42889,7 +42886,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1541" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42915,7 +42912,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1542" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42941,7 +42938,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1543" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42967,7 +42964,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1544" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42993,7 +42990,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1545" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -43019,7 +43016,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1546" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -43045,7 +43042,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1547" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -43071,7 +43068,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1548" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -43097,7 +43094,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1549" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -43123,7 +43120,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1550" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -43149,7 +43146,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1551" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -43175,7 +43172,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1552" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -43201,7 +43198,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1553" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -43227,7 +43224,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1554" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -43253,7 +43250,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1555" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -43279,7 +43276,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1556" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43305,7 +43302,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1557" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43331,7 +43328,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1558" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43357,7 +43354,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1559" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43383,7 +43380,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1560" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43409,7 +43406,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1561" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43435,7 +43432,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1562" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43461,7 +43458,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1563" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43487,7 +43484,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1564" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43513,7 +43510,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1565" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43539,7 +43536,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1566" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43565,7 +43562,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1567" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43591,7 +43588,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1568" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43617,7 +43614,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1569" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43643,7 +43640,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1570" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43669,7 +43666,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1571" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43695,7 +43692,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1572" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43721,7 +43718,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1573" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43747,7 +43744,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1574" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43773,7 +43770,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1575" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43799,7 +43796,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1576" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43825,7 +43822,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1577" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43851,7 +43848,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1578" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43877,7 +43874,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1579" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43903,7 +43900,7 @@
         <v>1.75</v>
       </c>
       <c r="G1580" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43929,7 +43926,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1581" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43955,7 +43952,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1582" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43981,7 +43978,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1583" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -44007,7 +44004,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1584" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -44033,7 +44030,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1585" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -44059,7 +44056,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1586" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -44085,7 +44082,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1587" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -44111,7 +44108,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1588" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -44137,7 +44134,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1589" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -44163,7 +44160,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1590" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -44189,7 +44186,7 @@
         <v>1.75</v>
       </c>
       <c r="G1591" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -44215,7 +44212,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1592" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -44241,7 +44238,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1593" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -44267,7 +44264,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1594" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44293,7 +44290,7 @@
         <v>1.75</v>
       </c>
       <c r="G1595" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44319,7 +44316,7 @@
         <v>1.75</v>
       </c>
       <c r="G1596" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44345,7 +44342,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1597" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44371,7 +44368,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1598" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44397,7 +44394,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1599" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44423,7 +44420,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1600" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44449,7 +44446,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1601" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44475,7 +44472,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1602" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44501,7 +44498,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1603" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44527,7 +44524,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1604" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44553,7 +44550,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1605" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44579,7 +44576,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1606" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44605,7 +44602,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1607" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44631,7 +44628,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1608" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44657,7 +44654,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1609" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44683,7 +44680,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1610" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44709,7 +44706,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1611" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44735,7 +44732,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1612" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44761,7 +44758,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1613" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44787,7 +44784,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1614" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44813,7 +44810,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1615" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44839,7 +44836,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1616" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44865,7 +44862,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1617" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44891,7 +44888,7 @@
         <v>2</v>
       </c>
       <c r="G1618" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44917,7 +44914,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1619" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44943,7 +44940,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1620" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44969,7 +44966,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1621" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44995,7 +44992,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1622" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -45021,7 +45018,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1623" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -45047,7 +45044,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1624" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -45073,7 +45070,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1625" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -45099,7 +45096,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -45125,7 +45122,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1627" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -45151,7 +45148,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1628" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -45177,7 +45174,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1629" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -45203,7 +45200,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1630" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -45229,7 +45226,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1631" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -45255,7 +45252,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1632" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -45281,7 +45278,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1633" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45307,7 +45304,7 @@
         <v>2.25</v>
       </c>
       <c r="G1634" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45333,7 +45330,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1635" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45359,7 +45356,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1636" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45385,7 +45382,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1637" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45411,7 +45408,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1638" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45437,7 +45434,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1639" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45463,7 +45460,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1640" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45489,7 +45486,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1641" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45515,7 +45512,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1642" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45541,7 +45538,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1643" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45567,7 +45564,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1644" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45593,7 +45590,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1645" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45619,7 +45616,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1646" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45645,7 +45642,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1647" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45671,7 +45668,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1648" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45697,7 +45694,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1649" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45723,7 +45720,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1650" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45749,7 +45746,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1651" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45775,7 +45772,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1652" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45801,7 +45798,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1653" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45827,7 +45824,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1654" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45853,7 +45850,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1655" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45879,7 +45876,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1656" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45905,7 +45902,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1657" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45931,7 +45928,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1658" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45957,7 +45954,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1659" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45983,7 +45980,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1660" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -46009,7 +46006,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1661" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -46035,7 +46032,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1662" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -46061,7 +46058,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1663" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -46087,7 +46084,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1664" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -46113,7 +46110,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1665" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -46139,7 +46136,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1666" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -46165,7 +46162,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1667" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -46191,7 +46188,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1668" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -46217,7 +46214,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1669" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -46243,7 +46240,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1670" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -46269,7 +46266,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1671" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -46295,7 +46292,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1672" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -46321,7 +46318,7 @@
         <v>2</v>
       </c>
       <c r="G1673" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -46347,7 +46344,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1674" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46373,7 +46370,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1675" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -46399,7 +46396,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1676" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -46425,7 +46422,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1677" t="s">
-        <v>584</v>
+        <v>604</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46477,7 +46474,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1679" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -46867,7 +46864,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1694" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46919,7 +46916,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1696" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -47361,7 +47358,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1713" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47439,7 +47436,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1716" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47465,7 +47462,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1717" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47491,7 +47488,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1718" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47543,7 +47540,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1720" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47569,7 +47566,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1721" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47595,7 +47592,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1722" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47647,7 +47644,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1724" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -48791,7 +48788,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1768" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48817,7 +48814,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1769" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48843,7 +48840,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1770" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48895,7 +48892,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1772" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48973,7 +48970,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1775" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48999,7 +48996,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1776" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -59503,7 +59500,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2180" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -59529,7 +59526,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2181" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59555,7 +59552,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2182" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59581,7 +59578,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2183" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59685,7 +59682,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2187" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59711,7 +59708,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2188" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59737,7 +59734,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2189" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59763,7 +59760,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2190" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59789,7 +59786,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2191" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59815,7 +59812,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2192" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59841,7 +59838,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2193" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60153,7 +60150,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2205" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60179,7 +60176,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2206" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60205,7 +60202,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2207" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60231,7 +60228,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2208" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60283,7 +60280,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2210" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60309,7 +60306,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2211" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60335,7 +60332,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2212" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60361,7 +60358,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2213" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60387,7 +60384,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2214" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60439,7 +60436,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2216" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60595,7 +60592,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60673,7 +60670,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2225" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60699,7 +60696,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2226" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60751,7 +60748,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2228" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60777,7 +60774,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2229" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60803,7 +60800,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2230" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60829,7 +60826,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2231" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60855,7 +60852,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2232" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60881,7 +60878,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2233" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60907,7 +60904,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2234" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60933,7 +60930,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2235" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60959,7 +60956,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2236" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60985,7 +60982,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2237" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61011,7 +61008,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2238" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61037,7 +61034,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2239" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61063,7 +61060,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2240" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61089,7 +61086,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G2241" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61115,7 +61112,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2242" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61141,7 +61138,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2243" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61167,7 +61164,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G2244" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61193,7 +61190,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2245" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61219,7 +61216,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2246" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61245,7 +61242,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2247" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61271,7 +61268,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2248" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61297,7 +61294,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2249" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61323,7 +61320,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2250" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61349,7 +61346,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2251" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61375,7 +61372,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2252" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61479,7 +61476,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2256" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -61505,7 +61502,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2257" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -61557,7 +61554,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2259" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -61583,7 +61580,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2260" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -61609,7 +61606,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2261" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -61635,7 +61632,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -61661,7 +61658,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2263" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -61713,7 +61710,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2265" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61739,7 +61736,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2266" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61869,7 +61866,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2271" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61895,7 +61892,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2272" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61921,7 +61918,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2273" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61947,7 +61944,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2274" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61973,7 +61970,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2275" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61999,7 +61996,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2276" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62025,7 +62022,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2277" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62051,7 +62048,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2278" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62077,7 +62074,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2279" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62103,7 +62100,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2280" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62129,7 +62126,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2281" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62155,7 +62152,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2282" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62181,7 +62178,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2283" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62207,7 +62204,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2284" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62233,7 +62230,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2285" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62259,7 +62256,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2286" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62285,7 +62282,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2287" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62311,7 +62308,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2288" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62337,7 +62334,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2289" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62363,7 +62360,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2290" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62389,7 +62386,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2291" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62415,7 +62412,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2292" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62441,7 +62438,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2293" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62467,7 +62464,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2294" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -62493,7 +62490,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2295" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -62519,7 +62516,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2296" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -62545,7 +62542,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2297" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -62571,7 +62568,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2298" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -62597,7 +62594,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2299" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -62623,7 +62620,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2300" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -62649,7 +62646,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2301" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -62675,7 +62672,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2302" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -62701,7 +62698,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2303" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62727,7 +62724,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2304" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62753,7 +62750,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62779,7 +62776,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2306" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62805,7 +62802,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G2307" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62831,7 +62828,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2308" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62857,7 +62854,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2309" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62883,7 +62880,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2310" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62909,7 +62906,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2311" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62935,7 +62932,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2312" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62961,7 +62958,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2313" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62987,7 +62984,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2314" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63013,7 +63010,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2315" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63039,7 +63036,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2316" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63065,7 +63062,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2317" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63091,7 +63088,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2318" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63117,7 +63114,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2319" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63143,7 +63140,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2320" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63169,7 +63166,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2321" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63195,7 +63192,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2322" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63221,7 +63218,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2323" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63247,7 +63244,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2324" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63273,7 +63270,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2325" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63299,7 +63296,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2326" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63325,7 +63322,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2327" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63351,7 +63348,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2328" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63377,7 +63374,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2329" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63403,7 +63400,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2330" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63429,7 +63426,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2331" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63455,7 +63452,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2332" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63481,7 +63478,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2333" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -63507,7 +63504,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2334" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -63533,7 +63530,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2335" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -63559,7 +63556,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2336" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -63585,7 +63582,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2337" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -63611,7 +63608,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2338" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -63637,7 +63634,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2339" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -63663,7 +63660,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G2340" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -63689,7 +63686,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2341" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63715,7 +63712,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2342" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63741,7 +63738,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63767,7 +63764,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2344" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63793,7 +63790,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2345" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63819,7 +63816,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2346" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63845,7 +63842,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2347" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63871,7 +63868,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63897,7 +63894,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63923,7 +63920,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2350" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63949,7 +63946,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2351" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63975,7 +63972,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G2352" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64001,7 +63998,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2353" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64027,7 +64024,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2354" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64053,7 +64050,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2355" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64079,7 +64076,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2356" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64105,7 +64102,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G2357" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64131,7 +64128,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2358" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64157,7 +64154,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G2359" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64183,7 +64180,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G2360" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64209,7 +64206,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2361" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64235,7 +64232,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2362" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64261,7 +64258,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2363" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64287,7 +64284,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G2364" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64313,7 +64310,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2365" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64339,7 +64336,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64365,7 +64362,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G2367" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64391,7 +64388,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2368" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64417,7 +64414,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2369" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64443,7 +64440,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2370" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64469,7 +64466,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2371" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64495,7 +64492,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2372" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -64521,7 +64518,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2373" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -64547,7 +64544,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G2374" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -64573,7 +64570,7 @@
         <v>1.625</v>
       </c>
       <c r="G2375" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -64599,7 +64596,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G2376" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -64625,7 +64622,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G2377" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -64651,7 +64648,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2378" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -64677,7 +64674,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G2379" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -64703,7 +64700,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2380" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64729,7 +64726,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2381" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64755,7 +64752,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2382" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64781,7 +64778,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G2383" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64807,7 +64804,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2384" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64833,7 +64830,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2385" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64859,7 +64856,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64885,7 +64882,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2387" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64911,7 +64908,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2388" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64937,7 +64934,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64963,7 +64960,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2390" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64989,7 +64986,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2391" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65015,7 +65012,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2392" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65041,7 +65038,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G2393" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65067,7 +65064,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G2394" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65093,7 +65090,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2395" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65119,7 +65116,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2396" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65145,7 +65142,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2397" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65171,7 +65168,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2398" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65197,7 +65194,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2399" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65223,7 +65220,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2400" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65249,7 +65246,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2401" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65275,7 +65272,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2402" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65301,7 +65298,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2403" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65327,7 +65324,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2404" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65353,7 +65350,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2405" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65379,7 +65376,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2406" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65431,7 +65428,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2408" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65457,7 +65454,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2409" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65483,7 +65480,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2410" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -65509,7 +65506,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2411" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65535,7 +65532,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2412" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65561,7 +65558,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2413" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65587,7 +65584,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2414" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65613,7 +65610,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2415" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65639,7 +65636,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2416" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65665,7 +65662,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2417" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65691,7 +65688,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2418" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65717,7 +65714,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2419" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65743,7 +65740,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2420" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65769,7 +65766,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2421" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65795,7 +65792,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65821,7 +65818,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2423" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65847,7 +65844,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2424" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65873,7 +65870,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2425" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65899,7 +65896,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2426" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65925,7 +65922,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2427" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65951,7 +65948,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2428" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65977,7 +65974,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2429" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66003,7 +66000,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2430" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66029,7 +66026,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2431" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66055,7 +66052,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2432" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66081,7 +66078,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2433" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66107,7 +66104,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2434" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66133,7 +66130,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2435" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66159,7 +66156,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2436" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66185,7 +66182,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2437" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66211,7 +66208,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2438" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66237,7 +66234,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2439" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66263,7 +66260,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2440" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66289,7 +66286,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2441" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66315,7 +66312,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2442" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66341,7 +66338,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2443" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66367,7 +66364,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2444" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66393,7 +66390,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2445" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66419,7 +66416,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2446" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66445,7 +66442,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2447" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66471,7 +66468,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2448" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -66497,7 +66494,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2449" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -66523,7 +66520,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2450" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66549,7 +66546,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2451" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66575,7 +66572,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2452" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66601,7 +66598,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2453" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66627,7 +66624,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2454" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66653,7 +66650,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2455" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66679,7 +66676,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2456" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66705,7 +66702,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2457" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66731,7 +66728,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2458" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66757,7 +66754,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2459" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66783,7 +66780,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2460" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66809,7 +66806,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2461" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66835,7 +66832,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2462" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66861,7 +66858,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2463" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66887,7 +66884,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2464" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66913,7 +66910,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2465" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66939,7 +66936,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2466" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66965,7 +66962,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2467" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66991,7 +66988,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2468" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67017,7 +67014,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2469" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67043,7 +67040,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2470" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67069,7 +67066,7 @@
         <v>2</v>
       </c>
       <c r="G2471" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67095,7 +67092,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2472" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67121,7 +67118,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2473" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67147,7 +67144,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2474" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67173,7 +67170,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2475" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67199,7 +67196,7 @@
         <v>2</v>
       </c>
       <c r="G2476" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67225,7 +67222,7 @@
         <v>2</v>
       </c>
       <c r="G2477" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67251,7 +67248,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2478" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67277,7 +67274,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2479" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67303,7 +67300,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2480" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67329,7 +67326,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2481" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67355,7 +67352,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2482" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67381,7 +67378,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2483" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67407,7 +67404,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2484" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67433,7 +67430,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2485" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67459,7 +67456,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2486" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67485,7 +67482,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2487" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -67511,7 +67508,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2488" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67537,7 +67534,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2489" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67563,7 +67560,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2490" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67589,7 +67586,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2491" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67615,7 +67612,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2492" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67641,7 +67638,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2493" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67667,7 +67664,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2494" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67693,7 +67690,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2495" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67719,7 +67716,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2496" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67745,7 +67742,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2497" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67771,7 +67768,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2498" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67797,7 +67794,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2499" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67823,7 +67820,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2500" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67849,7 +67846,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2501" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67875,7 +67872,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2502" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -67901,7 +67898,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2503" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -67927,7 +67924,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2504" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67953,7 +67950,7 @@
         <v>2</v>
       </c>
       <c r="G2505" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67979,7 +67976,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2506" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68005,7 +68002,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2507" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68031,7 +68028,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2508" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68057,7 +68054,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2509" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68083,7 +68080,7 @@
         <v>2</v>
       </c>
       <c r="G2510" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68109,7 +68106,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2511" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68135,7 +68132,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2512" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68161,7 +68158,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2513" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -68187,7 +68184,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2514" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -68213,7 +68210,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2515" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -68239,7 +68236,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2516" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -68265,7 +68262,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2517" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -68291,7 +68288,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2518" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -68317,7 +68314,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2519" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -68343,7 +68340,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2520" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -68369,7 +68366,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2521" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -68395,7 +68392,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2522" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -68421,7 +68418,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2523" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -68447,7 +68444,7 @@
         <v>2</v>
       </c>
       <c r="G2524" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -68473,7 +68470,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2525" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -68499,7 +68496,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2526" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -68525,7 +68522,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2527" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -68551,7 +68548,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2528" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -68577,7 +68574,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2529" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -68603,7 +68600,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2530" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -68629,7 +68626,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2531" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -68655,7 +68652,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2532" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -68681,7 +68678,7 @@
         <v>2</v>
       </c>
       <c r="G2533" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -68707,7 +68704,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2534" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -68733,7 +68730,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2535" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -68759,7 +68756,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2536" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -68785,7 +68782,7 @@
         <v>2</v>
       </c>
       <c r="G2537" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2537" t="s">
         <v>9</v>
@@ -68811,7 +68808,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2538" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2538" t="s">
         <v>9</v>
@@ -68837,9 +68834,35 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2539" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2539" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2540">
+      <c r="A2540" s="1" t="n">
+        <v>46020.6687384259</v>
+      </c>
+      <c r="B2540" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C2540" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="D2540" t="n">
+        <v>1.95000004768372</v>
+      </c>
+      <c r="E2540" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="F2540" t="n">
+        <v>1.98000001907349</v>
+      </c>
+      <c r="G2540" t="s">
+        <v>814</v>
+      </c>
+      <c r="H2540" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DGT.MI.xlsx
+++ b/data/DGT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="827">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08123874664307</t>
+    <t xml:space="preserve">2.08123898506165</t>
   </si>
   <si>
     <t xml:space="preserve">DGT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05767035484314</t>
+    <t xml:space="preserve">2.0576708316803</t>
   </si>
   <si>
     <t xml:space="preserve">2.03047680854797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96702456474304</t>
+    <t xml:space="preserve">1.96702468395233</t>
   </si>
   <si>
     <t xml:space="preserve">2.00509572029114</t>
@@ -59,55 +59,55 @@
     <t xml:space="preserve">2.04860615730286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99421858787537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971487045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94889521598816</t>
+    <t xml:space="preserve">1.9942182302475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971498966217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94889533519745</t>
   </si>
   <si>
     <t xml:space="preserve">1.88544285297394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91444957256317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89632070064545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87637829780579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97065007686615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92714011669159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93076598644257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85824882984161</t>
+    <t xml:space="preserve">1.91444981098175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89632046222687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8763781785965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97065043449402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9271399974823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93076622486115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8582489490509</t>
   </si>
   <si>
     <t xml:space="preserve">1.80839359760284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8256162405014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75128626823425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64704310894012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75581860542297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71321487426758</t>
+    <t xml:space="preserve">1.82561612129211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75128638744354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64704298973083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75581872463226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71321475505829</t>
   </si>
   <si>
     <t xml:space="preserve">1.68964684009552</t>
@@ -116,16 +116,16 @@
     <t xml:space="preserve">1.73134434223175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76760280132294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72862470149994</t>
+    <t xml:space="preserve">1.76760268211365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72862493991852</t>
   </si>
   <si>
     <t xml:space="preserve">1.7585381269455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81292593479156</t>
+    <t xml:space="preserve">1.81292581558228</t>
   </si>
   <si>
     <t xml:space="preserve">1.83105516433716</t>
@@ -134,13 +134,13 @@
     <t xml:space="preserve">1.76850914955139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67514336109161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74947345256805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69871151447296</t>
+    <t xml:space="preserve">1.6751434803009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74947333335876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69871139526367</t>
   </si>
   <si>
     <t xml:space="preserve">1.74766051769257</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">1.70777606964111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70868265628815</t>
+    <t xml:space="preserve">1.70868241786957</t>
   </si>
   <si>
     <t xml:space="preserve">1.69508564472198</t>
@@ -161,19 +161,19 @@
     <t xml:space="preserve">1.7014307975769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69055354595184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73496997356415</t>
+    <t xml:space="preserve">1.69055342674255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73496985435486</t>
   </si>
   <si>
     <t xml:space="preserve">1.64069783687592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62982022762299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63163316249847</t>
+    <t xml:space="preserve">1.62982034683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63163328170776</t>
   </si>
   <si>
     <t xml:space="preserve">1.686927318573</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve">1.68602120876312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67333054542542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74040877819061</t>
+    <t xml:space="preserve">1.67333042621613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7404088973999</t>
   </si>
   <si>
     <t xml:space="preserve">1.70415031909943</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">1.68783390522003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64885604381561</t>
+    <t xml:space="preserve">1.6488561630249</t>
   </si>
   <si>
     <t xml:space="preserve">1.64794957637787</t>
@@ -209,49 +209,49 @@
     <t xml:space="preserve">1.72137320041656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72227954864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67786276340485</t>
+    <t xml:space="preserve">1.72227942943573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67786288261414</t>
   </si>
   <si>
     <t xml:space="preserve">1.63253962993622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66335952281952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66517233848572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65429496765137</t>
+    <t xml:space="preserve">1.66335940361023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66517245769501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65429472923279</t>
   </si>
   <si>
     <t xml:space="preserve">1.81111299991608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79026436805725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78754496574402</t>
+    <t xml:space="preserve">1.79026448726654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78754484653473</t>
   </si>
   <si>
     <t xml:space="preserve">1.78935766220093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66154634952545</t>
+    <t xml:space="preserve">1.66154646873474</t>
   </si>
   <si>
     <t xml:space="preserve">1.69961798191071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66245305538177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6833016872406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65882730484009</t>
+    <t xml:space="preserve">1.66245293617249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68330156803131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65882706642151</t>
   </si>
   <si>
     <t xml:space="preserve">1.60353291034698</t>
@@ -263,31 +263,31 @@
     <t xml:space="preserve">1.58902943134308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48297345638275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49566376209259</t>
+    <t xml:space="preserve">1.48297333717346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49566388130188</t>
   </si>
   <si>
     <t xml:space="preserve">1.4920380115509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53192222118378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48387968540192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45215356349945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48569273948669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42858564853668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4594053030014</t>
+    <t xml:space="preserve">1.53192245960236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48387956619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45215368270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48569285869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42858552932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45940542221069</t>
   </si>
   <si>
     <t xml:space="preserve">1.49294447898865</t>
@@ -296,16 +296,16 @@
     <t xml:space="preserve">1.46031165122986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44127595424652</t>
+    <t xml:space="preserve">1.4412761926651</t>
   </si>
   <si>
     <t xml:space="preserve">1.45034062862396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46846973896027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42586612701416</t>
+    <t xml:space="preserve">1.46846997737885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42586624622345</t>
   </si>
   <si>
     <t xml:space="preserve">1.31255829334259</t>
@@ -329,34 +329,34 @@
     <t xml:space="preserve">1.19653117656708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17296314239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18746650218964</t>
+    <t xml:space="preserve">1.17296290397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18746638298035</t>
   </si>
   <si>
     <t xml:space="preserve">1.17568242549896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15483391284943</t>
+    <t xml:space="preserve">1.15483379364014</t>
   </si>
   <si>
     <t xml:space="preserve">1.09863317012787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12401390075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13307869434357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1258270740509</t>
+    <t xml:space="preserve">1.12401413917542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13307857513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12582683563232</t>
   </si>
   <si>
     <t xml:space="preserve">1.11313652992249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06962609291077</t>
+    <t xml:space="preserve">1.06962621212006</t>
   </si>
   <si>
     <t xml:space="preserve">1.08684897422791</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">1.09500706195831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09410071372986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12038791179657</t>
+    <t xml:space="preserve">1.09410059452057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12038815021515</t>
   </si>
   <si>
     <t xml:space="preserve">1.09228777885437</t>
@@ -380,67 +380,67 @@
     <t xml:space="preserve">1.10951066017151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12129473686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09682011604309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08956861495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08866190910339</t>
+    <t xml:space="preserve">1.1212944984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09682023525238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08956849575043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08866202831268</t>
   </si>
   <si>
     <t xml:space="preserve">1.07234561443329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05149686336517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12310755252838</t>
+    <t xml:space="preserve">1.05149698257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12310743331909</t>
   </si>
   <si>
     <t xml:space="preserve">1.10135245323181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08322322368622</t>
+    <t xml:space="preserve">1.08322310447693</t>
   </si>
   <si>
     <t xml:space="preserve">1.08775568008423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11404287815094</t>
+    <t xml:space="preserve">1.11404275894165</t>
   </si>
   <si>
     <t xml:space="preserve">1.15120804309845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21466028690338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1847470998764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1457691192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12220096588135</t>
+    <t xml:space="preserve">1.21466052532196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18474686145782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14576923847198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12220108509064</t>
   </si>
   <si>
     <t xml:space="preserve">1.06237471103668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03336763381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934563338756561</t>
+    <t xml:space="preserve">1.03336775302887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934563219547272</t>
   </si>
   <si>
     <t xml:space="preserve">0.945440828800201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977167010307312</t>
+    <t xml:space="preserve">0.977166891098022</t>
   </si>
   <si>
     <t xml:space="preserve">0.956318318843842</t>
@@ -452,22 +452,22 @@
     <t xml:space="preserve">1.01523840427399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04877746105194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0360871553421</t>
+    <t xml:space="preserve">1.04877758026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03608703613281</t>
   </si>
   <si>
     <t xml:space="preserve">1.02430307865143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990764021873474</t>
+    <t xml:space="preserve">0.990764141082764</t>
   </si>
   <si>
     <t xml:space="preserve">1.05059051513672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11494934558868</t>
+    <t xml:space="preserve">1.11494946479797</t>
   </si>
   <si>
     <t xml:space="preserve">1.12854635715485</t>
@@ -476,28 +476,28 @@
     <t xml:space="preserve">1.07506501674652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06418752670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02067732810974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997109293937683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00617396831512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988044559955597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03880631923676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05965518951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04243242740631</t>
+    <t xml:space="preserve">1.06418764591217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02067720890045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997109115123749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00617372989655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988044619560242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03880655765533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05965507030487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04243218898773</t>
   </si>
   <si>
     <t xml:space="preserve">1.06328105926514</t>
@@ -506,55 +506,55 @@
     <t xml:space="preserve">1.05693566799164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10407185554504</t>
+    <t xml:space="preserve">1.10407197475433</t>
   </si>
   <si>
     <t xml:space="preserve">1.1049782037735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07597160339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12492060661316</t>
+    <t xml:space="preserve">1.07597148418427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12492072582245</t>
   </si>
   <si>
     <t xml:space="preserve">1.1031653881073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2110344171524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19562458992004</t>
+    <t xml:space="preserve">1.21103429794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19562470912933</t>
   </si>
   <si>
     <t xml:space="preserve">1.21284735202789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14667570590973</t>
+    <t xml:space="preserve">1.14667558670044</t>
   </si>
   <si>
     <t xml:space="preserve">1.15392732620239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20559573173523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20196986198425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23188304901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25363826751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25817060470581</t>
+    <t xml:space="preserve">1.20559585094452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20196974277496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23188292980194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2536381483078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25817048549652</t>
   </si>
   <si>
     <t xml:space="preserve">1.26089000701904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25545108318329</t>
+    <t xml:space="preserve">1.25545120239258</t>
   </si>
   <si>
     <t xml:space="preserve">1.28717732429504</t>
@@ -563,28 +563,28 @@
     <t xml:space="preserve">1.3089325428009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30530667304993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41226923465729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3796364068985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40320456027985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35244274139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35697495937347</t>
+    <t xml:space="preserve">1.30530655384064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.412269115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37963664531708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40320444107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35244262218475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35697484016418</t>
   </si>
   <si>
     <t xml:space="preserve">1.35969436168671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34065866470337</t>
+    <t xml:space="preserve">1.34065854549408</t>
   </si>
   <si>
     <t xml:space="preserve">1.32343590259552</t>
@@ -593,25 +593,25 @@
     <t xml:space="preserve">1.35062980651855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32887470722198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26995444297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1947181224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1439563035965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2454799413681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25001239776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26814150810242</t>
+    <t xml:space="preserve">1.32887446880341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26995468139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19471800327301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14395618438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24548006057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25001227855682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26814162731171</t>
   </si>
   <si>
     <t xml:space="preserve">1.23278963565826</t>
@@ -623,34 +623,34 @@
     <t xml:space="preserve">1.28173863887787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26451587677002</t>
+    <t xml:space="preserve">1.26451563835144</t>
   </si>
   <si>
     <t xml:space="preserve">1.28264498710632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25091886520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26904821395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33159387111664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29624199867249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28536450862885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31437146663666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30983889102936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31799697875977</t>
+    <t xml:space="preserve">1.25091874599457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26904809474945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33159399032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29624211788177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28536438941956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31437122821808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30983901023865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31799709796906</t>
   </si>
   <si>
     <t xml:space="preserve">1.29896140098572</t>
@@ -659,43 +659,43 @@
     <t xml:space="preserve">1.3778235912323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33521997928619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2617963552475</t>
+    <t xml:space="preserve">1.33522009849548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26179623603821</t>
   </si>
   <si>
     <t xml:space="preserve">1.3107453584671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30711960792542</t>
+    <t xml:space="preserve">1.30711948871613</t>
   </si>
   <si>
     <t xml:space="preserve">1.34247159957886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.294429063797</t>
+    <t xml:space="preserve">1.29442894458771</t>
   </si>
   <si>
     <t xml:space="preserve">1.32434225082397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33884572982788</t>
+    <t xml:space="preserve">1.33884584903717</t>
   </si>
   <si>
     <t xml:space="preserve">1.31165182590485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2799254655838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30621290206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31618404388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30349361896515</t>
+    <t xml:space="preserve">1.27992558479309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30621314048767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31618416309357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30349349975586</t>
   </si>
   <si>
     <t xml:space="preserve">1.27720630168915</t>
@@ -704,22 +704,22 @@
     <t xml:space="preserve">1.26632857322693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28355169296265</t>
+    <t xml:space="preserve">1.28355145454407</t>
   </si>
   <si>
     <t xml:space="preserve">1.25907707214355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24910593032837</t>
+    <t xml:space="preserve">1.24910581111908</t>
   </si>
   <si>
     <t xml:space="preserve">1.27539324760437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25273156166077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34700381755829</t>
+    <t xml:space="preserve">1.25273168087006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34700393676758</t>
   </si>
   <si>
     <t xml:space="preserve">1.34972321987152</t>
@@ -728,25 +728,25 @@
     <t xml:space="preserve">1.29261612892151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32978117465973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23369598388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22372508049011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.229163646698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20468926429749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22191190719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21919274330139</t>
+    <t xml:space="preserve">1.32978105545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2336962223053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22372496128082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22916376590729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2046891450882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22191214561462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2191926240921</t>
   </si>
   <si>
     <t xml:space="preserve">1.22100555896759</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">1.21828615665436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22463119029999</t>
+    <t xml:space="preserve">1.22463130950928</t>
   </si>
   <si>
     <t xml:space="preserve">1.21012806892395</t>
@@ -764,73 +764,73 @@
     <t xml:space="preserve">1.1865599155426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17477595806122</t>
+    <t xml:space="preserve">1.17477607727051</t>
   </si>
   <si>
     <t xml:space="preserve">1.17840182781219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15211451053619</t>
+    <t xml:space="preserve">1.15211427211761</t>
   </si>
   <si>
     <t xml:space="preserve">1.15845954418182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08594250679016</t>
+    <t xml:space="preserve">1.08594238758087</t>
   </si>
   <si>
     <t xml:space="preserve">1.10588479042053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07959735393524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10679125785828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13217210769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16933715343475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22644424438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23822855949402</t>
+    <t xml:space="preserve">1.07959723472595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1067910194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13217198848724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16933727264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22644436359406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23822832107544</t>
   </si>
   <si>
     <t xml:space="preserve">1.24457359313965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25182545185089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24004137516022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20378255844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20650219917297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24094760417938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23097681999207</t>
+    <t xml:space="preserve">1.2518253326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24004125595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20378279685974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20650207996368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24094772338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23097658157349</t>
   </si>
   <si>
     <t xml:space="preserve">1.21194088459015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23460233211517</t>
+    <t xml:space="preserve">1.23460257053375</t>
   </si>
   <si>
     <t xml:space="preserve">1.24638652801514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2762998342514</t>
+    <t xml:space="preserve">1.27629971504211</t>
   </si>
   <si>
     <t xml:space="preserve">1.27086102962494</t>
@@ -842,19 +842,19 @@
     <t xml:space="preserve">1.22553789615631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15574014186859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11857533454895</t>
+    <t xml:space="preserve">1.15574026107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11857509613037</t>
   </si>
   <si>
     <t xml:space="preserve">1.1602725982666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16661787033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16480493545532</t>
+    <t xml:space="preserve">1.16661763191223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16480481624603</t>
   </si>
   <si>
     <t xml:space="preserve">1.18112111091614</t>
@@ -863,46 +863,46 @@
     <t xml:space="preserve">1.19925022125244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11676239967346</t>
+    <t xml:space="preserve">1.11676251888275</t>
   </si>
   <si>
     <t xml:space="preserve">1.09319412708282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09772670269012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17658877372742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17930829524994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21375381946564</t>
+    <t xml:space="preserve">1.09772658348083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17658889293671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17930841445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21375370025635</t>
   </si>
   <si>
     <t xml:space="preserve">1.21556675434113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2862708568573</t>
+    <t xml:space="preserve">1.28627097606659</t>
   </si>
   <si>
     <t xml:space="preserve">1.28989672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28445792198181</t>
+    <t xml:space="preserve">1.2844580411911</t>
   </si>
   <si>
     <t xml:space="preserve">1.38960766792297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40048515796661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41408205032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38235592842102</t>
+    <t xml:space="preserve">1.4004852771759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41408216953278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38235604763031</t>
   </si>
   <si>
     <t xml:space="preserve">1.37057185173035</t>
@@ -920,61 +920,61 @@
     <t xml:space="preserve">1.38416886329651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42224025726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38054311275482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38870096206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36694610118866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40773677825928</t>
+    <t xml:space="preserve">1.42224037647247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38054299354553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38870120048523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36694598197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40773689746857</t>
   </si>
   <si>
     <t xml:space="preserve">1.39957869052887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39685928821564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38326263427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38688802719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50926065444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5772453546524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57271301746368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54551935195923</t>
+    <t xml:space="preserve">1.39685940742493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38326227664948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38688838481903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50926077365875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57724547386169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57271325588226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54551923274994</t>
   </si>
   <si>
     <t xml:space="preserve">1.55005156993866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51379287242889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48659896850586</t>
+    <t xml:space="preserve">1.51379323005676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48659908771515</t>
   </si>
   <si>
     <t xml:space="preserve">1.44580829143524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48206686973572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43221127986908</t>
+    <t xml:space="preserve">1.48206675052643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43221139907837</t>
   </si>
   <si>
     <t xml:space="preserve">1.54098689556122</t>
@@ -986,52 +986,52 @@
     <t xml:space="preserve">1.52738988399506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37329137325287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39142048358917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34609746932983</t>
+    <t xml:space="preserve">1.37329125404358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39142060279846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34609758853912</t>
   </si>
   <si>
     <t xml:space="preserve">1.29170966148376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31890368461609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33703291416168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27358055114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39595282077789</t>
+    <t xml:space="preserve">1.31890344619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33703279495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27358043193817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3959527015686</t>
   </si>
   <si>
     <t xml:space="preserve">1.30077421665192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33341014385223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3147611618042</t>
+    <t xml:space="preserve">1.33341038227081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31476104259491</t>
   </si>
   <si>
     <t xml:space="preserve">1.30543661117554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31942343711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24482703208923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24948942661285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23084032535553</t>
+    <t xml:space="preserve">1.31942331790924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24482715129852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24948930740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23084044456482</t>
   </si>
   <si>
     <t xml:space="preserve">1.21219110488892</t>
@@ -1040,13 +1040,13 @@
     <t xml:space="preserve">1.2541515827179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23550260066986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22617816925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19354212284088</t>
+    <t xml:space="preserve">1.23550248146057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22617793083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19354200363159</t>
   </si>
   <si>
     <t xml:space="preserve">1.19820427894592</t>
@@ -1055,31 +1055,31 @@
     <t xml:space="preserve">1.2401647567749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27280068397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29611194133759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31009888648987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32874798774719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28212523460388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26813852787018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30077433586121</t>
+    <t xml:space="preserve">1.27280080318451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29611217975616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31009876728058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3287478685379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28212535381317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26813840866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30077409744263</t>
   </si>
   <si>
     <t xml:space="preserve">1.21685326099396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18887984752655</t>
+    <t xml:space="preserve">1.18887972831726</t>
   </si>
   <si>
     <t xml:space="preserve">1.16556823253632</t>
@@ -1088,58 +1088,58 @@
     <t xml:space="preserve">1.20286655426025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17489302158356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17955529689789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20752882957458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32408559322357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34739708900452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17023062705994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14691913127899</t>
+    <t xml:space="preserve">1.17489290237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1795551776886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2075287103653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32408571243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34739720821381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17023074626923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14691936969757</t>
   </si>
   <si>
     <t xml:space="preserve">1.13293254375458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25881397724152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746307849884</t>
+    <t xml:space="preserve">1.25881385803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746284008026</t>
   </si>
   <si>
     <t xml:space="preserve">1.22151565551758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15624380111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18421757221222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28678739070892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16090595722198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1515816450119</t>
+    <t xml:space="preserve">1.15624392032623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18421745300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28678750991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16090607643127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15158152580261</t>
   </si>
   <si>
     <t xml:space="preserve">1.13759469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3613840341568</t>
+    <t xml:space="preserve">1.36138379573822</t>
   </si>
   <si>
     <t xml:space="preserve">1.29144978523254</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">1.34273481369019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33807241916656</t>
+    <t xml:space="preserve">1.33807253837585</t>
   </si>
   <si>
     <t xml:space="preserve">1.11428332328796</t>
@@ -1157,13 +1157,13 @@
     <t xml:space="preserve">1.1049587726593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14225709438324</t>
+    <t xml:space="preserve">1.14225697517395</t>
   </si>
   <si>
     <t xml:space="preserve">1.27810609340668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29230725765228</t>
+    <t xml:space="preserve">1.29230737686157</t>
   </si>
   <si>
     <t xml:space="preserve">1.37278068065643</t>
@@ -1175,10 +1175,10 @@
     <t xml:space="preserve">1.32544326782227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30177462100983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55266225337982</t>
+    <t xml:space="preserve">1.30177450180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55266213417053</t>
   </si>
   <si>
     <t xml:space="preserve">1.41065037250519</t>
@@ -1187,28 +1187,28 @@
     <t xml:space="preserve">1.31124210357666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31597578525543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2875736951828</t>
+    <t xml:space="preserve">1.31597590446472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28757345676422</t>
   </si>
   <si>
     <t xml:space="preserve">1.30650842189789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33964455127716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42011785507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40591669082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35384559631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39644908905029</t>
+    <t xml:space="preserve">1.33964431285858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42011773586273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40591657161713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35384571552277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39644920825958</t>
   </si>
   <si>
     <t xml:space="preserve">1.32070958614349</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">1.3349107503891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28283977508545</t>
+    <t xml:space="preserve">1.28283965587616</t>
   </si>
   <si>
     <t xml:space="preserve">1.27337229251862</t>
@@ -1226,22 +1226,22 @@
     <t xml:space="preserve">1.26390480995178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25917112827301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29704105854034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24497008323669</t>
+    <t xml:space="preserve">1.2591712474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29704082012177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2449699640274</t>
   </si>
   <si>
     <t xml:space="preserve">1.23076868057251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22130119800568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21656763553619</t>
+    <t xml:space="preserve">1.22130131721497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2165675163269</t>
   </si>
   <si>
     <t xml:space="preserve">1.22603499889374</t>
@@ -1250,31 +1250,31 @@
     <t xml:space="preserve">1.24023616313934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21183395385742</t>
+    <t xml:space="preserve">1.21183383464813</t>
   </si>
   <si>
     <t xml:space="preserve">1.26863861083984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20710015296936</t>
+    <t xml:space="preserve">1.20710003376007</t>
   </si>
   <si>
     <t xml:space="preserve">1.24970376491547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25443756580353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23550248146057</t>
+    <t xml:space="preserve">1.25443744659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23550236225128</t>
   </si>
   <si>
     <t xml:space="preserve">1.16923034191132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18343138694763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20236647129059</t>
+    <t xml:space="preserve">1.18343162536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2023663520813</t>
   </si>
   <si>
     <t xml:space="preserve">1.1408280134201</t>
@@ -1289,28 +1289,28 @@
     <t xml:space="preserve">1.10295808315277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06982207298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01775109767914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989348709583282</t>
+    <t xml:space="preserve">1.0698219537735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01775121688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989348649978638</t>
   </si>
   <si>
     <t xml:space="preserve">0.979881286621094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965680181980133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914555847644806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937277793884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.920236349105835</t>
+    <t xml:space="preserve">0.965680122375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914555907249451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937277734279633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92023640871048</t>
   </si>
   <si>
     <t xml:space="preserve">0.880473077297211</t>
@@ -1319,31 +1319,31 @@
     <t xml:space="preserve">0.927810311317444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946745216846466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956212639808655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02248477935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07928943634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10769188404083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13609409332275</t>
+    <t xml:space="preserve">0.946745276451111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9562126994133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0224848985672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07928955554962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10769200325012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13609421253204</t>
   </si>
   <si>
     <t xml:space="preserve">1.05562090873718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09349048137665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06035447120667</t>
+    <t xml:space="preserve">1.09349083900452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06035459041595</t>
   </si>
   <si>
     <t xml:space="preserve">1.06508839130402</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">1.07455587387085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04615342617035</t>
+    <t xml:space="preserve">1.04615354537964</t>
   </si>
   <si>
     <t xml:space="preserve">1.03668606281281</t>
@@ -1361,22 +1361,22 @@
     <t xml:space="preserve">1.04141962528229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11242544651031</t>
+    <t xml:space="preserve">1.1124255657196</t>
   </si>
   <si>
     <t xml:space="preserve">1.12662696838379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08875691890717</t>
+    <t xml:space="preserve">1.08875703811646</t>
   </si>
   <si>
     <t xml:space="preserve">1.09822428226471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05088710784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03195238113403</t>
+    <t xml:space="preserve">1.05088722705841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03195226192474</t>
   </si>
   <si>
     <t xml:space="preserve">1.02721858024597</t>
@@ -1388,25 +1388,25 @@
     <t xml:space="preserve">1.15976297855377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15029537677765</t>
+    <t xml:space="preserve">1.15029549598694</t>
   </si>
   <si>
     <t xml:space="preserve">1.16449654102325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15502905845642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14556169509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1739639043808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13136041164398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08402335643768</t>
+    <t xml:space="preserve">1.15502917766571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14556181430817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17396402359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13136053085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08402323722839</t>
   </si>
   <si>
     <t xml:space="preserve">1.0082836151123</t>
@@ -1415,31 +1415,31 @@
     <t xml:space="preserve">0.98461502790451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.994082450866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01301741600037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18816518783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33017706871033</t>
+    <t xml:space="preserve">0.994082391262054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01301753520966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18816530704498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33017694950104</t>
   </si>
   <si>
     <t xml:space="preserve">1.40118288993835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3633131980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33027994632721</t>
+    <t xml:space="preserve">1.36331295967102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33027982711792</t>
   </si>
   <si>
     <t xml:space="preserve">1.32551181316376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33981597423553</t>
+    <t xml:space="preserve">1.33981585502625</t>
   </si>
   <si>
     <t xml:space="preserve">1.33504784107208</t>
@@ -1448,34 +1448,34 @@
     <t xml:space="preserve">1.36365604400635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32074379920959</t>
+    <t xml:space="preserve">1.32074391841888</t>
   </si>
   <si>
     <t xml:space="preserve">1.35411989688873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3445839881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40180039405823</t>
+    <t xml:space="preserve">1.34458386898041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40180027484894</t>
   </si>
   <si>
     <t xml:space="preserve">1.36842405796051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34935212135315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35888803005219</t>
+    <t xml:space="preserve">1.34935188293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3588879108429</t>
   </si>
   <si>
     <t xml:space="preserve">1.30167174339294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3922643661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38272833824158</t>
+    <t xml:space="preserve">1.39226424694061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38272821903229</t>
   </si>
   <si>
     <t xml:space="preserve">1.41133630275726</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">1.38749623298645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37319219112396</t>
+    <t xml:space="preserve">1.37319207191467</t>
   </si>
   <si>
     <t xml:space="preserve">1.4304084777832</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">1.42087244987488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43517661094666</t>
+    <t xml:space="preserve">1.43517649173737</t>
   </si>
   <si>
     <t xml:space="preserve">1.45901656150818</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">1.43994450569153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41610443592072</t>
+    <t xml:space="preserve">1.41610431671143</t>
   </si>
   <si>
     <t xml:space="preserve">1.51623296737671</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">1.54007315635681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58298540115356</t>
+    <t xml:space="preserve">1.58298528194427</t>
   </si>
   <si>
     <t xml:space="preserve">1.57344925403595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68788206577301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65450572967529</t>
+    <t xml:space="preserve">1.68788194656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65450584888458</t>
   </si>
   <si>
     <t xml:space="preserve">1.70695412158966</t>
@@ -1547,25 +1547,25 @@
     <t xml:space="preserve">1.76417052745819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74509847164154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7260262966156</t>
+    <t xml:space="preserve">1.74509835243225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72602617740631</t>
   </si>
   <si>
     <t xml:space="preserve">1.69741797447205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66881000995636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67357802391052</t>
+    <t xml:space="preserve">1.66880989074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67357790470123</t>
   </si>
   <si>
     <t xml:space="preserve">1.64020168781281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61159348487854</t>
+    <t xml:space="preserve">1.61159360408783</t>
   </si>
   <si>
     <t xml:space="preserve">1.60682547092438</t>
@@ -1574,31 +1574,31 @@
     <t xml:space="preserve">1.64973783493042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71172213554382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64496970176697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61636161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62112951278687</t>
+    <t xml:space="preserve">1.71172201633453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64496982097626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6163614988327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62112963199615</t>
   </si>
   <si>
     <t xml:space="preserve">1.63066565990448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63543379306793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77847468852997</t>
+    <t xml:space="preserve">1.63543367385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77847456932068</t>
   </si>
   <si>
     <t xml:space="preserve">1.75940251350403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68311405181885</t>
+    <t xml:space="preserve">1.68311393260956</t>
   </si>
   <si>
     <t xml:space="preserve">1.71649014949799</t>
@@ -1610,28 +1610,28 @@
     <t xml:space="preserve">1.81185078620911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8261547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79754674434662</t>
+    <t xml:space="preserve">1.82615482807159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79754662513733</t>
   </si>
   <si>
     <t xml:space="preserve">1.788010597229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81661891937256</t>
+    <t xml:space="preserve">1.81661880016327</t>
   </si>
   <si>
     <t xml:space="preserve">1.83092284202576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80708277225494</t>
+    <t xml:space="preserve">1.80708265304565</t>
   </si>
   <si>
     <t xml:space="preserve">1.76893854141235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73556244373322</t>
+    <t xml:space="preserve">1.73556232452393</t>
   </si>
   <si>
     <t xml:space="preserve">1.73079431056976</t>
@@ -1640,22 +1640,22 @@
     <t xml:space="preserve">1.74033033847809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72125828266144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78324246406555</t>
+    <t xml:space="preserve">1.72125816345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78324258327484</t>
   </si>
   <si>
     <t xml:space="preserve">1.74986636638641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67834603786469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66404175758362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69265007972717</t>
+    <t xml:space="preserve">1.6783459186554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66404187679291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69264996051788</t>
   </si>
   <si>
     <t xml:space="preserve">1.80231463909149</t>
@@ -1664,16 +1664,16 @@
     <t xml:space="preserve">1.75463449954987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79277861118317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5686811208725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65927374362946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5925213098526</t>
+    <t xml:space="preserve">1.79277849197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56868124008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65927386283875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59252142906189</t>
   </si>
   <si>
     <t xml:space="preserve">1.52576899528503</t>
@@ -1685,31 +1685,31 @@
     <t xml:space="preserve">1.7021861076355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85953116416931</t>
+    <t xml:space="preserve">1.85953104496002</t>
   </si>
   <si>
     <t xml:space="preserve">1.89767527580261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92628335952759</t>
+    <t xml:space="preserve">1.92628347873688</t>
   </si>
   <si>
     <t xml:space="preserve">1.82138681411743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83569073677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86429917812347</t>
+    <t xml:space="preserve">1.83569085597992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86429905891418</t>
   </si>
   <si>
     <t xml:space="preserve">1.90721130371094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94535565376282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99303579330444</t>
+    <t xml:space="preserve">1.94535553455353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99303567409515</t>
   </si>
   <si>
     <t xml:space="preserve">2.0597882270813</t>
@@ -1724,25 +1724,25 @@
     <t xml:space="preserve">2.12654066085815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10746836662292</t>
+    <t xml:space="preserve">2.1074686050415</t>
   </si>
   <si>
     <t xml:space="preserve">2.08839654922485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0979323387146</t>
+    <t xml:space="preserve">2.09793257713318</t>
   </si>
   <si>
     <t xml:space="preserve">2.1456127166748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27911734580994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19329285621643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22190093994141</t>
+    <t xml:space="preserve">2.27911758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19329309463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22190117835999</t>
   </si>
   <si>
     <t xml:space="preserve">2.25050926208496</t>
@@ -1754,13 +1754,13 @@
     <t xml:space="preserve">2.01210784912109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97396373748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98349976539612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03117990493774</t>
+    <t xml:space="preserve">1.9739636182785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98349988460541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03118014335632</t>
   </si>
   <si>
     <t xml:space="preserve">2.04071617126465</t>
@@ -1769,34 +1769,34 @@
     <t xml:space="preserve">2.09847211837769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08884620666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10809803009033</t>
+    <t xml:space="preserve">2.08884644508362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10809826850891</t>
   </si>
   <si>
     <t xml:space="preserve">2.00221180915833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95408177375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03108978271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02146410942078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05996799468994</t>
+    <t xml:space="preserve">1.95408189296722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03109002113342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0214638710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05996823310852</t>
   </si>
   <si>
     <t xml:space="preserve">1.94445586204529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97333383560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93482995033264</t>
+    <t xml:space="preserve">1.9733339548111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93482971191406</t>
   </si>
   <si>
     <t xml:space="preserve">1.85782170295715</t>
@@ -1814,25 +1814,25 @@
     <t xml:space="preserve">1.88669979572296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87707364559174</t>
+    <t xml:space="preserve">1.87707388401031</t>
   </si>
   <si>
     <t xml:space="preserve">1.89632570743561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92520391941071</t>
+    <t xml:space="preserve">1.92520380020142</t>
   </si>
   <si>
     <t xml:space="preserve">1.99258589744568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04071593284607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05034208297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11772441864014</t>
+    <t xml:space="preserve">2.04071569442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05034232139587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11772418022156</t>
   </si>
   <si>
     <t xml:space="preserve">2.1562283039093</t>
@@ -1844,16 +1844,16 @@
     <t xml:space="preserve">2.16585445404053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14660239219666</t>
+    <t xml:space="preserve">2.14660215377808</t>
   </si>
   <si>
     <t xml:space="preserve">2.07922005653381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24286246299744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25248837471008</t>
+    <t xml:space="preserve">2.24286222457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25248861312866</t>
   </si>
   <si>
     <t xml:space="preserve">2.27174043655396</t>
@@ -1862,10 +1862,10 @@
     <t xml:space="preserve">2.30061864852905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2813663482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18510627746582</t>
+    <t xml:space="preserve">2.28136610984802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1851065158844</t>
   </si>
   <si>
     <t xml:space="preserve">2.19473242759705</t>
@@ -1877,19 +1877,19 @@
     <t xml:space="preserve">2.13697624206543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01183795928955</t>
+    <t xml:space="preserve">2.01183772087097</t>
   </si>
   <si>
     <t xml:space="preserve">1.8722608089447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96370792388916</t>
+    <t xml:space="preserve">1.96370780467987</t>
   </si>
   <si>
     <t xml:space="preserve">2.06959414482117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17548036575317</t>
+    <t xml:space="preserve">2.17548012733459</t>
   </si>
   <si>
     <t xml:space="preserve">2.23323631286621</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">2.42575693130493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39687895774841</t>
+    <t xml:space="preserve">2.39687871932983</t>
   </si>
   <si>
     <t xml:space="preserve">2.40650486946106</t>
@@ -1916,28 +1916,28 @@
     <t xml:space="preserve">2.41613078117371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37762689590454</t>
+    <t xml:space="preserve">2.37762665748596</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874868392944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29099249839783</t>
+    <t xml:space="preserve">2.29099273681641</t>
   </si>
   <si>
     <t xml:space="preserve">2.36800074577332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38725280761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21398448944092</t>
+    <t xml:space="preserve">2.38725304603577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21398425102234</t>
   </si>
   <si>
     <t xml:space="preserve">2.31987071037292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4450089931488</t>
+    <t xml:space="preserve">2.44500875473022</t>
   </si>
   <si>
     <t xml:space="preserve">2.45463490486145</t>
@@ -1946,16 +1946,16 @@
     <t xml:space="preserve">2.4642608165741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49313879013062</t>
+    <t xml:space="preserve">2.49313902854919</t>
   </si>
   <si>
     <t xml:space="preserve">2.52201700210571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50276494026184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59902501106262</t>
+    <t xml:space="preserve">2.50276470184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5990252494812</t>
   </si>
   <si>
     <t xml:space="preserve">2.64715528488159</t>
@@ -1967,13 +1967,13 @@
     <t xml:space="preserve">2.51239085197449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47388696670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48351287841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53164291381836</t>
+    <t xml:space="preserve">2.47388672828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48351263999939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53164315223694</t>
   </si>
   <si>
     <t xml:space="preserve">2.63752913475037</t>
@@ -1988,22 +1988,22 @@
     <t xml:space="preserve">2.71453738212585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67603349685669</t>
+    <t xml:space="preserve">2.67603325843811</t>
   </si>
   <si>
     <t xml:space="preserve">2.60865116119385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66640734672546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5701470375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58939909934998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56052088737488</t>
+    <t xml:space="preserve">2.66640710830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57014727592468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58939933776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56052112579346</t>
   </si>
   <si>
     <t xml:space="preserve">2.6279034614563</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">2.57977318763733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38258790969849</t>
+    <t xml:space="preserve">2.38258814811707</t>
   </si>
   <si>
     <t xml:space="preserve">2.29506421089172</t>
@@ -2024,13 +2024,13 @@
     <t xml:space="preserve">2.28533935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32423877716064</t>
+    <t xml:space="preserve">2.32423901557922</t>
   </si>
   <si>
     <t xml:space="preserve">2.25616478919983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23671531677246</t>
+    <t xml:space="preserve">2.23671507835388</t>
   </si>
   <si>
     <t xml:space="preserve">2.21726560592651</t>
@@ -2042,16 +2042,16 @@
     <t xml:space="preserve">2.34368872642517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26588988304138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3047890663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24643993377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1102921962738</t>
+    <t xml:space="preserve">2.2658896446228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30478882789612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24644017219543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11029243469238</t>
   </si>
   <si>
     <t xml:space="preserve">2.15891647338867</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">2.19781565666199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16864132881165</t>
+    <t xml:space="preserve">2.16864109039307</t>
   </si>
   <si>
     <t xml:space="preserve">2.18809103965759</t>
@@ -2081,16 +2081,16 @@
     <t xml:space="preserve">2.13946676254272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09084272384644</t>
+    <t xml:space="preserve">2.09084248542786</t>
   </si>
   <si>
     <t xml:space="preserve">2.10056734085083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27561450004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08111763000488</t>
+    <t xml:space="preserve">2.27561473846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08111786842346</t>
   </si>
   <si>
     <t xml:space="preserve">1.97414433956146</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">1.98386907577515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9644193649292</t>
+    <t xml:space="preserve">1.96441948413849</t>
   </si>
   <si>
     <t xml:space="preserve">1.94496977329254</t>
@@ -2117,13 +2117,13 @@
     <t xml:space="preserve">2.02276849746704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03249335289001</t>
+    <t xml:space="preserve">2.03249311447144</t>
   </si>
   <si>
     <t xml:space="preserve">2.01304364204407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07139277458191</t>
+    <t xml:space="preserve">2.07139301300049</t>
   </si>
   <si>
     <t xml:space="preserve">2.04221820831299</t>
@@ -2135,76 +2135,79 @@
     <t xml:space="preserve">1.93524491786957</t>
   </si>
   <si>
+    <t xml:space="preserve">1.95469450950623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91579520702362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93038249015808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06166768074036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91093277931213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1491916179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00331878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86717092990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92552006244659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81854665279388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84772121906281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8866206407547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83313393592834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85258364677429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89634561538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92065763473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95961833000183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96946561336517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01870226860046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96454191207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98916029930115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00885486602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99900758266449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97931289672852</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.95469462871552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91579520702362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93038249015808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06166791915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91093289852142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1491916179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00331878662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86717092990875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92552006244659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81854677200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84772133827209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8866206407547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83313405513763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85258364677429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89634561538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92065763473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95961833000183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96946561336517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01870226860046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96454191207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98916029930115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00885486602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99900758266449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97931289672852</t>
   </si>
   <si>
     <t xml:space="preserve">1.9497709274292</t>
@@ -59500,7 +59503,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2180" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -59526,7 +59529,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2181" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59552,7 +59555,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2182" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59578,7 +59581,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2183" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59682,7 +59685,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2187" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59708,7 +59711,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2188" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59734,7 +59737,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2189" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59760,7 +59763,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2190" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59786,7 +59789,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2191" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59812,7 +59815,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2192" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59838,7 +59841,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2193" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60150,7 +60153,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2205" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60176,7 +60179,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2206" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60202,7 +60205,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2207" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60228,7 +60231,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2208" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60280,7 +60283,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2210" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60306,7 +60309,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2211" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60332,7 +60335,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2212" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60358,7 +60361,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2213" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60384,7 +60387,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2214" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60436,7 +60439,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2216" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60592,7 +60595,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60670,7 +60673,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2225" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60696,7 +60699,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2226" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60748,7 +60751,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2228" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60774,7 +60777,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2229" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60800,7 +60803,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2230" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60826,7 +60829,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2231" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60852,7 +60855,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2232" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60878,7 +60881,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2233" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60904,7 +60907,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2234" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60930,7 +60933,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2235" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60956,7 +60959,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2236" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60982,7 +60985,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2237" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61008,7 +61011,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2238" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61034,7 +61037,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2239" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61060,7 +61063,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2240" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61086,7 +61089,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G2241" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61112,7 +61115,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2242" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61138,7 +61141,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2243" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61164,7 +61167,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G2244" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61190,7 +61193,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2245" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61216,7 +61219,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2246" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61242,7 +61245,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2247" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61268,7 +61271,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2248" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61294,7 +61297,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2249" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61320,7 +61323,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2250" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61346,7 +61349,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2251" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61372,7 +61375,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2252" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61476,7 +61479,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2256" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -61502,7 +61505,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2257" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -61554,7 +61557,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2259" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -61580,7 +61583,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2260" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -61606,7 +61609,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2261" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -61632,7 +61635,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -61658,7 +61661,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2263" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -61710,7 +61713,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2265" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61736,7 +61739,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2266" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61866,7 +61869,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2271" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61892,7 +61895,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2272" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61918,7 +61921,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2273" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61944,7 +61947,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2274" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61970,7 +61973,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2275" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61996,7 +61999,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2276" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62022,7 +62025,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2277" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62048,7 +62051,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2278" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62074,7 +62077,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2279" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62100,7 +62103,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2280" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62126,7 +62129,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2281" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62152,7 +62155,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2282" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62178,7 +62181,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2283" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62204,7 +62207,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2284" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62230,7 +62233,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2285" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62256,7 +62259,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2286" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62282,7 +62285,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2287" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62308,7 +62311,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2288" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62334,7 +62337,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2289" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62360,7 +62363,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2290" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62386,7 +62389,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2291" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62412,7 +62415,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2292" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62438,7 +62441,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2293" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62464,7 +62467,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2294" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -62490,7 +62493,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2295" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -62516,7 +62519,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2296" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -62542,7 +62545,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2297" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -62568,7 +62571,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2298" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -62594,7 +62597,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2299" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -62620,7 +62623,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2300" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -62646,7 +62649,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2301" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -62672,7 +62675,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2302" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -62698,7 +62701,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2303" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62724,7 +62727,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2304" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62750,7 +62753,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62776,7 +62779,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2306" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62802,7 +62805,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G2307" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62828,7 +62831,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2308" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62854,7 +62857,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2309" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62880,7 +62883,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2310" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62906,7 +62909,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2311" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62932,7 +62935,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2312" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62958,7 +62961,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2313" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62984,7 +62987,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2314" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63010,7 +63013,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2315" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63036,7 +63039,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2316" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63062,7 +63065,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2317" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63088,7 +63091,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2318" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63114,7 +63117,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2319" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63140,7 +63143,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2320" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63166,7 +63169,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2321" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63192,7 +63195,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2322" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63218,7 +63221,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2323" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63244,7 +63247,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2324" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63270,7 +63273,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2325" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63296,7 +63299,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2326" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63322,7 +63325,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2327" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63348,7 +63351,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2328" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63374,7 +63377,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2329" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63400,7 +63403,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2330" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63426,7 +63429,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2331" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63452,7 +63455,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2332" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63478,7 +63481,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2333" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -63504,7 +63507,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2334" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -63530,7 +63533,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2335" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -63556,7 +63559,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2336" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -63582,7 +63585,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2337" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -63608,7 +63611,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2338" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -63634,7 +63637,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2339" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -63660,7 +63663,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G2340" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -63686,7 +63689,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2341" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63712,7 +63715,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2342" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63738,7 +63741,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63764,7 +63767,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2344" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63790,7 +63793,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2345" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63816,7 +63819,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2346" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63842,7 +63845,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2347" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63868,7 +63871,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63894,7 +63897,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63920,7 +63923,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2350" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63946,7 +63949,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2351" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63972,7 +63975,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G2352" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63998,7 +64001,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2353" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64024,7 +64027,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2354" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64050,7 +64053,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2355" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64076,7 +64079,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2356" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64102,7 +64105,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G2357" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64128,7 +64131,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2358" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64154,7 +64157,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G2359" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64180,7 +64183,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G2360" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64206,7 +64209,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2361" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64232,7 +64235,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2362" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64258,7 +64261,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2363" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64284,7 +64287,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G2364" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64310,7 +64313,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2365" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64336,7 +64339,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64362,7 +64365,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G2367" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64388,7 +64391,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2368" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64414,7 +64417,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2369" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64440,7 +64443,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2370" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64466,7 +64469,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2371" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64492,7 +64495,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2372" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -64518,7 +64521,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2373" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -64544,7 +64547,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G2374" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -64570,7 +64573,7 @@
         <v>1.625</v>
       </c>
       <c r="G2375" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -64596,7 +64599,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G2376" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -64622,7 +64625,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G2377" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -64648,7 +64651,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2378" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -64674,7 +64677,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G2379" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -64700,7 +64703,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2380" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64726,7 +64729,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2381" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64752,7 +64755,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2382" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64778,7 +64781,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G2383" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64804,7 +64807,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2384" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64830,7 +64833,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2385" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64856,7 +64859,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64882,7 +64885,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2387" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64908,7 +64911,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2388" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64934,7 +64937,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64960,7 +64963,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2390" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64986,7 +64989,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2391" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65012,7 +65015,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2392" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65038,7 +65041,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G2393" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65064,7 +65067,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G2394" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65090,7 +65093,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2395" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65116,7 +65119,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2396" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65142,7 +65145,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2397" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65168,7 +65171,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2398" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65194,7 +65197,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2399" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65220,7 +65223,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2400" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65246,7 +65249,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2401" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65272,7 +65275,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2402" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65298,7 +65301,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2403" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65324,7 +65327,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2404" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65350,7 +65353,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2405" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65376,7 +65379,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2406" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65428,7 +65431,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2408" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65454,7 +65457,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2409" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65480,7 +65483,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2410" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -65506,7 +65509,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2411" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65532,7 +65535,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2412" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65558,7 +65561,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2413" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65584,7 +65587,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2414" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65610,7 +65613,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2415" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65636,7 +65639,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2416" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65662,7 +65665,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2417" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65688,7 +65691,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2418" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65714,7 +65717,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2419" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65740,7 +65743,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2420" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65766,7 +65769,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2421" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65792,7 +65795,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65818,7 +65821,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2423" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65844,7 +65847,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2424" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65870,7 +65873,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2425" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65896,7 +65899,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2426" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65922,7 +65925,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2427" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65948,7 +65951,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2428" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65974,7 +65977,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2429" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66000,7 +66003,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2430" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66026,7 +66029,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2431" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66052,7 +66055,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2432" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66078,7 +66081,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2433" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66104,7 +66107,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2434" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66130,7 +66133,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2435" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66156,7 +66159,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2436" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66182,7 +66185,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2437" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66208,7 +66211,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2438" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66234,7 +66237,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2439" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66260,7 +66263,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2440" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66286,7 +66289,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2441" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66312,7 +66315,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2442" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66338,7 +66341,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2443" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66364,7 +66367,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2444" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66390,7 +66393,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2445" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66416,7 +66419,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2446" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66442,7 +66445,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2447" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66468,7 +66471,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2448" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -66494,7 +66497,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2449" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -66520,7 +66523,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2450" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66546,7 +66549,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2451" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66572,7 +66575,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2452" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66598,7 +66601,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2453" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66624,7 +66627,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2454" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66650,7 +66653,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2455" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66676,7 +66679,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2456" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66702,7 +66705,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2457" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66728,7 +66731,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2458" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66754,7 +66757,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2459" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66780,7 +66783,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2460" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66806,7 +66809,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2461" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66832,7 +66835,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2462" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66858,7 +66861,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2463" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66884,7 +66887,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2464" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66910,7 +66913,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2465" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66936,7 +66939,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2466" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66962,7 +66965,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2467" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66988,7 +66991,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2468" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67014,7 +67017,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2469" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67040,7 +67043,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2470" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67066,7 +67069,7 @@
         <v>2</v>
       </c>
       <c r="G2471" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67092,7 +67095,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2472" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67118,7 +67121,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2473" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67144,7 +67147,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2474" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67170,7 +67173,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2475" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67196,7 +67199,7 @@
         <v>2</v>
       </c>
       <c r="G2476" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67222,7 +67225,7 @@
         <v>2</v>
       </c>
       <c r="G2477" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67248,7 +67251,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2478" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67274,7 +67277,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2479" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67300,7 +67303,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2480" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67326,7 +67329,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2481" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67352,7 +67355,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2482" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67378,7 +67381,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2483" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67404,7 +67407,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2484" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67430,7 +67433,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2485" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67456,7 +67459,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2486" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67482,7 +67485,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2487" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -67508,7 +67511,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2488" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67534,7 +67537,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2489" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67560,7 +67563,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2490" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67586,7 +67589,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2491" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67612,7 +67615,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2492" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67638,7 +67641,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2493" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67664,7 +67667,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2494" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67690,7 +67693,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2495" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67716,7 +67719,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2496" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67742,7 +67745,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2497" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67768,7 +67771,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2498" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67794,7 +67797,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2499" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67820,7 +67823,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2500" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67846,7 +67849,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2501" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67872,7 +67875,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2502" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -67898,7 +67901,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2503" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -67924,7 +67927,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2504" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67950,7 +67953,7 @@
         <v>2</v>
       </c>
       <c r="G2505" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67976,7 +67979,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2506" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68002,7 +68005,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2507" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68028,7 +68031,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2508" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68054,7 +68057,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2509" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68080,7 +68083,7 @@
         <v>2</v>
       </c>
       <c r="G2510" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68106,7 +68109,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2511" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68132,7 +68135,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2512" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68158,7 +68161,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2513" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -68184,7 +68187,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2514" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -68210,7 +68213,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2515" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -68236,7 +68239,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2516" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -68262,7 +68265,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2517" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -68288,7 +68291,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2518" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -68314,7 +68317,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2519" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -68340,7 +68343,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2520" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -68366,7 +68369,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2521" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -68392,7 +68395,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2522" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -68418,7 +68421,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2523" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -68444,7 +68447,7 @@
         <v>2</v>
       </c>
       <c r="G2524" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -68470,7 +68473,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2525" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -68496,7 +68499,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2526" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -68522,7 +68525,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2527" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -68548,7 +68551,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2528" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -68574,7 +68577,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2529" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -68600,7 +68603,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2530" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -68626,7 +68629,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2531" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -68652,7 +68655,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2532" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -68678,7 +68681,7 @@
         <v>2</v>
       </c>
       <c r="G2533" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -68704,7 +68707,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2534" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -68730,7 +68733,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2535" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -68756,7 +68759,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2536" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -68782,7 +68785,7 @@
         <v>2</v>
       </c>
       <c r="G2537" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2537" t="s">
         <v>9</v>
@@ -68808,7 +68811,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2538" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2538" t="s">
         <v>9</v>
@@ -68834,7 +68837,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2539" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2539" t="s">
         <v>9</v>
@@ -68842,7 +68845,7 @@
     </row>
     <row r="2540">
       <c r="A2540" s="1" t="n">
-        <v>46020.6687384259</v>
+        <v>46020.3333333333</v>
       </c>
       <c r="B2540" t="n">
         <v>30000</v>
@@ -68860,9 +68863,35 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2540" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2540" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" s="1" t="n">
+        <v>46021.5648958333</v>
+      </c>
+      <c r="B2541" t="n">
+        <v>17500</v>
+      </c>
+      <c r="C2541" t="n">
+        <v>1.99500000476837</v>
+      </c>
+      <c r="D2541" t="n">
+        <v>1.92499995231628</v>
+      </c>
+      <c r="E2541" t="n">
+        <v>1.95500004291534</v>
+      </c>
+      <c r="F2541" t="n">
+        <v>1.96000003814697</v>
+      </c>
+      <c r="G2541" t="s">
+        <v>816</v>
+      </c>
+      <c r="H2541" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DGT.MI.xlsx
+++ b/data/DGT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="826">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08123898506165</t>
+    <t xml:space="preserve">2.08123874664307</t>
   </si>
   <si>
     <t xml:space="preserve">DGT.MI</t>
@@ -53,61 +53,61 @@
     <t xml:space="preserve">1.96702468395233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00509572029114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04860615730286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9942182302475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971498966217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94889533519745</t>
+    <t xml:space="preserve">2.0050961971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04860639572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99421834945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971510887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94889509677887</t>
   </si>
   <si>
     <t xml:space="preserve">1.88544285297394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91444981098175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89632046222687</t>
+    <t xml:space="preserve">1.91444993019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89632022380829</t>
   </si>
   <si>
     <t xml:space="preserve">1.8763781785965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97065043449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9271399974823</t>
+    <t xml:space="preserve">1.97065031528473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92714011669159</t>
   </si>
   <si>
     <t xml:space="preserve">1.93076622486115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8582489490509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80839359760284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82561612129211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75128638744354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64704298973083</t>
+    <t xml:space="preserve">1.85824906826019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80839335918427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8256162405014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75128650665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64704322814941</t>
   </si>
   <si>
     <t xml:space="preserve">1.75581872463226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71321475505829</t>
+    <t xml:space="preserve">1.71321487426758</t>
   </si>
   <si>
     <t xml:space="preserve">1.68964684009552</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">1.76760268211365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72862493991852</t>
+    <t xml:space="preserve">1.72862482070923</t>
   </si>
   <si>
     <t xml:space="preserve">1.7585381269455</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">1.81292581558228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83105516433716</t>
+    <t xml:space="preserve">1.83105504512787</t>
   </si>
   <si>
     <t xml:space="preserve">1.76850914955139</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">1.74947333335876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69871139526367</t>
+    <t xml:space="preserve">1.69871151447296</t>
   </si>
   <si>
     <t xml:space="preserve">1.74766051769257</t>
@@ -149,100 +149,100 @@
     <t xml:space="preserve">1.70777606964111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70868241786957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69508564472198</t>
+    <t xml:space="preserve">1.70868253707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6950855255127</t>
   </si>
   <si>
     <t xml:space="preserve">1.77666735649109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7014307975769</t>
+    <t xml:space="preserve">1.70143103599548</t>
   </si>
   <si>
     <t xml:space="preserve">1.69055342674255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73496985435486</t>
+    <t xml:space="preserve">1.73497009277344</t>
   </si>
   <si>
     <t xml:space="preserve">1.64069783687592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62982034683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63163328170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.686927318573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68602120876312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67333042621613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7404088973999</t>
+    <t xml:space="preserve">1.62982046604156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63163316249847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68692755699158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68602097034454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67333054542542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74040877819061</t>
   </si>
   <si>
     <t xml:space="preserve">1.70415031909943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75672519207001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68783390522003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6488561630249</t>
+    <t xml:space="preserve">1.75672507286072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68783414363861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64885592460632</t>
   </si>
   <si>
     <t xml:space="preserve">1.64794957637787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68420815467834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72137320041656</t>
+    <t xml:space="preserve">1.68420791625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72137296199799</t>
   </si>
   <si>
     <t xml:space="preserve">1.72227942943573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67786288261414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63253962993622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66335940361023</t>
+    <t xml:space="preserve">1.67786276340485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63253974914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66335952281952</t>
   </si>
   <si>
     <t xml:space="preserve">1.66517245769501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65429472923279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81111299991608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79026448726654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78754484653473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78935766220093</t>
+    <t xml:space="preserve">1.65429484844208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81111288070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79026436805725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78754496574402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78935790061951</t>
   </si>
   <si>
     <t xml:space="preserve">1.66154646873474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69961798191071</t>
+    <t xml:space="preserve">1.69961774349213</t>
   </si>
   <si>
     <t xml:space="preserve">1.66245293617249</t>
@@ -254,13 +254,13 @@
     <t xml:space="preserve">1.65882706642151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60353291034698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.569087266922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58902943134308</t>
+    <t xml:space="preserve">1.60353302955627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56908714771271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58902955055237</t>
   </si>
   <si>
     <t xml:space="preserve">1.48297333717346</t>
@@ -269,70 +269,70 @@
     <t xml:space="preserve">1.49566388130188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4920380115509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53192245960236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48387956619263</t>
+    <t xml:space="preserve">1.49203789234161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53192234039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48387980461121</t>
   </si>
   <si>
     <t xml:space="preserve">1.45215368270874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48569285869598</t>
+    <t xml:space="preserve">1.48569273948669</t>
   </si>
   <si>
     <t xml:space="preserve">1.42858552932739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45940542221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49294447898865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46031165122986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4412761926651</t>
+    <t xml:space="preserve">1.45940518379211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49294435977936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46031177043915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44127595424652</t>
   </si>
   <si>
     <t xml:space="preserve">1.45034062862396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46846997737885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42586624622345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31255829334259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36422669887543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34156513214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36875903606415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33250057697296</t>
+    <t xml:space="preserve">1.46846985816956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42586612701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31255841255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36422681808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34156501293182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36875915527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33250033855438</t>
   </si>
   <si>
     <t xml:space="preserve">1.2781126499176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19653117656708</t>
+    <t xml:space="preserve">1.19653105735779</t>
   </si>
   <si>
     <t xml:space="preserve">1.17296290397644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18746638298035</t>
+    <t xml:space="preserve">1.18746650218964</t>
   </si>
   <si>
     <t xml:space="preserve">1.17568242549896</t>
@@ -344,16 +344,16 @@
     <t xml:space="preserve">1.09863317012787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12401413917542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13307857513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12582683563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11313652992249</t>
+    <t xml:space="preserve">1.12401401996613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13307881355286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1258270740509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1131364107132</t>
   </si>
   <si>
     <t xml:space="preserve">1.06962621212006</t>
@@ -362,28 +362,28 @@
     <t xml:space="preserve">1.08684897422791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09500706195831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09410059452057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12038815021515</t>
+    <t xml:space="preserve">1.0950071811676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09410083293915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12038838863373</t>
   </si>
   <si>
     <t xml:space="preserve">1.09228777885437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10769772529602</t>
+    <t xml:space="preserve">1.10769748687744</t>
   </si>
   <si>
     <t xml:space="preserve">1.10951066017151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1212944984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09682023525238</t>
+    <t xml:space="preserve">1.12129473686218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0968199968338</t>
   </si>
   <si>
     <t xml:space="preserve">1.08956849575043</t>
@@ -395,37 +395,37 @@
     <t xml:space="preserve">1.07234561443329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05149698257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12310743331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10135245323181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08322310447693</t>
+    <t xml:space="preserve">1.05149686336517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12310755252838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10135233402252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08322322368622</t>
   </si>
   <si>
     <t xml:space="preserve">1.08775568008423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11404275894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15120804309845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21466052532196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18474686145782</t>
+    <t xml:space="preserve">1.11404287815094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15120792388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21466028690338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18474698066711</t>
   </si>
   <si>
     <t xml:space="preserve">1.14576923847198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12220108509064</t>
+    <t xml:space="preserve">1.12220120429993</t>
   </si>
   <si>
     <t xml:space="preserve">1.06237471103668</t>
@@ -434,61 +434,61 @@
     <t xml:space="preserve">1.03336775302887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.934563219547272</t>
+    <t xml:space="preserve">0.934563279151917</t>
   </si>
   <si>
     <t xml:space="preserve">0.945440828800201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977166891098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956318318843842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933656811714172</t>
+    <t xml:space="preserve">0.977167010307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956318378448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933656752109528</t>
   </si>
   <si>
     <t xml:space="preserve">1.01523840427399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04877758026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03608703613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02430307865143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990764141082764</t>
+    <t xml:space="preserve">1.04877746105194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0360871553421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02430319786072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990764021873474</t>
   </si>
   <si>
     <t xml:space="preserve">1.05059051513672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11494946479797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12854635715485</t>
+    <t xml:space="preserve">1.11494934558868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12854647636414</t>
   </si>
   <si>
     <t xml:space="preserve">1.07506501674652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06418764591217</t>
+    <t xml:space="preserve">1.06418740749359</t>
   </si>
   <si>
     <t xml:space="preserve">1.02067720890045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997109115123749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00617372989655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988044619560242</t>
+    <t xml:space="preserve">0.997109174728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00617396831512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988044381141663</t>
   </si>
   <si>
     <t xml:space="preserve">1.03880655765533</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">1.04243218898773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06328105926514</t>
+    <t xml:space="preserve">1.06328117847443</t>
   </si>
   <si>
     <t xml:space="preserve">1.05693566799164</t>
@@ -509,43 +509,43 @@
     <t xml:space="preserve">1.10407197475433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1049782037735</t>
+    <t xml:space="preserve">1.10497832298279</t>
   </si>
   <si>
     <t xml:space="preserve">1.07597148418427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12492072582245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1031653881073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21103429794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19562470912933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21284735202789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14667558670044</t>
+    <t xml:space="preserve">1.12492060661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10316550731659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2110344171524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19562458992004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2128472328186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14667570590973</t>
   </si>
   <si>
     <t xml:space="preserve">1.15392732620239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20559585094452</t>
+    <t xml:space="preserve">1.20559573173523</t>
   </si>
   <si>
     <t xml:space="preserve">1.20196974277496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23188292980194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2536381483078</t>
+    <t xml:space="preserve">1.23188304901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25363826751709</t>
   </si>
   <si>
     <t xml:space="preserve">1.25817048549652</t>
@@ -557,22 +557,22 @@
     <t xml:space="preserve">1.25545120239258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28717732429504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3089325428009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30530655384064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.412269115448</t>
+    <t xml:space="preserve">1.28717720508575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30893242359161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30530667304993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41226923465729</t>
   </si>
   <si>
     <t xml:space="preserve">1.37963664531708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40320444107056</t>
+    <t xml:space="preserve">1.40320456027985</t>
   </si>
   <si>
     <t xml:space="preserve">1.35244262218475</t>
@@ -581,28 +581,28 @@
     <t xml:space="preserve">1.35697484016418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35969436168671</t>
+    <t xml:space="preserve">1.35969424247742</t>
   </si>
   <si>
     <t xml:space="preserve">1.34065854549408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32343590259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35062980651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32887446880341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26995468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19471800327301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14395618438721</t>
+    <t xml:space="preserve">1.32343602180481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35062968730927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32887470722198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26995456218719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19471824169159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1439563035965</t>
   </si>
   <si>
     <t xml:space="preserve">1.24548006057739</t>
@@ -614,34 +614,34 @@
     <t xml:space="preserve">1.26814162731171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23278963565826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24185431003571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28173863887787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26451563835144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28264498710632</t>
+    <t xml:space="preserve">1.23278951644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24185419082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28173851966858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26451575756073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28264486789703</t>
   </si>
   <si>
     <t xml:space="preserve">1.25091874599457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26904809474945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33159399032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29624211788177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28536438941956</t>
+    <t xml:space="preserve">1.26904821395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33159410953522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29624199867249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28536450862885</t>
   </si>
   <si>
     <t xml:space="preserve">1.31437122821808</t>
@@ -650,28 +650,28 @@
     <t xml:space="preserve">1.30983901023865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31799709796906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29896140098572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3778235912323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33522009849548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26179623603821</t>
+    <t xml:space="preserve">1.31799721717834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29896128177643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37782382965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33521997928619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2617963552475</t>
   </si>
   <si>
     <t xml:space="preserve">1.3107453584671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30711948871613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34247159957886</t>
+    <t xml:space="preserve">1.30711960792542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34247148036957</t>
   </si>
   <si>
     <t xml:space="preserve">1.29442894458771</t>
@@ -680,43 +680,43 @@
     <t xml:space="preserve">1.32434225082397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33884584903717</t>
+    <t xml:space="preserve">1.33884572982788</t>
   </si>
   <si>
     <t xml:space="preserve">1.31165182590485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27992558479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30621314048767</t>
+    <t xml:space="preserve">1.27992570400238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30621302127838</t>
   </si>
   <si>
     <t xml:space="preserve">1.31618416309357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30349349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27720630168915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26632857322693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28355145454407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25907707214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24910581111908</t>
+    <t xml:space="preserve">1.30349385738373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27720642089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26632869243622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28355133533478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25907695293427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24910593032837</t>
   </si>
   <si>
     <t xml:space="preserve">1.27539324760437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25273168087006</t>
+    <t xml:space="preserve">1.25273191928864</t>
   </si>
   <si>
     <t xml:space="preserve">1.34700393676758</t>
@@ -731,82 +731,82 @@
     <t xml:space="preserve">1.32978105545044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2336962223053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22372496128082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22916376590729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2046891450882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22191214561462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2191926240921</t>
+    <t xml:space="preserve">1.23369598388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22372472286224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22916352748871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20468926429749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22191202640533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21919274330139</t>
   </si>
   <si>
     <t xml:space="preserve">1.22100555896759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21828615665436</t>
+    <t xml:space="preserve">1.21828603744507</t>
   </si>
   <si>
     <t xml:space="preserve">1.22463130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21012806892395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1865599155426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17477607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17840182781219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15211427211761</t>
+    <t xml:space="preserve">1.21012794971466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18656003475189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17477595806122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17840170860291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1521143913269</t>
   </si>
   <si>
     <t xml:space="preserve">1.15845954418182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08594238758087</t>
+    <t xml:space="preserve">1.08594250679016</t>
   </si>
   <si>
     <t xml:space="preserve">1.10588479042053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07959723472595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1067910194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13217198848724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16933727264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22644436359406</t>
+    <t xml:space="preserve">1.07959735393524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10679125785828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13217222690582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16933715343475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22644424438477</t>
   </si>
   <si>
     <t xml:space="preserve">1.23822832107544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24457359313965</t>
+    <t xml:space="preserve">1.24457371234894</t>
   </si>
   <si>
     <t xml:space="preserve">1.2518253326416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24004125595093</t>
+    <t xml:space="preserve">1.24004113674164</t>
   </si>
   <si>
     <t xml:space="preserve">1.20378279685974</t>
@@ -815,19 +815,19 @@
     <t xml:space="preserve">1.20650207996368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24094772338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23097658157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21194088459015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23460257053375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24638652801514</t>
+    <t xml:space="preserve">1.24094760417938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23097670078278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21194100379944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23460233211517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24638664722443</t>
   </si>
   <si>
     <t xml:space="preserve">1.27629971504211</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">1.29805481433868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22553789615631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15574026107788</t>
+    <t xml:space="preserve">1.22553777694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15574014186859</t>
   </si>
   <si>
     <t xml:space="preserve">1.11857509613037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1602725982666</t>
+    <t xml:space="preserve">1.16027247905731</t>
   </si>
   <si>
     <t xml:space="preserve">1.16661763191223</t>
@@ -857,52 +857,52 @@
     <t xml:space="preserve">1.16480481624603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18112111091614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19925022125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11676251888275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09319412708282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09772658348083</t>
+    <t xml:space="preserve">1.18112123012543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19925045967102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11676216125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0931943655014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09772646427155</t>
   </si>
   <si>
     <t xml:space="preserve">1.17658889293671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17930841445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21375370025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21556675434113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28627097606659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28989672660828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2844580411911</t>
+    <t xml:space="preserve">1.17930829524994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21375381946564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21556663513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2862708568573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28989660739899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28445780277252</t>
   </si>
   <si>
     <t xml:space="preserve">1.38960766792297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4004852771759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41408216953278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38235604763031</t>
+    <t xml:space="preserve">1.40048503875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4140819311142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38235592842102</t>
   </si>
   <si>
     <t xml:space="preserve">1.37057185173035</t>
@@ -911,94 +911,94 @@
     <t xml:space="preserve">1.32796823978424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36513328552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35516202449799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38416886329651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42224037647247</t>
+    <t xml:space="preserve">1.36513316631317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3551619052887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38416874408722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42224025726318</t>
   </si>
   <si>
     <t xml:space="preserve">1.38054299354553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38870120048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36694598197937</t>
+    <t xml:space="preserve">1.38870131969452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36694622039795</t>
   </si>
   <si>
     <t xml:space="preserve">1.40773689746857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39957869052887</t>
+    <t xml:space="preserve">1.39957880973816</t>
   </si>
   <si>
     <t xml:space="preserve">1.39685940742493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38326227664948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38688838481903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50926077365875</t>
+    <t xml:space="preserve">1.38326239585876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38688826560974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50926065444946</t>
   </si>
   <si>
     <t xml:space="preserve">1.57724547386169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57271325588226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54551923274994</t>
+    <t xml:space="preserve">1.57271313667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54551947116852</t>
   </si>
   <si>
     <t xml:space="preserve">1.55005156993866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51379323005676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48659908771515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44580829143524</t>
+    <t xml:space="preserve">1.51379299163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48659920692444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44580852985382</t>
   </si>
   <si>
     <t xml:space="preserve">1.48206675052643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43221139907837</t>
+    <t xml:space="preserve">1.43221151828766</t>
   </si>
   <si>
     <t xml:space="preserve">1.54098689556122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52285766601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52738988399506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37329125404358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39142060279846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34609758853912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29170966148376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31890344619751</t>
+    <t xml:space="preserve">1.52285754680634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52739000320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37329137325287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39142048358917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34609746932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29170954227448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31890368461609</t>
   </si>
   <si>
     <t xml:space="preserve">1.33703279495239</t>
@@ -1007,139 +1007,139 @@
     <t xml:space="preserve">1.27358043193817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3959527015686</t>
+    <t xml:space="preserve">1.39595282077789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30077409744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33341026306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31476104259491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30543661117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31942331790924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24482703208923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24948930740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23084020614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21219098567963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25415170192719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23550248146057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2261780500412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19354212284088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19820427894592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2401647567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27280068397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29611217975616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31009900569916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3287478685379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28212535381317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26813840866089</t>
   </si>
   <si>
     <t xml:space="preserve">1.30077421665192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33341038227081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31476104259491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30543661117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31942331790924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24482715129852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24948930740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23084044456482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21219110488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2541515827179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23550248146057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22617793083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19354200363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19820427894592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2401647567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27280080318451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29611217975616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31009876728058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3287478685379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28212535381317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26813840866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30077409744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21685326099396</t>
+    <t xml:space="preserve">1.21685349941254</t>
   </si>
   <si>
     <t xml:space="preserve">1.18887972831726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16556823253632</t>
+    <t xml:space="preserve">1.16556859016418</t>
   </si>
   <si>
     <t xml:space="preserve">1.20286655426025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17489290237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1795551776886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2075287103653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32408571243286</t>
+    <t xml:space="preserve">1.17489302158356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17955529689789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20752882957458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32408559322357</t>
   </si>
   <si>
     <t xml:space="preserve">1.34739720821381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17023074626923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14691936969757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13293254375458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25881385803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746284008026</t>
+    <t xml:space="preserve">1.17023062705994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14691925048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13293242454529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25881373882294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746295928955</t>
   </si>
   <si>
     <t xml:space="preserve">1.22151565551758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15624392032623</t>
+    <t xml:space="preserve">1.15624380111694</t>
   </si>
   <si>
     <t xml:space="preserve">1.18421745300293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28678750991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16090607643127</t>
+    <t xml:space="preserve">1.28678739070892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16090619564056</t>
   </si>
   <si>
     <t xml:space="preserve">1.15158152580261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13759469985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36138379573822</t>
+    <t xml:space="preserve">1.13759481906891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3613840341568</t>
   </si>
   <si>
     <t xml:space="preserve">1.29144978523254</t>
@@ -1148,40 +1148,40 @@
     <t xml:space="preserve">1.34273481369019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33807253837585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11428332328796</t>
+    <t xml:space="preserve">1.33807241916656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11428344249725</t>
   </si>
   <si>
     <t xml:space="preserve">1.1049587726593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14225697517395</t>
+    <t xml:space="preserve">1.14225709438324</t>
   </si>
   <si>
     <t xml:space="preserve">1.27810609340668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29230737686157</t>
+    <t xml:space="preserve">1.29230725765228</t>
   </si>
   <si>
     <t xml:space="preserve">1.37278068065643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34437811374664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32544326782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30177450180054</t>
+    <t xml:space="preserve">1.34437823295593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32544314861298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30177462100983</t>
   </si>
   <si>
     <t xml:space="preserve">1.55266213417053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41065037250519</t>
+    <t xml:space="preserve">1.4106502532959</t>
   </si>
   <si>
     <t xml:space="preserve">1.31124210357666</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">1.31597590446472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28757345676422</t>
+    <t xml:space="preserve">1.28757357597351</t>
   </si>
   <si>
     <t xml:space="preserve">1.30650842189789</t>
@@ -1199,43 +1199,43 @@
     <t xml:space="preserve">1.33964431285858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42011773586273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40591657161713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35384571552277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39644920825958</t>
+    <t xml:space="preserve">1.42011785507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40591669082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35384559631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39644908905029</t>
   </si>
   <si>
     <t xml:space="preserve">1.32070958614349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3349107503891</t>
+    <t xml:space="preserve">1.33491086959839</t>
   </si>
   <si>
     <t xml:space="preserve">1.28283965587616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27337229251862</t>
+    <t xml:space="preserve">1.27337241172791</t>
   </si>
   <si>
     <t xml:space="preserve">1.26390480995178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2591712474823</t>
+    <t xml:space="preserve">1.25917112827301</t>
   </si>
   <si>
     <t xml:space="preserve">1.29704082012177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2449699640274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23076868057251</t>
+    <t xml:space="preserve">1.24497008323669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2307687997818</t>
   </si>
   <si>
     <t xml:space="preserve">1.22130131721497</t>
@@ -1247,28 +1247,28 @@
     <t xml:space="preserve">1.22603499889374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24023616313934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21183383464813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26863861083984</t>
+    <t xml:space="preserve">1.24023628234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21183395385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26863849163055</t>
   </si>
   <si>
     <t xml:space="preserve">1.20710003376007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24970376491547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25443744659424</t>
+    <t xml:space="preserve">1.24970364570618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25443756580353</t>
   </si>
   <si>
     <t xml:space="preserve">1.23550236225128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16923034191132</t>
+    <t xml:space="preserve">1.16923022270203</t>
   </si>
   <si>
     <t xml:space="preserve">1.18343162536621</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">1.1408280134201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12189304828644</t>
+    <t xml:space="preserve">1.12189316749573</t>
   </si>
   <si>
     <t xml:space="preserve">1.11715924739838</t>
@@ -1289,10 +1289,10 @@
     <t xml:space="preserve">1.10295808315277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0698219537735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01775121688843</t>
+    <t xml:space="preserve">1.06982207298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01775109767914</t>
   </si>
   <si>
     <t xml:space="preserve">0.989348649978638</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">0.979881286621094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965680122375488</t>
+    <t xml:space="preserve">0.965680062770844</t>
   </si>
   <si>
     <t xml:space="preserve">0.914555907249451</t>
@@ -1310,10 +1310,10 @@
     <t xml:space="preserve">0.937277734279633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92023640871048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880473077297211</t>
+    <t xml:space="preserve">0.92023628950119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880473017692566</t>
   </si>
   <si>
     <t xml:space="preserve">0.927810311317444</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">0.946745276451111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9562126994133</t>
+    <t xml:space="preserve">0.956212639808655</t>
   </si>
   <si>
     <t xml:space="preserve">1.0224848985672</t>
@@ -1334,43 +1334,43 @@
     <t xml:space="preserve">1.10769200325012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13609421253204</t>
+    <t xml:space="preserve">1.13609433174133</t>
   </si>
   <si>
     <t xml:space="preserve">1.05562090873718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09349083900452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06035459041595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06508839130402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07455587387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04615354537964</t>
+    <t xml:space="preserve">1.09349071979523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06035447120667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06508851051331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07455563545227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04615342617035</t>
   </si>
   <si>
     <t xml:space="preserve">1.03668606281281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04141962528229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1124255657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12662696838379</t>
+    <t xml:space="preserve">1.04141974449158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11242544651031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12662672996521</t>
   </si>
   <si>
     <t xml:space="preserve">1.08875703811646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09822428226471</t>
+    <t xml:space="preserve">1.098224401474</t>
   </si>
   <si>
     <t xml:space="preserve">1.05088722705841</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">1.17869770526886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15976297855377</t>
+    <t xml:space="preserve">1.15976285934448</t>
   </si>
   <si>
     <t xml:space="preserve">1.15029549598694</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">1.15502917766571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14556181430817</t>
+    <t xml:space="preserve">1.14556157588959</t>
   </si>
   <si>
     <t xml:space="preserve">1.17396402359009</t>
@@ -1409,37 +1409,40 @@
     <t xml:space="preserve">1.08402323722839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0082836151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98461502790451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994082391262054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01301753520966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18816530704498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33017694950104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40118288993835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36331295967102</t>
+    <t xml:space="preserve">1.00828385353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984614968299866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994082510471344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01301729679108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18816518783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33017706871033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40118300914764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3633131980896</t>
   </si>
   <si>
     <t xml:space="preserve">1.33027982711792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32551181316376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33981585502625</t>
+    <t xml:space="preserve">1.31597578525543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32551193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33981597423553</t>
   </si>
   <si>
     <t xml:space="preserve">1.33504784107208</t>
@@ -1448,73 +1451,73 @@
     <t xml:space="preserve">1.36365604400635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32074391841888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35411989688873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34458386898041</t>
+    <t xml:space="preserve">1.32074379920959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35412001609802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3445839881897</t>
   </si>
   <si>
     <t xml:space="preserve">1.40180027484894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36842405796051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34935188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3588879108429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30167174339294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39226424694061</t>
+    <t xml:space="preserve">1.36842393875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34935200214386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35888803005219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30167186260223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3922643661499</t>
   </si>
   <si>
     <t xml:space="preserve">1.38272821903229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41133630275726</t>
+    <t xml:space="preserve">1.41133642196655</t>
   </si>
   <si>
     <t xml:space="preserve">1.38749623298645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37319207191467</t>
+    <t xml:space="preserve">1.37319219112396</t>
   </si>
   <si>
     <t xml:space="preserve">1.4304084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47808873653412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44471251964569</t>
+    <t xml:space="preserve">1.47808885574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4447124004364</t>
   </si>
   <si>
     <t xml:space="preserve">1.4065682888031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42087244987488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43517649173737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45901656150818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43994450569153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41610431671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51623296737671</t>
+    <t xml:space="preserve">1.42087233066559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43517661094666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45901668071747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43994462490082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41610443592072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.516233086586</t>
   </si>
   <si>
     <t xml:space="preserve">1.50669693946838</t>
@@ -1535,22 +1538,22 @@
     <t xml:space="preserve">1.57344925403595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68788194656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65450584888458</t>
+    <t xml:space="preserve">1.68788206577301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65450572967529</t>
   </si>
   <si>
     <t xml:space="preserve">1.70695412158966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76417052745819</t>
+    <t xml:space="preserve">1.7641704082489</t>
   </si>
   <si>
     <t xml:space="preserve">1.74509835243225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72602617740631</t>
+    <t xml:space="preserve">1.7260262966156</t>
   </si>
   <si>
     <t xml:space="preserve">1.69741797447205</t>
@@ -1562,10 +1565,10 @@
     <t xml:space="preserve">1.67357790470123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64020168781281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61159360408783</t>
+    <t xml:space="preserve">1.64020180702209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61159348487854</t>
   </si>
   <si>
     <t xml:space="preserve">1.60682547092438</t>
@@ -1580,7 +1583,7 @@
     <t xml:space="preserve">1.64496982097626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6163614988327</t>
+    <t xml:space="preserve">1.61636161804199</t>
   </si>
   <si>
     <t xml:space="preserve">1.62112963199615</t>
@@ -1592,10 +1595,10 @@
     <t xml:space="preserve">1.63543367385864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77847456932068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75940251350403</t>
+    <t xml:space="preserve">1.77847468852997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75940239429474</t>
   </si>
   <si>
     <t xml:space="preserve">1.68311393260956</t>
@@ -1607,16 +1610,16 @@
     <t xml:space="preserve">1.77370655536652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81185078620911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82615482807159</t>
+    <t xml:space="preserve">1.81185066699982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8261547088623</t>
   </si>
   <si>
     <t xml:space="preserve">1.79754662513733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.788010597229</t>
+    <t xml:space="preserve">1.78801047801971</t>
   </si>
   <si>
     <t xml:space="preserve">1.81661880016327</t>
@@ -1625,7 +1628,7 @@
     <t xml:space="preserve">1.83092284202576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80708265304565</t>
+    <t xml:space="preserve">1.80708277225494</t>
   </si>
   <si>
     <t xml:space="preserve">1.76893854141235</t>
@@ -1634,7 +1637,7 @@
     <t xml:space="preserve">1.73556232452393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73079431056976</t>
+    <t xml:space="preserve">1.73079442977905</t>
   </si>
   <si>
     <t xml:space="preserve">1.74033033847809</t>
@@ -1643,7 +1646,7 @@
     <t xml:space="preserve">1.72125816345215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78324258327484</t>
+    <t xml:space="preserve">1.78324246406555</t>
   </si>
   <si>
     <t xml:space="preserve">1.74986636638641</t>
@@ -1655,25 +1658,25 @@
     <t xml:space="preserve">1.66404187679291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69264996051788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80231463909149</t>
+    <t xml:space="preserve">1.69265007972717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80231475830078</t>
   </si>
   <si>
     <t xml:space="preserve">1.75463449954987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79277849197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56868124008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65927386283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59252142906189</t>
+    <t xml:space="preserve">1.79277861118317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56868135929108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65927374362946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59252154827118</t>
   </si>
   <si>
     <t xml:space="preserve">1.52576899528503</t>
@@ -1688,10 +1691,10 @@
     <t xml:space="preserve">1.85953104496002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89767527580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92628347873688</t>
+    <t xml:space="preserve">1.89767515659332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92628335952759</t>
   </si>
   <si>
     <t xml:space="preserve">1.82138681411743</t>
@@ -1703,19 +1706,19 @@
     <t xml:space="preserve">1.86429905891418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90721130371094</t>
+    <t xml:space="preserve">1.90721142292023</t>
   </si>
   <si>
     <t xml:space="preserve">1.94535553455353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99303567409515</t>
+    <t xml:space="preserve">1.99303579330444</t>
   </si>
   <si>
     <t xml:space="preserve">2.0597882270813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00257182121277</t>
+    <t xml:space="preserve">2.00257205963135</t>
   </si>
   <si>
     <t xml:space="preserve">2.07886052131653</t>
@@ -1724,10 +1727,10 @@
     <t xml:space="preserve">2.12654066085815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1074686050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08839654922485</t>
+    <t xml:space="preserve">2.10746836662292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08839631080627</t>
   </si>
   <si>
     <t xml:space="preserve">2.09793257713318</t>
@@ -1754,49 +1757,49 @@
     <t xml:space="preserve">2.01210784912109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9739636182785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98349988460541</t>
+    <t xml:space="preserve">1.97396373748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98349952697754</t>
   </si>
   <si>
     <t xml:space="preserve">2.03118014335632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04071617126465</t>
+    <t xml:space="preserve">2.04071593284607</t>
   </si>
   <si>
     <t xml:space="preserve">2.09847211837769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08884644508362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10809826850891</t>
+    <t xml:space="preserve">2.08884620666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10809803009033</t>
   </si>
   <si>
     <t xml:space="preserve">2.00221180915833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95408189296722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03109002113342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0214638710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05996823310852</t>
+    <t xml:space="preserve">1.95408177375793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03108978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02146410942078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05996799468994</t>
   </si>
   <si>
     <t xml:space="preserve">1.94445586204529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9733339548111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93482971191406</t>
+    <t xml:space="preserve">1.97333383560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93482995033264</t>
   </si>
   <si>
     <t xml:space="preserve">1.85782170295715</t>
@@ -1814,25 +1817,22 @@
     <t xml:space="preserve">1.88669979572296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87707388401031</t>
+    <t xml:space="preserve">1.87707364559174</t>
   </si>
   <si>
     <t xml:space="preserve">1.89632570743561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92520380020142</t>
+    <t xml:space="preserve">1.92520391941071</t>
   </si>
   <si>
     <t xml:space="preserve">1.99258589744568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04071569442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05034232139587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11772418022156</t>
+    <t xml:space="preserve">2.05034208297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11772441864014</t>
   </si>
   <si>
     <t xml:space="preserve">2.1562283039093</t>
@@ -1844,16 +1844,16 @@
     <t xml:space="preserve">2.16585445404053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14660215377808</t>
+    <t xml:space="preserve">2.14660239219666</t>
   </si>
   <si>
     <t xml:space="preserve">2.07922005653381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24286222457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25248861312866</t>
+    <t xml:space="preserve">2.24286246299744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25248837471008</t>
   </si>
   <si>
     <t xml:space="preserve">2.27174043655396</t>
@@ -1862,10 +1862,10 @@
     <t xml:space="preserve">2.30061864852905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28136610984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1851065158844</t>
+    <t xml:space="preserve">2.2813663482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18510627746582</t>
   </si>
   <si>
     <t xml:space="preserve">2.19473242759705</t>
@@ -1877,19 +1877,19 @@
     <t xml:space="preserve">2.13697624206543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01183772087097</t>
+    <t xml:space="preserve">2.01183795928955</t>
   </si>
   <si>
     <t xml:space="preserve">1.8722608089447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96370780467987</t>
+    <t xml:space="preserve">1.96370792388916</t>
   </si>
   <si>
     <t xml:space="preserve">2.06959414482117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17548012733459</t>
+    <t xml:space="preserve">2.17548036575317</t>
   </si>
   <si>
     <t xml:space="preserve">2.23323631286621</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">2.42575693130493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39687871932983</t>
+    <t xml:space="preserve">2.39687895774841</t>
   </si>
   <si>
     <t xml:space="preserve">2.40650486946106</t>
@@ -1916,28 +1916,28 @@
     <t xml:space="preserve">2.41613078117371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37762665748596</t>
+    <t xml:space="preserve">2.37762689590454</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874868392944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29099273681641</t>
+    <t xml:space="preserve">2.29099249839783</t>
   </si>
   <si>
     <t xml:space="preserve">2.36800074577332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38725304603577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21398425102234</t>
+    <t xml:space="preserve">2.38725280761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21398448944092</t>
   </si>
   <si>
     <t xml:space="preserve">2.31987071037292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44500875473022</t>
+    <t xml:space="preserve">2.4450089931488</t>
   </si>
   <si>
     <t xml:space="preserve">2.45463490486145</t>
@@ -1946,16 +1946,16 @@
     <t xml:space="preserve">2.4642608165741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49313902854919</t>
+    <t xml:space="preserve">2.49313879013062</t>
   </si>
   <si>
     <t xml:space="preserve">2.52201700210571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50276470184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5990252494812</t>
+    <t xml:space="preserve">2.50276494026184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59902501106262</t>
   </si>
   <si>
     <t xml:space="preserve">2.64715528488159</t>
@@ -1967,13 +1967,13 @@
     <t xml:space="preserve">2.51239085197449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47388672828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48351263999939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53164315223694</t>
+    <t xml:space="preserve">2.47388696670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48351287841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53164291381836</t>
   </si>
   <si>
     <t xml:space="preserve">2.63752913475037</t>
@@ -1988,22 +1988,22 @@
     <t xml:space="preserve">2.71453738212585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67603325843811</t>
+    <t xml:space="preserve">2.67603349685669</t>
   </si>
   <si>
     <t xml:space="preserve">2.60865116119385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66640710830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57014727592468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58939933776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56052112579346</t>
+    <t xml:space="preserve">2.66640734672546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5701470375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58939909934998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56052088737488</t>
   </si>
   <si>
     <t xml:space="preserve">2.6279034614563</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">2.57977318763733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38258814811707</t>
+    <t xml:space="preserve">2.38258790969849</t>
   </si>
   <si>
     <t xml:space="preserve">2.29506421089172</t>
@@ -2024,13 +2024,13 @@
     <t xml:space="preserve">2.28533935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32423901557922</t>
+    <t xml:space="preserve">2.32423877716064</t>
   </si>
   <si>
     <t xml:space="preserve">2.25616478919983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23671507835388</t>
+    <t xml:space="preserve">2.23671531677246</t>
   </si>
   <si>
     <t xml:space="preserve">2.21726560592651</t>
@@ -2042,16 +2042,16 @@
     <t xml:space="preserve">2.34368872642517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2658896446228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30478882789612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24644017219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11029243469238</t>
+    <t xml:space="preserve">2.26588988304138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3047890663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24643993377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1102921962738</t>
   </si>
   <si>
     <t xml:space="preserve">2.15891647338867</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">2.19781565666199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16864109039307</t>
+    <t xml:space="preserve">2.16864132881165</t>
   </si>
   <si>
     <t xml:space="preserve">2.18809103965759</t>
@@ -2081,16 +2081,16 @@
     <t xml:space="preserve">2.13946676254272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09084248542786</t>
+    <t xml:space="preserve">2.09084272384644</t>
   </si>
   <si>
     <t xml:space="preserve">2.10056734085083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27561473846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08111786842346</t>
+    <t xml:space="preserve">2.27561450004578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08111763000488</t>
   </si>
   <si>
     <t xml:space="preserve">1.97414433956146</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">1.98386907577515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96441948413849</t>
+    <t xml:space="preserve">1.9644193649292</t>
   </si>
   <si>
     <t xml:space="preserve">1.94496977329254</t>
@@ -2117,13 +2117,13 @@
     <t xml:space="preserve">2.02276849746704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03249311447144</t>
+    <t xml:space="preserve">2.03249335289001</t>
   </si>
   <si>
     <t xml:space="preserve">2.01304364204407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07139301300049</t>
+    <t xml:space="preserve">2.07139277458191</t>
   </si>
   <si>
     <t xml:space="preserve">2.04221820831299</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">1.93524491786957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95469450950623</t>
+    <t xml:space="preserve">1.95469462871552</t>
   </si>
   <si>
     <t xml:space="preserve">1.91579520702362</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">1.93038249015808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06166768074036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91093277931213</t>
+    <t xml:space="preserve">2.06166791915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91093289852142</t>
   </si>
   <si>
     <t xml:space="preserve">2.1491916179657</t>
@@ -2162,16 +2162,16 @@
     <t xml:space="preserve">1.92552006244659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81854665279388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84772121906281</t>
+    <t xml:space="preserve">1.81854677200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84772133827209</t>
   </si>
   <si>
     <t xml:space="preserve">1.8866206407547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83313393592834</t>
+    <t xml:space="preserve">1.83313405513763</t>
   </si>
   <si>
     <t xml:space="preserve">1.85258364677429</t>
@@ -2205,9 +2205,6 @@
   </si>
   <si>
     <t xml:space="preserve">1.97931289672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95469462871552</t>
   </si>
   <si>
     <t xml:space="preserve">1.9497709274292</t>
@@ -39093,7 +39090,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1395" t="s">
-        <v>391</v>
+        <v>474</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -39119,7 +39116,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1396" t="s">
-        <v>391</v>
+        <v>474</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -39145,7 +39142,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1397" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -39171,7 +39168,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1398" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -39197,7 +39194,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1399" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -39223,7 +39220,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1400" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -39249,7 +39246,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1401" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -39275,7 +39272,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1402" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39301,7 +39298,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1403" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39327,7 +39324,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1404" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39353,7 +39350,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1405" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39379,7 +39376,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1406" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39405,7 +39402,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1407" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39431,7 +39428,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1408" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39457,7 +39454,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1409" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39483,7 +39480,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1410" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39509,7 +39506,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1411" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39535,7 +39532,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1412" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39561,7 +39558,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1413" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39587,7 +39584,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1414" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39613,7 +39610,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1415" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39639,7 +39636,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1416" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39665,7 +39662,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1417" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39691,7 +39688,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1418" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39717,7 +39714,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1419" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39743,7 +39740,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1420" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39769,7 +39766,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1421" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39795,7 +39792,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1422" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39821,7 +39818,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1423" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39873,7 +39870,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1425" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39899,7 +39896,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1426" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39951,7 +39948,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1428" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39977,7 +39974,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1429" t="s">
-        <v>391</v>
+        <v>474</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -40003,7 +40000,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1430" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -40029,7 +40026,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1431" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -40055,7 +40052,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1432" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -40081,7 +40078,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1433" t="s">
-        <v>391</v>
+        <v>474</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -40107,7 +40104,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1434" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -40133,7 +40130,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1435" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -40159,7 +40156,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1436" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -40185,7 +40182,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1437" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -40211,7 +40208,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1438" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -40237,7 +40234,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1439" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -40263,7 +40260,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1440" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40289,7 +40286,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1441" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40315,7 +40312,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1442" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40341,7 +40338,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1443" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40367,7 +40364,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1444" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40393,7 +40390,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1445" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40419,7 +40416,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1446" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40445,7 +40442,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1447" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40471,7 +40468,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1448" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40497,7 +40494,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1449" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40523,7 +40520,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1450" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40549,7 +40546,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1451" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40575,7 +40572,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1452" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40601,7 +40598,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40627,7 +40624,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1454" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40653,7 +40650,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1455" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40679,7 +40676,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1456" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40705,7 +40702,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1457" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40731,7 +40728,7 @@
         <v>1.5</v>
       </c>
       <c r="G1458" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40757,7 +40754,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1459" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40783,7 +40780,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1460" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40809,7 +40806,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1461" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40835,7 +40832,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1462" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40861,7 +40858,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1463" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40887,7 +40884,7 @@
         <v>1.5</v>
       </c>
       <c r="G1464" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40913,7 +40910,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1465" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40939,7 +40936,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1466" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40965,7 +40962,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1467" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40991,7 +40988,7 @@
         <v>1.5</v>
       </c>
       <c r="G1468" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -41017,7 +41014,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1469" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -41043,7 +41040,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1470" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -41069,7 +41066,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1471" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -41095,7 +41092,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1472" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -41121,7 +41118,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1473" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -41147,7 +41144,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1474" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -41173,7 +41170,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1475" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -41199,7 +41196,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1476" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -41225,7 +41222,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1477" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -41251,7 +41248,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1478" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41277,7 +41274,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1479" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41303,7 +41300,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1480" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41329,7 +41326,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1481" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41355,7 +41352,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1482" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41381,7 +41378,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1483" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41407,7 +41404,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1484" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41433,7 +41430,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1485" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41459,7 +41456,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1486" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41485,7 +41482,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1487" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41511,7 +41508,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1488" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41537,7 +41534,7 @@
         <v>1.75</v>
       </c>
       <c r="G1489" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41563,7 +41560,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1490" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41589,7 +41586,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1491" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41615,7 +41612,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1492" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41641,7 +41638,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1493" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41667,7 +41664,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1494" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41693,7 +41690,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1495" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41719,7 +41716,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1496" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41745,7 +41742,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1497" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41771,7 +41768,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1498" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41797,7 +41794,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1499" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41823,7 +41820,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1500" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41849,7 +41846,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1501" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41875,7 +41872,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1502" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41901,7 +41898,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1503" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41927,7 +41924,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1504" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41953,7 +41950,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1505" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41979,7 +41976,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1506" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -42005,7 +42002,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1507" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -42031,7 +42028,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1508" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -42057,7 +42054,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1509" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -42083,7 +42080,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1510" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -42109,7 +42106,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1511" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -42135,7 +42132,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1512" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -42161,7 +42158,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1513" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -42187,7 +42184,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1514" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -42213,7 +42210,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1515" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -42239,7 +42236,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1516" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -42265,7 +42262,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1517" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42291,7 +42288,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1518" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42317,7 +42314,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1519" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42343,7 +42340,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1520" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42369,7 +42366,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1521" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42395,7 +42392,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1522" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42421,7 +42418,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1523" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42447,7 +42444,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1524" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42473,7 +42470,7 @@
         <v>1.875</v>
       </c>
       <c r="G1525" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42499,7 +42496,7 @@
         <v>1.875</v>
       </c>
       <c r="G1526" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42525,7 +42522,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1527" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42551,7 +42548,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1528" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42577,7 +42574,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1529" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42603,7 +42600,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1530" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42629,7 +42626,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1531" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42655,7 +42652,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1532" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42681,7 +42678,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1533" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42707,7 +42704,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1534" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42733,7 +42730,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1535" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42759,7 +42756,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1536" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42785,7 +42782,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1537" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42811,7 +42808,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1538" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42837,7 +42834,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1539" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42863,7 +42860,7 @@
         <v>1.875</v>
       </c>
       <c r="G1540" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42889,7 +42886,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1541" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42915,7 +42912,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1542" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42941,7 +42938,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1543" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42967,7 +42964,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1544" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42993,7 +42990,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1545" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -43019,7 +43016,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1546" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -43045,7 +43042,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1547" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -43071,7 +43068,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1548" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -43097,7 +43094,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1549" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -43123,7 +43120,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1550" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -43149,7 +43146,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1551" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -43175,7 +43172,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1552" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -43201,7 +43198,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1553" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -43227,7 +43224,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1554" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -43253,7 +43250,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1555" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -43279,7 +43276,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1556" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43305,7 +43302,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1557" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43331,7 +43328,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1558" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43357,7 +43354,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1559" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43383,7 +43380,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1560" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43409,7 +43406,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1561" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43435,7 +43432,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1562" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43461,7 +43458,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1563" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43487,7 +43484,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1564" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43513,7 +43510,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1565" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43539,7 +43536,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1566" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43565,7 +43562,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1567" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43591,7 +43588,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1568" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43617,7 +43614,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1569" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43643,7 +43640,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1570" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43669,7 +43666,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1571" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43695,7 +43692,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1572" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43721,7 +43718,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1573" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43747,7 +43744,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1574" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43773,7 +43770,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1575" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43799,7 +43796,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1576" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43825,7 +43822,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1577" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43851,7 +43848,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1578" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43877,7 +43874,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1579" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43903,7 +43900,7 @@
         <v>1.75</v>
       </c>
       <c r="G1580" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43929,7 +43926,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1581" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43955,7 +43952,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1582" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43981,7 +43978,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1583" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -44007,7 +44004,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1584" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -44033,7 +44030,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1585" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -44059,7 +44056,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1586" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -44085,7 +44082,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1587" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -44111,7 +44108,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1588" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -44137,7 +44134,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1589" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -44163,7 +44160,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1590" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -44189,7 +44186,7 @@
         <v>1.75</v>
       </c>
       <c r="G1591" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -44215,7 +44212,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1592" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -44241,7 +44238,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1593" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -44267,7 +44264,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1594" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44293,7 +44290,7 @@
         <v>1.75</v>
       </c>
       <c r="G1595" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44319,7 +44316,7 @@
         <v>1.75</v>
       </c>
       <c r="G1596" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44345,7 +44342,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1597" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44371,7 +44368,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1598" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44397,7 +44394,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1599" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44423,7 +44420,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1600" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44449,7 +44446,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1601" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44475,7 +44472,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1602" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44501,7 +44498,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1603" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44527,7 +44524,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1604" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44553,7 +44550,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1605" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44579,7 +44576,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1606" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44605,7 +44602,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1607" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44631,7 +44628,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1608" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44657,7 +44654,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1609" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44683,7 +44680,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1610" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44709,7 +44706,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1611" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44735,7 +44732,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1612" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44761,7 +44758,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1613" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44787,7 +44784,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1614" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44813,7 +44810,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1615" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44839,7 +44836,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1616" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44865,7 +44862,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1617" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44891,7 +44888,7 @@
         <v>2</v>
       </c>
       <c r="G1618" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44917,7 +44914,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1619" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44943,7 +44940,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1620" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44969,7 +44966,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1621" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44995,7 +44992,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1622" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -45021,7 +45018,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1623" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -45047,7 +45044,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1624" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -45073,7 +45070,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1625" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -45099,7 +45096,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -45125,7 +45122,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1627" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -45151,7 +45148,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1628" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -45177,7 +45174,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1629" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -45203,7 +45200,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1630" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -45229,7 +45226,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1631" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -45255,7 +45252,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1632" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -45281,7 +45278,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1633" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45307,7 +45304,7 @@
         <v>2.25</v>
       </c>
       <c r="G1634" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45333,7 +45330,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1635" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45359,7 +45356,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1636" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45385,7 +45382,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1637" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45411,7 +45408,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1638" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45437,7 +45434,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1639" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45463,7 +45460,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1640" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45489,7 +45486,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1641" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45515,7 +45512,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1642" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45541,7 +45538,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1643" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45567,7 +45564,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1644" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45593,7 +45590,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1645" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45619,7 +45616,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1646" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45645,7 +45642,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1647" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45671,7 +45668,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1648" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45697,7 +45694,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1649" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45723,7 +45720,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1650" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45749,7 +45746,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1651" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45775,7 +45772,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1652" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45801,7 +45798,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1653" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45827,7 +45824,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1654" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45853,7 +45850,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1655" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45879,7 +45876,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1656" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45905,7 +45902,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1657" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45931,7 +45928,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1658" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45957,7 +45954,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1659" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45983,7 +45980,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1660" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -46009,7 +46006,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1661" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -46035,7 +46032,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1662" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -46061,7 +46058,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1663" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -46087,7 +46084,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1664" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -46113,7 +46110,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1665" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -46139,7 +46136,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1666" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -46165,7 +46162,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1667" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -46191,7 +46188,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1668" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -46217,7 +46214,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1669" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -46243,7 +46240,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1670" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -46269,7 +46266,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1671" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -46295,7 +46292,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1672" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -46321,7 +46318,7 @@
         <v>2</v>
       </c>
       <c r="G1673" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -46347,7 +46344,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1674" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46373,7 +46370,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1675" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -46399,7 +46396,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1676" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -46425,7 +46422,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1677" t="s">
-        <v>604</v>
+        <v>584</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46477,7 +46474,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1679" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -46867,7 +46864,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1694" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46919,7 +46916,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1696" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -47361,7 +47358,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1713" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47439,7 +47436,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1716" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47465,7 +47462,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1717" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47491,7 +47488,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1718" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47543,7 +47540,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1720" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47569,7 +47566,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1721" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47595,7 +47592,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1722" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47647,7 +47644,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1724" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -48791,7 +48788,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1768" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48817,7 +48814,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1769" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48843,7 +48840,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1770" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48895,7 +48892,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1772" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48973,7 +48970,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1775" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48999,7 +48996,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1776" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -59503,7 +59500,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2180" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -59529,7 +59526,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2181" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59555,7 +59552,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2182" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59581,7 +59578,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2183" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59685,7 +59682,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2187" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59711,7 +59708,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2188" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59737,7 +59734,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2189" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59763,7 +59760,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2190" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59789,7 +59786,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2191" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59815,7 +59812,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2192" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59841,7 +59838,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2193" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60153,7 +60150,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2205" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60179,7 +60176,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2206" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60205,7 +60202,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2207" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60231,7 +60228,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2208" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60283,7 +60280,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2210" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60309,7 +60306,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2211" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60335,7 +60332,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2212" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60361,7 +60358,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2213" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60387,7 +60384,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2214" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60439,7 +60436,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2216" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60595,7 +60592,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60673,7 +60670,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2225" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60699,7 +60696,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2226" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60751,7 +60748,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2228" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60777,7 +60774,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2229" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60803,7 +60800,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2230" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60829,7 +60826,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2231" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60855,7 +60852,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2232" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60881,7 +60878,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2233" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60907,7 +60904,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2234" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60933,7 +60930,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2235" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60959,7 +60956,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2236" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60985,7 +60982,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2237" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61011,7 +61008,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2238" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61037,7 +61034,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2239" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61063,7 +61060,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2240" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61089,7 +61086,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G2241" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61115,7 +61112,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2242" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61141,7 +61138,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2243" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61167,7 +61164,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G2244" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61193,7 +61190,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2245" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61219,7 +61216,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2246" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61245,7 +61242,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2247" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61271,7 +61268,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2248" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61297,7 +61294,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2249" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61323,7 +61320,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2250" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61349,7 +61346,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2251" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61375,7 +61372,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2252" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61479,7 +61476,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2256" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -61505,7 +61502,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2257" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -61557,7 +61554,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2259" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -61583,7 +61580,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2260" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -61609,7 +61606,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2261" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -61635,7 +61632,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -61661,7 +61658,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2263" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -61713,7 +61710,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2265" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61739,7 +61736,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2266" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61869,7 +61866,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2271" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61895,7 +61892,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2272" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61921,7 +61918,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2273" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61947,7 +61944,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2274" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61973,7 +61970,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2275" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61999,7 +61996,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2276" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62025,7 +62022,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2277" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62051,7 +62048,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2278" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62077,7 +62074,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2279" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62103,7 +62100,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2280" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62129,7 +62126,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2281" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62155,7 +62152,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2282" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62181,7 +62178,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2283" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62207,7 +62204,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2284" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62233,7 +62230,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2285" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62259,7 +62256,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2286" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62285,7 +62282,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2287" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62311,7 +62308,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2288" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62337,7 +62334,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2289" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62363,7 +62360,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2290" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62389,7 +62386,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2291" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62415,7 +62412,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2292" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62441,7 +62438,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2293" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62467,7 +62464,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2294" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -62493,7 +62490,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2295" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -62519,7 +62516,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2296" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -62545,7 +62542,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2297" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -62571,7 +62568,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2298" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -62597,7 +62594,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2299" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -62623,7 +62620,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2300" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -62649,7 +62646,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2301" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -62675,7 +62672,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2302" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -62701,7 +62698,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2303" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62727,7 +62724,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2304" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62753,7 +62750,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62779,7 +62776,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2306" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62805,7 +62802,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G2307" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62831,7 +62828,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2308" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62857,7 +62854,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2309" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62883,7 +62880,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2310" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62909,7 +62906,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2311" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62935,7 +62932,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2312" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62961,7 +62958,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2313" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62987,7 +62984,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2314" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63013,7 +63010,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2315" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63039,7 +63036,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2316" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63065,7 +63062,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2317" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63091,7 +63088,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2318" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63117,7 +63114,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2319" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63143,7 +63140,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2320" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63169,7 +63166,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2321" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63195,7 +63192,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2322" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63221,7 +63218,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2323" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63247,7 +63244,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2324" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63273,7 +63270,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2325" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63299,7 +63296,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2326" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63325,7 +63322,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2327" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63351,7 +63348,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2328" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63377,7 +63374,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2329" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63403,7 +63400,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2330" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63429,7 +63426,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2331" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63455,7 +63452,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2332" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63481,7 +63478,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2333" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -63507,7 +63504,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2334" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -63533,7 +63530,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2335" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -63559,7 +63556,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2336" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -63585,7 +63582,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2337" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -63611,7 +63608,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2338" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -63637,7 +63634,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2339" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -63663,7 +63660,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G2340" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -63689,7 +63686,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2341" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63715,7 +63712,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2342" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63741,7 +63738,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63767,7 +63764,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2344" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63793,7 +63790,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2345" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63819,7 +63816,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2346" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63845,7 +63842,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2347" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63871,7 +63868,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63897,7 +63894,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63923,7 +63920,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2350" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63949,7 +63946,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2351" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63975,7 +63972,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G2352" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64001,7 +63998,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2353" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64027,7 +64024,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2354" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64053,7 +64050,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2355" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64079,7 +64076,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2356" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64105,7 +64102,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G2357" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64131,7 +64128,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2358" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64157,7 +64154,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G2359" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64183,7 +64180,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G2360" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64209,7 +64206,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2361" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64235,7 +64232,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2362" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64261,7 +64258,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2363" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64287,7 +64284,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G2364" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64313,7 +64310,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2365" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64339,7 +64336,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64365,7 +64362,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G2367" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64391,7 +64388,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2368" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64417,7 +64414,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2369" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64443,7 +64440,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2370" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64469,7 +64466,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2371" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64495,7 +64492,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2372" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -64521,7 +64518,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2373" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -64547,7 +64544,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G2374" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -64573,7 +64570,7 @@
         <v>1.625</v>
       </c>
       <c r="G2375" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -64599,7 +64596,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G2376" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -64625,7 +64622,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G2377" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -64651,7 +64648,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2378" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -64677,7 +64674,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G2379" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -64703,7 +64700,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2380" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64729,7 +64726,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2381" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64755,7 +64752,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2382" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64781,7 +64778,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G2383" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64807,7 +64804,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2384" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64833,7 +64830,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2385" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64859,7 +64856,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64885,7 +64882,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2387" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64911,7 +64908,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2388" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64937,7 +64934,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64963,7 +64960,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2390" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64989,7 +64986,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2391" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65015,7 +65012,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2392" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65041,7 +65038,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G2393" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65067,7 +65064,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G2394" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65093,7 +65090,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2395" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65119,7 +65116,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2396" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65145,7 +65142,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2397" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65171,7 +65168,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2398" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65197,7 +65194,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2399" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65223,7 +65220,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2400" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65249,7 +65246,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2401" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65275,7 +65272,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2402" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65301,7 +65298,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2403" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65327,7 +65324,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2404" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65353,7 +65350,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2405" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65379,7 +65376,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2406" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65431,7 +65428,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2408" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65457,7 +65454,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2409" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65483,7 +65480,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2410" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -65509,7 +65506,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2411" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65535,7 +65532,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2412" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65561,7 +65558,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2413" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65587,7 +65584,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2414" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65613,7 +65610,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2415" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65639,7 +65636,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2416" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65665,7 +65662,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2417" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65691,7 +65688,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2418" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65717,7 +65714,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2419" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65743,7 +65740,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2420" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65769,7 +65766,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2421" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65795,7 +65792,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65821,7 +65818,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2423" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65847,7 +65844,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2424" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65873,7 +65870,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2425" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65899,7 +65896,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2426" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65925,7 +65922,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2427" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65951,7 +65948,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2428" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65977,7 +65974,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2429" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66003,7 +66000,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2430" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66029,7 +66026,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2431" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66055,7 +66052,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2432" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66081,7 +66078,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2433" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66107,7 +66104,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2434" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66133,7 +66130,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2435" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66159,7 +66156,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2436" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66185,7 +66182,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2437" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66211,7 +66208,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2438" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66237,7 +66234,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2439" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66263,7 +66260,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2440" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66289,7 +66286,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2441" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66315,7 +66312,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2442" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66341,7 +66338,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2443" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66367,7 +66364,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2444" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66393,7 +66390,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2445" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66419,7 +66416,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2446" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66445,7 +66442,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2447" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66471,7 +66468,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2448" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -66497,7 +66494,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2449" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -66523,7 +66520,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2450" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66549,7 +66546,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2451" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66575,7 +66572,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2452" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66601,7 +66598,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2453" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66627,7 +66624,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2454" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66653,7 +66650,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2455" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66679,7 +66676,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2456" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66705,7 +66702,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2457" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66731,7 +66728,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2458" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66757,7 +66754,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2459" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66783,7 +66780,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2460" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66809,7 +66806,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2461" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66835,7 +66832,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2462" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66861,7 +66858,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2463" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66887,7 +66884,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2464" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66913,7 +66910,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2465" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66939,7 +66936,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2466" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66965,7 +66962,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2467" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66991,7 +66988,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2468" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67017,7 +67014,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2469" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67043,7 +67040,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2470" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67069,7 +67066,7 @@
         <v>2</v>
       </c>
       <c r="G2471" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67095,7 +67092,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2472" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67121,7 +67118,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2473" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67147,7 +67144,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2474" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67173,7 +67170,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2475" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67199,7 +67196,7 @@
         <v>2</v>
       </c>
       <c r="G2476" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67225,7 +67222,7 @@
         <v>2</v>
       </c>
       <c r="G2477" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67251,7 +67248,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2478" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67277,7 +67274,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2479" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67303,7 +67300,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2480" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67329,7 +67326,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2481" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67355,7 +67352,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2482" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67381,7 +67378,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2483" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67407,7 +67404,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2484" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67433,7 +67430,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2485" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67459,7 +67456,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2486" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67485,7 +67482,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2487" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -67511,7 +67508,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2488" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67537,7 +67534,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2489" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67563,7 +67560,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2490" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67589,7 +67586,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2491" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67615,7 +67612,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2492" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67641,7 +67638,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2493" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67667,7 +67664,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2494" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67693,7 +67690,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2495" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67719,7 +67716,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2496" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67745,7 +67742,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2497" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67771,7 +67768,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2498" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67797,7 +67794,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2499" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67823,7 +67820,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2500" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67849,7 +67846,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2501" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67875,7 +67872,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2502" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -67901,7 +67898,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2503" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -67927,7 +67924,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2504" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67953,7 +67950,7 @@
         <v>2</v>
       </c>
       <c r="G2505" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67979,7 +67976,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2506" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68005,7 +68002,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2507" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68031,7 +68028,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2508" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68057,7 +68054,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2509" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68083,7 +68080,7 @@
         <v>2</v>
       </c>
       <c r="G2510" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68109,7 +68106,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2511" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68135,7 +68132,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2512" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68161,7 +68158,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2513" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -68187,7 +68184,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2514" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -68213,7 +68210,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2515" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -68239,7 +68236,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2516" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -68265,7 +68262,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2517" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -68291,7 +68288,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2518" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -68317,7 +68314,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2519" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -68343,7 +68340,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2520" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -68369,7 +68366,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2521" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -68395,7 +68392,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2522" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -68421,7 +68418,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2523" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -68447,7 +68444,7 @@
         <v>2</v>
       </c>
       <c r="G2524" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -68473,7 +68470,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2525" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -68499,7 +68496,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2526" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -68525,7 +68522,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2527" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -68551,7 +68548,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2528" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -68577,7 +68574,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2529" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -68603,7 +68600,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2530" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -68629,7 +68626,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2531" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -68655,7 +68652,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2532" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -68681,7 +68678,7 @@
         <v>2</v>
       </c>
       <c r="G2533" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -68707,7 +68704,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2534" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -68733,7 +68730,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2535" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -68759,7 +68756,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2536" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -68785,7 +68782,7 @@
         <v>2</v>
       </c>
       <c r="G2537" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2537" t="s">
         <v>9</v>
@@ -68811,7 +68808,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2538" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2538" t="s">
         <v>9</v>
@@ -68837,7 +68834,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2539" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2539" t="s">
         <v>9</v>
@@ -68863,7 +68860,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2540" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2540" t="s">
         <v>9</v>
@@ -68871,7 +68868,7 @@
     </row>
     <row r="2541">
       <c r="A2541" s="1" t="n">
-        <v>46021.5648958333</v>
+        <v>46021.3333333333</v>
       </c>
       <c r="B2541" t="n">
         <v>17500</v>
@@ -68889,7 +68886,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2541" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2541" t="s">
         <v>9</v>

--- a/data/DGT.MI.xlsx
+++ b/data/DGT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="826">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,61 +38,61 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08123922348022</t>
+    <t xml:space="preserve">2.08123874664307</t>
   </si>
   <si>
     <t xml:space="preserve">DGT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0576708316803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03047704696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96702480316162</t>
+    <t xml:space="preserve">2.05767059326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03047680854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96702468395233</t>
   </si>
   <si>
     <t xml:space="preserve">2.00509595870972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04860615730286</t>
+    <t xml:space="preserve">2.04860639572144</t>
   </si>
   <si>
     <t xml:space="preserve">1.99421846866608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97971510887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94889533519745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88544297218323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91444969177246</t>
+    <t xml:space="preserve">1.97971522808075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94889545440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88544285297394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91444981098175</t>
   </si>
   <si>
     <t xml:space="preserve">1.89632046222687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87637805938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97065019607544</t>
+    <t xml:space="preserve">1.8763781785965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9706506729126</t>
   </si>
   <si>
     <t xml:space="preserve">1.92714023590088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93076622486115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8582489490509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80839347839355</t>
+    <t xml:space="preserve">1.93076598644257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85824906826019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80839359760284</t>
   </si>
   <si>
     <t xml:space="preserve">1.8256162405014</t>
@@ -101,85 +101,85 @@
     <t xml:space="preserve">1.75128638744354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64704322814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75581860542297</t>
+    <t xml:space="preserve">1.6470433473587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75581884384155</t>
   </si>
   <si>
     <t xml:space="preserve">1.71321487426758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68964684009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73134398460388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76760280132294</t>
+    <t xml:space="preserve">1.68964695930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73134434223175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76760268211365</t>
   </si>
   <si>
     <t xml:space="preserve">1.72862470149994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75853800773621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81292581558228</t>
+    <t xml:space="preserve">1.7585381269455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81292593479156</t>
   </si>
   <si>
     <t xml:space="preserve">1.83105504512787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7685090303421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6751434803009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74947333335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69871151447296</t>
+    <t xml:space="preserve">1.76850914955139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67514359951019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74947345256805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69871139526367</t>
   </si>
   <si>
     <t xml:space="preserve">1.74766051769257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70777595043182</t>
+    <t xml:space="preserve">1.70777606964111</t>
   </si>
   <si>
     <t xml:space="preserve">1.70868253707886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69508576393127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77666735649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7014307975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69055330753326</t>
+    <t xml:space="preserve">1.6950855255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7766672372818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70143091678619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69055342674255</t>
   </si>
   <si>
     <t xml:space="preserve">1.73497009277344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64069783687592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62982034683228</t>
+    <t xml:space="preserve">1.64069771766663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62982022762299</t>
   </si>
   <si>
     <t xml:space="preserve">1.63163316249847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68692755699158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68602108955383</t>
+    <t xml:space="preserve">1.68692743778229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68602097034454</t>
   </si>
   <si>
     <t xml:space="preserve">1.67333054542542</t>
@@ -188,16 +188,16 @@
     <t xml:space="preserve">1.74040877819061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70415019989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75672507286072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68783414363861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6488561630249</t>
+    <t xml:space="preserve">1.70415031909943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75672519207001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68783402442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64885604381561</t>
   </si>
   <si>
     <t xml:space="preserve">1.64794957637787</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">1.68420815467834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72137320041656</t>
+    <t xml:space="preserve">1.72137308120728</t>
   </si>
   <si>
     <t xml:space="preserve">1.72227954864502</t>
@@ -218,22 +218,22 @@
     <t xml:space="preserve">1.63253962993622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66335952281952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66517245769501</t>
+    <t xml:space="preserve">1.66335964202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66517233848572</t>
   </si>
   <si>
     <t xml:space="preserve">1.65429472923279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81111288070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79026436805725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78754496574402</t>
+    <t xml:space="preserve">1.81111299991608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79026424884796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78754484653473</t>
   </si>
   <si>
     <t xml:space="preserve">1.78935778141022</t>
@@ -251,61 +251,61 @@
     <t xml:space="preserve">1.6833016872406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6588271856308</t>
+    <t xml:space="preserve">1.65882730484009</t>
   </si>
   <si>
     <t xml:space="preserve">1.60353291034698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.569087266922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58902955055237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48297345638275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49566376209259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4920380115509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53192245960236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48387980461121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45215368270874</t>
+    <t xml:space="preserve">1.56908738613129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58902943134308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48297333717346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49566388130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49203813076019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53192234039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48387968540192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45215356349945</t>
   </si>
   <si>
     <t xml:space="preserve">1.4856926202774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4285854101181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45940542221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49294435977936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46031177043915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44127607345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45034062862396</t>
+    <t xml:space="preserve">1.42858564853668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4594053030014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49294459819794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46031153202057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4412761926651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45034074783325</t>
   </si>
   <si>
     <t xml:space="preserve">1.46846997737885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42586612701416</t>
+    <t xml:space="preserve">1.42586600780487</t>
   </si>
   <si>
     <t xml:space="preserve">1.31255829334259</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">1.34156513214111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36875915527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33250057697296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27811276912689</t>
+    <t xml:space="preserve">1.36875903606415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33250033855438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2781126499176</t>
   </si>
   <si>
     <t xml:space="preserve">1.19653105735779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17296314239502</t>
+    <t xml:space="preserve">1.17296302318573</t>
   </si>
   <si>
     <t xml:space="preserve">1.18746638298035</t>
@@ -338,13 +338,13 @@
     <t xml:space="preserve">1.17568242549896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15483379364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09863317012787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12401413917542</t>
+    <t xml:space="preserve">1.15483391284943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09863305091858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12401401996613</t>
   </si>
   <si>
     <t xml:space="preserve">1.13307857513428</t>
@@ -353,49 +353,49 @@
     <t xml:space="preserve">1.12582695484161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1131364107132</t>
+    <t xml:space="preserve">1.11313652992249</t>
   </si>
   <si>
     <t xml:space="preserve">1.06962621212006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08684897422791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0950071811676</t>
+    <t xml:space="preserve">1.08684909343719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09500730037689</t>
   </si>
   <si>
     <t xml:space="preserve">1.09410071372986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12038826942444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09228777885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10769772529602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10951054096222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12129473686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09682011604309</t>
+    <t xml:space="preserve">1.12038803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09228789806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10769760608673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10951066017151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12129461765289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09682023525238</t>
   </si>
   <si>
     <t xml:space="preserve">1.08956849575043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08866202831268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07234573364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05149686336517</t>
+    <t xml:space="preserve">1.08866190910339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.072345495224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05149698257446</t>
   </si>
   <si>
     <t xml:space="preserve">1.12310755252838</t>
@@ -404,61 +404,61 @@
     <t xml:space="preserve">1.1013525724411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08322322368622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08775544166565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11404275894165</t>
+    <t xml:space="preserve">1.08322310447693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08775556087494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11404299736023</t>
   </si>
   <si>
     <t xml:space="preserve">1.15120780467987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21466028690338</t>
+    <t xml:space="preserve">1.21466040611267</t>
   </si>
   <si>
     <t xml:space="preserve">1.18474698066711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14576935768127</t>
+    <t xml:space="preserve">1.1457691192627</t>
   </si>
   <si>
     <t xml:space="preserve">1.12220120429993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06237459182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03336775302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934563219547272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945440769195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977167069911957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956318318843842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933656692504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01523852348328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04877746105194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03608703613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02430307865143</t>
+    <t xml:space="preserve">1.06237471103668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03336787223816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934563159942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945440709590912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977167010307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956318378448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933656752109528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01523840427399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04877769947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0360871553421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02430319786072</t>
   </si>
   <si>
     <t xml:space="preserve">0.990764021873474</t>
@@ -473,10 +473,10 @@
     <t xml:space="preserve">1.12854635715485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07506489753723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0641872882843</t>
+    <t xml:space="preserve">1.07506501674652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06418752670288</t>
   </si>
   <si>
     <t xml:space="preserve">1.02067744731903</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">1.00617384910583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988044500350952</t>
+    <t xml:space="preserve">0.988044619560242</t>
   </si>
   <si>
     <t xml:space="preserve">1.03880655765533</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">1.05965518951416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04243230819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06328082084656</t>
+    <t xml:space="preserve">1.04243218898773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06328117847443</t>
   </si>
   <si>
     <t xml:space="preserve">1.05693566799164</t>
@@ -509,34 +509,34 @@
     <t xml:space="preserve">1.10407185554504</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1049782037735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07597148418427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12492072582245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10316526889801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2110344171524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19562458992004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21284747123718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14667570590973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1539272069931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20559573173523</t>
+    <t xml:space="preserve">1.10497808456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07597160339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12492060661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1031653881073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21103429794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19562470912933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21284735202789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14667558670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15392732620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20559561252594</t>
   </si>
   <si>
     <t xml:space="preserve">1.20196986198425</t>
@@ -548,28 +548,28 @@
     <t xml:space="preserve">1.2536381483078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25817060470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26088988780975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25545120239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28717732429504</t>
+    <t xml:space="preserve">1.25817048549652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26089000701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25545108318329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28717720508575</t>
   </si>
   <si>
     <t xml:space="preserve">1.30893242359161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30530667304993</t>
+    <t xml:space="preserve">1.30530655384064</t>
   </si>
   <si>
     <t xml:space="preserve">1.41226923465729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3796364068985</t>
+    <t xml:space="preserve">1.37963628768921</t>
   </si>
   <si>
     <t xml:space="preserve">1.40320467948914</t>
@@ -581,31 +581,31 @@
     <t xml:space="preserve">1.35697495937347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.359694480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34065854549408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32343590259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35062992572784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32887470722198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26995444297791</t>
+    <t xml:space="preserve">1.35969424247742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34065866470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32343602180481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35062980651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3288745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26995468139648</t>
   </si>
   <si>
     <t xml:space="preserve">1.1947181224823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14395618438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24548006057739</t>
+    <t xml:space="preserve">1.1439563035965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24548017978668</t>
   </si>
   <si>
     <t xml:space="preserve">1.25001239776611</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">1.26814162731171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23278951644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24185419082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28173863887787</t>
+    <t xml:space="preserve">1.23278963565826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24185431003571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28173851966858</t>
   </si>
   <si>
     <t xml:space="preserve">1.26451575756073</t>
@@ -629,37 +629,37 @@
     <t xml:space="preserve">1.28264498710632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25091886520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26904785633087</t>
+    <t xml:space="preserve">1.25091874599457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26904809474945</t>
   </si>
   <si>
     <t xml:space="preserve">1.33159399032593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29624199867249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28536438941956</t>
+    <t xml:space="preserve">1.29624211788177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28536427021027</t>
   </si>
   <si>
     <t xml:space="preserve">1.31437134742737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30983889102936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31799697875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29896128177643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3778235912323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33521997928619</t>
+    <t xml:space="preserve">1.30983901023865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31799721717834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29896140098572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37782371044159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3352198600769</t>
   </si>
   <si>
     <t xml:space="preserve">1.26179623603821</t>
@@ -680,28 +680,28 @@
     <t xml:space="preserve">1.32434237003326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33884572982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31165194511414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2799254655838</t>
+    <t xml:space="preserve">1.33884584903717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31165170669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27992558479309</t>
   </si>
   <si>
     <t xml:space="preserve">1.30621302127838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31618428230286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30349373817444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27720642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26632869243622</t>
+    <t xml:space="preserve">1.31618416309357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30349349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27720630168915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26632881164551</t>
   </si>
   <si>
     <t xml:space="preserve">1.28355145454407</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">1.27539336681366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25273180007935</t>
+    <t xml:space="preserve">1.25273168087006</t>
   </si>
   <si>
     <t xml:space="preserve">1.34700381755829</t>
@@ -725,13 +725,13 @@
     <t xml:space="preserve">1.34972321987152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29261589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32978129386902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23369598388672</t>
+    <t xml:space="preserve">1.2926162481308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32978105545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23369610309601</t>
   </si>
   <si>
     <t xml:space="preserve">1.22372496128082</t>
@@ -746,22 +746,22 @@
     <t xml:space="preserve">1.22191202640533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2191926240921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22100555896759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21828615665436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22463154792786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21012794971466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1865599155426</t>
+    <t xml:space="preserve">1.21919274330139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22100567817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21828627586365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22463130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21012783050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18656003475189</t>
   </si>
   <si>
     <t xml:space="preserve">1.17477595806122</t>
@@ -773,49 +773,49 @@
     <t xml:space="preserve">1.1521143913269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15845966339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08594262599945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10588467121124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07959723472595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10679125785828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13217210769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16933703422546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22644448280334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23822844028473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24457359313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25182545185089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24004125595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20378267765045</t>
+    <t xml:space="preserve">1.15845954418182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08594250679016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10588479042053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07959735393524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10679113864899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13217198848724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16933739185333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22644424438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23822832107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24457383155823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25182521343231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24004137516022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20378279685974</t>
   </si>
   <si>
     <t xml:space="preserve">1.20650219917297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24094760417938</t>
+    <t xml:space="preserve">1.24094772338867</t>
   </si>
   <si>
     <t xml:space="preserve">1.23097670078278</t>
@@ -830,64 +830,64 @@
     <t xml:space="preserve">1.24638664722443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27629995346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27086079120636</t>
+    <t xml:space="preserve">1.2762998342514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27086102962494</t>
   </si>
   <si>
     <t xml:space="preserve">1.29805493354797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2255380153656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15574014186859</t>
+    <t xml:space="preserve">1.22553777694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15574026107788</t>
   </si>
   <si>
     <t xml:space="preserve">1.11857521533966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16027247905731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16661751270294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16480469703674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18112099170685</t>
+    <t xml:space="preserve">1.1602725982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16661775112152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16480481624603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18112111091614</t>
   </si>
   <si>
     <t xml:space="preserve">1.19925045967102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11676228046417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09319424629211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09772670269012</t>
+    <t xml:space="preserve">1.11676239967346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0931943655014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09772658348083</t>
   </si>
   <si>
     <t xml:space="preserve">1.17658889293671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17930829524994</t>
+    <t xml:space="preserve">1.17930817604065</t>
   </si>
   <si>
     <t xml:space="preserve">1.21375381946564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21556675434113</t>
+    <t xml:space="preserve">1.21556687355042</t>
   </si>
   <si>
     <t xml:space="preserve">1.2862708568573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28989660739899</t>
+    <t xml:space="preserve">1.28989672660828</t>
   </si>
   <si>
     <t xml:space="preserve">1.28445792198181</t>
@@ -899,46 +899,46 @@
     <t xml:space="preserve">1.40048515796661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41408205032349</t>
+    <t xml:space="preserve">1.41408216953278</t>
   </si>
   <si>
     <t xml:space="preserve">1.38235592842102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37057185173035</t>
+    <t xml:space="preserve">1.37057197093964</t>
   </si>
   <si>
     <t xml:space="preserve">1.32796812057495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36513328552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35516226291656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38416886329651</t>
+    <t xml:space="preserve">1.36513340473175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35516202449799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38416874408722</t>
   </si>
   <si>
     <t xml:space="preserve">1.42224025726318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38054299354553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38870096206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36694610118866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40773701667786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39957880973816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39685916900635</t>
+    <t xml:space="preserve">1.38054287433624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38870120048523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36694622039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40773689746857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39957892894745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39685940742493</t>
   </si>
   <si>
     <t xml:space="preserve">1.38326239585876</t>
@@ -950,58 +950,58 @@
     <t xml:space="preserve">1.50926077365875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57724559307098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57271301746368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54551923274994</t>
+    <t xml:space="preserve">1.57724547386169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57271325588226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54551935195923</t>
   </si>
   <si>
     <t xml:space="preserve">1.55005156993866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51379299163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48659920692444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44580829143524</t>
+    <t xml:space="preserve">1.51379311084747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48659908771515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44580852985382</t>
   </si>
   <si>
     <t xml:space="preserve">1.48206686973572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43221151828766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5409871339798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52285778522491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52738988399506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37329125404358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39142048358917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34609758853912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29170954227448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31890344619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3370326757431</t>
+    <t xml:space="preserve">1.43221139907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54098701477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52285766601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52739000320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37329137325287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39142072200775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34609746932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29170978069305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31890368461609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33703279495239</t>
   </si>
   <si>
     <t xml:space="preserve">1.27358031272888</t>
@@ -1010,292 +1010,292 @@
     <t xml:space="preserve">1.3959527015686</t>
   </si>
   <si>
+    <t xml:space="preserve">1.30077409744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33341026306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3147611618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30543661117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31942331790924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24482703208923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24948930740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23084032535553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21219110488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2541515827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23550260066986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22617793083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19354200363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19820415973663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2401647567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27280068397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29611206054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31009888648987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3287478685379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28212535381317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2681382894516</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.30077421665192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33341026306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3147611618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30543637275696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31942331790924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24482703208923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24948930740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23084020614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21219098567963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2541515827179</t>
+    <t xml:space="preserve">1.21685338020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18887984752655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16556835174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20286655426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17489302158356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17955529689789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20752882957458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32408571243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34739708900452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17023074626923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14691925048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13293254375458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25881385803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22151565551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15624380111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18421757221222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28678750991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16090619564056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15158152580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13759469985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36138391494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29144990444183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34273493289948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33807253837585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11428344249725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10495865345001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14225709438324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27810609340668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29230725765228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37278056144714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34437823295593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32544326782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30177474021912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55266213417053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41065037250519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31124210357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31597578525543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28757345676422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30650842189789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33964443206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42011785507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40591657161713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35384559631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39644920825958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32070970535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33491063117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28283989429474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27337229251862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26390480995178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2591712474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29704105854034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2449699640274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2307687997818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22130131721497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2165675163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22603499889374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24023616313934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21183383464813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26863861083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20710015296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24970388412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25443744659424</t>
   </si>
   <si>
     <t xml:space="preserve">1.23550248146057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22617793083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19354200363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19820415973663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2401647567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27280080318451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29611206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31009876728058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3287478685379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28212535381317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26813840866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30077433586121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21685326099396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18887972831726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16556835174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20286643505096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17489290237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17955529689789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20752882957458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32408571243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34739696979523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17023086547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14691925048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13293254375458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25881385803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746295928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22151565551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15624392032623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18421733379364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28678750991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16090619564056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15158176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13759469985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36138391494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29144978523254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34273481369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33807241916656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11428344249725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10495865345001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14225721359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27810609340668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29230725765228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37278068065643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34437823295593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32544314861298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30177474021912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55266213417053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41065049171448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31124198436737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31597578525543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28757345676422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3065083026886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33964443206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42011773586273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40591669082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35384571552277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39644908905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32070958614349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3349107503891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28283977508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27337229251862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26390492916107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25917112827301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29704082012177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2449699640274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23076868057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22130119800568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2165675163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22603511810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24023628234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21183383464813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26863861083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20710015296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24970364570618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25443744659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23550236225128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16923046112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18343138694763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20236623287201</t>
+    <t xml:space="preserve">1.16923034191132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18343150615692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20236659049988</t>
   </si>
   <si>
     <t xml:space="preserve">1.1408280134201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12189292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11715936660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10295820236206</t>
+    <t xml:space="preserve">1.12189304828644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11715912818909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10295808315277</t>
   </si>
   <si>
     <t xml:space="preserve">1.0698219537735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01775121688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989348769187927</t>
+    <t xml:space="preserve">1.01775109767914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989348649978638</t>
   </si>
   <si>
     <t xml:space="preserve">0.979881167411804</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">0.956212639808655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0224848985672</t>
+    <t xml:space="preserve">1.02248477935791</t>
   </si>
   <si>
     <t xml:space="preserve">1.07928955554962</t>
@@ -1337,79 +1337,79 @@
     <t xml:space="preserve">1.13609421253204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05562090873718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09349083900452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06035459041595</t>
+    <t xml:space="preserve">1.05562078952789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09349071979523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06035470962524</t>
   </si>
   <si>
     <t xml:space="preserve">1.06508839130402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07455575466156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04615354537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03668606281281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04141974449158</t>
+    <t xml:space="preserve">1.07455587387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04615342617035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03668594360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04141962528229</t>
   </si>
   <si>
     <t xml:space="preserve">1.1124255657196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12662672996521</t>
+    <t xml:space="preserve">1.1266268491745</t>
   </si>
   <si>
     <t xml:space="preserve">1.08875691890717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.098224401474</t>
+    <t xml:space="preserve">1.09822428226471</t>
   </si>
   <si>
     <t xml:space="preserve">1.05088710784912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03195226192474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02721869945526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17869782447815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15976297855377</t>
+    <t xml:space="preserve">1.03195238113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02721858024597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17869770526886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15976285934448</t>
   </si>
   <si>
     <t xml:space="preserve">1.15029549598694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16449654102325</t>
+    <t xml:space="preserve">1.16449642181396</t>
   </si>
   <si>
     <t xml:space="preserve">1.15502917766571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14556169509888</t>
+    <t xml:space="preserve">1.14556157588959</t>
   </si>
   <si>
     <t xml:space="preserve">1.17396402359009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13136065006256</t>
+    <t xml:space="preserve">1.13136053085327</t>
   </si>
   <si>
     <t xml:space="preserve">1.08402323722839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00828373432159</t>
+    <t xml:space="preserve">1.0082836151123</t>
   </si>
   <si>
     <t xml:space="preserve">0.984615087509155</t>
@@ -1418,19 +1418,19 @@
     <t xml:space="preserve">0.994082391262054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01301741600037</t>
+    <t xml:space="preserve">1.01301753520966</t>
   </si>
   <si>
     <t xml:space="preserve">1.18816530704498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33017694950104</t>
+    <t xml:space="preserve">1.33017706871033</t>
   </si>
   <si>
     <t xml:space="preserve">1.40118300914764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3633131980896</t>
+    <t xml:space="preserve">1.36331307888031</t>
   </si>
   <si>
     <t xml:space="preserve">1.33027994632721</t>
@@ -1439,22 +1439,22 @@
     <t xml:space="preserve">1.32551181316376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33981585502625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33504784107208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36365616321564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32074379920959</t>
+    <t xml:space="preserve">1.33981597423553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33504796028137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36365604400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32074391841888</t>
   </si>
   <si>
     <t xml:space="preserve">1.35412001609802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3445839881897</t>
+    <t xml:space="preserve">1.34458386898041</t>
   </si>
   <si>
     <t xml:space="preserve">1.40180039405823</t>
@@ -1472,25 +1472,25 @@
     <t xml:space="preserve">1.30167174339294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3922643661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38272833824158</t>
+    <t xml:space="preserve">1.39226424694061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38272821903229</t>
   </si>
   <si>
     <t xml:space="preserve">1.41133642196655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38749623298645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37319219112396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4304084777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47808885574341</t>
+    <t xml:space="preserve">1.38749635219574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37319207191467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43040859699249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47808873653412</t>
   </si>
   <si>
     <t xml:space="preserve">1.44471251964569</t>
@@ -1499,43 +1499,43 @@
     <t xml:space="preserve">1.40656840801239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42087256908417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43517661094666</t>
+    <t xml:space="preserve">1.42087244987488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43517649173737</t>
   </si>
   <si>
     <t xml:space="preserve">1.45901668071747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43994462490082</t>
+    <t xml:space="preserve">1.43994450569153</t>
   </si>
   <si>
     <t xml:space="preserve">1.41610443592072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.516233086586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50669705867767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53530514240265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54484117031097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54007303714752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58298540115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57344937324524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68788194656372</t>
+    <t xml:space="preserve">1.51623296737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50669693946838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53530502319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54484105110168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54007315635681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58298528194427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57344925403595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68788206577301</t>
   </si>
   <si>
     <t xml:space="preserve">1.65450572967529</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">1.70695412158966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76417052745819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74509835243225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72602605819702</t>
+    <t xml:space="preserve">1.7641704082489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74509847164154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7260262966156</t>
   </si>
   <si>
     <t xml:space="preserve">1.69741809368134</t>
@@ -1559,10 +1559,10 @@
     <t xml:space="preserve">1.66880989074707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67357778549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64020180702209</t>
+    <t xml:space="preserve">1.67357802391052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64020168781281</t>
   </si>
   <si>
     <t xml:space="preserve">1.61159360408783</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">1.6163614988327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62112975120544</t>
+    <t xml:space="preserve">1.62112963199615</t>
   </si>
   <si>
     <t xml:space="preserve">1.63066565990448</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">1.77847456932068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75940239429474</t>
+    <t xml:space="preserve">1.75940251350403</t>
   </si>
   <si>
     <t xml:space="preserve">1.68311393260956</t>
@@ -1613,37 +1613,37 @@
     <t xml:space="preserve">1.82615482807159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79754650592804</t>
+    <t xml:space="preserve">1.79754674434662</t>
   </si>
   <si>
     <t xml:space="preserve">1.788010597229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81661880016327</t>
+    <t xml:space="preserve">1.81661868095398</t>
   </si>
   <si>
     <t xml:space="preserve">1.83092284202576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80708265304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76893842220306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73556244373322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73079431056976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7403302192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72125816345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78324246406555</t>
+    <t xml:space="preserve">1.80708277225494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76893866062164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73556232452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73079442977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74033045768738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72125828266144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78324258327484</t>
   </si>
   <si>
     <t xml:space="preserve">1.7498664855957</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">1.67834603786469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66404187679291</t>
+    <t xml:space="preserve">1.66404175758362</t>
   </si>
   <si>
     <t xml:space="preserve">1.69264996051788</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">1.80231463909149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75463438034058</t>
+    <t xml:space="preserve">1.75463449954987</t>
   </si>
   <si>
     <t xml:space="preserve">1.79277861118317</t>
@@ -1673,70 +1673,70 @@
     <t xml:space="preserve">1.65927386283875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59252142906189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52576899528503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59728932380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70218598842621</t>
+    <t xml:space="preserve">1.5925213098526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52576911449432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59728944301605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7021861076355</t>
   </si>
   <si>
     <t xml:space="preserve">1.85953104496002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8976753950119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92628347873688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82138669490814</t>
+    <t xml:space="preserve">1.89767527580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92628335952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82138681411743</t>
   </si>
   <si>
     <t xml:space="preserve">1.83569085597992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86429917812347</t>
+    <t xml:space="preserve">1.86429905891418</t>
   </si>
   <si>
     <t xml:space="preserve">1.90721130371094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94535541534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99303579330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05978846549988</t>
+    <t xml:space="preserve">1.94535553455353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99303567409515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0597882270813</t>
   </si>
   <si>
     <t xml:space="preserve">2.00257182121277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07886028289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12654042243958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1074686050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08839654922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0979323387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14561295509338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27911782264709</t>
+    <t xml:space="preserve">2.07886052131653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12654066085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10746836662292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08839631080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09793257713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1456127166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27911758422852</t>
   </si>
   <si>
     <t xml:space="preserve">2.19329285621643</t>
@@ -1745,13 +1745,13 @@
     <t xml:space="preserve">2.22190117835999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25050926208496</t>
+    <t xml:space="preserve">2.25050902366638</t>
   </si>
   <si>
     <t xml:space="preserve">2.02164387702942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01210784912109</t>
+    <t xml:space="preserve">2.01210761070251</t>
   </si>
   <si>
     <t xml:space="preserve">1.97396349906921</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">1.98349988460541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0311803817749</t>
+    <t xml:space="preserve">2.03118014335632</t>
   </si>
   <si>
     <t xml:space="preserve">2.04071617126465</t>
@@ -1769,13 +1769,13 @@
     <t xml:space="preserve">2.09847211837769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08884644508362</t>
+    <t xml:space="preserve">2.08884620666504</t>
   </si>
   <si>
     <t xml:space="preserve">2.10809826850891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0022120475769</t>
+    <t xml:space="preserve">2.00221180915833</t>
   </si>
   <si>
     <t xml:space="preserve">1.95408189296722</t>
@@ -1787,10 +1787,10 @@
     <t xml:space="preserve">2.0214638710022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05996823310852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94445586204529</t>
+    <t xml:space="preserve">2.05996799468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.944455742836</t>
   </si>
   <si>
     <t xml:space="preserve">1.9733339548111</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">1.93482983112335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85782158374786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83856952190399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82894361019135</t>
+    <t xml:space="preserve">1.85782170295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83856964111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82894372940063</t>
   </si>
   <si>
     <t xml:space="preserve">1.86744773387909</t>
@@ -1814,22 +1814,22 @@
     <t xml:space="preserve">1.88669979572296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87707376480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8963258266449</t>
+    <t xml:space="preserve">1.87707388401031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89632570743561</t>
   </si>
   <si>
     <t xml:space="preserve">1.92520380020142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99258577823639</t>
+    <t xml:space="preserve">1.99258589744568</t>
   </si>
   <si>
     <t xml:space="preserve">2.04071593284607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05034232139587</t>
+    <t xml:space="preserve">2.05034208297729</t>
   </si>
   <si>
     <t xml:space="preserve">2.11772418022156</t>
@@ -1844,10 +1844,10 @@
     <t xml:space="preserve">2.16585445404053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14660215377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07922029495239</t>
+    <t xml:space="preserve">2.14660239219666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07922005653381</t>
   </si>
   <si>
     <t xml:space="preserve">2.24286246299744</t>
@@ -1859,13 +1859,13 @@
     <t xml:space="preserve">2.27174043655396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30061888694763</t>
+    <t xml:space="preserve">2.30061841011047</t>
   </si>
   <si>
     <t xml:space="preserve">2.2813663482666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18510627746582</t>
+    <t xml:space="preserve">2.1851065158844</t>
   </si>
   <si>
     <t xml:space="preserve">2.19473242759705</t>
@@ -1880,13 +1880,13 @@
     <t xml:space="preserve">2.01183795928955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8722608089447</t>
+    <t xml:space="preserve">1.87226068973541</t>
   </si>
   <si>
     <t xml:space="preserve">1.96370780467987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06959414482117</t>
+    <t xml:space="preserve">2.06959438323975</t>
   </si>
   <si>
     <t xml:space="preserve">2.17548012733459</t>
@@ -1895,49 +1895,49 @@
     <t xml:space="preserve">2.23323631286621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3102445602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35837483406067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42575669288635</t>
+    <t xml:space="preserve">2.31024479866028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35837459564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42575693130493</t>
   </si>
   <si>
     <t xml:space="preserve">2.39687871932983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40650463104248</t>
+    <t xml:space="preserve">2.40650486946106</t>
   </si>
   <si>
     <t xml:space="preserve">2.43538284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41613101959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37762689590454</t>
+    <t xml:space="preserve">2.41613078117371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37762665748596</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874868392944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29099249839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36800050735474</t>
+    <t xml:space="preserve">2.29099273681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36800098419189</t>
   </si>
   <si>
     <t xml:space="preserve">2.38725280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21398425102234</t>
+    <t xml:space="preserve">2.21398448944092</t>
   </si>
   <si>
     <t xml:space="preserve">2.31987071037292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44500851631165</t>
+    <t xml:space="preserve">2.44500875473022</t>
   </si>
   <si>
     <t xml:space="preserve">2.45463490486145</t>
@@ -1949,13 +1949,13 @@
     <t xml:space="preserve">2.49313902854919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52201700210571</t>
+    <t xml:space="preserve">2.52201676368713</t>
   </si>
   <si>
     <t xml:space="preserve">2.50276470184326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5990252494812</t>
+    <t xml:space="preserve">2.59902501106262</t>
   </si>
   <si>
     <t xml:space="preserve">2.64715528488159</t>
@@ -1964,22 +1964,22 @@
     <t xml:space="preserve">2.54126906394958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51239085197449</t>
+    <t xml:space="preserve">2.51239109039307</t>
   </si>
   <si>
     <t xml:space="preserve">2.47388672828674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48351263999939</t>
+    <t xml:space="preserve">2.48351287841797</t>
   </si>
   <si>
     <t xml:space="preserve">2.53164315223694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63752913475037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6952850818634</t>
+    <t xml:space="preserve">2.63752937316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69528532028198</t>
   </si>
   <si>
     <t xml:space="preserve">2.82042360305786</t>
@@ -1991,16 +1991,16 @@
     <t xml:space="preserve">2.67603325843811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60865116119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66640710830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57014727592468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58939909934998</t>
+    <t xml:space="preserve">2.60865139961243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66640734672546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5701470375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58939933776855</t>
   </si>
   <si>
     <t xml:space="preserve">2.56052112579346</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">2.57977318763733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38258814811707</t>
+    <t xml:space="preserve">2.38258790969849</t>
   </si>
   <si>
     <t xml:space="preserve">2.29506421089172</t>
@@ -2024,13 +2024,13 @@
     <t xml:space="preserve">2.28533935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32423901557922</t>
+    <t xml:space="preserve">2.32423877716064</t>
   </si>
   <si>
     <t xml:space="preserve">2.25616478919983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23671507835388</t>
+    <t xml:space="preserve">2.23671531677246</t>
   </si>
   <si>
     <t xml:space="preserve">2.21726560592651</t>
@@ -2042,16 +2042,16 @@
     <t xml:space="preserve">2.34368872642517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2658896446228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30478882789612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24644017219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11029243469238</t>
+    <t xml:space="preserve">2.26588988304138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3047890663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24643993377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1102921962738</t>
   </si>
   <si>
     <t xml:space="preserve">2.15891647338867</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">2.19781565666199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16864109039307</t>
+    <t xml:space="preserve">2.16864132881165</t>
   </si>
   <si>
     <t xml:space="preserve">2.18809103965759</t>
@@ -2081,16 +2081,16 @@
     <t xml:space="preserve">2.13946676254272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09084248542786</t>
+    <t xml:space="preserve">2.09084272384644</t>
   </si>
   <si>
     <t xml:space="preserve">2.10056734085083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27561473846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08111786842346</t>
+    <t xml:space="preserve">2.27561450004578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08111763000488</t>
   </si>
   <si>
     <t xml:space="preserve">1.97414433956146</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">1.98386907577515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96441948413849</t>
+    <t xml:space="preserve">1.9644193649292</t>
   </si>
   <si>
     <t xml:space="preserve">1.94496977329254</t>
@@ -2117,13 +2117,13 @@
     <t xml:space="preserve">2.02276849746704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03249311447144</t>
+    <t xml:space="preserve">2.03249335289001</t>
   </si>
   <si>
     <t xml:space="preserve">2.01304364204407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07139301300049</t>
+    <t xml:space="preserve">2.07139277458191</t>
   </si>
   <si>
     <t xml:space="preserve">2.04221820831299</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">1.93524491786957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95469450950623</t>
+    <t xml:space="preserve">1.95469462871552</t>
   </si>
   <si>
     <t xml:space="preserve">1.91579520702362</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">1.93038249015808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06166768074036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91093277931213</t>
+    <t xml:space="preserve">2.06166791915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91093289852142</t>
   </si>
   <si>
     <t xml:space="preserve">2.1491916179657</t>
@@ -2162,16 +2162,16 @@
     <t xml:space="preserve">1.92552006244659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81854665279388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84772121906281</t>
+    <t xml:space="preserve">1.81854677200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84772133827209</t>
   </si>
   <si>
     <t xml:space="preserve">1.8866206407547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83313393592834</t>
+    <t xml:space="preserve">1.83313405513763</t>
   </si>
   <si>
     <t xml:space="preserve">1.85258364677429</t>
@@ -2205,9 +2205,6 @@
   </si>
   <si>
     <t xml:space="preserve">1.97931289672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95469462871552</t>
   </si>
   <si>
     <t xml:space="preserve">1.9497709274292</t>
@@ -59503,7 +59500,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2180" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -59529,7 +59526,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2181" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59555,7 +59552,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2182" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59581,7 +59578,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2183" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59685,7 +59682,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2187" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59711,7 +59708,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2188" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59737,7 +59734,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2189" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59763,7 +59760,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2190" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59789,7 +59786,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2191" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59815,7 +59812,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2192" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59841,7 +59838,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2193" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60153,7 +60150,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2205" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60179,7 +60176,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2206" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60205,7 +60202,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2207" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60231,7 +60228,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2208" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60283,7 +60280,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2210" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60309,7 +60306,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2211" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60335,7 +60332,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2212" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60361,7 +60358,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2213" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60387,7 +60384,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2214" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60439,7 +60436,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2216" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60595,7 +60592,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60673,7 +60670,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2225" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60699,7 +60696,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2226" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60751,7 +60748,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2228" t="s">
-        <v>731</v>
+        <v>707</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60777,7 +60774,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2229" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60803,7 +60800,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2230" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60829,7 +60826,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2231" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60855,7 +60852,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2232" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60881,7 +60878,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2233" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60907,7 +60904,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2234" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60933,7 +60930,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2235" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60959,7 +60956,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2236" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60985,7 +60982,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2237" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61011,7 +61008,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2238" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61037,7 +61034,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2239" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61063,7 +61060,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2240" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61089,7 +61086,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G2241" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61115,7 +61112,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2242" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61141,7 +61138,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2243" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61167,7 +61164,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G2244" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61193,7 +61190,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2245" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61219,7 +61216,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2246" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61245,7 +61242,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2247" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61271,7 +61268,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2248" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61297,7 +61294,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2249" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61323,7 +61320,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2250" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61349,7 +61346,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2251" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61375,7 +61372,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2252" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61479,7 +61476,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2256" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -61505,7 +61502,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2257" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -61557,7 +61554,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2259" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -61583,7 +61580,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2260" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -61609,7 +61606,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2261" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -61635,7 +61632,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -61661,7 +61658,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2263" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -61713,7 +61710,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2265" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61739,7 +61736,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2266" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61869,7 +61866,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2271" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61895,7 +61892,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2272" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61921,7 +61918,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2273" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61947,7 +61944,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2274" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61973,7 +61970,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2275" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61999,7 +61996,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2276" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62025,7 +62022,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2277" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62051,7 +62048,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2278" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62077,7 +62074,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2279" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62103,7 +62100,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2280" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62129,7 +62126,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2281" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62155,7 +62152,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2282" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62181,7 +62178,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2283" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62207,7 +62204,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2284" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62233,7 +62230,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2285" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62259,7 +62256,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2286" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62285,7 +62282,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2287" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62311,7 +62308,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2288" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62337,7 +62334,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2289" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62363,7 +62360,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2290" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62389,7 +62386,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2291" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62415,7 +62412,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2292" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62441,7 +62438,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2293" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62467,7 +62464,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2294" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -62493,7 +62490,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2295" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -62519,7 +62516,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2296" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -62545,7 +62542,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2297" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -62571,7 +62568,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2298" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -62597,7 +62594,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2299" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -62623,7 +62620,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2300" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -62649,7 +62646,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2301" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -62675,7 +62672,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2302" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -62701,7 +62698,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2303" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62727,7 +62724,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2304" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62753,7 +62750,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62779,7 +62776,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2306" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62805,7 +62802,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G2307" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62831,7 +62828,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2308" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62857,7 +62854,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2309" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62883,7 +62880,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2310" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62909,7 +62906,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2311" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62935,7 +62932,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2312" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62961,7 +62958,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2313" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62987,7 +62984,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2314" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63013,7 +63010,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2315" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63039,7 +63036,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2316" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63065,7 +63062,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2317" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63091,7 +63088,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2318" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63117,7 +63114,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2319" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63143,7 +63140,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2320" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63169,7 +63166,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2321" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63195,7 +63192,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2322" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63221,7 +63218,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2323" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63247,7 +63244,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2324" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63273,7 +63270,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2325" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63299,7 +63296,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2326" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63325,7 +63322,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2327" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63351,7 +63348,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2328" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63377,7 +63374,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2329" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63403,7 +63400,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2330" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63429,7 +63426,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2331" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63455,7 +63452,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2332" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63481,7 +63478,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2333" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -63507,7 +63504,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2334" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -63533,7 +63530,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2335" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -63559,7 +63556,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2336" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -63585,7 +63582,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2337" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -63611,7 +63608,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2338" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -63637,7 +63634,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2339" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -63663,7 +63660,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G2340" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -63689,7 +63686,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2341" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63715,7 +63712,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2342" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63741,7 +63738,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63767,7 +63764,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2344" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63793,7 +63790,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2345" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63819,7 +63816,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2346" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63845,7 +63842,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2347" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63871,7 +63868,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63897,7 +63894,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63923,7 +63920,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2350" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63949,7 +63946,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2351" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63975,7 +63972,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G2352" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64001,7 +63998,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2353" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64027,7 +64024,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2354" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64053,7 +64050,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2355" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64079,7 +64076,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2356" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64105,7 +64102,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G2357" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64131,7 +64128,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2358" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64157,7 +64154,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G2359" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64183,7 +64180,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G2360" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64209,7 +64206,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2361" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64235,7 +64232,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2362" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64261,7 +64258,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2363" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64287,7 +64284,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G2364" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64313,7 +64310,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2365" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64339,7 +64336,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64365,7 +64362,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G2367" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64391,7 +64388,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2368" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64417,7 +64414,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2369" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64443,7 +64440,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2370" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64469,7 +64466,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2371" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64495,7 +64492,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2372" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -64521,7 +64518,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2373" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -64547,7 +64544,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G2374" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -64573,7 +64570,7 @@
         <v>1.625</v>
       </c>
       <c r="G2375" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -64599,7 +64596,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G2376" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -64625,7 +64622,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G2377" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -64651,7 +64648,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2378" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -64677,7 +64674,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G2379" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -64703,7 +64700,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2380" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64729,7 +64726,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2381" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64755,7 +64752,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2382" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64781,7 +64778,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G2383" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64807,7 +64804,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2384" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64833,7 +64830,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2385" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64859,7 +64856,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64885,7 +64882,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2387" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64911,7 +64908,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2388" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64937,7 +64934,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64963,7 +64960,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2390" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64989,7 +64986,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2391" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65015,7 +65012,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2392" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65041,7 +65038,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G2393" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65067,7 +65064,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G2394" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65093,7 +65090,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2395" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65119,7 +65116,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2396" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65145,7 +65142,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2397" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65171,7 +65168,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2398" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65197,7 +65194,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2399" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65223,7 +65220,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2400" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65249,7 +65246,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2401" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65275,7 +65272,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2402" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65301,7 +65298,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2403" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65327,7 +65324,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2404" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65353,7 +65350,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2405" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65379,7 +65376,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2406" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65431,7 +65428,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2408" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65457,7 +65454,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2409" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65483,7 +65480,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2410" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -65509,7 +65506,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2411" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65535,7 +65532,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2412" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65561,7 +65558,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2413" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65587,7 +65584,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2414" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65613,7 +65610,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2415" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65639,7 +65636,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2416" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65665,7 +65662,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2417" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65691,7 +65688,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2418" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65717,7 +65714,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2419" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65743,7 +65740,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2420" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65769,7 +65766,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2421" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65795,7 +65792,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65821,7 +65818,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2423" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65847,7 +65844,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2424" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65873,7 +65870,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2425" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65899,7 +65896,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2426" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65925,7 +65922,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2427" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65951,7 +65948,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2428" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65977,7 +65974,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2429" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66003,7 +66000,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2430" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66029,7 +66026,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2431" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66055,7 +66052,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2432" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66081,7 +66078,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2433" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66107,7 +66104,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2434" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66133,7 +66130,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2435" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66159,7 +66156,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2436" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66185,7 +66182,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2437" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66211,7 +66208,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2438" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66237,7 +66234,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2439" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66263,7 +66260,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2440" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66289,7 +66286,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2441" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66315,7 +66312,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2442" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66341,7 +66338,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2443" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66367,7 +66364,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2444" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66393,7 +66390,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2445" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66419,7 +66416,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2446" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66445,7 +66442,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2447" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66471,7 +66468,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2448" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -66497,7 +66494,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2449" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -66523,7 +66520,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2450" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66549,7 +66546,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2451" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66575,7 +66572,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2452" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66601,7 +66598,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2453" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66627,7 +66624,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2454" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66653,7 +66650,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2455" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66679,7 +66676,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2456" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66705,7 +66702,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2457" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66731,7 +66728,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2458" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66757,7 +66754,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2459" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66783,7 +66780,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2460" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66809,7 +66806,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2461" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66835,7 +66832,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2462" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66861,7 +66858,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2463" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66887,7 +66884,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2464" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66913,7 +66910,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2465" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66939,7 +66936,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2466" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66965,7 +66962,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2467" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66991,7 +66988,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2468" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67017,7 +67014,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2469" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67043,7 +67040,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2470" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67069,7 +67066,7 @@
         <v>2</v>
       </c>
       <c r="G2471" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67095,7 +67092,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2472" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67121,7 +67118,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2473" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67147,7 +67144,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2474" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67173,7 +67170,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2475" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67199,7 +67196,7 @@
         <v>2</v>
       </c>
       <c r="G2476" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67225,7 +67222,7 @@
         <v>2</v>
       </c>
       <c r="G2477" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67251,7 +67248,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2478" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67277,7 +67274,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2479" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67303,7 +67300,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2480" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67329,7 +67326,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2481" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67355,7 +67352,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2482" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67381,7 +67378,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2483" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67407,7 +67404,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2484" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67433,7 +67430,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2485" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67459,7 +67456,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2486" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67485,7 +67482,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2487" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -67511,7 +67508,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2488" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67537,7 +67534,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2489" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67563,7 +67560,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2490" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67589,7 +67586,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2491" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67615,7 +67612,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2492" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67641,7 +67638,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2493" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67667,7 +67664,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2494" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67693,7 +67690,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2495" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67719,7 +67716,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2496" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67745,7 +67742,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2497" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67771,7 +67768,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2498" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67797,7 +67794,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2499" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67823,7 +67820,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2500" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67849,7 +67846,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2501" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67875,7 +67872,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2502" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -67901,7 +67898,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2503" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -67927,7 +67924,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2504" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67953,7 +67950,7 @@
         <v>2</v>
       </c>
       <c r="G2505" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67979,7 +67976,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2506" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68005,7 +68002,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2507" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68031,7 +68028,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2508" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68057,7 +68054,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2509" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68083,7 +68080,7 @@
         <v>2</v>
       </c>
       <c r="G2510" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68109,7 +68106,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2511" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68135,7 +68132,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2512" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68161,7 +68158,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2513" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -68187,7 +68184,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2514" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -68213,7 +68210,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2515" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -68239,7 +68236,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2516" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -68265,7 +68262,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2517" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -68291,7 +68288,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2518" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -68317,7 +68314,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2519" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -68343,7 +68340,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2520" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -68369,7 +68366,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2521" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -68395,7 +68392,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2522" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -68421,7 +68418,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2523" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -68447,7 +68444,7 @@
         <v>2</v>
       </c>
       <c r="G2524" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -68473,7 +68470,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2525" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -68499,7 +68496,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2526" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -68525,7 +68522,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2527" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -68551,7 +68548,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2528" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -68577,7 +68574,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2529" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -68603,7 +68600,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2530" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -68629,7 +68626,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2531" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -68655,7 +68652,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2532" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -68681,7 +68678,7 @@
         <v>2</v>
       </c>
       <c r="G2533" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -68707,7 +68704,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2534" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -68733,7 +68730,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2535" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -68759,7 +68756,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2536" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -68785,7 +68782,7 @@
         <v>2</v>
       </c>
       <c r="G2537" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2537" t="s">
         <v>9</v>
@@ -68811,7 +68808,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2538" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2538" t="s">
         <v>9</v>
@@ -68837,7 +68834,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2539" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2539" t="s">
         <v>9</v>
@@ -68863,7 +68860,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2540" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2540" t="s">
         <v>9</v>
@@ -68889,7 +68886,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2541" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2541" t="s">
         <v>9</v>
@@ -68915,7 +68912,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2542" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2542" t="s">
         <v>9</v>
@@ -68923,7 +68920,7 @@
     </row>
     <row r="2543">
       <c r="A2543" s="1" t="n">
-        <v>46027.6782986111</v>
+        <v>46027.3333333333</v>
       </c>
       <c r="B2543" t="n">
         <v>4000</v>
@@ -68941,9 +68938,35 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2543" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2543" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2544">
+      <c r="A2544" s="1" t="n">
+        <v>46028.6349884259</v>
+      </c>
+      <c r="B2544" t="n">
+        <v>18500</v>
+      </c>
+      <c r="C2544" t="n">
+        <v>2.00999999046326</v>
+      </c>
+      <c r="D2544" t="n">
+        <v>1.99500000476837</v>
+      </c>
+      <c r="E2544" t="n">
+        <v>1.99500000476837</v>
+      </c>
+      <c r="F2544" t="n">
+        <v>2.00999999046326</v>
+      </c>
+      <c r="G2544" t="s">
+        <v>800</v>
+      </c>
+      <c r="H2544" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DGT.MI.xlsx
+++ b/data/DGT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="827">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -56,28 +56,28 @@
     <t xml:space="preserve">2.00509595870972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04860639572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99421846866608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971522808075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94889545440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88544285297394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91444981098175</t>
+    <t xml:space="preserve">2.04860591888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99421858787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971510887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94889557361603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88544297218323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91444945335388</t>
   </si>
   <si>
     <t xml:space="preserve">1.89632046222687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8763781785965</t>
+    <t xml:space="preserve">1.87637829780579</t>
   </si>
   <si>
     <t xml:space="preserve">1.9706506729126</t>
@@ -86,34 +86,34 @@
     <t xml:space="preserve">1.92714023590088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93076598644257</t>
+    <t xml:space="preserve">1.93076622486115</t>
   </si>
   <si>
     <t xml:space="preserve">1.85824906826019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80839359760284</t>
+    <t xml:space="preserve">1.80839347839355</t>
   </si>
   <si>
     <t xml:space="preserve">1.8256162405014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75128638744354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6470433473587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75581884384155</t>
+    <t xml:space="preserve">1.75128626823425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64704298973083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75581872463226</t>
   </si>
   <si>
     <t xml:space="preserve">1.71321487426758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68964695930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73134434223175</t>
+    <t xml:space="preserve">1.68964684009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73134422302246</t>
   </si>
   <si>
     <t xml:space="preserve">1.76760268211365</t>
@@ -122,37 +122,37 @@
     <t xml:space="preserve">1.72862470149994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7585381269455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81292593479156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83105504512787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76850914955139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67514359951019</t>
+    <t xml:space="preserve">1.75853824615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81292569637299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83105516433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7685090303421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6751434803009</t>
   </si>
   <si>
     <t xml:space="preserve">1.74947345256805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69871139526367</t>
+    <t xml:space="preserve">1.69871151447296</t>
   </si>
   <si>
     <t xml:space="preserve">1.74766051769257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70777606964111</t>
+    <t xml:space="preserve">1.7077761888504</t>
   </si>
   <si>
     <t xml:space="preserve">1.70868253707886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6950855255127</t>
+    <t xml:space="preserve">1.69508576393127</t>
   </si>
   <si>
     <t xml:space="preserve">1.7766672372818</t>
@@ -161,28 +161,28 @@
     <t xml:space="preserve">1.70143091678619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69055342674255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73497009277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64069771766663</t>
+    <t xml:space="preserve">1.69055330753326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73496997356415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64069783687592</t>
   </si>
   <si>
     <t xml:space="preserve">1.62982022762299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63163316249847</t>
+    <t xml:space="preserve">1.63163328170776</t>
   </si>
   <si>
     <t xml:space="preserve">1.68692743778229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68602097034454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67333054542542</t>
+    <t xml:space="preserve">1.68602085113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6733306646347</t>
   </si>
   <si>
     <t xml:space="preserve">1.74040877819061</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">1.70415031909943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75672519207001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68783402442932</t>
+    <t xml:space="preserve">1.75672507286072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68783390522003</t>
   </si>
   <si>
     <t xml:space="preserve">1.64885604381561</t>
@@ -203,28 +203,28 @@
     <t xml:space="preserve">1.64794957637787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68420815467834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72137308120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72227954864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67786288261414</t>
+    <t xml:space="preserve">1.68420827388763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72137320041656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72227942943573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67786276340485</t>
   </si>
   <si>
     <t xml:space="preserve">1.63253962993622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66335964202881</t>
+    <t xml:space="preserve">1.66335952281952</t>
   </si>
   <si>
     <t xml:space="preserve">1.66517233848572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65429472923279</t>
+    <t xml:space="preserve">1.65429496765137</t>
   </si>
   <si>
     <t xml:space="preserve">1.81111299991608</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">1.78754484653473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78935778141022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66154646873474</t>
+    <t xml:space="preserve">1.7893580198288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66154634952545</t>
   </si>
   <si>
     <t xml:space="preserve">1.69961798191071</t>
@@ -248,52 +248,52 @@
     <t xml:space="preserve">1.66245305538177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6833016872406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65882730484009</t>
+    <t xml:space="preserve">1.68330156803131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6588271856308</t>
   </si>
   <si>
     <t xml:space="preserve">1.60353291034698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56908738613129</t>
+    <t xml:space="preserve">1.569087266922</t>
   </si>
   <si>
     <t xml:space="preserve">1.58902943134308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48297333717346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49566388130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49203813076019</t>
+    <t xml:space="preserve">1.48297345638275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49566376209259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4920380115509</t>
   </si>
   <si>
     <t xml:space="preserve">1.53192234039307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48387968540192</t>
+    <t xml:space="preserve">1.48387980461121</t>
   </si>
   <si>
     <t xml:space="preserve">1.45215356349945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4856926202774</t>
+    <t xml:space="preserve">1.48569285869598</t>
   </si>
   <si>
     <t xml:space="preserve">1.42858564853668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4594053030014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49294459819794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46031153202057</t>
+    <t xml:space="preserve">1.45940518379211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49294447898865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46031165122986</t>
   </si>
   <si>
     <t xml:space="preserve">1.4412761926651</t>
@@ -302,28 +302,28 @@
     <t xml:space="preserve">1.45034074783325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46846997737885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42586600780487</t>
+    <t xml:space="preserve">1.46846985816956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42586624622345</t>
   </si>
   <si>
     <t xml:space="preserve">1.31255829334259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36422681808472</t>
+    <t xml:space="preserve">1.36422657966614</t>
   </si>
   <si>
     <t xml:space="preserve">1.34156513214111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36875903606415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33250033855438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2781126499176</t>
+    <t xml:space="preserve">1.36875891685486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33250057697296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27811253070831</t>
   </si>
   <si>
     <t xml:space="preserve">1.19653105735779</t>
@@ -344,13 +344,13 @@
     <t xml:space="preserve">1.09863305091858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12401401996613</t>
+    <t xml:space="preserve">1.12401413917542</t>
   </si>
   <si>
     <t xml:space="preserve">1.13307857513428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12582695484161</t>
+    <t xml:space="preserve">1.12582683563232</t>
   </si>
   <si>
     <t xml:space="preserve">1.11313652992249</t>
@@ -359,10 +359,10 @@
     <t xml:space="preserve">1.06962621212006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08684909343719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09500730037689</t>
+    <t xml:space="preserve">1.08684897422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0950071811676</t>
   </si>
   <si>
     <t xml:space="preserve">1.09410071372986</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">1.10769760608673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10951066017151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12129461765289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09682023525238</t>
+    <t xml:space="preserve">1.10951054096222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12129473686218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09682011604309</t>
   </si>
   <si>
     <t xml:space="preserve">1.08956849575043</t>
@@ -392,10 +392,10 @@
     <t xml:space="preserve">1.08866190910339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.072345495224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05149698257446</t>
+    <t xml:space="preserve">1.07234561443329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05149674415588</t>
   </si>
   <si>
     <t xml:space="preserve">1.12310755252838</t>
@@ -404,22 +404,22 @@
     <t xml:space="preserve">1.1013525724411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08322310447693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08775556087494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11404299736023</t>
+    <t xml:space="preserve">1.08322322368622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08775544166565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11404287815094</t>
   </si>
   <si>
     <t xml:space="preserve">1.15120780467987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21466040611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18474698066711</t>
+    <t xml:space="preserve">1.21466028690338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1847470998764</t>
   </si>
   <si>
     <t xml:space="preserve">1.1457691192627</t>
@@ -428,22 +428,22 @@
     <t xml:space="preserve">1.12220120429993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06237471103668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03336787223816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934563159942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945440709590912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977167010307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956318378448486</t>
+    <t xml:space="preserve">1.0623744726181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03336775302887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934563219547272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945440828800201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977166950702667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956318318843842</t>
   </si>
   <si>
     <t xml:space="preserve">0.933656752109528</t>
@@ -452,22 +452,22 @@
     <t xml:space="preserve">1.01523840427399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04877769947052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0360871553421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02430319786072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990764021873474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05059051513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11494934558868</t>
+    <t xml:space="preserve">1.04877746105194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03608727455139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02430295944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990764081478119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05059063434601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11494946479797</t>
   </si>
   <si>
     <t xml:space="preserve">1.12854635715485</t>
@@ -476,13 +476,13 @@
     <t xml:space="preserve">1.07506501674652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06418752670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02067744731903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997109234333038</t>
+    <t xml:space="preserve">1.06418764591217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02067732810974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997109293937683</t>
   </si>
   <si>
     <t xml:space="preserve">1.00617384910583</t>
@@ -494,40 +494,40 @@
     <t xml:space="preserve">1.03880655765533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05965518951416</t>
+    <t xml:space="preserve">1.05965507030487</t>
   </si>
   <si>
     <t xml:space="preserve">1.04243218898773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06328117847443</t>
+    <t xml:space="preserve">1.06328105926514</t>
   </si>
   <si>
     <t xml:space="preserve">1.05693566799164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10407185554504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10497808456421</t>
+    <t xml:space="preserve">1.10407173633575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1049782037735</t>
   </si>
   <si>
     <t xml:space="preserve">1.07597160339355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12492060661316</t>
+    <t xml:space="preserve">1.12492048740387</t>
   </si>
   <si>
     <t xml:space="preserve">1.1031653881073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21103429794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19562470912933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21284735202789</t>
+    <t xml:space="preserve">1.2110344171524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19562458992004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21284747123718</t>
   </si>
   <si>
     <t xml:space="preserve">1.14667558670044</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">1.15392732620239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20559561252594</t>
+    <t xml:space="preserve">1.20559573173523</t>
   </si>
   <si>
     <t xml:space="preserve">1.20196986198425</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">1.23188304901123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2536381483078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25817048549652</t>
+    <t xml:space="preserve">1.25363838672638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25817036628723</t>
   </si>
   <si>
     <t xml:space="preserve">1.26089000701904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25545108318329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28717720508575</t>
+    <t xml:space="preserve">1.25545120239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28717744350433</t>
   </si>
   <si>
     <t xml:space="preserve">1.30893242359161</t>
@@ -566,16 +566,16 @@
     <t xml:space="preserve">1.30530655384064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41226923465729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37963628768921</t>
+    <t xml:space="preserve">1.41226899623871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37963652610779</t>
   </si>
   <si>
     <t xml:space="preserve">1.40320467948914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35244274139404</t>
+    <t xml:space="preserve">1.35244262218475</t>
   </si>
   <si>
     <t xml:space="preserve">1.35697495937347</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">1.34065866470337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32343602180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35062980651855</t>
+    <t xml:space="preserve">1.32343590259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35062968730927</t>
   </si>
   <si>
     <t xml:space="preserve">1.3288745880127</t>
@@ -599,13 +599,13 @@
     <t xml:space="preserve">1.26995468139648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1947181224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1439563035965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24548017978668</t>
+    <t xml:space="preserve">1.19471800327301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14395606517792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24548006057739</t>
   </si>
   <si>
     <t xml:space="preserve">1.25001239776611</t>
@@ -617,10 +617,10 @@
     <t xml:space="preserve">1.23278963565826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24185431003571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28173851966858</t>
+    <t xml:space="preserve">1.24185419082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28173863887787</t>
   </si>
   <si>
     <t xml:space="preserve">1.26451575756073</t>
@@ -629,10 +629,10 @@
     <t xml:space="preserve">1.28264498710632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25091874599457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26904809474945</t>
+    <t xml:space="preserve">1.25091886520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26904797554016</t>
   </si>
   <si>
     <t xml:space="preserve">1.33159399032593</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">1.29624211788177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28536427021027</t>
+    <t xml:space="preserve">1.28536415100098</t>
   </si>
   <si>
     <t xml:space="preserve">1.31437134742737</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">1.30983901023865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31799721717834</t>
+    <t xml:space="preserve">1.31799709796906</t>
   </si>
   <si>
     <t xml:space="preserve">1.29896140098572</t>
@@ -659,61 +659,61 @@
     <t xml:space="preserve">1.37782371044159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3352198600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26179623603821</t>
+    <t xml:space="preserve">1.33522009849548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2617963552475</t>
   </si>
   <si>
     <t xml:space="preserve">1.31074523925781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30711960792542</t>
+    <t xml:space="preserve">1.3071197271347</t>
   </si>
   <si>
     <t xml:space="preserve">1.34247159957886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.294429063797</t>
+    <t xml:space="preserve">1.29442894458771</t>
   </si>
   <si>
     <t xml:space="preserve">1.32434237003326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33884584903717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31165170669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27992558479309</t>
+    <t xml:space="preserve">1.33884572982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31165194511414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2799254655838</t>
   </si>
   <si>
     <t xml:space="preserve">1.30621302127838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31618416309357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30349349975586</t>
+    <t xml:space="preserve">1.31618404388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30349373817444</t>
   </si>
   <si>
     <t xml:space="preserve">1.27720630168915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26632881164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28355145454407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25907707214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24910593032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27539336681366</t>
+    <t xml:space="preserve">1.26632869243622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28355133533478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25907731056213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24910604953766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27539324760437</t>
   </si>
   <si>
     <t xml:space="preserve">1.25273168087006</t>
@@ -722,25 +722,25 @@
     <t xml:space="preserve">1.34700381755829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34972321987152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2926162481308</t>
+    <t xml:space="preserve">1.34972333908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29261612892151</t>
   </si>
   <si>
     <t xml:space="preserve">1.32978105545044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23369610309601</t>
+    <t xml:space="preserve">1.23369598388672</t>
   </si>
   <si>
     <t xml:space="preserve">1.22372496128082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22916376590729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2046891450882</t>
+    <t xml:space="preserve">1.229163646698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20468926429749</t>
   </si>
   <si>
     <t xml:space="preserve">1.22191202640533</t>
@@ -749,28 +749,28 @@
     <t xml:space="preserve">1.21919274330139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22100567817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21828627586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22463130950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21012783050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18656003475189</t>
+    <t xml:space="preserve">1.22100555896759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21828615665436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22463142871857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21012806892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1865599155426</t>
   </si>
   <si>
     <t xml:space="preserve">1.17477595806122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17840170860291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1521143913269</t>
+    <t xml:space="preserve">1.17840158939362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15211451053619</t>
   </si>
   <si>
     <t xml:space="preserve">1.15845954418182</t>
@@ -782,43 +782,43 @@
     <t xml:space="preserve">1.10588479042053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07959735393524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10679113864899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13217198848724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16933739185333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22644424438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23822832107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24457383155823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25182521343231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24004137516022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20378279685974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20650219917297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24094772338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23097670078278</t>
+    <t xml:space="preserve">1.07959723472595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10679125785828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13217234611511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16933703422546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22644436359406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23822844028473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24457371234894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25182545185089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24004125595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20378267765045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20650207996368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24094760417938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23097658157349</t>
   </si>
   <si>
     <t xml:space="preserve">1.21194100379944</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">1.23460245132446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24638664722443</t>
+    <t xml:space="preserve">1.24638652801514</t>
   </si>
   <si>
     <t xml:space="preserve">1.2762998342514</t>
@@ -836,13 +836,13 @@
     <t xml:space="preserve">1.27086102962494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29805493354797</t>
+    <t xml:space="preserve">1.29805505275726</t>
   </si>
   <si>
     <t xml:space="preserve">1.22553777694702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15574026107788</t>
+    <t xml:space="preserve">1.15574014186859</t>
   </si>
   <si>
     <t xml:space="preserve">1.11857521533966</t>
@@ -863,10 +863,10 @@
     <t xml:space="preserve">1.19925045967102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11676239967346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0931943655014</t>
+    <t xml:space="preserve">1.11676228046417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09319400787354</t>
   </si>
   <si>
     <t xml:space="preserve">1.09772658348083</t>
@@ -881,67 +881,67 @@
     <t xml:space="preserve">1.21375381946564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21556687355042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2862708568573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28989672660828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28445792198181</t>
+    <t xml:space="preserve">1.21556675434113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28627097606659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28989684581757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2844580411911</t>
   </si>
   <si>
     <t xml:space="preserve">1.38960766792297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40048515796661</t>
+    <t xml:space="preserve">1.4004852771759</t>
   </si>
   <si>
     <t xml:space="preserve">1.41408216953278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38235592842102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37057197093964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32796812057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36513340473175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35516202449799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38416874408722</t>
+    <t xml:space="preserve">1.38235604763031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37057185173035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32796823978424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36513328552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35516214370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38416886329651</t>
   </si>
   <si>
     <t xml:space="preserve">1.42224025726318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38054287433624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38870120048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36694622039795</t>
+    <t xml:space="preserve">1.38054311275482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38870131969452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36694598197937</t>
   </si>
   <si>
     <t xml:space="preserve">1.40773689746857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39957892894745</t>
+    <t xml:space="preserve">1.39957880973816</t>
   </si>
   <si>
     <t xml:space="preserve">1.39685940742493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38326239585876</t>
+    <t xml:space="preserve">1.38326263427734</t>
   </si>
   <si>
     <t xml:space="preserve">1.38688826560974</t>
@@ -950,16 +950,16 @@
     <t xml:space="preserve">1.50926077365875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57724547386169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57271325588226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54551935195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55005156993866</t>
+    <t xml:space="preserve">1.57724559307098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57271313667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54551923274994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55005168914795</t>
   </si>
   <si>
     <t xml:space="preserve">1.51379311084747</t>
@@ -968,58 +968,58 @@
     <t xml:space="preserve">1.48659908771515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44580852985382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48206686973572</t>
+    <t xml:space="preserve">1.44580841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48206698894501</t>
   </si>
   <si>
     <t xml:space="preserve">1.43221139907837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54098701477051</t>
+    <t xml:space="preserve">1.5409871339798</t>
   </si>
   <si>
     <t xml:space="preserve">1.52285766601562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52739000320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37329137325287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39142072200775</t>
+    <t xml:space="preserve">1.52739012241364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37329125404358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39142060279846</t>
   </si>
   <si>
     <t xml:space="preserve">1.34609746932983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29170978069305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31890368461609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33703279495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27358031272888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3959527015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30077409744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33341026306152</t>
+    <t xml:space="preserve">1.29170966148376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3189035654068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33703291416168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27358043193817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39595282077789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30077433586121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33341014385223</t>
   </si>
   <si>
     <t xml:space="preserve">1.3147611618042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30543661117554</t>
+    <t xml:space="preserve">1.30543649196625</t>
   </si>
   <si>
     <t xml:space="preserve">1.31942331790924</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">1.24948930740356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23084032535553</t>
+    <t xml:space="preserve">1.23084020614624</t>
   </si>
   <si>
     <t xml:space="preserve">1.21219110488892</t>
@@ -1040,13 +1040,13 @@
     <t xml:space="preserve">1.2541515827179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23550260066986</t>
+    <t xml:space="preserve">1.23550248146057</t>
   </si>
   <si>
     <t xml:space="preserve">1.22617793083191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19354200363159</t>
+    <t xml:space="preserve">1.19354212284088</t>
   </si>
   <si>
     <t xml:space="preserve">1.19820415973663</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">1.27280068397522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29611206054688</t>
+    <t xml:space="preserve">1.29611217975616</t>
   </si>
   <si>
     <t xml:space="preserve">1.31009888648987</t>
@@ -1070,49 +1070,49 @@
     <t xml:space="preserve">1.28212535381317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2681382894516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30077421665192</t>
+    <t xml:space="preserve">1.26813852787018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3007744550705</t>
   </si>
   <si>
     <t xml:space="preserve">1.21685338020325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18887984752655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16556835174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20286655426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17489302158356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17955529689789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20752882957458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32408571243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34739708900452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17023074626923</t>
+    <t xml:space="preserve">1.18887972831726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1655684709549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20286643505096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17489290237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1795551776886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20752894878387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32408559322357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34739696979523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17023086547852</t>
   </si>
   <si>
     <t xml:space="preserve">1.14691925048828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13293254375458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25881385803223</t>
+    <t xml:space="preserve">1.132932305336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25881397724152</t>
   </si>
   <si>
     <t xml:space="preserve">1.27746295928955</t>
@@ -1121,40 +1121,40 @@
     <t xml:space="preserve">1.22151565551758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15624380111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18421757221222</t>
+    <t xml:space="preserve">1.15624392032623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18421733379364</t>
   </si>
   <si>
     <t xml:space="preserve">1.28678750991821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16090619564056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15158152580261</t>
+    <t xml:space="preserve">1.16090607643127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15158176422119</t>
   </si>
   <si>
     <t xml:space="preserve">1.13759469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36138391494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29144990444183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34273493289948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33807253837585</t>
+    <t xml:space="preserve">1.36138379573822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29144966602325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34273481369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33807241916656</t>
   </si>
   <si>
     <t xml:space="preserve">1.11428344249725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10495865345001</t>
+    <t xml:space="preserve">1.1049587726593</t>
   </si>
   <si>
     <t xml:space="preserve">1.14225709438324</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">1.37278056144714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34437823295593</t>
+    <t xml:space="preserve">1.34437811374664</t>
   </si>
   <si>
     <t xml:space="preserve">1.32544326782227</t>
@@ -1181,10 +1181,10 @@
     <t xml:space="preserve">1.55266213417053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41065037250519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31124210357666</t>
+    <t xml:space="preserve">1.41065049171448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31124198436737</t>
   </si>
   <si>
     <t xml:space="preserve">1.31597578525543</t>
@@ -1199,37 +1199,37 @@
     <t xml:space="preserve">1.33964443206787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42011785507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40591657161713</t>
+    <t xml:space="preserve">1.42011773586273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40591669082642</t>
   </si>
   <si>
     <t xml:space="preserve">1.35384559631348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39644920825958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32070970535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33491063117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28283989429474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27337229251862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26390480995178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2591712474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29704105854034</t>
+    <t xml:space="preserve">1.39644908905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32070958614349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3349107503891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28283965587616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27337217330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26390504837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25917112827301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29704093933105</t>
   </si>
   <si>
     <t xml:space="preserve">1.2449699640274</t>
@@ -1238,34 +1238,34 @@
     <t xml:space="preserve">1.2307687997818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22130131721497</t>
+    <t xml:space="preserve">1.22130119800568</t>
   </si>
   <si>
     <t xml:space="preserve">1.2165675163269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22603499889374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24023616313934</t>
+    <t xml:space="preserve">1.22603511810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24023628234863</t>
   </si>
   <si>
     <t xml:space="preserve">1.21183383464813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26863861083984</t>
+    <t xml:space="preserve">1.26863873004913</t>
   </si>
   <si>
     <t xml:space="preserve">1.20710015296936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24970388412476</t>
+    <t xml:space="preserve">1.24970364570618</t>
   </si>
   <si>
     <t xml:space="preserve">1.25443744659424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23550248146057</t>
+    <t xml:space="preserve">1.23550236225128</t>
   </si>
   <si>
     <t xml:space="preserve">1.16923034191132</t>
@@ -1274,34 +1274,34 @@
     <t xml:space="preserve">1.18343150615692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20236659049988</t>
+    <t xml:space="preserve">1.2023663520813</t>
   </si>
   <si>
     <t xml:space="preserve">1.1408280134201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12189304828644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11715912818909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10295808315277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0698219537735</t>
+    <t xml:space="preserve">1.12189292907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11715936660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10295820236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06982207298279</t>
   </si>
   <si>
     <t xml:space="preserve">1.01775109767914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989348649978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979881167411804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965680062770844</t>
+    <t xml:space="preserve">0.989348709583282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979881227016449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965680122375488</t>
   </si>
   <si>
     <t xml:space="preserve">0.914555907249451</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">0.937277734279633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92023628950119</t>
+    <t xml:space="preserve">0.920236349105835</t>
   </si>
   <si>
     <t xml:space="preserve">0.880473077297211</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">0.956212639808655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02248477935791</t>
+    <t xml:space="preserve">1.0224848985672</t>
   </si>
   <si>
     <t xml:space="preserve">1.07928955554962</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">1.05562078952789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09349071979523</t>
+    <t xml:space="preserve">1.09349083900452</t>
   </si>
   <si>
     <t xml:space="preserve">1.06035470962524</t>
@@ -1349,28 +1349,28 @@
     <t xml:space="preserve">1.06508839130402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07455587387085</t>
+    <t xml:space="preserve">1.07455575466156</t>
   </si>
   <si>
     <t xml:space="preserve">1.04615342617035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03668594360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04141962528229</t>
+    <t xml:space="preserve">1.03668606281281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04141974449158</t>
   </si>
   <si>
     <t xml:space="preserve">1.1124255657196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1266268491745</t>
+    <t xml:space="preserve">1.12662672996521</t>
   </si>
   <si>
     <t xml:space="preserve">1.08875691890717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09822428226471</t>
+    <t xml:space="preserve">1.098224401474</t>
   </si>
   <si>
     <t xml:space="preserve">1.05088710784912</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">1.02721858024597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17869770526886</t>
+    <t xml:space="preserve">1.17869782447815</t>
   </si>
   <si>
     <t xml:space="preserve">1.15976285934448</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">1.15029549598694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16449642181396</t>
+    <t xml:space="preserve">1.16449654102325</t>
   </si>
   <si>
     <t xml:space="preserve">1.15502917766571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14556157588959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17396402359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13136053085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08402323722839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0082836151123</t>
+    <t xml:space="preserve">1.14556181430817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17396414279938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13136065006256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0840231180191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00828373432159</t>
   </si>
   <si>
     <t xml:space="preserve">0.984615087509155</t>
@@ -1418,16 +1418,16 @@
     <t xml:space="preserve">0.994082391262054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01301753520966</t>
+    <t xml:space="preserve">1.01301741600037</t>
   </si>
   <si>
     <t xml:space="preserve">1.18816530704498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33017706871033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40118300914764</t>
+    <t xml:space="preserve">1.33017694950104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40118288993835</t>
   </si>
   <si>
     <t xml:space="preserve">1.36331307888031</t>
@@ -1439,22 +1439,22 @@
     <t xml:space="preserve">1.32551181316376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33981597423553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33504796028137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36365604400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32074391841888</t>
+    <t xml:space="preserve">1.33981585502625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33504784107208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36365616321564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32074379920959</t>
   </si>
   <si>
     <t xml:space="preserve">1.35412001609802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34458386898041</t>
+    <t xml:space="preserve">1.3445839881897</t>
   </si>
   <si>
     <t xml:space="preserve">1.40180039405823</t>
@@ -1472,25 +1472,25 @@
     <t xml:space="preserve">1.30167174339294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39226424694061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38272821903229</t>
+    <t xml:space="preserve">1.3922643661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38272833824158</t>
   </si>
   <si>
     <t xml:space="preserve">1.41133642196655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38749635219574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37319207191467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43040859699249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47808873653412</t>
+    <t xml:space="preserve">1.38749623298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37319219112396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4304084777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47808885574341</t>
   </si>
   <si>
     <t xml:space="preserve">1.44471251964569</t>
@@ -1499,43 +1499,43 @@
     <t xml:space="preserve">1.40656840801239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42087244987488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43517649173737</t>
+    <t xml:space="preserve">1.42087256908417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43517661094666</t>
   </si>
   <si>
     <t xml:space="preserve">1.45901668071747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43994450569153</t>
+    <t xml:space="preserve">1.43994462490082</t>
   </si>
   <si>
     <t xml:space="preserve">1.41610443592072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51623296737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50669693946838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53530502319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54484105110168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54007315635681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58298528194427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57344925403595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68788206577301</t>
+    <t xml:space="preserve">1.516233086586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50669705867767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53530514240265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54484117031097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54007303714752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58298540115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57344937324524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68788194656372</t>
   </si>
   <si>
     <t xml:space="preserve">1.65450572967529</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">1.70695412158966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7641704082489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74509847164154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7260262966156</t>
+    <t xml:space="preserve">1.76417052745819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74509835243225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72602605819702</t>
   </si>
   <si>
     <t xml:space="preserve">1.69741809368134</t>
@@ -1559,10 +1559,10 @@
     <t xml:space="preserve">1.66880989074707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67357802391052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64020168781281</t>
+    <t xml:space="preserve">1.67357778549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64020180702209</t>
   </si>
   <si>
     <t xml:space="preserve">1.61159360408783</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">1.6163614988327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62112963199615</t>
+    <t xml:space="preserve">1.62112975120544</t>
   </si>
   <si>
     <t xml:space="preserve">1.63066565990448</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">1.77847456932068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75940251350403</t>
+    <t xml:space="preserve">1.75940239429474</t>
   </si>
   <si>
     <t xml:space="preserve">1.68311393260956</t>
@@ -1613,37 +1613,37 @@
     <t xml:space="preserve">1.82615482807159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79754674434662</t>
+    <t xml:space="preserve">1.79754650592804</t>
   </si>
   <si>
     <t xml:space="preserve">1.788010597229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81661868095398</t>
+    <t xml:space="preserve">1.81661880016327</t>
   </si>
   <si>
     <t xml:space="preserve">1.83092284202576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80708277225494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76893866062164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73556232452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73079442977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74033045768738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72125828266144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78324258327484</t>
+    <t xml:space="preserve">1.80708265304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76893842220306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73556244373322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73079431056976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7403302192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72125816345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78324246406555</t>
   </si>
   <si>
     <t xml:space="preserve">1.7498664855957</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">1.67834603786469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66404175758362</t>
+    <t xml:space="preserve">1.66404187679291</t>
   </si>
   <si>
     <t xml:space="preserve">1.69264996051788</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">1.80231463909149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75463449954987</t>
+    <t xml:space="preserve">1.75463438034058</t>
   </si>
   <si>
     <t xml:space="preserve">1.79277861118317</t>
@@ -1673,70 +1673,70 @@
     <t xml:space="preserve">1.65927386283875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5925213098526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52576911449432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59728944301605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7021861076355</t>
+    <t xml:space="preserve">1.59252142906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52576899528503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59728932380676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70218598842621</t>
   </si>
   <si>
     <t xml:space="preserve">1.85953104496002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89767527580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92628335952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82138681411743</t>
+    <t xml:space="preserve">1.8976753950119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92628347873688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82138669490814</t>
   </si>
   <si>
     <t xml:space="preserve">1.83569085597992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86429905891418</t>
+    <t xml:space="preserve">1.86429917812347</t>
   </si>
   <si>
     <t xml:space="preserve">1.90721130371094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94535553455353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99303567409515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0597882270813</t>
+    <t xml:space="preserve">1.94535541534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99303579330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05978846549988</t>
   </si>
   <si>
     <t xml:space="preserve">2.00257182121277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07886052131653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12654066085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10746836662292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08839631080627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09793257713318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1456127166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27911758422852</t>
+    <t xml:space="preserve">2.07886028289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12654042243958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1074686050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08839654922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0979323387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14561295509338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27911782264709</t>
   </si>
   <si>
     <t xml:space="preserve">2.19329285621643</t>
@@ -1745,13 +1745,13 @@
     <t xml:space="preserve">2.22190117835999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25050902366638</t>
+    <t xml:space="preserve">2.25050926208496</t>
   </si>
   <si>
     <t xml:space="preserve">2.02164387702942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01210761070251</t>
+    <t xml:space="preserve">2.01210784912109</t>
   </si>
   <si>
     <t xml:space="preserve">1.97396349906921</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">1.98349988460541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03118014335632</t>
+    <t xml:space="preserve">2.0311803817749</t>
   </si>
   <si>
     <t xml:space="preserve">2.04071617126465</t>
@@ -1769,13 +1769,13 @@
     <t xml:space="preserve">2.09847211837769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08884620666504</t>
+    <t xml:space="preserve">2.08884644508362</t>
   </si>
   <si>
     <t xml:space="preserve">2.10809826850891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00221180915833</t>
+    <t xml:space="preserve">2.0022120475769</t>
   </si>
   <si>
     <t xml:space="preserve">1.95408189296722</t>
@@ -1787,10 +1787,10 @@
     <t xml:space="preserve">2.0214638710022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05996799468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.944455742836</t>
+    <t xml:space="preserve">2.05996823310852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94445586204529</t>
   </si>
   <si>
     <t xml:space="preserve">1.9733339548111</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">1.93482983112335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85782170295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83856964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82894372940063</t>
+    <t xml:space="preserve">1.85782158374786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83856952190399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82894361019135</t>
   </si>
   <si>
     <t xml:space="preserve">1.86744773387909</t>
@@ -1814,22 +1814,22 @@
     <t xml:space="preserve">1.88669979572296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87707388401031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89632570743561</t>
+    <t xml:space="preserve">1.87707376480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8963258266449</t>
   </si>
   <si>
     <t xml:space="preserve">1.92520380020142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99258589744568</t>
+    <t xml:space="preserve">1.99258577823639</t>
   </si>
   <si>
     <t xml:space="preserve">2.04071593284607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05034208297729</t>
+    <t xml:space="preserve">2.05034232139587</t>
   </si>
   <si>
     <t xml:space="preserve">2.11772418022156</t>
@@ -1844,10 +1844,10 @@
     <t xml:space="preserve">2.16585445404053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14660239219666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07922005653381</t>
+    <t xml:space="preserve">2.14660215377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07922029495239</t>
   </si>
   <si>
     <t xml:space="preserve">2.24286246299744</t>
@@ -1859,13 +1859,13 @@
     <t xml:space="preserve">2.27174043655396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30061841011047</t>
+    <t xml:space="preserve">2.30061888694763</t>
   </si>
   <si>
     <t xml:space="preserve">2.2813663482666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1851065158844</t>
+    <t xml:space="preserve">2.18510627746582</t>
   </si>
   <si>
     <t xml:space="preserve">2.19473242759705</t>
@@ -1880,13 +1880,13 @@
     <t xml:space="preserve">2.01183795928955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87226068973541</t>
+    <t xml:space="preserve">1.8722608089447</t>
   </si>
   <si>
     <t xml:space="preserve">1.96370780467987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06959438323975</t>
+    <t xml:space="preserve">2.06959414482117</t>
   </si>
   <si>
     <t xml:space="preserve">2.17548012733459</t>
@@ -1895,49 +1895,49 @@
     <t xml:space="preserve">2.23323631286621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31024479866028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35837459564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42575693130493</t>
+    <t xml:space="preserve">2.3102445602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35837483406067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42575669288635</t>
   </si>
   <si>
     <t xml:space="preserve">2.39687871932983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40650486946106</t>
+    <t xml:space="preserve">2.40650463104248</t>
   </si>
   <si>
     <t xml:space="preserve">2.43538284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41613078117371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37762665748596</t>
+    <t xml:space="preserve">2.41613101959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37762689590454</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874868392944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29099273681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36800098419189</t>
+    <t xml:space="preserve">2.29099249839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36800050735474</t>
   </si>
   <si>
     <t xml:space="preserve">2.38725280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21398448944092</t>
+    <t xml:space="preserve">2.21398425102234</t>
   </si>
   <si>
     <t xml:space="preserve">2.31987071037292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44500875473022</t>
+    <t xml:space="preserve">2.44500851631165</t>
   </si>
   <si>
     <t xml:space="preserve">2.45463490486145</t>
@@ -1949,13 +1949,13 @@
     <t xml:space="preserve">2.49313902854919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52201676368713</t>
+    <t xml:space="preserve">2.52201700210571</t>
   </si>
   <si>
     <t xml:space="preserve">2.50276470184326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59902501106262</t>
+    <t xml:space="preserve">2.5990252494812</t>
   </si>
   <si>
     <t xml:space="preserve">2.64715528488159</t>
@@ -1964,22 +1964,22 @@
     <t xml:space="preserve">2.54126906394958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51239109039307</t>
+    <t xml:space="preserve">2.51239085197449</t>
   </si>
   <si>
     <t xml:space="preserve">2.47388672828674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48351287841797</t>
+    <t xml:space="preserve">2.48351263999939</t>
   </si>
   <si>
     <t xml:space="preserve">2.53164315223694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63752937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69528532028198</t>
+    <t xml:space="preserve">2.63752913475037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6952850818634</t>
   </si>
   <si>
     <t xml:space="preserve">2.82042360305786</t>
@@ -1991,16 +1991,16 @@
     <t xml:space="preserve">2.67603325843811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60865139961243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66640734672546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5701470375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58939933776855</t>
+    <t xml:space="preserve">2.60865116119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66640710830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57014727592468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58939909934998</t>
   </si>
   <si>
     <t xml:space="preserve">2.56052112579346</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">2.57977318763733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38258790969849</t>
+    <t xml:space="preserve">2.38258814811707</t>
   </si>
   <si>
     <t xml:space="preserve">2.29506421089172</t>
@@ -2024,13 +2024,13 @@
     <t xml:space="preserve">2.28533935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32423877716064</t>
+    <t xml:space="preserve">2.32423901557922</t>
   </si>
   <si>
     <t xml:space="preserve">2.25616478919983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23671531677246</t>
+    <t xml:space="preserve">2.23671507835388</t>
   </si>
   <si>
     <t xml:space="preserve">2.21726560592651</t>
@@ -2042,16 +2042,16 @@
     <t xml:space="preserve">2.34368872642517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26588988304138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3047890663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24643993377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1102921962738</t>
+    <t xml:space="preserve">2.2658896446228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30478882789612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24644017219543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11029243469238</t>
   </si>
   <si>
     <t xml:space="preserve">2.15891647338867</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">2.19781565666199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16864132881165</t>
+    <t xml:space="preserve">2.16864109039307</t>
   </si>
   <si>
     <t xml:space="preserve">2.18809103965759</t>
@@ -2081,16 +2081,16 @@
     <t xml:space="preserve">2.13946676254272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09084272384644</t>
+    <t xml:space="preserve">2.09084248542786</t>
   </si>
   <si>
     <t xml:space="preserve">2.10056734085083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27561450004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08111763000488</t>
+    <t xml:space="preserve">2.27561473846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08111786842346</t>
   </si>
   <si>
     <t xml:space="preserve">1.97414433956146</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">1.98386907577515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9644193649292</t>
+    <t xml:space="preserve">1.96441948413849</t>
   </si>
   <si>
     <t xml:space="preserve">1.94496977329254</t>
@@ -2117,13 +2117,13 @@
     <t xml:space="preserve">2.02276849746704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03249335289001</t>
+    <t xml:space="preserve">2.03249311447144</t>
   </si>
   <si>
     <t xml:space="preserve">2.01304364204407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07139277458191</t>
+    <t xml:space="preserve">2.07139301300049</t>
   </si>
   <si>
     <t xml:space="preserve">2.04221820831299</t>
@@ -2135,76 +2135,79 @@
     <t xml:space="preserve">1.93524491786957</t>
   </si>
   <si>
+    <t xml:space="preserve">1.95469450950623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91579520702362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93038249015808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06166768074036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91093277931213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1491916179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00331878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86717092990875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92552006244659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81854665279388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84772121906281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8866206407547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83313393592834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85258364677429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89634561538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92065763473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95961833000183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96946561336517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01870226860046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96454191207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98916029930115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00885486602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99900758266449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97931289672852</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.95469462871552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91579520702362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93038249015808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06166791915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91093289852142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1491916179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00331878662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86717092990875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92552006244659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81854677200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84772133827209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8866206407547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83313405513763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85258364677429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89634561538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92065763473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95961833000183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96946561336517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01870226860046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96454191207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98916029930115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00885486602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99900758266449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97931289672852</t>
   </si>
   <si>
     <t xml:space="preserve">1.9497709274292</t>
@@ -59500,7 +59503,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2180" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -59526,7 +59529,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2181" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59552,7 +59555,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2182" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59578,7 +59581,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2183" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59682,7 +59685,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2187" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59708,7 +59711,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2188" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59734,7 +59737,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2189" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59760,7 +59763,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2190" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59786,7 +59789,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2191" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59812,7 +59815,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2192" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59838,7 +59841,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2193" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60150,7 +60153,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2205" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60176,7 +60179,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2206" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60202,7 +60205,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2207" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60228,7 +60231,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2208" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60280,7 +60283,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2210" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60306,7 +60309,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2211" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60332,7 +60335,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2212" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60358,7 +60361,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2213" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60384,7 +60387,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2214" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60436,7 +60439,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2216" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60592,7 +60595,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60670,7 +60673,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2225" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60696,7 +60699,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2226" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60748,7 +60751,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2228" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60774,7 +60777,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2229" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60800,7 +60803,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2230" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60826,7 +60829,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2231" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60852,7 +60855,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2232" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60878,7 +60881,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2233" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60904,7 +60907,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2234" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60930,7 +60933,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2235" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60956,7 +60959,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2236" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60982,7 +60985,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2237" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61008,7 +61011,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2238" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61034,7 +61037,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2239" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61060,7 +61063,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2240" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61086,7 +61089,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G2241" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61112,7 +61115,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2242" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61138,7 +61141,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2243" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61164,7 +61167,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G2244" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61190,7 +61193,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2245" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61216,7 +61219,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2246" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61242,7 +61245,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2247" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61268,7 +61271,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2248" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61294,7 +61297,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2249" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61320,7 +61323,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2250" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61346,7 +61349,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2251" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61372,7 +61375,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2252" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61476,7 +61479,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2256" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -61502,7 +61505,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2257" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -61554,7 +61557,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2259" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -61580,7 +61583,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2260" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -61606,7 +61609,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2261" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -61632,7 +61635,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -61658,7 +61661,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2263" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -61710,7 +61713,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2265" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61736,7 +61739,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2266" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61866,7 +61869,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2271" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61892,7 +61895,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2272" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61918,7 +61921,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2273" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61944,7 +61947,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2274" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61970,7 +61973,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2275" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61996,7 +61999,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2276" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62022,7 +62025,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2277" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62048,7 +62051,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2278" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62074,7 +62077,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2279" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62100,7 +62103,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2280" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62126,7 +62129,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2281" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62152,7 +62155,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2282" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62178,7 +62181,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2283" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62204,7 +62207,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2284" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62230,7 +62233,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2285" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62256,7 +62259,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2286" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62282,7 +62285,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2287" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62308,7 +62311,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2288" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62334,7 +62337,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2289" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62360,7 +62363,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2290" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62386,7 +62389,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2291" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62412,7 +62415,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2292" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62438,7 +62441,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2293" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62464,7 +62467,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2294" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -62490,7 +62493,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2295" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -62516,7 +62519,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2296" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -62542,7 +62545,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2297" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -62568,7 +62571,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2298" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -62594,7 +62597,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2299" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -62620,7 +62623,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2300" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -62646,7 +62649,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2301" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -62672,7 +62675,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2302" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -62698,7 +62701,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2303" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62724,7 +62727,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2304" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62750,7 +62753,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2305" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62776,7 +62779,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2306" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62802,7 +62805,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G2307" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62828,7 +62831,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2308" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62854,7 +62857,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2309" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62880,7 +62883,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2310" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62906,7 +62909,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2311" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62932,7 +62935,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G2312" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62958,7 +62961,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2313" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62984,7 +62987,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2314" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63010,7 +63013,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2315" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63036,7 +63039,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2316" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63062,7 +63065,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2317" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63088,7 +63091,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2318" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63114,7 +63117,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2319" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63140,7 +63143,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2320" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63166,7 +63169,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2321" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63192,7 +63195,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2322" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63218,7 +63221,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2323" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63244,7 +63247,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2324" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63270,7 +63273,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2325" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63296,7 +63299,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2326" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63322,7 +63325,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2327" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63348,7 +63351,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2328" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63374,7 +63377,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2329" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63400,7 +63403,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2330" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63426,7 +63429,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2331" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63452,7 +63455,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2332" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63478,7 +63481,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2333" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -63504,7 +63507,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2334" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -63530,7 +63533,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2335" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -63556,7 +63559,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2336" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -63582,7 +63585,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2337" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -63608,7 +63611,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2338" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -63634,7 +63637,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2339" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -63660,7 +63663,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G2340" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -63686,7 +63689,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2341" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63712,7 +63715,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2342" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63738,7 +63741,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63764,7 +63767,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2344" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63790,7 +63793,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2345" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63816,7 +63819,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2346" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63842,7 +63845,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2347" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63868,7 +63871,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63894,7 +63897,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63920,7 +63923,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2350" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63946,7 +63949,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2351" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63972,7 +63975,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G2352" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63998,7 +64001,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2353" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64024,7 +64027,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2354" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64050,7 +64053,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2355" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64076,7 +64079,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2356" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64102,7 +64105,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G2357" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64128,7 +64131,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2358" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64154,7 +64157,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G2359" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64180,7 +64183,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G2360" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64206,7 +64209,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2361" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64232,7 +64235,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2362" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64258,7 +64261,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2363" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64284,7 +64287,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G2364" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64310,7 +64313,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2365" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64336,7 +64339,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64362,7 +64365,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G2367" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64388,7 +64391,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2368" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64414,7 +64417,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2369" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64440,7 +64443,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2370" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64466,7 +64469,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2371" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64492,7 +64495,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2372" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -64518,7 +64521,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2373" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -64544,7 +64547,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G2374" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -64570,7 +64573,7 @@
         <v>1.625</v>
       </c>
       <c r="G2375" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -64596,7 +64599,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G2376" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -64622,7 +64625,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G2377" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -64648,7 +64651,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2378" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -64674,7 +64677,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G2379" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -64700,7 +64703,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2380" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64726,7 +64729,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2381" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64752,7 +64755,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2382" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64778,7 +64781,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G2383" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64804,7 +64807,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2384" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64830,7 +64833,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G2385" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64856,7 +64859,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64882,7 +64885,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2387" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64908,7 +64911,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2388" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64934,7 +64937,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64960,7 +64963,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2390" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64986,7 +64989,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2391" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65012,7 +65015,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2392" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65038,7 +65041,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G2393" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65064,7 +65067,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G2394" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65090,7 +65093,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2395" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65116,7 +65119,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2396" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65142,7 +65145,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2397" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65168,7 +65171,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2398" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65194,7 +65197,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2399" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65220,7 +65223,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2400" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65246,7 +65249,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2401" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65272,7 +65275,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2402" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65298,7 +65301,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2403" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65324,7 +65327,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2404" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65350,7 +65353,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2405" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65376,7 +65379,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2406" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65428,7 +65431,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2408" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65454,7 +65457,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2409" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65480,7 +65483,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2410" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -65506,7 +65509,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2411" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65532,7 +65535,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2412" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65558,7 +65561,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G2413" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65584,7 +65587,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2414" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65610,7 +65613,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2415" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65636,7 +65639,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2416" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65662,7 +65665,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2417" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65688,7 +65691,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2418" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65714,7 +65717,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2419" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65740,7 +65743,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2420" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65766,7 +65769,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2421" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65792,7 +65795,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65818,7 +65821,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2423" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65844,7 +65847,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2424" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65870,7 +65873,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2425" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65896,7 +65899,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2426" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65922,7 +65925,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2427" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65948,7 +65951,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2428" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65974,7 +65977,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2429" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66000,7 +66003,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2430" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66026,7 +66029,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2431" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66052,7 +66055,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2432" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66078,7 +66081,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2433" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66104,7 +66107,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2434" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66130,7 +66133,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2435" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66156,7 +66159,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2436" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66182,7 +66185,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2437" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66208,7 +66211,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2438" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66234,7 +66237,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2439" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66260,7 +66263,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2440" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66286,7 +66289,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2441" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66312,7 +66315,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2442" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66338,7 +66341,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2443" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66364,7 +66367,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2444" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66390,7 +66393,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2445" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66416,7 +66419,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2446" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66442,7 +66445,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2447" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66468,7 +66471,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2448" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -66494,7 +66497,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2449" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -66520,7 +66523,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2450" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66546,7 +66549,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2451" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66572,7 +66575,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2452" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66598,7 +66601,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2453" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66624,7 +66627,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2454" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66650,7 +66653,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2455" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66676,7 +66679,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2456" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66702,7 +66705,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2457" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66728,7 +66731,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2458" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66754,7 +66757,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2459" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66780,7 +66783,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2460" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66806,7 +66809,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2461" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66832,7 +66835,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2462" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66858,7 +66861,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2463" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66884,7 +66887,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2464" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66910,7 +66913,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2465" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66936,7 +66939,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2466" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66962,7 +66965,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2467" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66988,7 +66991,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2468" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67014,7 +67017,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2469" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67040,7 +67043,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2470" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67066,7 +67069,7 @@
         <v>2</v>
       </c>
       <c r="G2471" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67092,7 +67095,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2472" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67118,7 +67121,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2473" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67144,7 +67147,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2474" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67170,7 +67173,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2475" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67196,7 +67199,7 @@
         <v>2</v>
       </c>
       <c r="G2476" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67222,7 +67225,7 @@
         <v>2</v>
       </c>
       <c r="G2477" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67248,7 +67251,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2478" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67274,7 +67277,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2479" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67300,7 +67303,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2480" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67326,7 +67329,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2481" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67352,7 +67355,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2482" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67378,7 +67381,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2483" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67404,7 +67407,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2484" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67430,7 +67433,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2485" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67456,7 +67459,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2486" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67482,7 +67485,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2487" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -67508,7 +67511,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2488" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67534,7 +67537,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2489" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67560,7 +67563,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2490" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67586,7 +67589,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2491" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67612,7 +67615,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2492" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67638,7 +67641,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G2493" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67664,7 +67667,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2494" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67690,7 +67693,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2495" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67716,7 +67719,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2496" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67742,7 +67745,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2497" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67768,7 +67771,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2498" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67794,7 +67797,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2499" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67820,7 +67823,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2500" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67846,7 +67849,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2501" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67872,7 +67875,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2502" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -67898,7 +67901,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2503" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -67924,7 +67927,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G2504" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67950,7 +67953,7 @@
         <v>2</v>
       </c>
       <c r="G2505" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67976,7 +67979,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2506" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68002,7 +68005,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2507" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68028,7 +68031,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2508" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68054,7 +68057,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2509" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68080,7 +68083,7 @@
         <v>2</v>
       </c>
       <c r="G2510" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68106,7 +68109,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2511" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68132,7 +68135,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2512" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68158,7 +68161,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2513" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -68184,7 +68187,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2514" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -68210,7 +68213,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2515" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -68236,7 +68239,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2516" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -68262,7 +68265,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2517" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -68288,7 +68291,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2518" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -68314,7 +68317,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2519" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -68340,7 +68343,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G2520" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -68366,7 +68369,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G2521" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -68392,7 +68395,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G2522" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -68418,7 +68421,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2523" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -68444,7 +68447,7 @@
         <v>2</v>
       </c>
       <c r="G2524" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -68470,7 +68473,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2525" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -68496,7 +68499,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2526" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -68522,7 +68525,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2527" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -68548,7 +68551,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2528" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -68574,7 +68577,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2529" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -68600,7 +68603,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2530" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -68626,7 +68629,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2531" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -68652,7 +68655,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2532" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -68678,7 +68681,7 @@
         <v>2</v>
       </c>
       <c r="G2533" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -68704,7 +68707,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G2534" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -68730,7 +68733,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G2535" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -68756,7 +68759,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G2536" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -68782,7 +68785,7 @@
         <v>2</v>
       </c>
       <c r="G2537" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2537" t="s">
         <v>9</v>
@@ -68808,7 +68811,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2538" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2538" t="s">
         <v>9</v>
@@ -68834,7 +68837,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2539" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2539" t="s">
         <v>9</v>
@@ -68860,7 +68863,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2540" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2540" t="s">
         <v>9</v>
@@ -68886,7 +68889,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2541" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2541" t="s">
         <v>9</v>
@@ -68912,7 +68915,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2542" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2542" t="s">
         <v>9</v>
@@ -68938,7 +68941,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2543" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2543" t="s">
         <v>9</v>
@@ -68946,7 +68949,7 @@
     </row>
     <row r="2544">
       <c r="A2544" s="1" t="n">
-        <v>46028.6349884259</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B2544" t="n">
         <v>18500</v>
@@ -68964,9 +68967,35 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2544" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2544" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" s="1" t="n">
+        <v>46029.3614814815</v>
+      </c>
+      <c r="B2545" t="n">
+        <v>5500</v>
+      </c>
+      <c r="C2545" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2545" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="E2545" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="F2545" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2545" t="s">
+        <v>818</v>
+      </c>
+      <c r="H2545" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DGT.MI.xlsx
+++ b/data/DGT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08123874664307</t>
+    <t xml:space="preserve">2.08123898506165</t>
   </si>
   <si>
     <t xml:space="preserve">DGT.MI</t>
@@ -56,34 +56,34 @@
     <t xml:space="preserve">2.00509595870972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04860591888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99421858787537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97971510887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94889557361603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88544297218323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91444945335388</t>
+    <t xml:space="preserve">2.04860639572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99421870708466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97971498966217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94889545440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88544285297394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91444981098175</t>
   </si>
   <si>
     <t xml:space="preserve">1.89632046222687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87637829780579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9706506729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92714023590088</t>
+    <t xml:space="preserve">1.8763781785965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97065019607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92714011669159</t>
   </si>
   <si>
     <t xml:space="preserve">1.93076622486115</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">1.85824906826019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80839347839355</t>
+    <t xml:space="preserve">1.80839359760284</t>
   </si>
   <si>
     <t xml:space="preserve">1.8256162405014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75128626823425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64704298973083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75581872463226</t>
+    <t xml:space="preserve">1.75128638744354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64704310894012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75581884384155</t>
   </si>
   <si>
     <t xml:space="preserve">1.71321487426758</t>
@@ -116,58 +116,58 @@
     <t xml:space="preserve">1.73134422302246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76760268211365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72862470149994</t>
+    <t xml:space="preserve">1.76760280132294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72862493991852</t>
   </si>
   <si>
     <t xml:space="preserve">1.75853824615479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81292569637299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83105516433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7685090303421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6751434803009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74947345256805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69871151447296</t>
+    <t xml:space="preserve">1.81292581558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83105528354645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76850914955139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67514359951019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74947321414948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69871163368225</t>
   </si>
   <si>
     <t xml:space="preserve">1.74766051769257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7077761888504</t>
+    <t xml:space="preserve">1.70777606964111</t>
   </si>
   <si>
     <t xml:space="preserve">1.70868253707886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69508576393127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7766672372818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70143091678619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69055330753326</t>
+    <t xml:space="preserve">1.6950855255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77666747570038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70143103599548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69055354595184</t>
   </si>
   <si>
     <t xml:space="preserve">1.73496997356415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64069783687592</t>
+    <t xml:space="preserve">1.64069771766663</t>
   </si>
   <si>
     <t xml:space="preserve">1.62982022762299</t>
@@ -176,25 +176,25 @@
     <t xml:space="preserve">1.63163328170776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68692743778229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68602085113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6733306646347</t>
+    <t xml:space="preserve">1.686927318573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68602108955383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67333042621613</t>
   </si>
   <si>
     <t xml:space="preserve">1.74040877819061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70415031909943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75672507286072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68783390522003</t>
+    <t xml:space="preserve">1.70415043830872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75672519207001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68783402442932</t>
   </si>
   <si>
     <t xml:space="preserve">1.64885604381561</t>
@@ -203,28 +203,28 @@
     <t xml:space="preserve">1.64794957637787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68420827388763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72137320041656</t>
+    <t xml:space="preserve">1.68420815467834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72137308120728</t>
   </si>
   <si>
     <t xml:space="preserve">1.72227942943573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67786276340485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63253962993622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66335952281952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66517233848572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65429496765137</t>
+    <t xml:space="preserve">1.67786300182343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63253974914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66335964202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66517221927643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65429484844208</t>
   </si>
   <si>
     <t xml:space="preserve">1.81111299991608</t>
@@ -236,19 +236,19 @@
     <t xml:space="preserve">1.78754484653473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7893580198288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66154634952545</t>
+    <t xml:space="preserve">1.78935766220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66154646873474</t>
   </si>
   <si>
     <t xml:space="preserve">1.69961798191071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66245305538177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68330156803131</t>
+    <t xml:space="preserve">1.66245293617249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6833016872406</t>
   </si>
   <si>
     <t xml:space="preserve">1.6588271856308</t>
@@ -260,28 +260,28 @@
     <t xml:space="preserve">1.569087266922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58902943134308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48297345638275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49566376209259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4920380115509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53192234039307</t>
+    <t xml:space="preserve">1.58902931213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48297333717346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49566388130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49203813076019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53192245960236</t>
   </si>
   <si>
     <t xml:space="preserve">1.48387980461121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45215356349945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48569285869598</t>
+    <t xml:space="preserve">1.45215368270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4856926202774</t>
   </si>
   <si>
     <t xml:space="preserve">1.42858564853668</t>
@@ -290,16 +290,16 @@
     <t xml:space="preserve">1.45940518379211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49294447898865</t>
+    <t xml:space="preserve">1.49294435977936</t>
   </si>
   <si>
     <t xml:space="preserve">1.46031165122986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4412761926651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45034074783325</t>
+    <t xml:space="preserve">1.44127607345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45034062862396</t>
   </si>
   <si>
     <t xml:space="preserve">1.46846985816956</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">1.42586624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31255829334259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36422657966614</t>
+    <t xml:space="preserve">1.31255841255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36422681808472</t>
   </si>
   <si>
     <t xml:space="preserve">1.34156513214111</t>
@@ -320,34 +320,34 @@
     <t xml:space="preserve">1.36875891685486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33250057697296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27811253070831</t>
+    <t xml:space="preserve">1.33250045776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27811276912689</t>
   </si>
   <si>
     <t xml:space="preserve">1.19653105735779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17296302318573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18746638298035</t>
+    <t xml:space="preserve">1.17296314239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18746650218964</t>
   </si>
   <si>
     <t xml:space="preserve">1.17568242549896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15483391284943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09863305091858</t>
+    <t xml:space="preserve">1.15483379364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09863317012787</t>
   </si>
   <si>
     <t xml:space="preserve">1.12401413917542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13307857513428</t>
+    <t xml:space="preserve">1.13307869434357</t>
   </si>
   <si>
     <t xml:space="preserve">1.12582683563232</t>
@@ -356,13 +356,13 @@
     <t xml:space="preserve">1.11313652992249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06962621212006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08684897422791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0950071811676</t>
+    <t xml:space="preserve">1.06962609291077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08684909343719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09500730037689</t>
   </si>
   <si>
     <t xml:space="preserve">1.09410071372986</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">1.10769760608673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10951054096222</t>
+    <t xml:space="preserve">1.10951066017151</t>
   </si>
   <si>
     <t xml:space="preserve">1.12129473686218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09682011604309</t>
+    <t xml:space="preserve">1.09682023525238</t>
   </si>
   <si>
     <t xml:space="preserve">1.08956849575043</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">1.07234561443329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05149674415588</t>
+    <t xml:space="preserve">1.05149698257446</t>
   </si>
   <si>
     <t xml:space="preserve">1.12310755252838</t>
@@ -413,10 +413,10 @@
     <t xml:space="preserve">1.11404287815094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15120780467987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21466028690338</t>
+    <t xml:space="preserve">1.15120792388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21466040611267</t>
   </si>
   <si>
     <t xml:space="preserve">1.1847470998764</t>
@@ -428,22 +428,22 @@
     <t xml:space="preserve">1.12220120429993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0623744726181</t>
+    <t xml:space="preserve">1.06237459182739</t>
   </si>
   <si>
     <t xml:space="preserve">1.03336775302887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.934563219547272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945440828800201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.977166950702667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956318318843842</t>
+    <t xml:space="preserve">0.934563279151917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945440769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977166891098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956318378448486</t>
   </si>
   <si>
     <t xml:space="preserve">0.933656752109528</t>
@@ -452,37 +452,37 @@
     <t xml:space="preserve">1.01523840427399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04877746105194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03608727455139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02430295944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990764081478119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05059063434601</t>
+    <t xml:space="preserve">1.04877769947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03608703613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02430319786072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990764021873474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05059051513672</t>
   </si>
   <si>
     <t xml:space="preserve">1.11494946479797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12854635715485</t>
+    <t xml:space="preserve">1.12854623794556</t>
   </si>
   <si>
     <t xml:space="preserve">1.07506501674652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06418764591217</t>
+    <t xml:space="preserve">1.06418740749359</t>
   </si>
   <si>
     <t xml:space="preserve">1.02067732810974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997109293937683</t>
+    <t xml:space="preserve">0.997109353542328</t>
   </si>
   <si>
     <t xml:space="preserve">1.00617384910583</t>
@@ -494,19 +494,19 @@
     <t xml:space="preserve">1.03880655765533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05965507030487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04243218898773</t>
+    <t xml:space="preserve">1.05965518951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04243230819702</t>
   </si>
   <si>
     <t xml:space="preserve">1.06328105926514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05693566799164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10407173633575</t>
+    <t xml:space="preserve">1.05693590641022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10407185554504</t>
   </si>
   <si>
     <t xml:space="preserve">1.1049782037735</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">1.07597160339355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12492048740387</t>
+    <t xml:space="preserve">1.12492072582245</t>
   </si>
   <si>
     <t xml:space="preserve">1.1031653881073</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">1.2110344171524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19562458992004</t>
+    <t xml:space="preserve">1.19562470912933</t>
   </si>
   <si>
     <t xml:space="preserve">1.21284747123718</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">1.14667558670044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15392732620239</t>
+    <t xml:space="preserve">1.1539272069931</t>
   </si>
   <si>
     <t xml:space="preserve">1.20559573173523</t>
@@ -545,22 +545,22 @@
     <t xml:space="preserve">1.23188304901123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25363838672638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25817036628723</t>
+    <t xml:space="preserve">1.25363826751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25817048549652</t>
   </si>
   <si>
     <t xml:space="preserve">1.26089000701904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25545120239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28717744350433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30893242359161</t>
+    <t xml:space="preserve">1.25545108318329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28717732429504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30893230438232</t>
   </si>
   <si>
     <t xml:space="preserve">1.30530655384064</t>
@@ -578,97 +578,97 @@
     <t xml:space="preserve">1.35244262218475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35697495937347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35969424247742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34065866470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32343590259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35062968730927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3288745880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26995468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19471800327301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14395606517792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24548006057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25001239776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26814162731171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23278963565826</t>
+    <t xml:space="preserve">1.35697484016418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35969436168671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34065854549408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32343602180481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35062992572784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32887470722198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26995456218719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1947181224823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14395618438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24548017978668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25001227855682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26814150810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23278951644897</t>
   </si>
   <si>
     <t xml:space="preserve">1.24185419082642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28173863887787</t>
+    <t xml:space="preserve">1.28173851966858</t>
   </si>
   <si>
     <t xml:space="preserve">1.26451575756073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28264498710632</t>
+    <t xml:space="preserve">1.28264486789703</t>
   </si>
   <si>
     <t xml:space="preserve">1.25091886520386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26904797554016</t>
+    <t xml:space="preserve">1.26904809474945</t>
   </si>
   <si>
     <t xml:space="preserve">1.33159399032593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29624211788177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28536415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31437134742737</t>
+    <t xml:space="preserve">1.2962418794632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28536438941956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31437110900879</t>
   </si>
   <si>
     <t xml:space="preserve">1.30983901023865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31799709796906</t>
+    <t xml:space="preserve">1.31799721717834</t>
   </si>
   <si>
     <t xml:space="preserve">1.29896140098572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37782371044159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33522009849548</t>
+    <t xml:space="preserve">1.37782382965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33521997928619</t>
   </si>
   <si>
     <t xml:space="preserve">1.2617963552475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31074523925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3071197271347</t>
+    <t xml:space="preserve">1.3107453584671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30711960792542</t>
   </si>
   <si>
     <t xml:space="preserve">1.34247159957886</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">1.33884572982788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31165194511414</t>
+    <t xml:space="preserve">1.31165182590485</t>
   </si>
   <si>
     <t xml:space="preserve">1.2799254655838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30621302127838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31618404388428</t>
+    <t xml:space="preserve">1.30621290206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31618416309357</t>
   </si>
   <si>
     <t xml:space="preserve">1.30349373817444</t>
@@ -704,19 +704,19 @@
     <t xml:space="preserve">1.26632869243622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28355133533478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25907731056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24910604953766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27539324760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25273168087006</t>
+    <t xml:space="preserve">1.28355157375336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25907707214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24910593032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27539336681366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25273180007935</t>
   </si>
   <si>
     <t xml:space="preserve">1.34700381755829</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">1.34972333908081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29261612892151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32978105545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23369598388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22372496128082</t>
+    <t xml:space="preserve">1.29261600971222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32978117465973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23369610309601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22372508049011</t>
   </si>
   <si>
     <t xml:space="preserve">1.229163646698</t>
@@ -746,19 +746,19 @@
     <t xml:space="preserve">1.22191202640533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21919274330139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22100555896759</t>
+    <t xml:space="preserve">1.2191926240921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22100567817688</t>
   </si>
   <si>
     <t xml:space="preserve">1.21828615665436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22463142871857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21012806892395</t>
+    <t xml:space="preserve">1.22463130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21012794971466</t>
   </si>
   <si>
     <t xml:space="preserve">1.1865599155426</t>
@@ -770,43 +770,43 @@
     <t xml:space="preserve">1.17840158939362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15211451053619</t>
+    <t xml:space="preserve">1.1521143913269</t>
   </si>
   <si>
     <t xml:space="preserve">1.15845954418182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08594250679016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10588479042053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07959723472595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10679125785828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13217234611511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16933703422546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22644436359406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23822844028473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24457371234894</t>
+    <t xml:space="preserve">1.08594262599945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10588467121124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07959711551666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10679113864899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13217198848724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16933715343475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22644448280334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23822832107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24457359313965</t>
   </si>
   <si>
     <t xml:space="preserve">1.25182545185089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24004125595093</t>
+    <t xml:space="preserve">1.24004137516022</t>
   </si>
   <si>
     <t xml:space="preserve">1.20378267765045</t>
@@ -818,28 +818,28 @@
     <t xml:space="preserve">1.24094760417938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23097658157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21194100379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23460245132446</t>
+    <t xml:space="preserve">1.23097670078278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21194088459015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23460257053375</t>
   </si>
   <si>
     <t xml:space="preserve">1.24638652801514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2762998342514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27086102962494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29805505275726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22553777694702</t>
+    <t xml:space="preserve">1.27629971504211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27086091041565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29805493354797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2255380153656</t>
   </si>
   <si>
     <t xml:space="preserve">1.15574014186859</t>
@@ -848,10 +848,10 @@
     <t xml:space="preserve">1.11857521533966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1602725982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16661775112152</t>
+    <t xml:space="preserve">1.16027247905731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16661763191223</t>
   </si>
   <si>
     <t xml:space="preserve">1.16480481624603</t>
@@ -863,22 +863,22 @@
     <t xml:space="preserve">1.19925045967102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11676228046417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09319400787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09772658348083</t>
+    <t xml:space="preserve">1.11676239967346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09319424629211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09772670269012</t>
   </si>
   <si>
     <t xml:space="preserve">1.17658889293671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17930817604065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21375381946564</t>
+    <t xml:space="preserve">1.17930829524994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21375393867493</t>
   </si>
   <si>
     <t xml:space="preserve">1.21556675434113</t>
@@ -887,22 +887,22 @@
     <t xml:space="preserve">1.28627097606659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28989684581757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2844580411911</t>
+    <t xml:space="preserve">1.28989672660828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28445792198181</t>
   </si>
   <si>
     <t xml:space="preserve">1.38960766792297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4004852771759</t>
+    <t xml:space="preserve">1.40048515796661</t>
   </si>
   <si>
     <t xml:space="preserve">1.41408216953278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38235604763031</t>
+    <t xml:space="preserve">1.38235569000244</t>
   </si>
   <si>
     <t xml:space="preserve">1.37057185173035</t>
@@ -914,88 +914,88 @@
     <t xml:space="preserve">1.36513328552246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35516214370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38416886329651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42224025726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38054311275482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38870131969452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36694598197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40773689746857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39957880973816</t>
+    <t xml:space="preserve">1.35516202449799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38416874408722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42224037647247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38054299354553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38870120048523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36694610118866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40773701667786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39957892894745</t>
   </si>
   <si>
     <t xml:space="preserve">1.39685940742493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38326263427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38688826560974</t>
+    <t xml:space="preserve">1.38326239585876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38688814640045</t>
   </si>
   <si>
     <t xml:space="preserve">1.50926077365875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57724559307098</t>
+    <t xml:space="preserve">1.57724547386169</t>
   </si>
   <si>
     <t xml:space="preserve">1.57271313667297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54551923274994</t>
+    <t xml:space="preserve">1.54551935195923</t>
   </si>
   <si>
     <t xml:space="preserve">1.55005168914795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51379311084747</t>
+    <t xml:space="preserve">1.51379299163818</t>
   </si>
   <si>
     <t xml:space="preserve">1.48659908771515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44580841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48206698894501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43221139907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5409871339798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52285766601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52739012241364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37329125404358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39142060279846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34609746932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29170966148376</t>
+    <t xml:space="preserve">1.44580852985382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48206686973572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43221151828766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54098689556122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52285754680634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52739000320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37329137325287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39142072200775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34609735012054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29170978069305</t>
   </si>
   <si>
     <t xml:space="preserve">1.3189035654068</t>
@@ -1007,10 +1007,10 @@
     <t xml:space="preserve">1.27358043193817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39595282077789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30077433586121</t>
+    <t xml:space="preserve">1.3959527015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30077421665192</t>
   </si>
   <si>
     <t xml:space="preserve">1.33341014385223</t>
@@ -1019,289 +1019,286 @@
     <t xml:space="preserve">1.3147611618042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30543649196625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31942331790924</t>
+    <t xml:space="preserve">1.30543661117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31942319869995</t>
   </si>
   <si>
     <t xml:space="preserve">1.24482703208923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24948930740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23084020614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21219110488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2541515827179</t>
+    <t xml:space="preserve">1.24948942661285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23084044456482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21219098567963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25415146350861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23550260066986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22617793083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19354200363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19820415973663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24016463756561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27280068397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29611206054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31009888648987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32874798774719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28212535381317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2681382894516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21685326099396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18887972831726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16556835174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20286655426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17489290237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1795551776886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20752894878387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32408571243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34739708900452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17023074626923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14691936969757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13293254375458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25881385803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746284008026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22151577472687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15624392032623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18421745300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28678750991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16090607643127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1515816450119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13759458065033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36138379573822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29144978523254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3427346944809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33807253837585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11428344249725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10495865345001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14225709438324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27810609340668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29230725765228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37278056144714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34437811374664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32544314861298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30177474021912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55266213417053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41065037250519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31124210357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31597578525543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28757345676422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30650854110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33964431285858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42011773586273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40591645240784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35384559631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39644908905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32070958614349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33491063117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28283977508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27337229251862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26390492916107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2591712474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29704093933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24497008323669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23076868057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22130131721497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2165675163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22603499889374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24023616313934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21183383464813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26863873004913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20710015296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24970388412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25443756580353</t>
   </si>
   <si>
     <t xml:space="preserve">1.23550248146057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22617793083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19354212284088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19820415973663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2401647567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27280068397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29611217975616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31009888648987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3287478685379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28212535381317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26813852787018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3007744550705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21685338020325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18887972831726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1655684709549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20286643505096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17489290237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1795551776886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20752894878387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32408559322357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34739696979523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17023086547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14691925048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.132932305336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25881397724152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746295928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22151565551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15624392032623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18421733379364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28678750991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16090607643127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15158176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13759469985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36138379573822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29144966602325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34273481369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33807241916656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11428344249725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1049587726593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14225709438324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27810609340668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29230725765228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37278056144714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34437811374664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32544326782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30177474021912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55266213417053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41065049171448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31124198436737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31597578525543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28757345676422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30650842189789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33964443206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42011773586273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40591669082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35384559631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39644908905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32070958614349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3349107503891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28283965587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27337217330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26390504837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25917112827301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29704093933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2449699640274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2307687997818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22130119800568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2165675163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22603511810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24023628234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21183383464813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26863873004913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20710015296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24970364570618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25443744659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23550236225128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16923034191132</t>
+    <t xml:space="preserve">1.16923046112061</t>
   </si>
   <si>
     <t xml:space="preserve">1.18343150615692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2023663520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1408280134201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12189292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11715936660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10295820236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06982207298279</t>
+    <t xml:space="preserve">1.20236647129059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14082813262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12189304828644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11715924739838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10295808315277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0698219537735</t>
   </si>
   <si>
     <t xml:space="preserve">1.01775109767914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989348709583282</t>
+    <t xml:space="preserve">0.989348649978638</t>
   </si>
   <si>
     <t xml:space="preserve">0.979881227016449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965680122375488</t>
+    <t xml:space="preserve">0.965680062770844</t>
   </si>
   <si>
     <t xml:space="preserve">0.914555907249451</t>
@@ -1322,19 +1319,19 @@
     <t xml:space="preserve">0.946745216846466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.956212639808655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0224848985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07928955554962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10769188404083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13609421253204</t>
+    <t xml:space="preserve">0.9562126994133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02248477935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07928967475891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10769200325012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13609433174133</t>
   </si>
   <si>
     <t xml:space="preserve">1.05562078952789</t>
@@ -1349,43 +1346,43 @@
     <t xml:space="preserve">1.06508839130402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07455575466156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04615342617035</t>
+    <t xml:space="preserve">1.07455587387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04615354537964</t>
   </si>
   <si>
     <t xml:space="preserve">1.03668606281281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04141974449158</t>
+    <t xml:space="preserve">1.04141962528229</t>
   </si>
   <si>
     <t xml:space="preserve">1.1124255657196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12662672996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08875691890717</t>
+    <t xml:space="preserve">1.1266268491745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08875703811646</t>
   </si>
   <si>
     <t xml:space="preserve">1.098224401474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05088710784912</t>
+    <t xml:space="preserve">1.05088722705841</t>
   </si>
   <si>
     <t xml:space="preserve">1.03195238113403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02721858024597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17869782447815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15976285934448</t>
+    <t xml:space="preserve">1.02721881866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17869770526886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15976297855377</t>
   </si>
   <si>
     <t xml:space="preserve">1.15029549598694</t>
@@ -1394,7 +1391,7 @@
     <t xml:space="preserve">1.16449654102325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15502917766571</t>
+    <t xml:space="preserve">1.155029296875</t>
   </si>
   <si>
     <t xml:space="preserve">1.14556181430817</t>
@@ -1403,13 +1400,13 @@
     <t xml:space="preserve">1.17396414279938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13136065006256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0840231180191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00828373432159</t>
+    <t xml:space="preserve">1.13136053085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08402323722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0082836151123</t>
   </si>
   <si>
     <t xml:space="preserve">0.984615087509155</t>
@@ -1418,7 +1415,7 @@
     <t xml:space="preserve">0.994082391262054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01301741600037</t>
+    <t xml:space="preserve">1.01301753520966</t>
   </si>
   <si>
     <t xml:space="preserve">1.18816530704498</t>
@@ -1433,7 +1430,10 @@
     <t xml:space="preserve">1.36331307888031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33027994632721</t>
+    <t xml:space="preserve">1.33027982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31597590446472</t>
   </si>
   <si>
     <t xml:space="preserve">1.32551181316376</t>
@@ -1445,100 +1445,100 @@
     <t xml:space="preserve">1.33504784107208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36365616321564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32074379920959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35412001609802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3445839881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40180039405823</t>
+    <t xml:space="preserve">1.36365604400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32074391841888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35411989688873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34458386898041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40180027484894</t>
   </si>
   <si>
     <t xml:space="preserve">1.36842405796051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34935200214386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35888803005219</t>
+    <t xml:space="preserve">1.34935188293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3588879108429</t>
   </si>
   <si>
     <t xml:space="preserve">1.30167174339294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3922643661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38272833824158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41133642196655</t>
+    <t xml:space="preserve">1.39226424694061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38272821903229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41133630275726</t>
   </si>
   <si>
     <t xml:space="preserve">1.38749623298645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37319219112396</t>
+    <t xml:space="preserve">1.37319207191467</t>
   </si>
   <si>
     <t xml:space="preserve">1.4304084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47808885574341</t>
+    <t xml:space="preserve">1.47808873653412</t>
   </si>
   <si>
     <t xml:space="preserve">1.44471251964569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40656840801239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42087256908417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43517661094666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45901668071747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43994462490082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41610443592072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.516233086586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50669705867767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53530514240265</t>
+    <t xml:space="preserve">1.4065682888031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42087244987488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43517649173737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45901656150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43994450569153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41610431671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51623296737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50669693946838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53530502319336</t>
   </si>
   <si>
     <t xml:space="preserve">1.54484117031097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54007303714752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58298540115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57344937324524</t>
+    <t xml:space="preserve">1.54007315635681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58298528194427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57344925403595</t>
   </si>
   <si>
     <t xml:space="preserve">1.68788194656372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65450572967529</t>
+    <t xml:space="preserve">1.65450584888458</t>
   </si>
   <si>
     <t xml:space="preserve">1.70695412158966</t>
@@ -1550,19 +1550,19 @@
     <t xml:space="preserve">1.74509835243225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72602605819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69741809368134</t>
+    <t xml:space="preserve">1.72602617740631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69741797447205</t>
   </si>
   <si>
     <t xml:space="preserve">1.66880989074707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67357778549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64020180702209</t>
+    <t xml:space="preserve">1.67357790470123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64020168781281</t>
   </si>
   <si>
     <t xml:space="preserve">1.61159360408783</t>
@@ -1577,13 +1577,13 @@
     <t xml:space="preserve">1.71172201633453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64496970176697</t>
+    <t xml:space="preserve">1.64496982097626</t>
   </si>
   <si>
     <t xml:space="preserve">1.6163614988327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62112975120544</t>
+    <t xml:space="preserve">1.62112963199615</t>
   </si>
   <si>
     <t xml:space="preserve">1.63066565990448</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">1.77847456932068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75940239429474</t>
+    <t xml:space="preserve">1.75940251350403</t>
   </si>
   <si>
     <t xml:space="preserve">1.68311393260956</t>
@@ -1607,13 +1607,13 @@
     <t xml:space="preserve">1.77370655536652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81185066699982</t>
+    <t xml:space="preserve">1.81185078620911</t>
   </si>
   <si>
     <t xml:space="preserve">1.82615482807159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79754650592804</t>
+    <t xml:space="preserve">1.79754662513733</t>
   </si>
   <si>
     <t xml:space="preserve">1.788010597229</t>
@@ -1628,28 +1628,28 @@
     <t xml:space="preserve">1.80708265304565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76893842220306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73556244373322</t>
+    <t xml:space="preserve">1.76893854141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73556232452393</t>
   </si>
   <si>
     <t xml:space="preserve">1.73079431056976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7403302192688</t>
+    <t xml:space="preserve">1.74033033847809</t>
   </si>
   <si>
     <t xml:space="preserve">1.72125816345215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78324246406555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7498664855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67834603786469</t>
+    <t xml:space="preserve">1.78324258327484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74986636638641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6783459186554</t>
   </si>
   <si>
     <t xml:space="preserve">1.66404187679291</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">1.80231463909149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75463438034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79277861118317</t>
+    <t xml:space="preserve">1.75463449954987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79277849197388</t>
   </si>
   <si>
     <t xml:space="preserve">1.56868124008179</t>
@@ -1679,49 +1679,49 @@
     <t xml:space="preserve">1.52576899528503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59728932380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70218598842621</t>
+    <t xml:space="preserve">1.59728944301605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7021861076355</t>
   </si>
   <si>
     <t xml:space="preserve">1.85953104496002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8976753950119</t>
+    <t xml:space="preserve">1.89767527580261</t>
   </si>
   <si>
     <t xml:space="preserve">1.92628347873688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82138669490814</t>
+    <t xml:space="preserve">1.82138681411743</t>
   </si>
   <si>
     <t xml:space="preserve">1.83569085597992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86429917812347</t>
+    <t xml:space="preserve">1.86429905891418</t>
   </si>
   <si>
     <t xml:space="preserve">1.90721130371094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94535541534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99303579330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05978846549988</t>
+    <t xml:space="preserve">1.94535553455353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99303567409515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0597882270813</t>
   </si>
   <si>
     <t xml:space="preserve">2.00257182121277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07886028289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12654042243958</t>
+    <t xml:space="preserve">2.07886052131653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12654066085815</t>
   </si>
   <si>
     <t xml:space="preserve">2.1074686050415</t>
@@ -1730,16 +1730,16 @@
     <t xml:space="preserve">2.08839654922485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0979323387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14561295509338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27911782264709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19329285621643</t>
+    <t xml:space="preserve">2.09793257713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1456127166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27911758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19329309463501</t>
   </si>
   <si>
     <t xml:space="preserve">2.22190117835999</t>
@@ -1754,13 +1754,13 @@
     <t xml:space="preserve">2.01210784912109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97396349906921</t>
+    <t xml:space="preserve">1.9739636182785</t>
   </si>
   <si>
     <t xml:space="preserve">1.98349988460541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0311803817749</t>
+    <t xml:space="preserve">2.03118014335632</t>
   </si>
   <si>
     <t xml:space="preserve">2.04071617126465</t>
@@ -1775,7 +1775,7 @@
     <t xml:space="preserve">2.10809826850891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0022120475769</t>
+    <t xml:space="preserve">2.00221180915833</t>
   </si>
   <si>
     <t xml:space="preserve">1.95408189296722</t>
@@ -1796,13 +1796,13 @@
     <t xml:space="preserve">1.9733339548111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93482983112335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85782158374786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83856952190399</t>
+    <t xml:space="preserve">1.93482971191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85782170295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83856964111328</t>
   </si>
   <si>
     <t xml:space="preserve">1.82894361019135</t>
@@ -1814,19 +1814,19 @@
     <t xml:space="preserve">1.88669979572296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87707376480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8963258266449</t>
+    <t xml:space="preserve">1.87707388401031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89632570743561</t>
   </si>
   <si>
     <t xml:space="preserve">1.92520380020142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99258577823639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04071593284607</t>
+    <t xml:space="preserve">1.99258589744568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04071569442749</t>
   </si>
   <si>
     <t xml:space="preserve">2.05034232139587</t>
@@ -1847,25 +1847,25 @@
     <t xml:space="preserve">2.14660215377808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07922029495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24286246299744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25248837471008</t>
+    <t xml:space="preserve">2.07922005653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24286222457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25248861312866</t>
   </si>
   <si>
     <t xml:space="preserve">2.27174043655396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30061888694763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2813663482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18510627746582</t>
+    <t xml:space="preserve">2.30061864852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28136610984802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1851065158844</t>
   </si>
   <si>
     <t xml:space="preserve">2.19473242759705</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">2.13697624206543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01183795928955</t>
+    <t xml:space="preserve">2.01183772087097</t>
   </si>
   <si>
     <t xml:space="preserve">1.8722608089447</t>
@@ -1901,34 +1901,34 @@
     <t xml:space="preserve">2.35837483406067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42575669288635</t>
+    <t xml:space="preserve">2.42575693130493</t>
   </si>
   <si>
     <t xml:space="preserve">2.39687871932983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40650463104248</t>
+    <t xml:space="preserve">2.40650486946106</t>
   </si>
   <si>
     <t xml:space="preserve">2.43538284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41613101959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37762689590454</t>
+    <t xml:space="preserve">2.41613078117371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37762665748596</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874868392944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29099249839783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36800050735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38725280761719</t>
+    <t xml:space="preserve">2.29099273681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36800074577332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38725304603577</t>
   </si>
   <si>
     <t xml:space="preserve">2.21398425102234</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">2.31987071037292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44500851631165</t>
+    <t xml:space="preserve">2.44500875473022</t>
   </si>
   <si>
     <t xml:space="preserve">2.45463490486145</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">2.63752913475037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6952850818634</t>
+    <t xml:space="preserve">2.69528532028198</t>
   </si>
   <si>
     <t xml:space="preserve">2.82042360305786</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">2.57014727592468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58939909934998</t>
+    <t xml:space="preserve">2.58939933776855</t>
   </si>
   <si>
     <t xml:space="preserve">2.56052112579346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62790322303772</t>
+    <t xml:space="preserve">2.6279034614563</t>
   </si>
   <si>
     <t xml:space="preserve">2.55089521408081</t>
@@ -20165,7 +20165,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G667" t="s">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20451,7 +20451,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G678" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20477,7 +20477,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G679" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20503,7 +20503,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G680" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20529,7 +20529,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G681" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20555,7 +20555,7 @@
         <v>1.25</v>
       </c>
       <c r="G682" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -20581,7 +20581,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G683" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20607,7 +20607,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G684" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20633,7 +20633,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G685" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20659,7 +20659,7 @@
         <v>1.25</v>
       </c>
       <c r="G686" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20789,7 +20789,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G691" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -20841,7 +20841,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G693" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20867,7 +20867,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G694" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -20997,7 +20997,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G699" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21023,7 +21023,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G700" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21049,7 +21049,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G701" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21127,7 +21127,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G704" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21205,7 +21205,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G707" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21231,7 +21231,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G708" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21257,7 +21257,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G709" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21283,7 +21283,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G710" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21309,7 +21309,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G711" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21335,7 +21335,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G712" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21387,7 +21387,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G714" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21413,7 +21413,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G715" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21439,7 +21439,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G716" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21465,7 +21465,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G717" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21569,7 +21569,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G721" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21647,7 +21647,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G724" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21699,7 +21699,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G726" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21725,7 +21725,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G727" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21829,7 +21829,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G731" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21855,7 +21855,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G732" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21907,7 +21907,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G734" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -21933,7 +21933,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G735" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -21959,7 +21959,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G736" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -21985,7 +21985,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G737" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22193,7 +22193,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G745" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22219,7 +22219,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G746" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22297,7 +22297,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G749" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22323,7 +22323,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G750" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22375,7 +22375,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G752" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22401,7 +22401,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G753" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22427,7 +22427,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G754" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22453,7 +22453,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G755" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22479,7 +22479,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G756" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22505,7 +22505,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G757" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22531,7 +22531,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G758" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22557,7 +22557,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G759" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22583,7 +22583,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G760" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22609,7 +22609,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G761" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22635,7 +22635,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G762" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22661,7 +22661,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G763" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22687,7 +22687,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G764" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22713,7 +22713,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G765" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22739,7 +22739,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G766" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -22843,7 +22843,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G770" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22869,7 +22869,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G771" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22895,7 +22895,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G772" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22921,7 +22921,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G773" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22947,7 +22947,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G774" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23129,7 +23129,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G781" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23155,7 +23155,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G782" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23233,7 +23233,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G785" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23259,7 +23259,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G786" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23285,7 +23285,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G787" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23311,7 +23311,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G788" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23337,7 +23337,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G789" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23363,7 +23363,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G790" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23389,7 +23389,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G791" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23415,7 +23415,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G792" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23441,7 +23441,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G793" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23467,7 +23467,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G794" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23493,7 +23493,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G795" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23519,7 +23519,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G796" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23545,7 +23545,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G797" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23571,7 +23571,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G798" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23597,7 +23597,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G799" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23623,7 +23623,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G800" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23675,7 +23675,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G802" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23701,7 +23701,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G803" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23727,7 +23727,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G804" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23805,7 +23805,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G807" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23883,7 +23883,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G810" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23935,7 +23935,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G812" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24013,7 +24013,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G815" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24091,7 +24091,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G818" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24117,7 +24117,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G819" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24169,7 +24169,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G821" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24195,7 +24195,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G822" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24221,7 +24221,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G823" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24247,7 +24247,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G824" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24273,7 +24273,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G825" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24299,7 +24299,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G826" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24325,7 +24325,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G827" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24351,7 +24351,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G828" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24377,7 +24377,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G829" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24403,7 +24403,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G830" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24429,7 +24429,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G831" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24481,7 +24481,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G833" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24507,7 +24507,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G834" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24533,7 +24533,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G835" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24585,7 +24585,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G837" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24611,7 +24611,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G838" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24793,7 +24793,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G845" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24845,7 +24845,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G847" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24871,7 +24871,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G848" t="s">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24923,7 +24923,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G850" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24949,7 +24949,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G851" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25053,7 +25053,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G855" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25079,7 +25079,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G856" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25105,7 +25105,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G857" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25131,7 +25131,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G858" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25157,7 +25157,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G859" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25183,7 +25183,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G860" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25235,7 +25235,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G862" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25261,7 +25261,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G863" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25287,7 +25287,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G864" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25313,7 +25313,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G865" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25339,7 +25339,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G866" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25365,7 +25365,7 @@
         <v>1.25</v>
       </c>
       <c r="G867" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25391,7 +25391,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G868" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25417,7 +25417,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G869" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25443,7 +25443,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G870" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25469,7 +25469,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G871" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25495,7 +25495,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G872" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25521,7 +25521,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G873" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25547,7 +25547,7 @@
         <v>1.25</v>
       </c>
       <c r="G874" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25573,7 +25573,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G875" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25599,7 +25599,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G876" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -25625,7 +25625,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G877" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -25651,7 +25651,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G878" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25677,7 +25677,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G879" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -25807,7 +25807,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G884" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25833,7 +25833,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G885" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25859,7 +25859,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G886" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -25885,7 +25885,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G887" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -25911,7 +25911,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G888" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -25937,7 +25937,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G889" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -25963,7 +25963,7 @@
         <v>1.375</v>
       </c>
       <c r="G890" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -25989,7 +25989,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G891" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26015,7 +26015,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G892" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26041,7 +26041,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G893" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26067,7 +26067,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G894" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26093,7 +26093,7 @@
         <v>1.375</v>
       </c>
       <c r="G895" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26119,7 +26119,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G896" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26145,7 +26145,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G897" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26171,7 +26171,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G898" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26197,7 +26197,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G899" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26223,7 +26223,7 @@
         <v>1.5</v>
       </c>
       <c r="G900" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26249,7 +26249,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G901" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26275,7 +26275,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G902" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26301,7 +26301,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G903" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26327,7 +26327,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G904" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26353,7 +26353,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G905" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26379,7 +26379,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G906" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26405,7 +26405,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G907" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26431,7 +26431,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G908" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26457,7 +26457,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G909" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26483,7 +26483,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G910" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26509,7 +26509,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G911" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26535,7 +26535,7 @@
         <v>1.375</v>
       </c>
       <c r="G912" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26561,7 +26561,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G913" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -26587,7 +26587,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G914" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -26613,7 +26613,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G915" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -26639,7 +26639,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G916" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -26665,7 +26665,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G917" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -26691,7 +26691,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G918" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26717,7 +26717,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G919" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -26743,7 +26743,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G920" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -26769,7 +26769,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G921" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26795,7 +26795,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G922" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26821,7 +26821,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G923" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26847,7 +26847,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G924" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26873,7 +26873,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G925" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -26899,7 +26899,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G926" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26925,7 +26925,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G927" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26951,7 +26951,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G928" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26977,7 +26977,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G929" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -27003,7 +27003,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G930" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27029,7 +27029,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G931" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27055,7 +27055,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G932" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27081,7 +27081,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G933" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -27107,7 +27107,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G934" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -27133,7 +27133,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G935" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -27159,7 +27159,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G936" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27185,7 +27185,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G937" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27211,7 +27211,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G938" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -27237,7 +27237,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G939" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27263,7 +27263,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G940" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27289,7 +27289,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G941" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27315,7 +27315,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G942" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27341,7 +27341,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G943" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27367,7 +27367,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G944" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27393,7 +27393,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G945" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27419,7 +27419,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G946" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27445,7 +27445,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G947" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27471,7 +27471,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G948" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27497,7 +27497,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G949" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27523,7 +27523,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G950" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27549,7 +27549,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G951" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -27575,7 +27575,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G952" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -27601,7 +27601,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G953" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27627,7 +27627,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G954" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -27653,7 +27653,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G955" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -27679,7 +27679,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G956" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27705,7 +27705,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G957" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27731,7 +27731,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G958" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27757,7 +27757,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G959" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27783,7 +27783,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G960" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27809,7 +27809,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G961" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27835,7 +27835,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G962" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27861,7 +27861,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G963" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27887,7 +27887,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G964" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27913,7 +27913,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G965" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27939,7 +27939,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G966" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27965,7 +27965,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G967" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27991,7 +27991,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G968" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28017,7 +28017,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G969" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -28043,7 +28043,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G970" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -28069,7 +28069,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G971" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -28095,7 +28095,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G972" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28121,7 +28121,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G973" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28147,7 +28147,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G974" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28173,7 +28173,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G975" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28199,7 +28199,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G976" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -28225,7 +28225,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G977" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28251,7 +28251,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G978" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28277,7 +28277,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G979" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28303,7 +28303,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G980" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28329,7 +28329,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G981" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28355,7 +28355,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G982" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28381,7 +28381,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G983" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28407,7 +28407,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G984" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28433,7 +28433,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G985" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28459,7 +28459,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G986" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28485,7 +28485,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G987" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28511,7 +28511,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G988" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28537,7 +28537,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G989" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28563,7 +28563,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G990" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -28589,7 +28589,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G991" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -28615,7 +28615,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G992" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28641,7 +28641,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G993" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28667,7 +28667,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G994" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -28693,7 +28693,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G995" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -28719,7 +28719,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G996" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -28745,7 +28745,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G997" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -28771,7 +28771,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G998" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28797,7 +28797,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G999" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28823,7 +28823,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1000" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28849,7 +28849,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1001" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28875,7 +28875,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1002" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28901,7 +28901,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1003" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28927,7 +28927,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1004" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28953,7 +28953,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1005" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28979,7 +28979,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1006" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29005,7 +29005,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1007" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29031,7 +29031,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1008" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29057,7 +29057,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1009" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29083,7 +29083,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1010" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29109,7 +29109,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1011" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29135,7 +29135,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1012" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29161,7 +29161,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1013" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29187,7 +29187,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1014" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29213,7 +29213,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1015" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -29239,7 +29239,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1016" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29265,7 +29265,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1017" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29291,7 +29291,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1018" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29317,7 +29317,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1019" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29343,7 +29343,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1020" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29369,7 +29369,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1021" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29395,7 +29395,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1022" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29421,7 +29421,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1023" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29447,7 +29447,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1024" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29473,7 +29473,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1025" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29499,7 +29499,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1026" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29525,7 +29525,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1027" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29551,7 +29551,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1028" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29577,7 +29577,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1029" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29603,7 +29603,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1030" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -29629,7 +29629,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1031" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -29655,7 +29655,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1032" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29681,7 +29681,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1033" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29707,7 +29707,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1034" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29733,7 +29733,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1035" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29759,7 +29759,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1036" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29785,7 +29785,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1037" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29811,7 +29811,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1038" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29837,7 +29837,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1039" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29863,7 +29863,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1040" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29889,7 +29889,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1041" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29915,7 +29915,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1042" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29941,7 +29941,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1043" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29967,7 +29967,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1044" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29993,7 +29993,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1045" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -30019,7 +30019,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1046" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30045,7 +30045,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1047" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -30071,7 +30071,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1048" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30097,7 +30097,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1049" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30123,7 +30123,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1050" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -30149,7 +30149,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1051" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30175,7 +30175,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1052" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30201,7 +30201,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1053" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -30227,7 +30227,7 @@
         <v>1.25</v>
       </c>
       <c r="G1054" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -30253,7 +30253,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1055" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -30279,7 +30279,7 @@
         <v>1.25</v>
       </c>
       <c r="G1056" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30305,7 +30305,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1057" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30331,7 +30331,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G1058" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30357,7 +30357,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1059" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30383,7 +30383,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1060" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1060" 